--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -441,7 +441,7 @@
         <v>FLCM</v>
       </c>
       <c r="E2" t="str">
-        <v>estimates</v>
+        <v>approved</v>
       </c>
       <c r="G2">
         <v>45672</v>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -441,7 +441,7 @@
         <v>FLCM</v>
       </c>
       <c r="E2" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G2">
         <v>45672</v>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G63"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -429,30 +429,33 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ENT-17062</v>
+        <v>1234</v>
       </c>
       <c r="B2" t="str">
-        <v>Account Open Enhancements and Outcome Orchestration</v>
+        <v>qwer2</v>
       </c>
       <c r="C2" t="str">
-        <v>Invite to JRM</v>
+        <v>qwer2</v>
       </c>
       <c r="D2" t="str">
-        <v>FLCM</v>
+        <v>flcm</v>
       </c>
       <c r="E2" t="str">
         <v>jrm</v>
       </c>
-      <c r="G2">
-        <v>45672</v>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v>2025-03-15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ENT-16949</v>
+        <v>ENT-17062</v>
       </c>
       <c r="B3" t="str">
-        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
+        <v>Account Open Enhancements and Outcome Orchestration</v>
       </c>
       <c r="C3" t="str">
         <v>Invite to JRM</v>
@@ -461,18 +464,18 @@
         <v>FLCM</v>
       </c>
       <c r="E3" t="str">
-        <v>estimates</v>
+        <v>jrm</v>
       </c>
       <c r="G3">
-        <v>45531</v>
+        <v>45672</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ENT-16881</v>
+        <v>ENT-16949</v>
       </c>
       <c r="B4" t="str">
-        <v>Split up Personal Overdraft P&amp;L</v>
+        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
       </c>
       <c r="C4" t="str">
         <v>Invite to JRM</v>
@@ -481,18 +484,18 @@
         <v>FLCM</v>
       </c>
       <c r="E4" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G4">
-        <v>45929</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ENT-16700</v>
+        <v>ENT-16881</v>
       </c>
       <c r="B5" t="str">
-        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
+        <v>Split up Personal Overdraft P&amp;L</v>
       </c>
       <c r="C5" t="str">
         <v>Invite to JRM</v>
@@ -504,15 +507,15 @@
         <v>jrm</v>
       </c>
       <c r="G5">
-        <v>45523</v>
+        <v>45929</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ENT-16621</v>
+        <v>ENT-16700</v>
       </c>
       <c r="B6" t="str">
-        <v>CIW Data Products to PROD</v>
+        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
       </c>
       <c r="C6" t="str">
         <v>Invite to JRM</v>
@@ -521,18 +524,18 @@
         <v>FLCM</v>
       </c>
       <c r="E6" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G6">
-        <v>45596</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENT-16374</v>
+        <v>ENT-16621</v>
       </c>
       <c r="B7" t="str">
-        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
+        <v>CIW Data Products to PROD</v>
       </c>
       <c r="C7" t="str">
         <v>Invite to JRM</v>
@@ -541,18 +544,18 @@
         <v>FLCM</v>
       </c>
       <c r="E7" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G7">
-        <v>45455</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENT-16031</v>
+        <v>ENT-16374</v>
       </c>
       <c r="B8" t="str">
-        <v>Fraud - Notes generator</v>
+        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
       </c>
       <c r="C8" t="str">
         <v>Invite to JRM</v>
@@ -564,15 +567,15 @@
         <v>jrm</v>
       </c>
       <c r="G8">
-        <v>45649</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-15917</v>
+        <v>ENT-16031</v>
       </c>
       <c r="B9" t="str">
-        <v>REBO Bill Payment Investigation Requests</v>
+        <v>Fraud - Notes generator</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -584,15 +587,15 @@
         <v>jrm</v>
       </c>
       <c r="G9">
-        <v>45613</v>
+        <v>45649</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-17286</v>
+        <v>ENT-15917</v>
       </c>
       <c r="B10" t="str">
-        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
+        <v>REBO Bill Payment Investigation Requests</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -601,18 +604,18 @@
         <v>FLCM</v>
       </c>
       <c r="E10" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G10">
-        <v>45699</v>
+        <v>45613</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-17202</v>
+        <v>ENT-17286</v>
       </c>
       <c r="B11" t="str">
-        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
+        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -621,18 +624,18 @@
         <v>FLCM</v>
       </c>
       <c r="E11" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G11">
-        <v>45690</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17202</v>
       </c>
       <c r="B12" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -641,21 +644,18 @@
         <v>FLCM</v>
       </c>
       <c r="E12" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F12" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G12">
-        <v>45686</v>
+        <v>45690</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B13" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -664,18 +664,21 @@
         <v>FLCM</v>
       </c>
       <c r="E13" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F13" t="str">
+        <v>PDF</v>
       </c>
       <c r="G13">
-        <v>45700</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B14" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -687,15 +690,15 @@
         <v>estimates</v>
       </c>
       <c r="G14">
-        <v>45656</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B15" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -707,15 +710,15 @@
         <v>estimates</v>
       </c>
       <c r="G15">
-        <v>45588</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B16" t="str">
-        <v>Data Source to EDGE</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -727,15 +730,15 @@
         <v>estimates</v>
       </c>
       <c r="G16">
-        <v>45664</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ENT-17054</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B17" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -744,21 +747,18 @@
         <v>FLCM</v>
       </c>
       <c r="E17" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F17" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G17">
-        <v>45691</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-17054</v>
       </c>
       <c r="B18" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
@@ -769,16 +769,19 @@
       <c r="E18" t="str">
         <v>approved</v>
       </c>
+      <c r="F18" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G18">
-        <v>45299</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ENT-14372</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B19" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
@@ -789,19 +792,16 @@
       <c r="E19" t="str">
         <v>approved</v>
       </c>
-      <c r="F19" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G19">
-        <v>45512</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-14372</v>
       </c>
       <c r="B20" t="str">
-        <v>RAMP Phase 2</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
@@ -816,58 +816,58 @@
         <v>PDF</v>
       </c>
       <c r="G20">
-        <v>45562</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B21" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D21" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E21" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F21" t="str">
+        <v>PDF</v>
       </c>
       <c r="G21">
-        <v>45695</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B22" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D22" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E22" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F22" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G22">
-        <v>45688</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B23" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
@@ -882,15 +882,15 @@
         <v>PDF</v>
       </c>
       <c r="G23">
-        <v>45701</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B24" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
@@ -905,15 +905,15 @@
         <v>PDF</v>
       </c>
       <c r="G24">
-        <v>45695</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B25" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
@@ -924,16 +924,19 @@
       <c r="E25" t="str">
         <v>approved</v>
       </c>
+      <c r="F25" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G25">
-        <v>45706</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B26" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
@@ -942,138 +945,138 @@
         <v>FLCM</v>
       </c>
       <c r="E26" t="str">
-        <v>estimates</v>
+        <v>approved</v>
       </c>
       <c r="G26">
-        <v>45559</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B27" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D27" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E27" t="str">
         <v>estimates</v>
       </c>
       <c r="G27">
-        <v>45623</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B28" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D28" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E28" t="str">
         <v>estimates</v>
       </c>
       <c r="G28">
-        <v>45355</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B29" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>CorpSec</v>
+        <v>FLCM</v>
       </c>
       <c r="E29" t="str">
         <v>estimates</v>
       </c>
       <c r="G29">
-        <v>45446</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B30" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D30" t="str">
-        <v>BSCM/ESCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E30" t="str">
         <v>estimates</v>
       </c>
       <c r="G30">
-        <v>45477</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B31" t="str">
-        <v>CSDM Upgrade</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D31" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E31" t="str">
         <v>estimates</v>
       </c>
       <c r="G31">
-        <v>45394</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B32" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D32" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E32" t="str">
-        <v>ofs</v>
+        <v>estimates</v>
       </c>
       <c r="G32">
-        <v>45531</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B33" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
@@ -1085,15 +1088,15 @@
         <v>ofs</v>
       </c>
       <c r="G33">
-        <v>45453</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B34" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
@@ -1105,15 +1108,15 @@
         <v>ofs</v>
       </c>
       <c r="G34">
-        <v>45461</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B35" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
@@ -1122,95 +1125,98 @@
         <v>FLCM</v>
       </c>
       <c r="E35" t="str">
-        <v>jrm</v>
+        <v>ofs</v>
       </c>
       <c r="G35">
-        <v>45714</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B36" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D36" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E36" t="str">
-        <v>estimates</v>
+        <v>jrm</v>
       </c>
       <c r="G36">
-        <v>45686</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ENT-15822</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B37" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D37" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E37" t="str">
         <v>estimates</v>
       </c>
       <c r="G37">
-        <v>45650</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-15822</v>
       </c>
       <c r="B38" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D38" t="str">
-        <v>BSCM/ESCM</v>
+        <v>FLCM</v>
       </c>
       <c r="E38" t="str">
         <v>estimates</v>
       </c>
       <c r="G38">
-        <v>45541</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ENT-17853</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B39" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
       </c>
+      <c r="D39" t="str">
+        <v>BSCM/ESCM</v>
+      </c>
       <c r="E39" t="str">
-        <v>ofs</v>
+        <v>estimates</v>
       </c>
       <c r="G39">
-        <v>45691</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-17853</v>
       </c>
       <c r="B40" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
@@ -1219,15 +1225,15 @@
         <v>ofs</v>
       </c>
       <c r="G40">
-        <v>45559</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B41" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1236,15 +1242,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45596</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B42" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1253,15 +1259,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45378</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B43" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1270,15 +1276,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45468</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B44" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1287,15 +1293,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45310</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B45" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1304,15 +1310,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45427</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B46" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1321,15 +1327,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45279</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B47" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1338,15 +1344,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45558</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B48" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1355,15 +1361,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45383</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B49" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1372,15 +1378,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45638</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B50" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1389,15 +1395,15 @@
         <v>ofs</v>
       </c>
       <c r="G50">
-        <v>45461</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B51" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1406,15 +1412,15 @@
         <v>ofs</v>
       </c>
       <c r="G51">
-        <v>45371</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B52" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1428,10 +1434,10 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B53" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1440,15 +1446,15 @@
         <v>ofs</v>
       </c>
       <c r="G53">
-        <v>45406</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B54" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1457,15 +1463,15 @@
         <v>ofs</v>
       </c>
       <c r="G54">
-        <v>45364</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B55" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1474,15 +1480,15 @@
         <v>ofs</v>
       </c>
       <c r="G55">
-        <v>45593</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B56" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1491,15 +1497,15 @@
         <v>ofs</v>
       </c>
       <c r="G56">
-        <v>45408</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B57" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
@@ -1508,15 +1514,15 @@
         <v>ofs</v>
       </c>
       <c r="G57">
-        <v>45595</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B58" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C58" t="str">
         <v>Invite to JRM</v>
@@ -1525,15 +1531,15 @@
         <v>ofs</v>
       </c>
       <c r="G58">
-        <v>45392</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B59" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C59" t="str">
         <v>Invite to JRM</v>
@@ -1542,15 +1548,15 @@
         <v>ofs</v>
       </c>
       <c r="G59">
-        <v>45411</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B60" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C60" t="str">
         <v>Invite to JRM</v>
@@ -1564,27 +1570,27 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B61" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C61" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E61" t="str">
-        <v>jrm</v>
+        <v>ofs</v>
       </c>
       <c r="G61">
-        <v>45721</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>ENT-18725</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B62" t="str">
-        <v>US Video System - Lenel to Genetec</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C62" t="str">
         <v>Invite to JRM</v>
@@ -1596,9 +1602,26 @@
         <v>45721</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>ENT-18725</v>
+      </c>
+      <c r="B63" t="str">
+        <v>US Video System - Lenel to Genetec</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Invite to JRM</v>
+      </c>
+      <c r="E63" t="str">
+        <v>jrm</v>
+      </c>
+      <c r="G63">
+        <v>45721</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G62"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G63"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G64"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -429,16 +429,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>1234</v>
+        <v>12345</v>
       </c>
       <c r="B2" t="str">
-        <v>qwer2</v>
+        <v>qew</v>
       </c>
       <c r="C2" t="str">
-        <v>qwer2</v>
+        <v>wq</v>
       </c>
       <c r="D2" t="str">
-        <v>flcm</v>
+        <v>re23</v>
       </c>
       <c r="E2" t="str">
         <v>jrm</v>
@@ -452,30 +452,33 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ENT-17062</v>
+        <v>1234</v>
       </c>
       <c r="B3" t="str">
-        <v>Account Open Enhancements and Outcome Orchestration</v>
+        <v>qwer2</v>
       </c>
       <c r="C3" t="str">
-        <v>Invite to JRM</v>
+        <v>qwer2</v>
       </c>
       <c r="D3" t="str">
-        <v>FLCM</v>
+        <v>flcm</v>
       </c>
       <c r="E3" t="str">
         <v>jrm</v>
       </c>
-      <c r="G3">
-        <v>45672</v>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v>2025-03-15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ENT-16949</v>
+        <v>ENT-17062</v>
       </c>
       <c r="B4" t="str">
-        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
+        <v>Account Open Enhancements and Outcome Orchestration</v>
       </c>
       <c r="C4" t="str">
         <v>Invite to JRM</v>
@@ -484,18 +487,18 @@
         <v>FLCM</v>
       </c>
       <c r="E4" t="str">
-        <v>estimates</v>
+        <v>jrm</v>
       </c>
       <c r="G4">
-        <v>45531</v>
+        <v>45672</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ENT-16881</v>
+        <v>ENT-16949</v>
       </c>
       <c r="B5" t="str">
-        <v>Split up Personal Overdraft P&amp;L</v>
+        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
       </c>
       <c r="C5" t="str">
         <v>Invite to JRM</v>
@@ -504,18 +507,18 @@
         <v>FLCM</v>
       </c>
       <c r="E5" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G5">
-        <v>45929</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ENT-16700</v>
+        <v>ENT-16881</v>
       </c>
       <c r="B6" t="str">
-        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
+        <v>Split up Personal Overdraft P&amp;L</v>
       </c>
       <c r="C6" t="str">
         <v>Invite to JRM</v>
@@ -527,15 +530,15 @@
         <v>jrm</v>
       </c>
       <c r="G6">
-        <v>45523</v>
+        <v>45929</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENT-16621</v>
+        <v>ENT-16700</v>
       </c>
       <c r="B7" t="str">
-        <v>CIW Data Products to PROD</v>
+        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
       </c>
       <c r="C7" t="str">
         <v>Invite to JRM</v>
@@ -544,18 +547,18 @@
         <v>FLCM</v>
       </c>
       <c r="E7" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G7">
-        <v>45596</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENT-16374</v>
+        <v>ENT-16621</v>
       </c>
       <c r="B8" t="str">
-        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
+        <v>CIW Data Products to PROD</v>
       </c>
       <c r="C8" t="str">
         <v>Invite to JRM</v>
@@ -564,18 +567,18 @@
         <v>FLCM</v>
       </c>
       <c r="E8" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G8">
-        <v>45455</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-16031</v>
+        <v>ENT-16374</v>
       </c>
       <c r="B9" t="str">
-        <v>Fraud - Notes generator</v>
+        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -587,15 +590,15 @@
         <v>jrm</v>
       </c>
       <c r="G9">
-        <v>45649</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-15917</v>
+        <v>ENT-16031</v>
       </c>
       <c r="B10" t="str">
-        <v>REBO Bill Payment Investigation Requests</v>
+        <v>Fraud - Notes generator</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -607,15 +610,15 @@
         <v>jrm</v>
       </c>
       <c r="G10">
-        <v>45613</v>
+        <v>45649</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-17286</v>
+        <v>ENT-15917</v>
       </c>
       <c r="B11" t="str">
-        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
+        <v>REBO Bill Payment Investigation Requests</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -624,18 +627,18 @@
         <v>FLCM</v>
       </c>
       <c r="E11" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G11">
-        <v>45699</v>
+        <v>45613</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-17202</v>
+        <v>ENT-17286</v>
       </c>
       <c r="B12" t="str">
-        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
+        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -644,18 +647,18 @@
         <v>FLCM</v>
       </c>
       <c r="E12" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G12">
-        <v>45690</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17202</v>
       </c>
       <c r="B13" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -664,21 +667,18 @@
         <v>FLCM</v>
       </c>
       <c r="E13" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F13" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G13">
-        <v>45686</v>
+        <v>45690</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B14" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -687,18 +687,21 @@
         <v>FLCM</v>
       </c>
       <c r="E14" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F14" t="str">
+        <v>PDF</v>
       </c>
       <c r="G14">
-        <v>45700</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B15" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -710,15 +713,15 @@
         <v>estimates</v>
       </c>
       <c r="G15">
-        <v>45656</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B16" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -730,15 +733,15 @@
         <v>estimates</v>
       </c>
       <c r="G16">
-        <v>45588</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B17" t="str">
-        <v>Data Source to EDGE</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -750,15 +753,15 @@
         <v>estimates</v>
       </c>
       <c r="G17">
-        <v>45664</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ENT-17054</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B18" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
@@ -767,21 +770,18 @@
         <v>FLCM</v>
       </c>
       <c r="E18" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F18" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G18">
-        <v>45691</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-17054</v>
       </c>
       <c r="B19" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
@@ -792,16 +792,19 @@
       <c r="E19" t="str">
         <v>approved</v>
       </c>
+      <c r="F19" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G19">
-        <v>45299</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ENT-14372</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B20" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
@@ -812,19 +815,16 @@
       <c r="E20" t="str">
         <v>approved</v>
       </c>
-      <c r="F20" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G20">
-        <v>45512</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-14372</v>
       </c>
       <c r="B21" t="str">
-        <v>RAMP Phase 2</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
@@ -839,58 +839,58 @@
         <v>PDF</v>
       </c>
       <c r="G21">
-        <v>45562</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B22" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D22" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E22" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F22" t="str">
+        <v>PDF</v>
       </c>
       <c r="G22">
-        <v>45695</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B23" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D23" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E23" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F23" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G23">
-        <v>45688</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B24" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
@@ -905,15 +905,15 @@
         <v>PDF</v>
       </c>
       <c r="G24">
-        <v>45701</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B25" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
@@ -928,15 +928,15 @@
         <v>PDF</v>
       </c>
       <c r="G25">
-        <v>45695</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B26" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
@@ -947,16 +947,19 @@
       <c r="E26" t="str">
         <v>approved</v>
       </c>
+      <c r="F26" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G26">
-        <v>45706</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B27" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
@@ -965,138 +968,138 @@
         <v>FLCM</v>
       </c>
       <c r="E27" t="str">
-        <v>estimates</v>
+        <v>approved</v>
       </c>
       <c r="G27">
-        <v>45559</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B28" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D28" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E28" t="str">
         <v>estimates</v>
       </c>
       <c r="G28">
-        <v>45623</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B29" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E29" t="str">
         <v>estimates</v>
       </c>
       <c r="G29">
-        <v>45355</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B30" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D30" t="str">
-        <v>CorpSec</v>
+        <v>FLCM</v>
       </c>
       <c r="E30" t="str">
         <v>estimates</v>
       </c>
       <c r="G30">
-        <v>45446</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B31" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D31" t="str">
-        <v>BSCM/ESCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E31" t="str">
         <v>estimates</v>
       </c>
       <c r="G31">
-        <v>45477</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B32" t="str">
-        <v>CSDM Upgrade</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D32" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E32" t="str">
         <v>estimates</v>
       </c>
       <c r="G32">
-        <v>45394</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B33" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D33" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E33" t="str">
-        <v>ofs</v>
+        <v>estimates</v>
       </c>
       <c r="G33">
-        <v>45531</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B34" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
@@ -1108,15 +1111,15 @@
         <v>ofs</v>
       </c>
       <c r="G34">
-        <v>45453</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B35" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
@@ -1128,15 +1131,15 @@
         <v>ofs</v>
       </c>
       <c r="G35">
-        <v>45461</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B36" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
@@ -1145,95 +1148,98 @@
         <v>FLCM</v>
       </c>
       <c r="E36" t="str">
-        <v>jrm</v>
+        <v>ofs</v>
       </c>
       <c r="G36">
-        <v>45714</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B37" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D37" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E37" t="str">
-        <v>estimates</v>
+        <v>jrm</v>
       </c>
       <c r="G37">
-        <v>45686</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ENT-15822</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B38" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D38" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E38" t="str">
         <v>estimates</v>
       </c>
       <c r="G38">
-        <v>45650</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-15822</v>
       </c>
       <c r="B39" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D39" t="str">
-        <v>BSCM/ESCM</v>
+        <v>FLCM</v>
       </c>
       <c r="E39" t="str">
         <v>estimates</v>
       </c>
       <c r="G39">
-        <v>45541</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENT-17853</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B40" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
       </c>
+      <c r="D40" t="str">
+        <v>BSCM/ESCM</v>
+      </c>
       <c r="E40" t="str">
-        <v>ofs</v>
+        <v>estimates</v>
       </c>
       <c r="G40">
-        <v>45691</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-17853</v>
       </c>
       <c r="B41" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1242,15 +1248,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45559</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B42" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1259,15 +1265,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45596</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B43" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1276,15 +1282,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45378</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B44" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1293,15 +1299,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45468</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B45" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1310,15 +1316,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45310</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B46" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1327,15 +1333,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45427</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B47" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1344,15 +1350,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45279</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B48" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1361,15 +1367,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45558</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B49" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1378,15 +1384,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45383</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B50" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1395,15 +1401,15 @@
         <v>ofs</v>
       </c>
       <c r="G50">
-        <v>45638</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B51" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1412,15 +1418,15 @@
         <v>ofs</v>
       </c>
       <c r="G51">
-        <v>45461</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B52" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1429,15 +1435,15 @@
         <v>ofs</v>
       </c>
       <c r="G52">
-        <v>45371</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B53" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1451,10 +1457,10 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B54" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1463,15 +1469,15 @@
         <v>ofs</v>
       </c>
       <c r="G54">
-        <v>45406</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B55" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1480,15 +1486,15 @@
         <v>ofs</v>
       </c>
       <c r="G55">
-        <v>45364</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B56" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1497,15 +1503,15 @@
         <v>ofs</v>
       </c>
       <c r="G56">
-        <v>45593</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B57" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
@@ -1514,15 +1520,15 @@
         <v>ofs</v>
       </c>
       <c r="G57">
-        <v>45408</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B58" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C58" t="str">
         <v>Invite to JRM</v>
@@ -1531,15 +1537,15 @@
         <v>ofs</v>
       </c>
       <c r="G58">
-        <v>45595</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B59" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C59" t="str">
         <v>Invite to JRM</v>
@@ -1548,15 +1554,15 @@
         <v>ofs</v>
       </c>
       <c r="G59">
-        <v>45392</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B60" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C60" t="str">
         <v>Invite to JRM</v>
@@ -1565,15 +1571,15 @@
         <v>ofs</v>
       </c>
       <c r="G60">
-        <v>45411</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B61" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C61" t="str">
         <v>Invite to JRM</v>
@@ -1587,27 +1593,27 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B62" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C62" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E62" t="str">
-        <v>jrm</v>
+        <v>ofs</v>
       </c>
       <c r="G62">
-        <v>45721</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>ENT-18725</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B63" t="str">
-        <v>US Video System - Lenel to Genetec</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C63" t="str">
         <v>Invite to JRM</v>
@@ -1619,9 +1625,26 @@
         <v>45721</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>ENT-18725</v>
+      </c>
+      <c r="B64" t="str">
+        <v>US Video System - Lenel to Genetec</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Invite to JRM</v>
+      </c>
+      <c r="E64" t="str">
+        <v>jrm</v>
+      </c>
+      <c r="G64">
+        <v>45721</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G63"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G64"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G63"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -429,16 +429,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>12345</v>
+        <v>1234</v>
       </c>
       <c r="B2" t="str">
-        <v>qew</v>
+        <v>qwer2</v>
       </c>
       <c r="C2" t="str">
-        <v>wq</v>
+        <v>qwer2</v>
       </c>
       <c r="D2" t="str">
-        <v>re23</v>
+        <v>flcm</v>
       </c>
       <c r="E2" t="str">
         <v>jrm</v>
@@ -452,33 +452,30 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>1234</v>
+        <v>ENT-17062</v>
       </c>
       <c r="B3" t="str">
-        <v>qwer2</v>
+        <v>Account Open Enhancements and Outcome Orchestration</v>
       </c>
       <c r="C3" t="str">
-        <v>qwer2</v>
+        <v>Invite to JRM</v>
       </c>
       <c r="D3" t="str">
-        <v>flcm</v>
+        <v>FLCM</v>
       </c>
       <c r="E3" t="str">
         <v>jrm</v>
       </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v>2025-03-15</v>
+      <c r="G3">
+        <v>45672</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ENT-17062</v>
+        <v>ENT-16949</v>
       </c>
       <c r="B4" t="str">
-        <v>Account Open Enhancements and Outcome Orchestration</v>
+        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
       </c>
       <c r="C4" t="str">
         <v>Invite to JRM</v>
@@ -487,18 +484,18 @@
         <v>FLCM</v>
       </c>
       <c r="E4" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G4">
-        <v>45672</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ENT-16949</v>
+        <v>ENT-16881</v>
       </c>
       <c r="B5" t="str">
-        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
+        <v>Split up Personal Overdraft P&amp;L</v>
       </c>
       <c r="C5" t="str">
         <v>Invite to JRM</v>
@@ -507,18 +504,18 @@
         <v>FLCM</v>
       </c>
       <c r="E5" t="str">
-        <v>estimates</v>
+        <v>jrm</v>
       </c>
       <c r="G5">
-        <v>45531</v>
+        <v>45929</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ENT-16881</v>
+        <v>ENT-16700</v>
       </c>
       <c r="B6" t="str">
-        <v>Split up Personal Overdraft P&amp;L</v>
+        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
       </c>
       <c r="C6" t="str">
         <v>Invite to JRM</v>
@@ -530,15 +527,15 @@
         <v>jrm</v>
       </c>
       <c r="G6">
-        <v>45929</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENT-16700</v>
+        <v>ENT-16621</v>
       </c>
       <c r="B7" t="str">
-        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
+        <v>CIW Data Products to PROD</v>
       </c>
       <c r="C7" t="str">
         <v>Invite to JRM</v>
@@ -547,18 +544,18 @@
         <v>FLCM</v>
       </c>
       <c r="E7" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G7">
-        <v>45523</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENT-16621</v>
+        <v>ENT-16374</v>
       </c>
       <c r="B8" t="str">
-        <v>CIW Data Products to PROD</v>
+        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
       </c>
       <c r="C8" t="str">
         <v>Invite to JRM</v>
@@ -567,18 +564,18 @@
         <v>FLCM</v>
       </c>
       <c r="E8" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G8">
-        <v>45596</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-16374</v>
+        <v>ENT-16031</v>
       </c>
       <c r="B9" t="str">
-        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
+        <v>Fraud - Notes generator</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -590,15 +587,15 @@
         <v>jrm</v>
       </c>
       <c r="G9">
-        <v>45455</v>
+        <v>45649</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-16031</v>
+        <v>ENT-15917</v>
       </c>
       <c r="B10" t="str">
-        <v>Fraud - Notes generator</v>
+        <v>REBO Bill Payment Investigation Requests</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -610,15 +607,15 @@
         <v>jrm</v>
       </c>
       <c r="G10">
-        <v>45649</v>
+        <v>45613</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-15917</v>
+        <v>ENT-17286</v>
       </c>
       <c r="B11" t="str">
-        <v>REBO Bill Payment Investigation Requests</v>
+        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -627,18 +624,18 @@
         <v>FLCM</v>
       </c>
       <c r="E11" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G11">
-        <v>45613</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-17286</v>
+        <v>ENT-17202</v>
       </c>
       <c r="B12" t="str">
-        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
+        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -647,18 +644,18 @@
         <v>FLCM</v>
       </c>
       <c r="E12" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G12">
-        <v>45699</v>
+        <v>45690</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-17202</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B13" t="str">
-        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -667,18 +664,21 @@
         <v>FLCM</v>
       </c>
       <c r="E13" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F13" t="str">
+        <v>PDF</v>
       </c>
       <c r="G13">
-        <v>45690</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B14" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -687,21 +687,18 @@
         <v>FLCM</v>
       </c>
       <c r="E14" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F14" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G14">
-        <v>45686</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B15" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -713,15 +710,15 @@
         <v>estimates</v>
       </c>
       <c r="G15">
-        <v>45700</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B16" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -733,15 +730,15 @@
         <v>estimates</v>
       </c>
       <c r="G16">
-        <v>45656</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B17" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -753,15 +750,15 @@
         <v>estimates</v>
       </c>
       <c r="G17">
-        <v>45588</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-17054</v>
       </c>
       <c r="B18" t="str">
-        <v>Data Source to EDGE</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
@@ -770,18 +767,21 @@
         <v>FLCM</v>
       </c>
       <c r="E18" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F18" t="str">
+        <v>PDF</v>
       </c>
       <c r="G18">
-        <v>45664</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ENT-17054</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B19" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
@@ -792,19 +792,16 @@
       <c r="E19" t="str">
         <v>approved</v>
       </c>
-      <c r="F19" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G19">
-        <v>45691</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-14372</v>
       </c>
       <c r="B20" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
@@ -815,16 +812,19 @@
       <c r="E20" t="str">
         <v>approved</v>
       </c>
+      <c r="F20" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G20">
-        <v>45299</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-14372</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B21" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
@@ -839,58 +839,58 @@
         <v>PDF</v>
       </c>
       <c r="G21">
-        <v>45512</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B22" t="str">
-        <v>RAMP Phase 2</v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D22" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E22" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F22" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G22">
-        <v>45562</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B23" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D23" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E23" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F23" t="str">
+        <v>PDF</v>
       </c>
       <c r="G23">
-        <v>45695</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B24" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
@@ -905,15 +905,15 @@
         <v>PDF</v>
       </c>
       <c r="G24">
-        <v>45688</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B25" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
@@ -928,15 +928,15 @@
         <v>PDF</v>
       </c>
       <c r="G25">
-        <v>45701</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B26" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
@@ -947,19 +947,16 @@
       <c r="E26" t="str">
         <v>approved</v>
       </c>
-      <c r="F26" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G26">
-        <v>45695</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B27" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
@@ -968,138 +965,138 @@
         <v>FLCM</v>
       </c>
       <c r="E27" t="str">
-        <v>approved</v>
+        <v>estimates</v>
       </c>
       <c r="G27">
-        <v>45706</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B28" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D28" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E28" t="str">
         <v>estimates</v>
       </c>
       <c r="G28">
-        <v>45559</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B29" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E29" t="str">
         <v>estimates</v>
       </c>
       <c r="G29">
-        <v>45623</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B30" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D30" t="str">
-        <v>FLCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E30" t="str">
         <v>estimates</v>
       </c>
       <c r="G30">
-        <v>45355</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B31" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D31" t="str">
-        <v>CorpSec</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E31" t="str">
         <v>estimates</v>
       </c>
       <c r="G31">
-        <v>45446</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B32" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D32" t="str">
-        <v>BSCM/ESCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E32" t="str">
         <v>estimates</v>
       </c>
       <c r="G32">
-        <v>45477</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B33" t="str">
-        <v>CSDM Upgrade</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D33" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E33" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G33">
-        <v>45394</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B34" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
@@ -1111,15 +1108,15 @@
         <v>ofs</v>
       </c>
       <c r="G34">
-        <v>45531</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B35" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
@@ -1131,15 +1128,15 @@
         <v>ofs</v>
       </c>
       <c r="G35">
-        <v>45453</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B36" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
@@ -1148,98 +1145,95 @@
         <v>FLCM</v>
       </c>
       <c r="E36" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G36">
-        <v>45461</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B37" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D37" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E37" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G37">
-        <v>45714</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-15822</v>
       </c>
       <c r="B38" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D38" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E38" t="str">
         <v>estimates</v>
       </c>
       <c r="G38">
-        <v>45686</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ENT-15822</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B39" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D39" t="str">
-        <v>FLCM</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E39" t="str">
         <v>estimates</v>
       </c>
       <c r="G39">
-        <v>45650</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-17853</v>
       </c>
       <c r="B40" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
       </c>
-      <c r="D40" t="str">
-        <v>BSCM/ESCM</v>
-      </c>
       <c r="E40" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G40">
-        <v>45541</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-17853</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B41" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1248,15 +1242,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45691</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B42" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1265,15 +1259,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45559</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B43" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1282,15 +1276,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45596</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B44" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1299,15 +1293,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45378</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B45" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1316,15 +1310,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45468</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B46" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1333,15 +1327,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45310</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B47" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1350,15 +1344,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45427</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B48" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1367,15 +1361,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45279</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B49" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1384,15 +1378,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45558</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B50" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1401,15 +1395,15 @@
         <v>ofs</v>
       </c>
       <c r="G50">
-        <v>45383</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B51" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1418,15 +1412,15 @@
         <v>ofs</v>
       </c>
       <c r="G51">
-        <v>45638</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B52" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1435,15 +1429,15 @@
         <v>ofs</v>
       </c>
       <c r="G52">
-        <v>45461</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B53" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1457,10 +1451,10 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B54" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1469,15 +1463,15 @@
         <v>ofs</v>
       </c>
       <c r="G54">
-        <v>45371</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B55" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1486,15 +1480,15 @@
         <v>ofs</v>
       </c>
       <c r="G55">
-        <v>45406</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B56" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1503,15 +1497,15 @@
         <v>ofs</v>
       </c>
       <c r="G56">
-        <v>45364</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B57" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
@@ -1520,15 +1514,15 @@
         <v>ofs</v>
       </c>
       <c r="G57">
-        <v>45593</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B58" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C58" t="str">
         <v>Invite to JRM</v>
@@ -1537,15 +1531,15 @@
         <v>ofs</v>
       </c>
       <c r="G58">
-        <v>45408</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B59" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C59" t="str">
         <v>Invite to JRM</v>
@@ -1554,15 +1548,15 @@
         <v>ofs</v>
       </c>
       <c r="G59">
-        <v>45595</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B60" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C60" t="str">
         <v>Invite to JRM</v>
@@ -1571,15 +1565,15 @@
         <v>ofs</v>
       </c>
       <c r="G60">
-        <v>45392</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B61" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C61" t="str">
         <v>Invite to JRM</v>
@@ -1593,27 +1587,27 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B62" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C62" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E62" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G62">
-        <v>45411</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-18725</v>
       </c>
       <c r="B63" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>US Video System - Lenel to Genetec</v>
       </c>
       <c r="C63" t="str">
         <v>Invite to JRM</v>
@@ -1625,26 +1619,9 @@
         <v>45721</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="str">
-        <v>ENT-18725</v>
-      </c>
-      <c r="B64" t="str">
-        <v>US Video System - Lenel to Genetec</v>
-      </c>
-      <c r="C64" t="str">
-        <v>Invite to JRM</v>
-      </c>
-      <c r="E64" t="str">
-        <v>jrm</v>
-      </c>
-      <c r="G64">
-        <v>45721</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G64"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G63"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G62"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -429,33 +429,30 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>1234</v>
+        <v>ENT-17062</v>
       </c>
       <c r="B2" t="str">
-        <v>qwer2</v>
+        <v>Account Open Enhancements and Outcome Orchestration</v>
       </c>
       <c r="C2" t="str">
-        <v>qwer2</v>
+        <v>Invite to JRM</v>
       </c>
       <c r="D2" t="str">
-        <v>flcm</v>
+        <v>FLCM</v>
       </c>
       <c r="E2" t="str">
         <v>jrm</v>
       </c>
-      <c r="F2" t="str">
-        <v/>
-      </c>
-      <c r="G2" t="str">
-        <v>2025-03-15</v>
+      <c r="G2">
+        <v>45672</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ENT-17062</v>
+        <v>ENT-16949</v>
       </c>
       <c r="B3" t="str">
-        <v>Account Open Enhancements and Outcome Orchestration</v>
+        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
       </c>
       <c r="C3" t="str">
         <v>Invite to JRM</v>
@@ -464,18 +461,18 @@
         <v>FLCM</v>
       </c>
       <c r="E3" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G3">
-        <v>45672</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ENT-16949</v>
+        <v>ENT-16881</v>
       </c>
       <c r="B4" t="str">
-        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
+        <v>Split up Personal Overdraft P&amp;L</v>
       </c>
       <c r="C4" t="str">
         <v>Invite to JRM</v>
@@ -484,18 +481,18 @@
         <v>FLCM</v>
       </c>
       <c r="E4" t="str">
-        <v>estimates</v>
+        <v>jrm</v>
       </c>
       <c r="G4">
-        <v>45531</v>
+        <v>45929</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ENT-16881</v>
+        <v>ENT-16700</v>
       </c>
       <c r="B5" t="str">
-        <v>Split up Personal Overdraft P&amp;L</v>
+        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
       </c>
       <c r="C5" t="str">
         <v>Invite to JRM</v>
@@ -507,15 +504,15 @@
         <v>jrm</v>
       </c>
       <c r="G5">
-        <v>45929</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ENT-16700</v>
+        <v>ENT-16621</v>
       </c>
       <c r="B6" t="str">
-        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
+        <v>CIW Data Products to PROD</v>
       </c>
       <c r="C6" t="str">
         <v>Invite to JRM</v>
@@ -524,18 +521,18 @@
         <v>FLCM</v>
       </c>
       <c r="E6" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G6">
-        <v>45523</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENT-16621</v>
+        <v>ENT-16374</v>
       </c>
       <c r="B7" t="str">
-        <v>CIW Data Products to PROD</v>
+        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
       </c>
       <c r="C7" t="str">
         <v>Invite to JRM</v>
@@ -544,18 +541,18 @@
         <v>FLCM</v>
       </c>
       <c r="E7" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G7">
-        <v>45596</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENT-16374</v>
+        <v>ENT-16031</v>
       </c>
       <c r="B8" t="str">
-        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
+        <v>Fraud - Notes generator</v>
       </c>
       <c r="C8" t="str">
         <v>Invite to JRM</v>
@@ -567,15 +564,15 @@
         <v>jrm</v>
       </c>
       <c r="G8">
-        <v>45455</v>
+        <v>45649</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-16031</v>
+        <v>ENT-15917</v>
       </c>
       <c r="B9" t="str">
-        <v>Fraud - Notes generator</v>
+        <v>REBO Bill Payment Investigation Requests</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -587,15 +584,15 @@
         <v>jrm</v>
       </c>
       <c r="G9">
-        <v>45649</v>
+        <v>45613</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-15917</v>
+        <v>ENT-17286</v>
       </c>
       <c r="B10" t="str">
-        <v>REBO Bill Payment Investigation Requests</v>
+        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -604,18 +601,18 @@
         <v>FLCM</v>
       </c>
       <c r="E10" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G10">
-        <v>45613</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-17286</v>
+        <v>ENT-17202</v>
       </c>
       <c r="B11" t="str">
-        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
+        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -624,18 +621,18 @@
         <v>FLCM</v>
       </c>
       <c r="E11" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G11">
-        <v>45699</v>
+        <v>45690</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-17202</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B12" t="str">
-        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -644,18 +641,21 @@
         <v>FLCM</v>
       </c>
       <c r="E12" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F12" t="str">
+        <v>PDF</v>
       </c>
       <c r="G12">
-        <v>45690</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B13" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -664,21 +664,18 @@
         <v>FLCM</v>
       </c>
       <c r="E13" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F13" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G13">
-        <v>45686</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B14" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -690,15 +687,15 @@
         <v>estimates</v>
       </c>
       <c r="G14">
-        <v>45700</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B15" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -710,15 +707,15 @@
         <v>estimates</v>
       </c>
       <c r="G15">
-        <v>45656</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B16" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -730,15 +727,15 @@
         <v>estimates</v>
       </c>
       <c r="G16">
-        <v>45588</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-17054</v>
       </c>
       <c r="B17" t="str">
-        <v>Data Source to EDGE</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -747,18 +744,21 @@
         <v>FLCM</v>
       </c>
       <c r="E17" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F17" t="str">
+        <v>PDF</v>
       </c>
       <c r="G17">
-        <v>45664</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ENT-17054</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B18" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
@@ -769,19 +769,16 @@
       <c r="E18" t="str">
         <v>approved</v>
       </c>
-      <c r="F18" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G18">
-        <v>45691</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-14372</v>
       </c>
       <c r="B19" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
@@ -792,16 +789,19 @@
       <c r="E19" t="str">
         <v>approved</v>
       </c>
+      <c r="F19" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G19">
-        <v>45299</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ENT-14372</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B20" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
@@ -816,58 +816,58 @@
         <v>PDF</v>
       </c>
       <c r="G20">
-        <v>45512</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B21" t="str">
-        <v>RAMP Phase 2</v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D21" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E21" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F21" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G21">
-        <v>45562</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B22" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D22" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E22" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F22" t="str">
+        <v>PDF</v>
       </c>
       <c r="G22">
-        <v>45695</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B23" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
@@ -882,15 +882,15 @@
         <v>PDF</v>
       </c>
       <c r="G23">
-        <v>45688</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B24" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
@@ -905,15 +905,15 @@
         <v>PDF</v>
       </c>
       <c r="G24">
-        <v>45701</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B25" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
@@ -924,19 +924,16 @@
       <c r="E25" t="str">
         <v>approved</v>
       </c>
-      <c r="F25" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G25">
-        <v>45695</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B26" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
@@ -945,138 +942,138 @@
         <v>FLCM</v>
       </c>
       <c r="E26" t="str">
-        <v>approved</v>
+        <v>estimates</v>
       </c>
       <c r="G26">
-        <v>45706</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B27" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D27" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E27" t="str">
         <v>estimates</v>
       </c>
       <c r="G27">
-        <v>45559</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B28" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D28" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E28" t="str">
         <v>estimates</v>
       </c>
       <c r="G28">
-        <v>45623</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B29" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>FLCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E29" t="str">
         <v>estimates</v>
       </c>
       <c r="G29">
-        <v>45355</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B30" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D30" t="str">
-        <v>CorpSec</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E30" t="str">
         <v>estimates</v>
       </c>
       <c r="G30">
-        <v>45446</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B31" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D31" t="str">
-        <v>BSCM/ESCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E31" t="str">
         <v>estimates</v>
       </c>
       <c r="G31">
-        <v>45477</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B32" t="str">
-        <v>CSDM Upgrade</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D32" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E32" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G32">
-        <v>45394</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B33" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
@@ -1088,15 +1085,15 @@
         <v>ofs</v>
       </c>
       <c r="G33">
-        <v>45531</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B34" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
@@ -1108,15 +1105,15 @@
         <v>ofs</v>
       </c>
       <c r="G34">
-        <v>45453</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B35" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
@@ -1125,98 +1122,95 @@
         <v>FLCM</v>
       </c>
       <c r="E35" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G35">
-        <v>45461</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B36" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D36" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E36" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G36">
-        <v>45714</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-15822</v>
       </c>
       <c r="B37" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D37" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E37" t="str">
         <v>estimates</v>
       </c>
       <c r="G37">
-        <v>45686</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ENT-15822</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B38" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D38" t="str">
-        <v>FLCM</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E38" t="str">
         <v>estimates</v>
       </c>
       <c r="G38">
-        <v>45650</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-17853</v>
       </c>
       <c r="B39" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
       </c>
-      <c r="D39" t="str">
-        <v>BSCM/ESCM</v>
-      </c>
       <c r="E39" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G39">
-        <v>45541</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENT-17853</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B40" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
@@ -1225,15 +1219,15 @@
         <v>ofs</v>
       </c>
       <c r="G40">
-        <v>45691</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B41" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1242,15 +1236,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45559</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B42" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1259,15 +1253,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45596</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B43" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1276,15 +1270,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45378</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B44" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1293,15 +1287,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45468</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B45" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1310,15 +1304,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45310</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B46" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1327,15 +1321,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45427</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B47" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1344,15 +1338,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45279</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B48" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1361,15 +1355,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45558</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B49" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1378,15 +1372,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45383</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B50" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1395,15 +1389,15 @@
         <v>ofs</v>
       </c>
       <c r="G50">
-        <v>45638</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B51" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1412,15 +1406,15 @@
         <v>ofs</v>
       </c>
       <c r="G51">
-        <v>45461</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B52" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1434,10 +1428,10 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B53" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1446,15 +1440,15 @@
         <v>ofs</v>
       </c>
       <c r="G53">
-        <v>45371</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B54" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1463,15 +1457,15 @@
         <v>ofs</v>
       </c>
       <c r="G54">
-        <v>45406</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B55" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1480,15 +1474,15 @@
         <v>ofs</v>
       </c>
       <c r="G55">
-        <v>45364</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B56" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1497,15 +1491,15 @@
         <v>ofs</v>
       </c>
       <c r="G56">
-        <v>45593</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B57" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
@@ -1514,15 +1508,15 @@
         <v>ofs</v>
       </c>
       <c r="G57">
-        <v>45408</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B58" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C58" t="str">
         <v>Invite to JRM</v>
@@ -1531,15 +1525,15 @@
         <v>ofs</v>
       </c>
       <c r="G58">
-        <v>45595</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B59" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C59" t="str">
         <v>Invite to JRM</v>
@@ -1548,15 +1542,15 @@
         <v>ofs</v>
       </c>
       <c r="G59">
-        <v>45392</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B60" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C60" t="str">
         <v>Invite to JRM</v>
@@ -1570,27 +1564,27 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B61" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C61" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E61" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G61">
-        <v>45411</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-18725</v>
       </c>
       <c r="B62" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>US Video System - Lenel to Genetec</v>
       </c>
       <c r="C62" t="str">
         <v>Invite to JRM</v>
@@ -1602,26 +1596,9 @@
         <v>45721</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="str">
-        <v>ENT-18725</v>
-      </c>
-      <c r="B63" t="str">
-        <v>US Video System - Lenel to Genetec</v>
-      </c>
-      <c r="C63" t="str">
-        <v>Invite to JRM</v>
-      </c>
-      <c r="E63" t="str">
-        <v>jrm</v>
-      </c>
-      <c r="G63">
-        <v>45721</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G63"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G62"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G63"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -429,30 +429,33 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ENT-17062</v>
+        <v>12323</v>
       </c>
       <c r="B2" t="str">
-        <v>Account Open Enhancements and Outcome Orchestration</v>
+        <v>123123</v>
       </c>
       <c r="C2" t="str">
-        <v>Invite to JRM</v>
+        <v>123123</v>
       </c>
       <c r="D2" t="str">
-        <v>FLCM</v>
+        <v>123213</v>
       </c>
       <c r="E2" t="str">
         <v>jrm</v>
       </c>
-      <c r="G2">
-        <v>45672</v>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v>2025-03-15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ENT-16949</v>
+        <v>ENT-17062</v>
       </c>
       <c r="B3" t="str">
-        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
+        <v>Account Open Enhancements and Outcome Orchestration</v>
       </c>
       <c r="C3" t="str">
         <v>Invite to JRM</v>
@@ -461,18 +464,18 @@
         <v>FLCM</v>
       </c>
       <c r="E3" t="str">
-        <v>estimates</v>
+        <v>jrm</v>
       </c>
       <c r="G3">
-        <v>45531</v>
+        <v>45672</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ENT-16881</v>
+        <v>ENT-16949</v>
       </c>
       <c r="B4" t="str">
-        <v>Split up Personal Overdraft P&amp;L</v>
+        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
       </c>
       <c r="C4" t="str">
         <v>Invite to JRM</v>
@@ -481,18 +484,18 @@
         <v>FLCM</v>
       </c>
       <c r="E4" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G4">
-        <v>45929</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ENT-16700</v>
+        <v>ENT-16881</v>
       </c>
       <c r="B5" t="str">
-        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
+        <v>Split up Personal Overdraft P&amp;L</v>
       </c>
       <c r="C5" t="str">
         <v>Invite to JRM</v>
@@ -504,15 +507,15 @@
         <v>jrm</v>
       </c>
       <c r="G5">
-        <v>45523</v>
+        <v>45929</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ENT-16621</v>
+        <v>ENT-16700</v>
       </c>
       <c r="B6" t="str">
-        <v>CIW Data Products to PROD</v>
+        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
       </c>
       <c r="C6" t="str">
         <v>Invite to JRM</v>
@@ -521,18 +524,18 @@
         <v>FLCM</v>
       </c>
       <c r="E6" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G6">
-        <v>45596</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENT-16374</v>
+        <v>ENT-16621</v>
       </c>
       <c r="B7" t="str">
-        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
+        <v>CIW Data Products to PROD</v>
       </c>
       <c r="C7" t="str">
         <v>Invite to JRM</v>
@@ -541,18 +544,18 @@
         <v>FLCM</v>
       </c>
       <c r="E7" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G7">
-        <v>45455</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENT-16031</v>
+        <v>ENT-16374</v>
       </c>
       <c r="B8" t="str">
-        <v>Fraud - Notes generator</v>
+        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
       </c>
       <c r="C8" t="str">
         <v>Invite to JRM</v>
@@ -564,15 +567,15 @@
         <v>jrm</v>
       </c>
       <c r="G8">
-        <v>45649</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-15917</v>
+        <v>ENT-16031</v>
       </c>
       <c r="B9" t="str">
-        <v>REBO Bill Payment Investigation Requests</v>
+        <v>Fraud - Notes generator</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -584,15 +587,15 @@
         <v>jrm</v>
       </c>
       <c r="G9">
-        <v>45613</v>
+        <v>45649</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-17286</v>
+        <v>ENT-15917</v>
       </c>
       <c r="B10" t="str">
-        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
+        <v>REBO Bill Payment Investigation Requests</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -601,18 +604,18 @@
         <v>FLCM</v>
       </c>
       <c r="E10" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G10">
-        <v>45699</v>
+        <v>45613</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-17202</v>
+        <v>ENT-17286</v>
       </c>
       <c r="B11" t="str">
-        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
+        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -621,18 +624,18 @@
         <v>FLCM</v>
       </c>
       <c r="E11" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G11">
-        <v>45690</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17202</v>
       </c>
       <c r="B12" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -641,21 +644,18 @@
         <v>FLCM</v>
       </c>
       <c r="E12" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F12" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G12">
-        <v>45686</v>
+        <v>45690</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B13" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -664,18 +664,21 @@
         <v>FLCM</v>
       </c>
       <c r="E13" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F13" t="str">
+        <v>PDF</v>
       </c>
       <c r="G13">
-        <v>45700</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B14" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -687,15 +690,15 @@
         <v>estimates</v>
       </c>
       <c r="G14">
-        <v>45656</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B15" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -707,15 +710,15 @@
         <v>estimates</v>
       </c>
       <c r="G15">
-        <v>45588</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B16" t="str">
-        <v>Data Source to EDGE</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -727,15 +730,15 @@
         <v>estimates</v>
       </c>
       <c r="G16">
-        <v>45664</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ENT-17054</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B17" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -744,21 +747,18 @@
         <v>FLCM</v>
       </c>
       <c r="E17" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F17" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G17">
-        <v>45691</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-17054</v>
       </c>
       <c r="B18" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
@@ -769,16 +769,19 @@
       <c r="E18" t="str">
         <v>approved</v>
       </c>
+      <c r="F18" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G18">
-        <v>45299</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ENT-14372</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B19" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
@@ -789,19 +792,16 @@
       <c r="E19" t="str">
         <v>approved</v>
       </c>
-      <c r="F19" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G19">
-        <v>45512</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-14372</v>
       </c>
       <c r="B20" t="str">
-        <v>RAMP Phase 2</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
@@ -816,58 +816,58 @@
         <v>PDF</v>
       </c>
       <c r="G20">
-        <v>45562</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B21" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D21" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E21" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F21" t="str">
+        <v>PDF</v>
       </c>
       <c r="G21">
-        <v>45695</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B22" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D22" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E22" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F22" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G22">
-        <v>45688</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B23" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
@@ -882,15 +882,15 @@
         <v>PDF</v>
       </c>
       <c r="G23">
-        <v>45701</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B24" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
@@ -905,15 +905,15 @@
         <v>PDF</v>
       </c>
       <c r="G24">
-        <v>45695</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B25" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
@@ -924,16 +924,19 @@
       <c r="E25" t="str">
         <v>approved</v>
       </c>
+      <c r="F25" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G25">
-        <v>45706</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B26" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
@@ -942,138 +945,138 @@
         <v>FLCM</v>
       </c>
       <c r="E26" t="str">
-        <v>estimates</v>
+        <v>approved</v>
       </c>
       <c r="G26">
-        <v>45559</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B27" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D27" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E27" t="str">
         <v>estimates</v>
       </c>
       <c r="G27">
-        <v>45623</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B28" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D28" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E28" t="str">
         <v>estimates</v>
       </c>
       <c r="G28">
-        <v>45355</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B29" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>CorpSec</v>
+        <v>FLCM</v>
       </c>
       <c r="E29" t="str">
         <v>estimates</v>
       </c>
       <c r="G29">
-        <v>45446</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B30" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D30" t="str">
-        <v>BSCM/ESCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E30" t="str">
         <v>estimates</v>
       </c>
       <c r="G30">
-        <v>45477</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B31" t="str">
-        <v>CSDM Upgrade</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D31" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E31" t="str">
         <v>estimates</v>
       </c>
       <c r="G31">
-        <v>45394</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B32" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D32" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E32" t="str">
-        <v>ofs</v>
+        <v>estimates</v>
       </c>
       <c r="G32">
-        <v>45531</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B33" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
@@ -1085,15 +1088,15 @@
         <v>ofs</v>
       </c>
       <c r="G33">
-        <v>45453</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B34" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
@@ -1105,15 +1108,15 @@
         <v>ofs</v>
       </c>
       <c r="G34">
-        <v>45461</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B35" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
@@ -1122,95 +1125,98 @@
         <v>FLCM</v>
       </c>
       <c r="E35" t="str">
-        <v>jrm</v>
+        <v>ofs</v>
       </c>
       <c r="G35">
-        <v>45714</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B36" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D36" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E36" t="str">
-        <v>estimates</v>
+        <v>jrm</v>
       </c>
       <c r="G36">
-        <v>45686</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ENT-15822</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B37" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D37" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E37" t="str">
         <v>estimates</v>
       </c>
       <c r="G37">
-        <v>45650</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-15822</v>
       </c>
       <c r="B38" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D38" t="str">
-        <v>BSCM/ESCM</v>
+        <v>FLCM</v>
       </c>
       <c r="E38" t="str">
         <v>estimates</v>
       </c>
       <c r="G38">
-        <v>45541</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ENT-17853</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B39" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
       </c>
+      <c r="D39" t="str">
+        <v>BSCM/ESCM</v>
+      </c>
       <c r="E39" t="str">
-        <v>ofs</v>
+        <v>estimates</v>
       </c>
       <c r="G39">
-        <v>45691</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-17853</v>
       </c>
       <c r="B40" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
@@ -1219,15 +1225,15 @@
         <v>ofs</v>
       </c>
       <c r="G40">
-        <v>45559</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B41" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1236,15 +1242,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45596</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B42" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1253,15 +1259,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45378</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B43" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1270,15 +1276,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45468</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B44" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1287,15 +1293,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45310</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B45" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1304,15 +1310,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45427</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B46" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1321,15 +1327,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45279</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B47" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1338,15 +1344,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45558</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B48" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1355,15 +1361,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45383</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B49" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1372,15 +1378,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45638</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B50" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1389,15 +1395,15 @@
         <v>ofs</v>
       </c>
       <c r="G50">
-        <v>45461</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B51" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1406,15 +1412,15 @@
         <v>ofs</v>
       </c>
       <c r="G51">
-        <v>45371</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B52" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1428,10 +1434,10 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B53" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1440,15 +1446,15 @@
         <v>ofs</v>
       </c>
       <c r="G53">
-        <v>45406</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B54" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1457,15 +1463,15 @@
         <v>ofs</v>
       </c>
       <c r="G54">
-        <v>45364</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B55" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1474,15 +1480,15 @@
         <v>ofs</v>
       </c>
       <c r="G55">
-        <v>45593</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B56" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1491,15 +1497,15 @@
         <v>ofs</v>
       </c>
       <c r="G56">
-        <v>45408</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B57" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
@@ -1508,15 +1514,15 @@
         <v>ofs</v>
       </c>
       <c r="G57">
-        <v>45595</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B58" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C58" t="str">
         <v>Invite to JRM</v>
@@ -1525,15 +1531,15 @@
         <v>ofs</v>
       </c>
       <c r="G58">
-        <v>45392</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B59" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C59" t="str">
         <v>Invite to JRM</v>
@@ -1542,15 +1548,15 @@
         <v>ofs</v>
       </c>
       <c r="G59">
-        <v>45411</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B60" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C60" t="str">
         <v>Invite to JRM</v>
@@ -1564,27 +1570,27 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B61" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C61" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E61" t="str">
-        <v>jrm</v>
+        <v>ofs</v>
       </c>
       <c r="G61">
-        <v>45721</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>ENT-18725</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B62" t="str">
-        <v>US Video System - Lenel to Genetec</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C62" t="str">
         <v>Invite to JRM</v>
@@ -1596,9 +1602,26 @@
         <v>45721</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>ENT-18725</v>
+      </c>
+      <c r="B63" t="str">
+        <v>US Video System - Lenel to Genetec</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Invite to JRM</v>
+      </c>
+      <c r="E63" t="str">
+        <v>jrm</v>
+      </c>
+      <c r="G63">
+        <v>45721</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G62"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G63"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G64"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -429,16 +429,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>12323</v>
+        <v>23434</v>
       </c>
       <c r="B2" t="str">
-        <v>123123</v>
+        <v>4324</v>
       </c>
       <c r="C2" t="str">
-        <v>123123</v>
+        <v>324</v>
       </c>
       <c r="D2" t="str">
-        <v>123213</v>
+        <v>435</v>
       </c>
       <c r="E2" t="str">
         <v>jrm</v>
@@ -452,30 +452,33 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ENT-17062</v>
+        <v>12323</v>
       </c>
       <c r="B3" t="str">
-        <v>Account Open Enhancements and Outcome Orchestration</v>
+        <v>123123</v>
       </c>
       <c r="C3" t="str">
-        <v>Invite to JRM</v>
+        <v>123123</v>
       </c>
       <c r="D3" t="str">
-        <v>FLCM</v>
+        <v>123213</v>
       </c>
       <c r="E3" t="str">
         <v>jrm</v>
       </c>
-      <c r="G3">
-        <v>45672</v>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v>2025-03-15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ENT-16949</v>
+        <v>ENT-17062</v>
       </c>
       <c r="B4" t="str">
-        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
+        <v>Account Open Enhancements and Outcome Orchestration</v>
       </c>
       <c r="C4" t="str">
         <v>Invite to JRM</v>
@@ -484,18 +487,18 @@
         <v>FLCM</v>
       </c>
       <c r="E4" t="str">
-        <v>estimates</v>
+        <v>jrm</v>
       </c>
       <c r="G4">
-        <v>45531</v>
+        <v>45672</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ENT-16881</v>
+        <v>ENT-16949</v>
       </c>
       <c r="B5" t="str">
-        <v>Split up Personal Overdraft P&amp;L</v>
+        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
       </c>
       <c r="C5" t="str">
         <v>Invite to JRM</v>
@@ -504,18 +507,18 @@
         <v>FLCM</v>
       </c>
       <c r="E5" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G5">
-        <v>45929</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ENT-16700</v>
+        <v>ENT-16881</v>
       </c>
       <c r="B6" t="str">
-        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
+        <v>Split up Personal Overdraft P&amp;L</v>
       </c>
       <c r="C6" t="str">
         <v>Invite to JRM</v>
@@ -527,15 +530,15 @@
         <v>jrm</v>
       </c>
       <c r="G6">
-        <v>45523</v>
+        <v>45929</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENT-16621</v>
+        <v>ENT-16700</v>
       </c>
       <c r="B7" t="str">
-        <v>CIW Data Products to PROD</v>
+        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
       </c>
       <c r="C7" t="str">
         <v>Invite to JRM</v>
@@ -544,18 +547,18 @@
         <v>FLCM</v>
       </c>
       <c r="E7" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G7">
-        <v>45596</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENT-16374</v>
+        <v>ENT-16621</v>
       </c>
       <c r="B8" t="str">
-        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
+        <v>CIW Data Products to PROD</v>
       </c>
       <c r="C8" t="str">
         <v>Invite to JRM</v>
@@ -564,18 +567,18 @@
         <v>FLCM</v>
       </c>
       <c r="E8" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G8">
-        <v>45455</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-16031</v>
+        <v>ENT-16374</v>
       </c>
       <c r="B9" t="str">
-        <v>Fraud - Notes generator</v>
+        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -587,15 +590,15 @@
         <v>jrm</v>
       </c>
       <c r="G9">
-        <v>45649</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-15917</v>
+        <v>ENT-16031</v>
       </c>
       <c r="B10" t="str">
-        <v>REBO Bill Payment Investigation Requests</v>
+        <v>Fraud - Notes generator</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -607,15 +610,15 @@
         <v>jrm</v>
       </c>
       <c r="G10">
-        <v>45613</v>
+        <v>45649</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-17286</v>
+        <v>ENT-15917</v>
       </c>
       <c r="B11" t="str">
-        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
+        <v>REBO Bill Payment Investigation Requests</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -624,18 +627,18 @@
         <v>FLCM</v>
       </c>
       <c r="E11" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G11">
-        <v>45699</v>
+        <v>45613</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-17202</v>
+        <v>ENT-17286</v>
       </c>
       <c r="B12" t="str">
-        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
+        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -644,18 +647,18 @@
         <v>FLCM</v>
       </c>
       <c r="E12" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G12">
-        <v>45690</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17202</v>
       </c>
       <c r="B13" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -664,21 +667,18 @@
         <v>FLCM</v>
       </c>
       <c r="E13" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F13" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G13">
-        <v>45686</v>
+        <v>45690</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B14" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -687,18 +687,21 @@
         <v>FLCM</v>
       </c>
       <c r="E14" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F14" t="str">
+        <v>PDF</v>
       </c>
       <c r="G14">
-        <v>45700</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B15" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -710,15 +713,15 @@
         <v>estimates</v>
       </c>
       <c r="G15">
-        <v>45656</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B16" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -730,15 +733,15 @@
         <v>estimates</v>
       </c>
       <c r="G16">
-        <v>45588</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B17" t="str">
-        <v>Data Source to EDGE</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -750,15 +753,15 @@
         <v>estimates</v>
       </c>
       <c r="G17">
-        <v>45664</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ENT-17054</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B18" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
@@ -767,21 +770,18 @@
         <v>FLCM</v>
       </c>
       <c r="E18" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F18" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G18">
-        <v>45691</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-17054</v>
       </c>
       <c r="B19" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
@@ -792,16 +792,19 @@
       <c r="E19" t="str">
         <v>approved</v>
       </c>
+      <c r="F19" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G19">
-        <v>45299</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ENT-14372</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B20" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
@@ -812,19 +815,16 @@
       <c r="E20" t="str">
         <v>approved</v>
       </c>
-      <c r="F20" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G20">
-        <v>45512</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-14372</v>
       </c>
       <c r="B21" t="str">
-        <v>RAMP Phase 2</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
@@ -839,58 +839,58 @@
         <v>PDF</v>
       </c>
       <c r="G21">
-        <v>45562</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B22" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D22" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E22" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F22" t="str">
+        <v>PDF</v>
       </c>
       <c r="G22">
-        <v>45695</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B23" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D23" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E23" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F23" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G23">
-        <v>45688</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B24" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
@@ -905,15 +905,15 @@
         <v>PDF</v>
       </c>
       <c r="G24">
-        <v>45701</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B25" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
@@ -928,15 +928,15 @@
         <v>PDF</v>
       </c>
       <c r="G25">
-        <v>45695</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B26" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
@@ -947,16 +947,19 @@
       <c r="E26" t="str">
         <v>approved</v>
       </c>
+      <c r="F26" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G26">
-        <v>45706</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B27" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
@@ -965,138 +968,138 @@
         <v>FLCM</v>
       </c>
       <c r="E27" t="str">
-        <v>estimates</v>
+        <v>approved</v>
       </c>
       <c r="G27">
-        <v>45559</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B28" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D28" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E28" t="str">
         <v>estimates</v>
       </c>
       <c r="G28">
-        <v>45623</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B29" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E29" t="str">
         <v>estimates</v>
       </c>
       <c r="G29">
-        <v>45355</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B30" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D30" t="str">
-        <v>CorpSec</v>
+        <v>FLCM</v>
       </c>
       <c r="E30" t="str">
         <v>estimates</v>
       </c>
       <c r="G30">
-        <v>45446</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B31" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D31" t="str">
-        <v>BSCM/ESCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E31" t="str">
         <v>estimates</v>
       </c>
       <c r="G31">
-        <v>45477</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B32" t="str">
-        <v>CSDM Upgrade</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D32" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E32" t="str">
         <v>estimates</v>
       </c>
       <c r="G32">
-        <v>45394</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B33" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D33" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E33" t="str">
-        <v>ofs</v>
+        <v>estimates</v>
       </c>
       <c r="G33">
-        <v>45531</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B34" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
@@ -1108,15 +1111,15 @@
         <v>ofs</v>
       </c>
       <c r="G34">
-        <v>45453</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B35" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
@@ -1128,15 +1131,15 @@
         <v>ofs</v>
       </c>
       <c r="G35">
-        <v>45461</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B36" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
@@ -1145,95 +1148,98 @@
         <v>FLCM</v>
       </c>
       <c r="E36" t="str">
-        <v>jrm</v>
+        <v>ofs</v>
       </c>
       <c r="G36">
-        <v>45714</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B37" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D37" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E37" t="str">
-        <v>estimates</v>
+        <v>jrm</v>
       </c>
       <c r="G37">
-        <v>45686</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ENT-15822</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B38" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D38" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E38" t="str">
         <v>estimates</v>
       </c>
       <c r="G38">
-        <v>45650</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-15822</v>
       </c>
       <c r="B39" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D39" t="str">
-        <v>BSCM/ESCM</v>
+        <v>FLCM</v>
       </c>
       <c r="E39" t="str">
         <v>estimates</v>
       </c>
       <c r="G39">
-        <v>45541</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENT-17853</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B40" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
       </c>
+      <c r="D40" t="str">
+        <v>BSCM/ESCM</v>
+      </c>
       <c r="E40" t="str">
-        <v>ofs</v>
+        <v>estimates</v>
       </c>
       <c r="G40">
-        <v>45691</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-17853</v>
       </c>
       <c r="B41" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1242,15 +1248,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45559</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B42" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1259,15 +1265,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45596</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B43" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1276,15 +1282,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45378</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B44" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1293,15 +1299,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45468</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B45" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1310,15 +1316,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45310</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B46" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1327,15 +1333,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45427</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B47" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1344,15 +1350,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45279</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B48" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1361,15 +1367,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45558</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B49" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1378,15 +1384,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45383</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B50" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1395,15 +1401,15 @@
         <v>ofs</v>
       </c>
       <c r="G50">
-        <v>45638</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B51" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1412,15 +1418,15 @@
         <v>ofs</v>
       </c>
       <c r="G51">
-        <v>45461</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B52" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1429,15 +1435,15 @@
         <v>ofs</v>
       </c>
       <c r="G52">
-        <v>45371</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B53" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1451,10 +1457,10 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B54" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1463,15 +1469,15 @@
         <v>ofs</v>
       </c>
       <c r="G54">
-        <v>45406</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B55" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1480,15 +1486,15 @@
         <v>ofs</v>
       </c>
       <c r="G55">
-        <v>45364</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B56" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1497,15 +1503,15 @@
         <v>ofs</v>
       </c>
       <c r="G56">
-        <v>45593</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B57" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
@@ -1514,15 +1520,15 @@
         <v>ofs</v>
       </c>
       <c r="G57">
-        <v>45408</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B58" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C58" t="str">
         <v>Invite to JRM</v>
@@ -1531,15 +1537,15 @@
         <v>ofs</v>
       </c>
       <c r="G58">
-        <v>45595</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B59" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C59" t="str">
         <v>Invite to JRM</v>
@@ -1548,15 +1554,15 @@
         <v>ofs</v>
       </c>
       <c r="G59">
-        <v>45392</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B60" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C60" t="str">
         <v>Invite to JRM</v>
@@ -1565,15 +1571,15 @@
         <v>ofs</v>
       </c>
       <c r="G60">
-        <v>45411</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B61" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C61" t="str">
         <v>Invite to JRM</v>
@@ -1587,27 +1593,27 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B62" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C62" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E62" t="str">
-        <v>jrm</v>
+        <v>ofs</v>
       </c>
       <c r="G62">
-        <v>45721</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>ENT-18725</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B63" t="str">
-        <v>US Video System - Lenel to Genetec</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C63" t="str">
         <v>Invite to JRM</v>
@@ -1619,9 +1625,26 @@
         <v>45721</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>ENT-18725</v>
+      </c>
+      <c r="B64" t="str">
+        <v>US Video System - Lenel to Genetec</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Invite to JRM</v>
+      </c>
+      <c r="E64" t="str">
+        <v>jrm</v>
+      </c>
+      <c r="G64">
+        <v>45721</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G63"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G64"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G63"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -452,33 +452,30 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>12323</v>
+        <v>ENT-17062</v>
       </c>
       <c r="B3" t="str">
-        <v>123123</v>
+        <v>Account Open Enhancements and Outcome Orchestration</v>
       </c>
       <c r="C3" t="str">
-        <v>123123</v>
+        <v>Invite to JRM</v>
       </c>
       <c r="D3" t="str">
-        <v>123213</v>
+        <v>FLCM</v>
       </c>
       <c r="E3" t="str">
         <v>jrm</v>
       </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v>2025-03-15</v>
+      <c r="G3">
+        <v>45672</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ENT-17062</v>
+        <v>ENT-16949</v>
       </c>
       <c r="B4" t="str">
-        <v>Account Open Enhancements and Outcome Orchestration</v>
+        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
       </c>
       <c r="C4" t="str">
         <v>Invite to JRM</v>
@@ -487,18 +484,18 @@
         <v>FLCM</v>
       </c>
       <c r="E4" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G4">
-        <v>45672</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ENT-16949</v>
+        <v>ENT-16881</v>
       </c>
       <c r="B5" t="str">
-        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
+        <v>Split up Personal Overdraft P&amp;L</v>
       </c>
       <c r="C5" t="str">
         <v>Invite to JRM</v>
@@ -507,18 +504,18 @@
         <v>FLCM</v>
       </c>
       <c r="E5" t="str">
-        <v>estimates</v>
+        <v>jrm</v>
       </c>
       <c r="G5">
-        <v>45531</v>
+        <v>45929</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ENT-16881</v>
+        <v>ENT-16700</v>
       </c>
       <c r="B6" t="str">
-        <v>Split up Personal Overdraft P&amp;L</v>
+        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
       </c>
       <c r="C6" t="str">
         <v>Invite to JRM</v>
@@ -530,15 +527,15 @@
         <v>jrm</v>
       </c>
       <c r="G6">
-        <v>45929</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENT-16700</v>
+        <v>ENT-16621</v>
       </c>
       <c r="B7" t="str">
-        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
+        <v>CIW Data Products to PROD</v>
       </c>
       <c r="C7" t="str">
         <v>Invite to JRM</v>
@@ -547,18 +544,18 @@
         <v>FLCM</v>
       </c>
       <c r="E7" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G7">
-        <v>45523</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENT-16621</v>
+        <v>ENT-16374</v>
       </c>
       <c r="B8" t="str">
-        <v>CIW Data Products to PROD</v>
+        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
       </c>
       <c r="C8" t="str">
         <v>Invite to JRM</v>
@@ -567,18 +564,18 @@
         <v>FLCM</v>
       </c>
       <c r="E8" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G8">
-        <v>45596</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-16374</v>
+        <v>ENT-16031</v>
       </c>
       <c r="B9" t="str">
-        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
+        <v>Fraud - Notes generator</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -590,15 +587,15 @@
         <v>jrm</v>
       </c>
       <c r="G9">
-        <v>45455</v>
+        <v>45649</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-16031</v>
+        <v>ENT-15917</v>
       </c>
       <c r="B10" t="str">
-        <v>Fraud - Notes generator</v>
+        <v>REBO Bill Payment Investigation Requests</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -610,15 +607,15 @@
         <v>jrm</v>
       </c>
       <c r="G10">
-        <v>45649</v>
+        <v>45613</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-15917</v>
+        <v>ENT-17286</v>
       </c>
       <c r="B11" t="str">
-        <v>REBO Bill Payment Investigation Requests</v>
+        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -627,18 +624,18 @@
         <v>FLCM</v>
       </c>
       <c r="E11" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G11">
-        <v>45613</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-17286</v>
+        <v>ENT-17202</v>
       </c>
       <c r="B12" t="str">
-        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
+        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -647,18 +644,18 @@
         <v>FLCM</v>
       </c>
       <c r="E12" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G12">
-        <v>45699</v>
+        <v>45690</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-17202</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B13" t="str">
-        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -667,18 +664,21 @@
         <v>FLCM</v>
       </c>
       <c r="E13" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F13" t="str">
+        <v>PDF</v>
       </c>
       <c r="G13">
-        <v>45690</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B14" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -687,21 +687,18 @@
         <v>FLCM</v>
       </c>
       <c r="E14" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F14" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G14">
-        <v>45686</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B15" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -713,15 +710,15 @@
         <v>estimates</v>
       </c>
       <c r="G15">
-        <v>45700</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B16" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -733,15 +730,15 @@
         <v>estimates</v>
       </c>
       <c r="G16">
-        <v>45656</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B17" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -753,15 +750,15 @@
         <v>estimates</v>
       </c>
       <c r="G17">
-        <v>45588</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-17054</v>
       </c>
       <c r="B18" t="str">
-        <v>Data Source to EDGE</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
@@ -770,18 +767,21 @@
         <v>FLCM</v>
       </c>
       <c r="E18" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F18" t="str">
+        <v>PDF</v>
       </c>
       <c r="G18">
-        <v>45664</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ENT-17054</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B19" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
@@ -792,19 +792,16 @@
       <c r="E19" t="str">
         <v>approved</v>
       </c>
-      <c r="F19" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G19">
-        <v>45691</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-14372</v>
       </c>
       <c r="B20" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
@@ -815,16 +812,19 @@
       <c r="E20" t="str">
         <v>approved</v>
       </c>
+      <c r="F20" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G20">
-        <v>45299</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-14372</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B21" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
@@ -839,58 +839,58 @@
         <v>PDF</v>
       </c>
       <c r="G21">
-        <v>45512</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B22" t="str">
-        <v>RAMP Phase 2</v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D22" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E22" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F22" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G22">
-        <v>45562</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B23" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D23" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E23" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F23" t="str">
+        <v>PDF</v>
       </c>
       <c r="G23">
-        <v>45695</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B24" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
@@ -905,15 +905,15 @@
         <v>PDF</v>
       </c>
       <c r="G24">
-        <v>45688</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B25" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
@@ -928,15 +928,15 @@
         <v>PDF</v>
       </c>
       <c r="G25">
-        <v>45701</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B26" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
@@ -947,19 +947,16 @@
       <c r="E26" t="str">
         <v>approved</v>
       </c>
-      <c r="F26" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G26">
-        <v>45695</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B27" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
@@ -968,138 +965,138 @@
         <v>FLCM</v>
       </c>
       <c r="E27" t="str">
-        <v>approved</v>
+        <v>estimates</v>
       </c>
       <c r="G27">
-        <v>45706</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B28" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D28" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E28" t="str">
         <v>estimates</v>
       </c>
       <c r="G28">
-        <v>45559</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B29" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E29" t="str">
         <v>estimates</v>
       </c>
       <c r="G29">
-        <v>45623</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B30" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D30" t="str">
-        <v>FLCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E30" t="str">
         <v>estimates</v>
       </c>
       <c r="G30">
-        <v>45355</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B31" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D31" t="str">
-        <v>CorpSec</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E31" t="str">
         <v>estimates</v>
       </c>
       <c r="G31">
-        <v>45446</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B32" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D32" t="str">
-        <v>BSCM/ESCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E32" t="str">
         <v>estimates</v>
       </c>
       <c r="G32">
-        <v>45477</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B33" t="str">
-        <v>CSDM Upgrade</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D33" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E33" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G33">
-        <v>45394</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B34" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
@@ -1111,15 +1108,15 @@
         <v>ofs</v>
       </c>
       <c r="G34">
-        <v>45531</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B35" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
@@ -1131,15 +1128,15 @@
         <v>ofs</v>
       </c>
       <c r="G35">
-        <v>45453</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B36" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
@@ -1148,98 +1145,95 @@
         <v>FLCM</v>
       </c>
       <c r="E36" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G36">
-        <v>45461</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B37" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D37" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E37" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G37">
-        <v>45714</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-15822</v>
       </c>
       <c r="B38" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D38" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E38" t="str">
         <v>estimates</v>
       </c>
       <c r="G38">
-        <v>45686</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ENT-15822</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B39" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D39" t="str">
-        <v>FLCM</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E39" t="str">
         <v>estimates</v>
       </c>
       <c r="G39">
-        <v>45650</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-17853</v>
       </c>
       <c r="B40" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
       </c>
-      <c r="D40" t="str">
-        <v>BSCM/ESCM</v>
-      </c>
       <c r="E40" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G40">
-        <v>45541</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-17853</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B41" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1248,15 +1242,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45691</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B42" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1265,15 +1259,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45559</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B43" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1282,15 +1276,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45596</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B44" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1299,15 +1293,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45378</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B45" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1316,15 +1310,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45468</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B46" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1333,15 +1327,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45310</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B47" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1350,15 +1344,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45427</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B48" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1367,15 +1361,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45279</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B49" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1384,15 +1378,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45558</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B50" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1401,15 +1395,15 @@
         <v>ofs</v>
       </c>
       <c r="G50">
-        <v>45383</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B51" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1418,15 +1412,15 @@
         <v>ofs</v>
       </c>
       <c r="G51">
-        <v>45638</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B52" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1435,15 +1429,15 @@
         <v>ofs</v>
       </c>
       <c r="G52">
-        <v>45461</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B53" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1457,10 +1451,10 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B54" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1469,15 +1463,15 @@
         <v>ofs</v>
       </c>
       <c r="G54">
-        <v>45371</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B55" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1486,15 +1480,15 @@
         <v>ofs</v>
       </c>
       <c r="G55">
-        <v>45406</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B56" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1503,15 +1497,15 @@
         <v>ofs</v>
       </c>
       <c r="G56">
-        <v>45364</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B57" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
@@ -1520,15 +1514,15 @@
         <v>ofs</v>
       </c>
       <c r="G57">
-        <v>45593</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B58" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C58" t="str">
         <v>Invite to JRM</v>
@@ -1537,15 +1531,15 @@
         <v>ofs</v>
       </c>
       <c r="G58">
-        <v>45408</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B59" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C59" t="str">
         <v>Invite to JRM</v>
@@ -1554,15 +1548,15 @@
         <v>ofs</v>
       </c>
       <c r="G59">
-        <v>45595</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B60" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C60" t="str">
         <v>Invite to JRM</v>
@@ -1571,15 +1565,15 @@
         <v>ofs</v>
       </c>
       <c r="G60">
-        <v>45392</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B61" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C61" t="str">
         <v>Invite to JRM</v>
@@ -1593,27 +1587,27 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B62" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C62" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E62" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G62">
-        <v>45411</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-18725</v>
       </c>
       <c r="B63" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>US Video System - Lenel to Genetec</v>
       </c>
       <c r="C63" t="str">
         <v>Invite to JRM</v>
@@ -1625,26 +1619,9 @@
         <v>45721</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="str">
-        <v>ENT-18725</v>
-      </c>
-      <c r="B64" t="str">
-        <v>US Video System - Lenel to Genetec</v>
-      </c>
-      <c r="C64" t="str">
-        <v>Invite to JRM</v>
-      </c>
-      <c r="E64" t="str">
-        <v>jrm</v>
-      </c>
-      <c r="G64">
-        <v>45721</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G64"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G63"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G62"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -429,33 +429,30 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>23434</v>
+        <v>ENT-17062</v>
       </c>
       <c r="B2" t="str">
-        <v>4324</v>
+        <v>Account Open Enhancements and Outcome Orchestration</v>
       </c>
       <c r="C2" t="str">
-        <v>324</v>
+        <v>Invite to JRM</v>
       </c>
       <c r="D2" t="str">
-        <v>435</v>
+        <v>FLCM</v>
       </c>
       <c r="E2" t="str">
         <v>jrm</v>
       </c>
-      <c r="F2" t="str">
-        <v/>
-      </c>
-      <c r="G2" t="str">
-        <v>2025-03-15</v>
+      <c r="G2">
+        <v>45672</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ENT-17062</v>
+        <v>ENT-16949</v>
       </c>
       <c r="B3" t="str">
-        <v>Account Open Enhancements and Outcome Orchestration</v>
+        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
       </c>
       <c r="C3" t="str">
         <v>Invite to JRM</v>
@@ -464,18 +461,18 @@
         <v>FLCM</v>
       </c>
       <c r="E3" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G3">
-        <v>45672</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ENT-16949</v>
+        <v>ENT-16881</v>
       </c>
       <c r="B4" t="str">
-        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
+        <v>Split up Personal Overdraft P&amp;L</v>
       </c>
       <c r="C4" t="str">
         <v>Invite to JRM</v>
@@ -484,18 +481,18 @@
         <v>FLCM</v>
       </c>
       <c r="E4" t="str">
-        <v>estimates</v>
+        <v>jrm</v>
       </c>
       <c r="G4">
-        <v>45531</v>
+        <v>45929</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ENT-16881</v>
+        <v>ENT-16700</v>
       </c>
       <c r="B5" t="str">
-        <v>Split up Personal Overdraft P&amp;L</v>
+        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
       </c>
       <c r="C5" t="str">
         <v>Invite to JRM</v>
@@ -507,15 +504,15 @@
         <v>jrm</v>
       </c>
       <c r="G5">
-        <v>45929</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ENT-16700</v>
+        <v>ENT-16621</v>
       </c>
       <c r="B6" t="str">
-        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
+        <v>CIW Data Products to PROD</v>
       </c>
       <c r="C6" t="str">
         <v>Invite to JRM</v>
@@ -524,18 +521,18 @@
         <v>FLCM</v>
       </c>
       <c r="E6" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G6">
-        <v>45523</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENT-16621</v>
+        <v>ENT-16374</v>
       </c>
       <c r="B7" t="str">
-        <v>CIW Data Products to PROD</v>
+        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
       </c>
       <c r="C7" t="str">
         <v>Invite to JRM</v>
@@ -544,18 +541,18 @@
         <v>FLCM</v>
       </c>
       <c r="E7" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G7">
-        <v>45596</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENT-16374</v>
+        <v>ENT-16031</v>
       </c>
       <c r="B8" t="str">
-        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
+        <v>Fraud - Notes generator</v>
       </c>
       <c r="C8" t="str">
         <v>Invite to JRM</v>
@@ -567,15 +564,15 @@
         <v>jrm</v>
       </c>
       <c r="G8">
-        <v>45455</v>
+        <v>45649</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-16031</v>
+        <v>ENT-15917</v>
       </c>
       <c r="B9" t="str">
-        <v>Fraud - Notes generator</v>
+        <v>REBO Bill Payment Investigation Requests</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -587,15 +584,15 @@
         <v>jrm</v>
       </c>
       <c r="G9">
-        <v>45649</v>
+        <v>45613</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-15917</v>
+        <v>ENT-17286</v>
       </c>
       <c r="B10" t="str">
-        <v>REBO Bill Payment Investigation Requests</v>
+        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -604,18 +601,18 @@
         <v>FLCM</v>
       </c>
       <c r="E10" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G10">
-        <v>45613</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-17286</v>
+        <v>ENT-17202</v>
       </c>
       <c r="B11" t="str">
-        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
+        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -624,18 +621,18 @@
         <v>FLCM</v>
       </c>
       <c r="E11" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G11">
-        <v>45699</v>
+        <v>45690</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-17202</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B12" t="str">
-        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -644,18 +641,21 @@
         <v>FLCM</v>
       </c>
       <c r="E12" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F12" t="str">
+        <v>PDF</v>
       </c>
       <c r="G12">
-        <v>45690</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B13" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -664,21 +664,18 @@
         <v>FLCM</v>
       </c>
       <c r="E13" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F13" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G13">
-        <v>45686</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B14" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -690,15 +687,15 @@
         <v>estimates</v>
       </c>
       <c r="G14">
-        <v>45700</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B15" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -710,15 +707,15 @@
         <v>estimates</v>
       </c>
       <c r="G15">
-        <v>45656</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B16" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -730,15 +727,15 @@
         <v>estimates</v>
       </c>
       <c r="G16">
-        <v>45588</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-17054</v>
       </c>
       <c r="B17" t="str">
-        <v>Data Source to EDGE</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -747,18 +744,21 @@
         <v>FLCM</v>
       </c>
       <c r="E17" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F17" t="str">
+        <v>PDF</v>
       </c>
       <c r="G17">
-        <v>45664</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ENT-17054</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B18" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
@@ -769,19 +769,16 @@
       <c r="E18" t="str">
         <v>approved</v>
       </c>
-      <c r="F18" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G18">
-        <v>45691</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-14372</v>
       </c>
       <c r="B19" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
@@ -792,16 +789,19 @@
       <c r="E19" t="str">
         <v>approved</v>
       </c>
+      <c r="F19" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G19">
-        <v>45299</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ENT-14372</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B20" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
@@ -816,58 +816,58 @@
         <v>PDF</v>
       </c>
       <c r="G20">
-        <v>45512</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B21" t="str">
-        <v>RAMP Phase 2</v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D21" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E21" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F21" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G21">
-        <v>45562</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B22" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D22" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E22" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F22" t="str">
+        <v>PDF</v>
       </c>
       <c r="G22">
-        <v>45695</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B23" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
@@ -882,15 +882,15 @@
         <v>PDF</v>
       </c>
       <c r="G23">
-        <v>45688</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B24" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
@@ -905,15 +905,15 @@
         <v>PDF</v>
       </c>
       <c r="G24">
-        <v>45701</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B25" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
@@ -924,19 +924,16 @@
       <c r="E25" t="str">
         <v>approved</v>
       </c>
-      <c r="F25" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G25">
-        <v>45695</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B26" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
@@ -945,138 +942,138 @@
         <v>FLCM</v>
       </c>
       <c r="E26" t="str">
-        <v>approved</v>
+        <v>estimates</v>
       </c>
       <c r="G26">
-        <v>45706</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B27" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D27" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E27" t="str">
         <v>estimates</v>
       </c>
       <c r="G27">
-        <v>45559</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B28" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D28" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E28" t="str">
         <v>estimates</v>
       </c>
       <c r="G28">
-        <v>45623</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B29" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>FLCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E29" t="str">
         <v>estimates</v>
       </c>
       <c r="G29">
-        <v>45355</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B30" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D30" t="str">
-        <v>CorpSec</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E30" t="str">
         <v>estimates</v>
       </c>
       <c r="G30">
-        <v>45446</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B31" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D31" t="str">
-        <v>BSCM/ESCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E31" t="str">
         <v>estimates</v>
       </c>
       <c r="G31">
-        <v>45477</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B32" t="str">
-        <v>CSDM Upgrade</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D32" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E32" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G32">
-        <v>45394</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B33" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
@@ -1088,15 +1085,15 @@
         <v>ofs</v>
       </c>
       <c r="G33">
-        <v>45531</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B34" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
@@ -1108,15 +1105,15 @@
         <v>ofs</v>
       </c>
       <c r="G34">
-        <v>45453</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B35" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
@@ -1125,98 +1122,95 @@
         <v>FLCM</v>
       </c>
       <c r="E35" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G35">
-        <v>45461</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B36" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D36" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E36" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G36">
-        <v>45714</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-15822</v>
       </c>
       <c r="B37" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D37" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E37" t="str">
         <v>estimates</v>
       </c>
       <c r="G37">
-        <v>45686</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ENT-15822</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B38" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D38" t="str">
-        <v>FLCM</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E38" t="str">
         <v>estimates</v>
       </c>
       <c r="G38">
-        <v>45650</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-17853</v>
       </c>
       <c r="B39" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
       </c>
-      <c r="D39" t="str">
-        <v>BSCM/ESCM</v>
-      </c>
       <c r="E39" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G39">
-        <v>45541</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENT-17853</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B40" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
@@ -1225,15 +1219,15 @@
         <v>ofs</v>
       </c>
       <c r="G40">
-        <v>45691</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B41" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1242,15 +1236,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45559</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B42" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1259,15 +1253,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45596</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B43" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1276,15 +1270,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45378</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B44" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1293,15 +1287,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45468</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B45" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1310,15 +1304,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45310</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B46" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1327,15 +1321,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45427</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B47" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1344,15 +1338,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45279</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B48" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1361,15 +1355,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45558</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B49" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1378,15 +1372,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45383</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B50" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1395,15 +1389,15 @@
         <v>ofs</v>
       </c>
       <c r="G50">
-        <v>45638</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B51" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1412,15 +1406,15 @@
         <v>ofs</v>
       </c>
       <c r="G51">
-        <v>45461</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B52" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1434,10 +1428,10 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B53" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1446,15 +1440,15 @@
         <v>ofs</v>
       </c>
       <c r="G53">
-        <v>45371</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B54" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1463,15 +1457,15 @@
         <v>ofs</v>
       </c>
       <c r="G54">
-        <v>45406</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B55" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1480,15 +1474,15 @@
         <v>ofs</v>
       </c>
       <c r="G55">
-        <v>45364</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B56" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1497,15 +1491,15 @@
         <v>ofs</v>
       </c>
       <c r="G56">
-        <v>45593</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B57" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
@@ -1514,15 +1508,15 @@
         <v>ofs</v>
       </c>
       <c r="G57">
-        <v>45408</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B58" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C58" t="str">
         <v>Invite to JRM</v>
@@ -1531,15 +1525,15 @@
         <v>ofs</v>
       </c>
       <c r="G58">
-        <v>45595</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B59" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C59" t="str">
         <v>Invite to JRM</v>
@@ -1548,15 +1542,15 @@
         <v>ofs</v>
       </c>
       <c r="G59">
-        <v>45392</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B60" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C60" t="str">
         <v>Invite to JRM</v>
@@ -1570,27 +1564,27 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B61" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C61" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E61" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G61">
-        <v>45411</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-18725</v>
       </c>
       <c r="B62" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>US Video System - Lenel to Genetec</v>
       </c>
       <c r="C62" t="str">
         <v>Invite to JRM</v>
@@ -1602,26 +1596,9 @@
         <v>45721</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="str">
-        <v>ENT-18725</v>
-      </c>
-      <c r="B63" t="str">
-        <v>US Video System - Lenel to Genetec</v>
-      </c>
-      <c r="C63" t="str">
-        <v>Invite to JRM</v>
-      </c>
-      <c r="E63" t="str">
-        <v>jrm</v>
-      </c>
-      <c r="G63">
-        <v>45721</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G63"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G62"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G61"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -429,10 +429,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ENT-17062</v>
+        <v>ENT-16949</v>
       </c>
       <c r="B2" t="str">
-        <v>Account Open Enhancements and Outcome Orchestration</v>
+        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
       </c>
       <c r="C2" t="str">
         <v>Invite to JRM</v>
@@ -441,18 +441,18 @@
         <v>FLCM</v>
       </c>
       <c r="E2" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G2">
-        <v>45672</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ENT-16949</v>
+        <v>ENT-16881</v>
       </c>
       <c r="B3" t="str">
-        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
+        <v>Split up Personal Overdraft P&amp;L</v>
       </c>
       <c r="C3" t="str">
         <v>Invite to JRM</v>
@@ -461,18 +461,18 @@
         <v>FLCM</v>
       </c>
       <c r="E3" t="str">
-        <v>estimates</v>
+        <v>jrm</v>
       </c>
       <c r="G3">
-        <v>45531</v>
+        <v>45929</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ENT-16881</v>
+        <v>ENT-16700</v>
       </c>
       <c r="B4" t="str">
-        <v>Split up Personal Overdraft P&amp;L</v>
+        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
       </c>
       <c r="C4" t="str">
         <v>Invite to JRM</v>
@@ -484,15 +484,15 @@
         <v>jrm</v>
       </c>
       <c r="G4">
-        <v>45929</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ENT-16700</v>
+        <v>ENT-16621</v>
       </c>
       <c r="B5" t="str">
-        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
+        <v>CIW Data Products to PROD</v>
       </c>
       <c r="C5" t="str">
         <v>Invite to JRM</v>
@@ -501,18 +501,18 @@
         <v>FLCM</v>
       </c>
       <c r="E5" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G5">
-        <v>45523</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ENT-16621</v>
+        <v>ENT-16374</v>
       </c>
       <c r="B6" t="str">
-        <v>CIW Data Products to PROD</v>
+        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
       </c>
       <c r="C6" t="str">
         <v>Invite to JRM</v>
@@ -521,18 +521,18 @@
         <v>FLCM</v>
       </c>
       <c r="E6" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G6">
-        <v>45596</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENT-16374</v>
+        <v>ENT-16031</v>
       </c>
       <c r="B7" t="str">
-        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
+        <v>Fraud - Notes generator</v>
       </c>
       <c r="C7" t="str">
         <v>Invite to JRM</v>
@@ -544,15 +544,15 @@
         <v>jrm</v>
       </c>
       <c r="G7">
-        <v>45455</v>
+        <v>45649</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENT-16031</v>
+        <v>ENT-15917</v>
       </c>
       <c r="B8" t="str">
-        <v>Fraud - Notes generator</v>
+        <v>REBO Bill Payment Investigation Requests</v>
       </c>
       <c r="C8" t="str">
         <v>Invite to JRM</v>
@@ -564,15 +564,15 @@
         <v>jrm</v>
       </c>
       <c r="G8">
-        <v>45649</v>
+        <v>45613</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-15917</v>
+        <v>ENT-17286</v>
       </c>
       <c r="B9" t="str">
-        <v>REBO Bill Payment Investigation Requests</v>
+        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -581,18 +581,18 @@
         <v>FLCM</v>
       </c>
       <c r="E9" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G9">
-        <v>45613</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-17286</v>
+        <v>ENT-17202</v>
       </c>
       <c r="B10" t="str">
-        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
+        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -601,18 +601,18 @@
         <v>FLCM</v>
       </c>
       <c r="E10" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G10">
-        <v>45699</v>
+        <v>45690</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-17202</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B11" t="str">
-        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -621,18 +621,21 @@
         <v>FLCM</v>
       </c>
       <c r="E11" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F11" t="str">
+        <v>PDF</v>
       </c>
       <c r="G11">
-        <v>45690</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B12" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -641,21 +644,18 @@
         <v>FLCM</v>
       </c>
       <c r="E12" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F12" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G12">
-        <v>45686</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B13" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -667,15 +667,15 @@
         <v>estimates</v>
       </c>
       <c r="G13">
-        <v>45700</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B14" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -687,15 +687,15 @@
         <v>estimates</v>
       </c>
       <c r="G14">
-        <v>45656</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B15" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -707,15 +707,15 @@
         <v>estimates</v>
       </c>
       <c r="G15">
-        <v>45588</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-17054</v>
       </c>
       <c r="B16" t="str">
-        <v>Data Source to EDGE</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -724,18 +724,21 @@
         <v>FLCM</v>
       </c>
       <c r="E16" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F16" t="str">
+        <v>PDF</v>
       </c>
       <c r="G16">
-        <v>45664</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ENT-17054</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B17" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -746,19 +749,16 @@
       <c r="E17" t="str">
         <v>approved</v>
       </c>
-      <c r="F17" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G17">
-        <v>45691</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-14372</v>
       </c>
       <c r="B18" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
@@ -769,16 +769,19 @@
       <c r="E18" t="str">
         <v>approved</v>
       </c>
+      <c r="F18" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G18">
-        <v>45299</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ENT-14372</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B19" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
@@ -793,58 +796,58 @@
         <v>PDF</v>
       </c>
       <c r="G19">
-        <v>45512</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B20" t="str">
-        <v>RAMP Phase 2</v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D20" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E20" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F20" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G20">
-        <v>45562</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B21" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D21" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E21" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F21" t="str">
+        <v>PDF</v>
       </c>
       <c r="G21">
-        <v>45695</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B22" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
@@ -859,15 +862,15 @@
         <v>PDF</v>
       </c>
       <c r="G22">
-        <v>45688</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B23" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
@@ -882,15 +885,15 @@
         <v>PDF</v>
       </c>
       <c r="G23">
-        <v>45701</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B24" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
@@ -901,19 +904,16 @@
       <c r="E24" t="str">
         <v>approved</v>
       </c>
-      <c r="F24" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G24">
-        <v>45695</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B25" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
@@ -922,138 +922,138 @@
         <v>FLCM</v>
       </c>
       <c r="E25" t="str">
-        <v>approved</v>
+        <v>estimates</v>
       </c>
       <c r="G25">
-        <v>45706</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B26" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D26" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E26" t="str">
         <v>estimates</v>
       </c>
       <c r="G26">
-        <v>45559</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B27" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D27" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E27" t="str">
         <v>estimates</v>
       </c>
       <c r="G27">
-        <v>45623</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B28" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D28" t="str">
-        <v>FLCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E28" t="str">
         <v>estimates</v>
       </c>
       <c r="G28">
-        <v>45355</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B29" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>CorpSec</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E29" t="str">
         <v>estimates</v>
       </c>
       <c r="G29">
-        <v>45446</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B30" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D30" t="str">
-        <v>BSCM/ESCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E30" t="str">
         <v>estimates</v>
       </c>
       <c r="G30">
-        <v>45477</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B31" t="str">
-        <v>CSDM Upgrade</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D31" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E31" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G31">
-        <v>45394</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B32" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
@@ -1065,15 +1065,15 @@
         <v>ofs</v>
       </c>
       <c r="G32">
-        <v>45531</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B33" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
@@ -1085,15 +1085,15 @@
         <v>ofs</v>
       </c>
       <c r="G33">
-        <v>45453</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B34" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
@@ -1102,98 +1102,95 @@
         <v>FLCM</v>
       </c>
       <c r="E34" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G34">
-        <v>45461</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B35" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D35" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E35" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G35">
-        <v>45714</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-15822</v>
       </c>
       <c r="B36" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D36" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E36" t="str">
         <v>estimates</v>
       </c>
       <c r="G36">
-        <v>45686</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ENT-15822</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B37" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D37" t="str">
-        <v>FLCM</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E37" t="str">
         <v>estimates</v>
       </c>
       <c r="G37">
-        <v>45650</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-17853</v>
       </c>
       <c r="B38" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
       </c>
-      <c r="D38" t="str">
-        <v>BSCM/ESCM</v>
-      </c>
       <c r="E38" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G38">
-        <v>45541</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ENT-17853</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B39" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
@@ -1202,15 +1199,15 @@
         <v>ofs</v>
       </c>
       <c r="G39">
-        <v>45691</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B40" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
@@ -1219,15 +1216,15 @@
         <v>ofs</v>
       </c>
       <c r="G40">
-        <v>45559</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B41" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1236,15 +1233,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45596</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B42" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1253,15 +1250,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45378</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B43" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1270,15 +1267,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45468</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B44" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1287,15 +1284,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45310</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B45" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1304,15 +1301,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45427</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B46" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1321,15 +1318,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45279</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B47" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1338,15 +1335,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45558</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B48" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1355,15 +1352,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45383</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B49" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1372,15 +1369,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45638</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B50" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1389,15 +1386,15 @@
         <v>ofs</v>
       </c>
       <c r="G50">
-        <v>45461</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B51" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1411,10 +1408,10 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B52" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1423,15 +1420,15 @@
         <v>ofs</v>
       </c>
       <c r="G52">
-        <v>45371</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B53" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1440,15 +1437,15 @@
         <v>ofs</v>
       </c>
       <c r="G53">
-        <v>45406</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B54" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1457,15 +1454,15 @@
         <v>ofs</v>
       </c>
       <c r="G54">
-        <v>45364</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B55" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1474,15 +1471,15 @@
         <v>ofs</v>
       </c>
       <c r="G55">
-        <v>45593</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B56" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1491,15 +1488,15 @@
         <v>ofs</v>
       </c>
       <c r="G56">
-        <v>45408</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B57" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
@@ -1508,15 +1505,15 @@
         <v>ofs</v>
       </c>
       <c r="G57">
-        <v>45595</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B58" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C58" t="str">
         <v>Invite to JRM</v>
@@ -1525,15 +1522,15 @@
         <v>ofs</v>
       </c>
       <c r="G58">
-        <v>45392</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B59" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C59" t="str">
         <v>Invite to JRM</v>
@@ -1547,27 +1544,27 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B60" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C60" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E60" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G60">
-        <v>45411</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-18725</v>
       </c>
       <c r="B61" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>US Video System - Lenel to Genetec</v>
       </c>
       <c r="C61" t="str">
         <v>Invite to JRM</v>
@@ -1579,26 +1576,9 @@
         <v>45721</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="str">
-        <v>ENT-18725</v>
-      </c>
-      <c r="B62" t="str">
-        <v>US Video System - Lenel to Genetec</v>
-      </c>
-      <c r="C62" t="str">
-        <v>Invite to JRM</v>
-      </c>
-      <c r="E62" t="str">
-        <v>jrm</v>
-      </c>
-      <c r="G62">
-        <v>45721</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G62"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G61"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G62"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -429,30 +429,33 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ENT-16949</v>
+        <v>1234</v>
       </c>
       <c r="B2" t="str">
-        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
+        <v>1234123</v>
       </c>
       <c r="C2" t="str">
-        <v>Invite to JRM</v>
+        <v>1234</v>
       </c>
       <c r="D2" t="str">
-        <v>FLCM</v>
+        <v>1234</v>
       </c>
       <c r="E2" t="str">
-        <v>estimates</v>
-      </c>
-      <c r="G2">
-        <v>45531</v>
+        <v>jrm</v>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v>2025-03-15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ENT-16881</v>
+        <v>ENT-16949</v>
       </c>
       <c r="B3" t="str">
-        <v>Split up Personal Overdraft P&amp;L</v>
+        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
       </c>
       <c r="C3" t="str">
         <v>Invite to JRM</v>
@@ -461,18 +464,18 @@
         <v>FLCM</v>
       </c>
       <c r="E3" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G3">
-        <v>45929</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ENT-16700</v>
+        <v>ENT-16881</v>
       </c>
       <c r="B4" t="str">
-        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
+        <v>Split up Personal Overdraft P&amp;L</v>
       </c>
       <c r="C4" t="str">
         <v>Invite to JRM</v>
@@ -484,15 +487,15 @@
         <v>jrm</v>
       </c>
       <c r="G4">
-        <v>45523</v>
+        <v>45929</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ENT-16621</v>
+        <v>ENT-16700</v>
       </c>
       <c r="B5" t="str">
-        <v>CIW Data Products to PROD</v>
+        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
       </c>
       <c r="C5" t="str">
         <v>Invite to JRM</v>
@@ -501,18 +504,18 @@
         <v>FLCM</v>
       </c>
       <c r="E5" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G5">
-        <v>45596</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ENT-16374</v>
+        <v>ENT-16621</v>
       </c>
       <c r="B6" t="str">
-        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
+        <v>CIW Data Products to PROD</v>
       </c>
       <c r="C6" t="str">
         <v>Invite to JRM</v>
@@ -521,18 +524,18 @@
         <v>FLCM</v>
       </c>
       <c r="E6" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G6">
-        <v>45455</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENT-16031</v>
+        <v>ENT-16374</v>
       </c>
       <c r="B7" t="str">
-        <v>Fraud - Notes generator</v>
+        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
       </c>
       <c r="C7" t="str">
         <v>Invite to JRM</v>
@@ -544,15 +547,15 @@
         <v>jrm</v>
       </c>
       <c r="G7">
-        <v>45649</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENT-15917</v>
+        <v>ENT-16031</v>
       </c>
       <c r="B8" t="str">
-        <v>REBO Bill Payment Investigation Requests</v>
+        <v>Fraud - Notes generator</v>
       </c>
       <c r="C8" t="str">
         <v>Invite to JRM</v>
@@ -564,15 +567,15 @@
         <v>jrm</v>
       </c>
       <c r="G8">
-        <v>45613</v>
+        <v>45649</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-17286</v>
+        <v>ENT-15917</v>
       </c>
       <c r="B9" t="str">
-        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
+        <v>REBO Bill Payment Investigation Requests</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -581,18 +584,18 @@
         <v>FLCM</v>
       </c>
       <c r="E9" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G9">
-        <v>45699</v>
+        <v>45613</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-17202</v>
+        <v>ENT-17286</v>
       </c>
       <c r="B10" t="str">
-        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
+        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -601,18 +604,18 @@
         <v>FLCM</v>
       </c>
       <c r="E10" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G10">
-        <v>45690</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17202</v>
       </c>
       <c r="B11" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -621,21 +624,18 @@
         <v>FLCM</v>
       </c>
       <c r="E11" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F11" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G11">
-        <v>45686</v>
+        <v>45690</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B12" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -644,18 +644,21 @@
         <v>FLCM</v>
       </c>
       <c r="E12" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F12" t="str">
+        <v>PDF</v>
       </c>
       <c r="G12">
-        <v>45700</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B13" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -667,15 +670,15 @@
         <v>estimates</v>
       </c>
       <c r="G13">
-        <v>45656</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B14" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -687,15 +690,15 @@
         <v>estimates</v>
       </c>
       <c r="G14">
-        <v>45588</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B15" t="str">
-        <v>Data Source to EDGE</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -707,15 +710,15 @@
         <v>estimates</v>
       </c>
       <c r="G15">
-        <v>45664</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-17054</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B16" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -724,21 +727,18 @@
         <v>FLCM</v>
       </c>
       <c r="E16" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F16" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G16">
-        <v>45691</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-17054</v>
       </c>
       <c r="B17" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -749,16 +749,19 @@
       <c r="E17" t="str">
         <v>approved</v>
       </c>
+      <c r="F17" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G17">
-        <v>45299</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ENT-14372</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B18" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
@@ -769,19 +772,16 @@
       <c r="E18" t="str">
         <v>approved</v>
       </c>
-      <c r="F18" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G18">
-        <v>45512</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-14372</v>
       </c>
       <c r="B19" t="str">
-        <v>RAMP Phase 2</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
@@ -796,58 +796,58 @@
         <v>PDF</v>
       </c>
       <c r="G19">
-        <v>45562</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B20" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D20" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E20" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F20" t="str">
+        <v>PDF</v>
       </c>
       <c r="G20">
-        <v>45695</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B21" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D21" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E21" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F21" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G21">
-        <v>45688</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B22" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
@@ -862,15 +862,15 @@
         <v>PDF</v>
       </c>
       <c r="G22">
-        <v>45701</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B23" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
@@ -885,15 +885,15 @@
         <v>PDF</v>
       </c>
       <c r="G23">
-        <v>45695</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B24" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
@@ -904,16 +904,19 @@
       <c r="E24" t="str">
         <v>approved</v>
       </c>
+      <c r="F24" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G24">
-        <v>45706</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B25" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
@@ -922,138 +925,138 @@
         <v>FLCM</v>
       </c>
       <c r="E25" t="str">
-        <v>estimates</v>
+        <v>approved</v>
       </c>
       <c r="G25">
-        <v>45559</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B26" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D26" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E26" t="str">
         <v>estimates</v>
       </c>
       <c r="G26">
-        <v>45623</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B27" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D27" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E27" t="str">
         <v>estimates</v>
       </c>
       <c r="G27">
-        <v>45355</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B28" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D28" t="str">
-        <v>CorpSec</v>
+        <v>FLCM</v>
       </c>
       <c r="E28" t="str">
         <v>estimates</v>
       </c>
       <c r="G28">
-        <v>45446</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B29" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>BSCM/ESCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E29" t="str">
         <v>estimates</v>
       </c>
       <c r="G29">
-        <v>45477</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B30" t="str">
-        <v>CSDM Upgrade</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D30" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E30" t="str">
         <v>estimates</v>
       </c>
       <c r="G30">
-        <v>45394</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B31" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D31" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E31" t="str">
-        <v>ofs</v>
+        <v>estimates</v>
       </c>
       <c r="G31">
-        <v>45531</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B32" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
@@ -1065,15 +1068,15 @@
         <v>ofs</v>
       </c>
       <c r="G32">
-        <v>45453</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B33" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
@@ -1085,15 +1088,15 @@
         <v>ofs</v>
       </c>
       <c r="G33">
-        <v>45461</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B34" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
@@ -1102,95 +1105,98 @@
         <v>FLCM</v>
       </c>
       <c r="E34" t="str">
-        <v>jrm</v>
+        <v>ofs</v>
       </c>
       <c r="G34">
-        <v>45714</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B35" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D35" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E35" t="str">
-        <v>estimates</v>
+        <v>jrm</v>
       </c>
       <c r="G35">
-        <v>45686</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-15822</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B36" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D36" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E36" t="str">
         <v>estimates</v>
       </c>
       <c r="G36">
-        <v>45650</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-15822</v>
       </c>
       <c r="B37" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D37" t="str">
-        <v>BSCM/ESCM</v>
+        <v>FLCM</v>
       </c>
       <c r="E37" t="str">
         <v>estimates</v>
       </c>
       <c r="G37">
-        <v>45541</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ENT-17853</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B38" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
       </c>
+      <c r="D38" t="str">
+        <v>BSCM/ESCM</v>
+      </c>
       <c r="E38" t="str">
-        <v>ofs</v>
+        <v>estimates</v>
       </c>
       <c r="G38">
-        <v>45691</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-17853</v>
       </c>
       <c r="B39" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
@@ -1199,15 +1205,15 @@
         <v>ofs</v>
       </c>
       <c r="G39">
-        <v>45559</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B40" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
@@ -1216,15 +1222,15 @@
         <v>ofs</v>
       </c>
       <c r="G40">
-        <v>45596</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B41" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1233,15 +1239,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45378</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B42" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1250,15 +1256,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45468</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B43" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1267,15 +1273,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45310</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B44" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1284,15 +1290,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45427</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B45" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1301,15 +1307,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45279</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B46" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1318,15 +1324,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45558</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B47" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1335,15 +1341,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45383</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B48" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1352,15 +1358,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45638</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B49" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1369,15 +1375,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45461</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B50" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1386,15 +1392,15 @@
         <v>ofs</v>
       </c>
       <c r="G50">
-        <v>45371</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B51" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1408,10 +1414,10 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B52" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1420,15 +1426,15 @@
         <v>ofs</v>
       </c>
       <c r="G52">
-        <v>45406</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B53" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1437,15 +1443,15 @@
         <v>ofs</v>
       </c>
       <c r="G53">
-        <v>45364</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B54" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1454,15 +1460,15 @@
         <v>ofs</v>
       </c>
       <c r="G54">
-        <v>45593</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B55" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1471,15 +1477,15 @@
         <v>ofs</v>
       </c>
       <c r="G55">
-        <v>45408</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B56" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1488,15 +1494,15 @@
         <v>ofs</v>
       </c>
       <c r="G56">
-        <v>45595</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B57" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
@@ -1505,15 +1511,15 @@
         <v>ofs</v>
       </c>
       <c r="G57">
-        <v>45392</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B58" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C58" t="str">
         <v>Invite to JRM</v>
@@ -1522,15 +1528,15 @@
         <v>ofs</v>
       </c>
       <c r="G58">
-        <v>45411</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B59" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C59" t="str">
         <v>Invite to JRM</v>
@@ -1544,27 +1550,27 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B60" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C60" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E60" t="str">
-        <v>jrm</v>
+        <v>ofs</v>
       </c>
       <c r="G60">
-        <v>45721</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ENT-18725</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B61" t="str">
-        <v>US Video System - Lenel to Genetec</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C61" t="str">
         <v>Invite to JRM</v>
@@ -1576,9 +1582,26 @@
         <v>45721</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>ENT-18725</v>
+      </c>
+      <c r="B62" t="str">
+        <v>US Video System - Lenel to Genetec</v>
+      </c>
+      <c r="C62" t="str">
+        <v>Invite to JRM</v>
+      </c>
+      <c r="E62" t="str">
+        <v>jrm</v>
+      </c>
+      <c r="G62">
+        <v>45721</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G62"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G63"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -429,10 +429,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>123445</v>
+      </c>
+      <c r="B2" t="str">
         <v>1234</v>
-      </c>
-      <c r="B2" t="str">
-        <v>1234123</v>
       </c>
       <c r="C2" t="str">
         <v>1234</v>
@@ -452,30 +452,33 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ENT-16949</v>
+        <v>1234</v>
       </c>
       <c r="B3" t="str">
-        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
+        <v>1234123</v>
       </c>
       <c r="C3" t="str">
-        <v>Invite to JRM</v>
+        <v>1234</v>
       </c>
       <c r="D3" t="str">
-        <v>FLCM</v>
+        <v>1234</v>
       </c>
       <c r="E3" t="str">
-        <v>estimates</v>
-      </c>
-      <c r="G3">
-        <v>45531</v>
+        <v>jrm</v>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v>2025-03-15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ENT-16881</v>
+        <v>ENT-16949</v>
       </c>
       <c r="B4" t="str">
-        <v>Split up Personal Overdraft P&amp;L</v>
+        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
       </c>
       <c r="C4" t="str">
         <v>Invite to JRM</v>
@@ -484,18 +487,18 @@
         <v>FLCM</v>
       </c>
       <c r="E4" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G4">
-        <v>45929</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ENT-16700</v>
+        <v>ENT-16881</v>
       </c>
       <c r="B5" t="str">
-        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
+        <v>Split up Personal Overdraft P&amp;L</v>
       </c>
       <c r="C5" t="str">
         <v>Invite to JRM</v>
@@ -507,15 +510,15 @@
         <v>jrm</v>
       </c>
       <c r="G5">
-        <v>45523</v>
+        <v>45929</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ENT-16621</v>
+        <v>ENT-16700</v>
       </c>
       <c r="B6" t="str">
-        <v>CIW Data Products to PROD</v>
+        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
       </c>
       <c r="C6" t="str">
         <v>Invite to JRM</v>
@@ -524,18 +527,18 @@
         <v>FLCM</v>
       </c>
       <c r="E6" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G6">
-        <v>45596</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENT-16374</v>
+        <v>ENT-16621</v>
       </c>
       <c r="B7" t="str">
-        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
+        <v>CIW Data Products to PROD</v>
       </c>
       <c r="C7" t="str">
         <v>Invite to JRM</v>
@@ -544,18 +547,18 @@
         <v>FLCM</v>
       </c>
       <c r="E7" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G7">
-        <v>45455</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENT-16031</v>
+        <v>ENT-16374</v>
       </c>
       <c r="B8" t="str">
-        <v>Fraud - Notes generator</v>
+        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
       </c>
       <c r="C8" t="str">
         <v>Invite to JRM</v>
@@ -567,15 +570,15 @@
         <v>jrm</v>
       </c>
       <c r="G8">
-        <v>45649</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-15917</v>
+        <v>ENT-16031</v>
       </c>
       <c r="B9" t="str">
-        <v>REBO Bill Payment Investigation Requests</v>
+        <v>Fraud - Notes generator</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -587,15 +590,15 @@
         <v>jrm</v>
       </c>
       <c r="G9">
-        <v>45613</v>
+        <v>45649</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-17286</v>
+        <v>ENT-15917</v>
       </c>
       <c r="B10" t="str">
-        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
+        <v>REBO Bill Payment Investigation Requests</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -604,18 +607,18 @@
         <v>FLCM</v>
       </c>
       <c r="E10" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G10">
-        <v>45699</v>
+        <v>45613</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-17202</v>
+        <v>ENT-17286</v>
       </c>
       <c r="B11" t="str">
-        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
+        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -624,18 +627,18 @@
         <v>FLCM</v>
       </c>
       <c r="E11" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G11">
-        <v>45690</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17202</v>
       </c>
       <c r="B12" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -644,21 +647,18 @@
         <v>FLCM</v>
       </c>
       <c r="E12" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F12" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G12">
-        <v>45686</v>
+        <v>45690</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B13" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -667,18 +667,21 @@
         <v>FLCM</v>
       </c>
       <c r="E13" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F13" t="str">
+        <v>PDF</v>
       </c>
       <c r="G13">
-        <v>45700</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B14" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -690,15 +693,15 @@
         <v>estimates</v>
       </c>
       <c r="G14">
-        <v>45656</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B15" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -710,15 +713,15 @@
         <v>estimates</v>
       </c>
       <c r="G15">
-        <v>45588</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B16" t="str">
-        <v>Data Source to EDGE</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -730,15 +733,15 @@
         <v>estimates</v>
       </c>
       <c r="G16">
-        <v>45664</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ENT-17054</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B17" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -747,21 +750,18 @@
         <v>FLCM</v>
       </c>
       <c r="E17" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F17" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G17">
-        <v>45691</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-17054</v>
       </c>
       <c r="B18" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
@@ -772,16 +772,19 @@
       <c r="E18" t="str">
         <v>approved</v>
       </c>
+      <c r="F18" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G18">
-        <v>45299</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ENT-14372</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B19" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
@@ -792,19 +795,16 @@
       <c r="E19" t="str">
         <v>approved</v>
       </c>
-      <c r="F19" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G19">
-        <v>45512</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-14372</v>
       </c>
       <c r="B20" t="str">
-        <v>RAMP Phase 2</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
@@ -819,58 +819,58 @@
         <v>PDF</v>
       </c>
       <c r="G20">
-        <v>45562</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B21" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D21" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E21" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F21" t="str">
+        <v>PDF</v>
       </c>
       <c r="G21">
-        <v>45695</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B22" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D22" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E22" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F22" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G22">
-        <v>45688</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B23" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
@@ -885,15 +885,15 @@
         <v>PDF</v>
       </c>
       <c r="G23">
-        <v>45701</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B24" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
@@ -908,15 +908,15 @@
         <v>PDF</v>
       </c>
       <c r="G24">
-        <v>45695</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B25" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
@@ -927,16 +927,19 @@
       <c r="E25" t="str">
         <v>approved</v>
       </c>
+      <c r="F25" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G25">
-        <v>45706</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B26" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
@@ -945,138 +948,138 @@
         <v>FLCM</v>
       </c>
       <c r="E26" t="str">
-        <v>estimates</v>
+        <v>approved</v>
       </c>
       <c r="G26">
-        <v>45559</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B27" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D27" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E27" t="str">
         <v>estimates</v>
       </c>
       <c r="G27">
-        <v>45623</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B28" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D28" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E28" t="str">
         <v>estimates</v>
       </c>
       <c r="G28">
-        <v>45355</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B29" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>CorpSec</v>
+        <v>FLCM</v>
       </c>
       <c r="E29" t="str">
         <v>estimates</v>
       </c>
       <c r="G29">
-        <v>45446</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B30" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D30" t="str">
-        <v>BSCM/ESCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E30" t="str">
         <v>estimates</v>
       </c>
       <c r="G30">
-        <v>45477</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B31" t="str">
-        <v>CSDM Upgrade</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D31" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E31" t="str">
         <v>estimates</v>
       </c>
       <c r="G31">
-        <v>45394</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B32" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D32" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E32" t="str">
-        <v>ofs</v>
+        <v>estimates</v>
       </c>
       <c r="G32">
-        <v>45531</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B33" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
@@ -1088,15 +1091,15 @@
         <v>ofs</v>
       </c>
       <c r="G33">
-        <v>45453</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B34" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
@@ -1108,15 +1111,15 @@
         <v>ofs</v>
       </c>
       <c r="G34">
-        <v>45461</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B35" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
@@ -1125,95 +1128,98 @@
         <v>FLCM</v>
       </c>
       <c r="E35" t="str">
-        <v>jrm</v>
+        <v>ofs</v>
       </c>
       <c r="G35">
-        <v>45714</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B36" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D36" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E36" t="str">
-        <v>estimates</v>
+        <v>jrm</v>
       </c>
       <c r="G36">
-        <v>45686</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ENT-15822</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B37" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D37" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E37" t="str">
         <v>estimates</v>
       </c>
       <c r="G37">
-        <v>45650</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-15822</v>
       </c>
       <c r="B38" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D38" t="str">
-        <v>BSCM/ESCM</v>
+        <v>FLCM</v>
       </c>
       <c r="E38" t="str">
         <v>estimates</v>
       </c>
       <c r="G38">
-        <v>45541</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ENT-17853</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B39" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
       </c>
+      <c r="D39" t="str">
+        <v>BSCM/ESCM</v>
+      </c>
       <c r="E39" t="str">
-        <v>ofs</v>
+        <v>estimates</v>
       </c>
       <c r="G39">
-        <v>45691</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-17853</v>
       </c>
       <c r="B40" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
@@ -1222,15 +1228,15 @@
         <v>ofs</v>
       </c>
       <c r="G40">
-        <v>45559</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B41" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1239,15 +1245,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45596</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B42" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1256,15 +1262,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45378</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B43" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1273,15 +1279,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45468</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B44" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1290,15 +1296,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45310</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B45" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1307,15 +1313,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45427</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B46" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1324,15 +1330,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45279</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B47" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1341,15 +1347,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45558</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B48" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1358,15 +1364,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45383</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B49" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1375,15 +1381,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45638</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B50" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1392,15 +1398,15 @@
         <v>ofs</v>
       </c>
       <c r="G50">
-        <v>45461</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B51" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1409,15 +1415,15 @@
         <v>ofs</v>
       </c>
       <c r="G51">
-        <v>45371</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B52" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1431,10 +1437,10 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B53" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1443,15 +1449,15 @@
         <v>ofs</v>
       </c>
       <c r="G53">
-        <v>45406</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B54" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1460,15 +1466,15 @@
         <v>ofs</v>
       </c>
       <c r="G54">
-        <v>45364</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B55" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1477,15 +1483,15 @@
         <v>ofs</v>
       </c>
       <c r="G55">
-        <v>45593</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B56" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1494,15 +1500,15 @@
         <v>ofs</v>
       </c>
       <c r="G56">
-        <v>45408</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B57" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
@@ -1511,15 +1517,15 @@
         <v>ofs</v>
       </c>
       <c r="G57">
-        <v>45595</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B58" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C58" t="str">
         <v>Invite to JRM</v>
@@ -1528,15 +1534,15 @@
         <v>ofs</v>
       </c>
       <c r="G58">
-        <v>45392</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B59" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C59" t="str">
         <v>Invite to JRM</v>
@@ -1545,15 +1551,15 @@
         <v>ofs</v>
       </c>
       <c r="G59">
-        <v>45411</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B60" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C60" t="str">
         <v>Invite to JRM</v>
@@ -1567,27 +1573,27 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B61" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C61" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E61" t="str">
-        <v>jrm</v>
+        <v>ofs</v>
       </c>
       <c r="G61">
-        <v>45721</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>ENT-18725</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B62" t="str">
-        <v>US Video System - Lenel to Genetec</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C62" t="str">
         <v>Invite to JRM</v>
@@ -1599,9 +1605,26 @@
         <v>45721</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>ENT-18725</v>
+      </c>
+      <c r="B63" t="str">
+        <v>US Video System - Lenel to Genetec</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Invite to JRM</v>
+      </c>
+      <c r="E63" t="str">
+        <v>jrm</v>
+      </c>
+      <c r="G63">
+        <v>45721</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G62"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G63"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G64"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -429,16 +429,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>123445</v>
+        <v>54354</v>
       </c>
       <c r="B2" t="str">
-        <v>1234</v>
+        <v>6546</v>
       </c>
       <c r="C2" t="str">
-        <v>1234</v>
+        <v>345</v>
       </c>
       <c r="D2" t="str">
-        <v>1234</v>
+        <v>6546</v>
       </c>
       <c r="E2" t="str">
         <v>jrm</v>
@@ -452,10 +452,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
+        <v>123445</v>
+      </c>
+      <c r="B3" t="str">
         <v>1234</v>
-      </c>
-      <c r="B3" t="str">
-        <v>1234123</v>
       </c>
       <c r="C3" t="str">
         <v>1234</v>
@@ -475,30 +475,33 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ENT-16949</v>
+        <v>1234</v>
       </c>
       <c r="B4" t="str">
-        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
+        <v>1234123</v>
       </c>
       <c r="C4" t="str">
-        <v>Invite to JRM</v>
+        <v>1234</v>
       </c>
       <c r="D4" t="str">
-        <v>FLCM</v>
+        <v>1234</v>
       </c>
       <c r="E4" t="str">
-        <v>estimates</v>
-      </c>
-      <c r="G4">
-        <v>45531</v>
+        <v>jrm</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v>2025-03-15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ENT-16881</v>
+        <v>ENT-16949</v>
       </c>
       <c r="B5" t="str">
-        <v>Split up Personal Overdraft P&amp;L</v>
+        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
       </c>
       <c r="C5" t="str">
         <v>Invite to JRM</v>
@@ -507,18 +510,18 @@
         <v>FLCM</v>
       </c>
       <c r="E5" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G5">
-        <v>45929</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ENT-16700</v>
+        <v>ENT-16881</v>
       </c>
       <c r="B6" t="str">
-        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
+        <v>Split up Personal Overdraft P&amp;L</v>
       </c>
       <c r="C6" t="str">
         <v>Invite to JRM</v>
@@ -530,15 +533,15 @@
         <v>jrm</v>
       </c>
       <c r="G6">
-        <v>45523</v>
+        <v>45929</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENT-16621</v>
+        <v>ENT-16700</v>
       </c>
       <c r="B7" t="str">
-        <v>CIW Data Products to PROD</v>
+        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
       </c>
       <c r="C7" t="str">
         <v>Invite to JRM</v>
@@ -547,18 +550,18 @@
         <v>FLCM</v>
       </c>
       <c r="E7" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G7">
-        <v>45596</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENT-16374</v>
+        <v>ENT-16621</v>
       </c>
       <c r="B8" t="str">
-        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
+        <v>CIW Data Products to PROD</v>
       </c>
       <c r="C8" t="str">
         <v>Invite to JRM</v>
@@ -567,18 +570,18 @@
         <v>FLCM</v>
       </c>
       <c r="E8" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G8">
-        <v>45455</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-16031</v>
+        <v>ENT-16374</v>
       </c>
       <c r="B9" t="str">
-        <v>Fraud - Notes generator</v>
+        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -590,15 +593,15 @@
         <v>jrm</v>
       </c>
       <c r="G9">
-        <v>45649</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-15917</v>
+        <v>ENT-16031</v>
       </c>
       <c r="B10" t="str">
-        <v>REBO Bill Payment Investigation Requests</v>
+        <v>Fraud - Notes generator</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -610,15 +613,15 @@
         <v>jrm</v>
       </c>
       <c r="G10">
-        <v>45613</v>
+        <v>45649</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-17286</v>
+        <v>ENT-15917</v>
       </c>
       <c r="B11" t="str">
-        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
+        <v>REBO Bill Payment Investigation Requests</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -627,18 +630,18 @@
         <v>FLCM</v>
       </c>
       <c r="E11" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G11">
-        <v>45699</v>
+        <v>45613</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-17202</v>
+        <v>ENT-17286</v>
       </c>
       <c r="B12" t="str">
-        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
+        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -647,18 +650,18 @@
         <v>FLCM</v>
       </c>
       <c r="E12" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G12">
-        <v>45690</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17202</v>
       </c>
       <c r="B13" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -667,21 +670,18 @@
         <v>FLCM</v>
       </c>
       <c r="E13" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F13" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G13">
-        <v>45686</v>
+        <v>45690</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B14" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -690,18 +690,21 @@
         <v>FLCM</v>
       </c>
       <c r="E14" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F14" t="str">
+        <v>PDF</v>
       </c>
       <c r="G14">
-        <v>45700</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B15" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -713,15 +716,15 @@
         <v>estimates</v>
       </c>
       <c r="G15">
-        <v>45656</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B16" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -733,15 +736,15 @@
         <v>estimates</v>
       </c>
       <c r="G16">
-        <v>45588</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B17" t="str">
-        <v>Data Source to EDGE</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -753,15 +756,15 @@
         <v>estimates</v>
       </c>
       <c r="G17">
-        <v>45664</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ENT-17054</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B18" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
@@ -770,21 +773,18 @@
         <v>FLCM</v>
       </c>
       <c r="E18" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F18" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G18">
-        <v>45691</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-17054</v>
       </c>
       <c r="B19" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
@@ -795,16 +795,19 @@
       <c r="E19" t="str">
         <v>approved</v>
       </c>
+      <c r="F19" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G19">
-        <v>45299</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ENT-14372</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B20" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
@@ -815,19 +818,16 @@
       <c r="E20" t="str">
         <v>approved</v>
       </c>
-      <c r="F20" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G20">
-        <v>45512</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-14372</v>
       </c>
       <c r="B21" t="str">
-        <v>RAMP Phase 2</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
@@ -842,58 +842,58 @@
         <v>PDF</v>
       </c>
       <c r="G21">
-        <v>45562</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B22" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D22" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E22" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F22" t="str">
+        <v>PDF</v>
       </c>
       <c r="G22">
-        <v>45695</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B23" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D23" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E23" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F23" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G23">
-        <v>45688</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B24" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
@@ -908,15 +908,15 @@
         <v>PDF</v>
       </c>
       <c r="G24">
-        <v>45701</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B25" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
@@ -931,15 +931,15 @@
         <v>PDF</v>
       </c>
       <c r="G25">
-        <v>45695</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B26" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
@@ -950,16 +950,19 @@
       <c r="E26" t="str">
         <v>approved</v>
       </c>
+      <c r="F26" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G26">
-        <v>45706</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B27" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
@@ -968,138 +971,138 @@
         <v>FLCM</v>
       </c>
       <c r="E27" t="str">
-        <v>estimates</v>
+        <v>approved</v>
       </c>
       <c r="G27">
-        <v>45559</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B28" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D28" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E28" t="str">
         <v>estimates</v>
       </c>
       <c r="G28">
-        <v>45623</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B29" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E29" t="str">
         <v>estimates</v>
       </c>
       <c r="G29">
-        <v>45355</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B30" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D30" t="str">
-        <v>CorpSec</v>
+        <v>FLCM</v>
       </c>
       <c r="E30" t="str">
         <v>estimates</v>
       </c>
       <c r="G30">
-        <v>45446</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B31" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D31" t="str">
-        <v>BSCM/ESCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E31" t="str">
         <v>estimates</v>
       </c>
       <c r="G31">
-        <v>45477</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B32" t="str">
-        <v>CSDM Upgrade</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D32" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E32" t="str">
         <v>estimates</v>
       </c>
       <c r="G32">
-        <v>45394</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B33" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D33" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E33" t="str">
-        <v>ofs</v>
+        <v>estimates</v>
       </c>
       <c r="G33">
-        <v>45531</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B34" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
@@ -1111,15 +1114,15 @@
         <v>ofs</v>
       </c>
       <c r="G34">
-        <v>45453</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B35" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
@@ -1131,15 +1134,15 @@
         <v>ofs</v>
       </c>
       <c r="G35">
-        <v>45461</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B36" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
@@ -1148,95 +1151,98 @@
         <v>FLCM</v>
       </c>
       <c r="E36" t="str">
-        <v>jrm</v>
+        <v>ofs</v>
       </c>
       <c r="G36">
-        <v>45714</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B37" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D37" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E37" t="str">
-        <v>estimates</v>
+        <v>jrm</v>
       </c>
       <c r="G37">
-        <v>45686</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ENT-15822</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B38" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D38" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E38" t="str">
         <v>estimates</v>
       </c>
       <c r="G38">
-        <v>45650</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-15822</v>
       </c>
       <c r="B39" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D39" t="str">
-        <v>BSCM/ESCM</v>
+        <v>FLCM</v>
       </c>
       <c r="E39" t="str">
         <v>estimates</v>
       </c>
       <c r="G39">
-        <v>45541</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENT-17853</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B40" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
       </c>
+      <c r="D40" t="str">
+        <v>BSCM/ESCM</v>
+      </c>
       <c r="E40" t="str">
-        <v>ofs</v>
+        <v>estimates</v>
       </c>
       <c r="G40">
-        <v>45691</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-17853</v>
       </c>
       <c r="B41" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1245,15 +1251,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45559</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B42" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1262,15 +1268,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45596</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B43" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1279,15 +1285,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45378</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B44" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1296,15 +1302,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45468</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B45" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1313,15 +1319,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45310</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B46" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1330,15 +1336,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45427</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B47" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1347,15 +1353,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45279</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B48" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1364,15 +1370,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45558</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B49" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1381,15 +1387,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45383</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B50" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1398,15 +1404,15 @@
         <v>ofs</v>
       </c>
       <c r="G50">
-        <v>45638</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B51" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1415,15 +1421,15 @@
         <v>ofs</v>
       </c>
       <c r="G51">
-        <v>45461</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B52" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1432,15 +1438,15 @@
         <v>ofs</v>
       </c>
       <c r="G52">
-        <v>45371</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B53" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1454,10 +1460,10 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B54" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1466,15 +1472,15 @@
         <v>ofs</v>
       </c>
       <c r="G54">
-        <v>45406</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B55" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1483,15 +1489,15 @@
         <v>ofs</v>
       </c>
       <c r="G55">
-        <v>45364</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B56" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1500,15 +1506,15 @@
         <v>ofs</v>
       </c>
       <c r="G56">
-        <v>45593</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B57" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
@@ -1517,15 +1523,15 @@
         <v>ofs</v>
       </c>
       <c r="G57">
-        <v>45408</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B58" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C58" t="str">
         <v>Invite to JRM</v>
@@ -1534,15 +1540,15 @@
         <v>ofs</v>
       </c>
       <c r="G58">
-        <v>45595</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B59" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C59" t="str">
         <v>Invite to JRM</v>
@@ -1551,15 +1557,15 @@
         <v>ofs</v>
       </c>
       <c r="G59">
-        <v>45392</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B60" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C60" t="str">
         <v>Invite to JRM</v>
@@ -1568,15 +1574,15 @@
         <v>ofs</v>
       </c>
       <c r="G60">
-        <v>45411</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B61" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C61" t="str">
         <v>Invite to JRM</v>
@@ -1590,27 +1596,27 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B62" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C62" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E62" t="str">
-        <v>jrm</v>
+        <v>ofs</v>
       </c>
       <c r="G62">
-        <v>45721</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>ENT-18725</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B63" t="str">
-        <v>US Video System - Lenel to Genetec</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C63" t="str">
         <v>Invite to JRM</v>
@@ -1622,9 +1628,26 @@
         <v>45721</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>ENT-18725</v>
+      </c>
+      <c r="B64" t="str">
+        <v>US Video System - Lenel to Genetec</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Invite to JRM</v>
+      </c>
+      <c r="E64" t="str">
+        <v>jrm</v>
+      </c>
+      <c r="G64">
+        <v>45721</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G63"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G64"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G63"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -518,10 +518,10 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ENT-16881</v>
+        <v>ENT-16700</v>
       </c>
       <c r="B6" t="str">
-        <v>Split up Personal Overdraft P&amp;L</v>
+        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
       </c>
       <c r="C6" t="str">
         <v>Invite to JRM</v>
@@ -533,15 +533,15 @@
         <v>jrm</v>
       </c>
       <c r="G6">
-        <v>45929</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENT-16700</v>
+        <v>ENT-16621</v>
       </c>
       <c r="B7" t="str">
-        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
+        <v>CIW Data Products to PROD</v>
       </c>
       <c r="C7" t="str">
         <v>Invite to JRM</v>
@@ -550,18 +550,18 @@
         <v>FLCM</v>
       </c>
       <c r="E7" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G7">
-        <v>45523</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENT-16621</v>
+        <v>ENT-16374</v>
       </c>
       <c r="B8" t="str">
-        <v>CIW Data Products to PROD</v>
+        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
       </c>
       <c r="C8" t="str">
         <v>Invite to JRM</v>
@@ -570,18 +570,18 @@
         <v>FLCM</v>
       </c>
       <c r="E8" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G8">
-        <v>45596</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-16374</v>
+        <v>ENT-16031</v>
       </c>
       <c r="B9" t="str">
-        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
+        <v>Fraud - Notes generator</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -593,15 +593,15 @@
         <v>jrm</v>
       </c>
       <c r="G9">
-        <v>45455</v>
+        <v>45649</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-16031</v>
+        <v>ENT-15917</v>
       </c>
       <c r="B10" t="str">
-        <v>Fraud - Notes generator</v>
+        <v>REBO Bill Payment Investigation Requests</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -613,15 +613,15 @@
         <v>jrm</v>
       </c>
       <c r="G10">
-        <v>45649</v>
+        <v>45613</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-15917</v>
+        <v>ENT-17286</v>
       </c>
       <c r="B11" t="str">
-        <v>REBO Bill Payment Investigation Requests</v>
+        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -630,18 +630,18 @@
         <v>FLCM</v>
       </c>
       <c r="E11" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G11">
-        <v>45613</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-17286</v>
+        <v>ENT-17202</v>
       </c>
       <c r="B12" t="str">
-        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
+        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -650,18 +650,18 @@
         <v>FLCM</v>
       </c>
       <c r="E12" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G12">
-        <v>45699</v>
+        <v>45690</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-17202</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B13" t="str">
-        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -670,18 +670,21 @@
         <v>FLCM</v>
       </c>
       <c r="E13" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F13" t="str">
+        <v>PDF</v>
       </c>
       <c r="G13">
-        <v>45690</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B14" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -690,21 +693,18 @@
         <v>FLCM</v>
       </c>
       <c r="E14" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F14" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G14">
-        <v>45686</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B15" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -716,15 +716,15 @@
         <v>estimates</v>
       </c>
       <c r="G15">
-        <v>45700</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B16" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -736,15 +736,15 @@
         <v>estimates</v>
       </c>
       <c r="G16">
-        <v>45656</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B17" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -756,15 +756,15 @@
         <v>estimates</v>
       </c>
       <c r="G17">
-        <v>45588</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-17054</v>
       </c>
       <c r="B18" t="str">
-        <v>Data Source to EDGE</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
@@ -773,18 +773,21 @@
         <v>FLCM</v>
       </c>
       <c r="E18" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F18" t="str">
+        <v>PDF</v>
       </c>
       <c r="G18">
-        <v>45664</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ENT-17054</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B19" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
@@ -795,19 +798,16 @@
       <c r="E19" t="str">
         <v>approved</v>
       </c>
-      <c r="F19" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G19">
-        <v>45691</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-14372</v>
       </c>
       <c r="B20" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
@@ -818,16 +818,19 @@
       <c r="E20" t="str">
         <v>approved</v>
       </c>
+      <c r="F20" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G20">
-        <v>45299</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-14372</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B21" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
@@ -842,58 +845,58 @@
         <v>PDF</v>
       </c>
       <c r="G21">
-        <v>45512</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B22" t="str">
-        <v>RAMP Phase 2</v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D22" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E22" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F22" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G22">
-        <v>45562</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B23" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D23" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E23" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F23" t="str">
+        <v>PDF</v>
       </c>
       <c r="G23">
-        <v>45695</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B24" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
@@ -908,15 +911,15 @@
         <v>PDF</v>
       </c>
       <c r="G24">
-        <v>45688</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B25" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
@@ -931,15 +934,15 @@
         <v>PDF</v>
       </c>
       <c r="G25">
-        <v>45701</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B26" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
@@ -950,19 +953,16 @@
       <c r="E26" t="str">
         <v>approved</v>
       </c>
-      <c r="F26" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G26">
-        <v>45695</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B27" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
@@ -971,138 +971,138 @@
         <v>FLCM</v>
       </c>
       <c r="E27" t="str">
-        <v>approved</v>
+        <v>estimates</v>
       </c>
       <c r="G27">
-        <v>45706</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B28" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D28" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E28" t="str">
         <v>estimates</v>
       </c>
       <c r="G28">
-        <v>45559</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B29" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E29" t="str">
         <v>estimates</v>
       </c>
       <c r="G29">
-        <v>45623</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B30" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D30" t="str">
-        <v>FLCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E30" t="str">
         <v>estimates</v>
       </c>
       <c r="G30">
-        <v>45355</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B31" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D31" t="str">
-        <v>CorpSec</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E31" t="str">
         <v>estimates</v>
       </c>
       <c r="G31">
-        <v>45446</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B32" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D32" t="str">
-        <v>BSCM/ESCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E32" t="str">
         <v>estimates</v>
       </c>
       <c r="G32">
-        <v>45477</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B33" t="str">
-        <v>CSDM Upgrade</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D33" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E33" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G33">
-        <v>45394</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B34" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
@@ -1114,15 +1114,15 @@
         <v>ofs</v>
       </c>
       <c r="G34">
-        <v>45531</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B35" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
@@ -1134,15 +1134,15 @@
         <v>ofs</v>
       </c>
       <c r="G35">
-        <v>45453</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B36" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
@@ -1151,98 +1151,95 @@
         <v>FLCM</v>
       </c>
       <c r="E36" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G36">
-        <v>45461</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B37" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D37" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E37" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G37">
-        <v>45714</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-15822</v>
       </c>
       <c r="B38" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D38" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E38" t="str">
         <v>estimates</v>
       </c>
       <c r="G38">
-        <v>45686</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ENT-15822</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B39" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D39" t="str">
-        <v>FLCM</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E39" t="str">
         <v>estimates</v>
       </c>
       <c r="G39">
-        <v>45650</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-17853</v>
       </c>
       <c r="B40" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
       </c>
-      <c r="D40" t="str">
-        <v>BSCM/ESCM</v>
-      </c>
       <c r="E40" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G40">
-        <v>45541</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-17853</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B41" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1251,15 +1248,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45691</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B42" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1268,15 +1265,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45559</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B43" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1285,15 +1282,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45596</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B44" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1302,15 +1299,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45378</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B45" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1319,15 +1316,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45468</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B46" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1336,15 +1333,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45310</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B47" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1353,15 +1350,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45427</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B48" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1370,15 +1367,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45279</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B49" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1387,15 +1384,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45558</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B50" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1404,15 +1401,15 @@
         <v>ofs</v>
       </c>
       <c r="G50">
-        <v>45383</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B51" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1421,15 +1418,15 @@
         <v>ofs</v>
       </c>
       <c r="G51">
-        <v>45638</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B52" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1438,15 +1435,15 @@
         <v>ofs</v>
       </c>
       <c r="G52">
-        <v>45461</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B53" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1460,10 +1457,10 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B54" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1472,15 +1469,15 @@
         <v>ofs</v>
       </c>
       <c r="G54">
-        <v>45371</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B55" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1489,15 +1486,15 @@
         <v>ofs</v>
       </c>
       <c r="G55">
-        <v>45406</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B56" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1506,15 +1503,15 @@
         <v>ofs</v>
       </c>
       <c r="G56">
-        <v>45364</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B57" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
@@ -1523,15 +1520,15 @@
         <v>ofs</v>
       </c>
       <c r="G57">
-        <v>45593</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B58" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C58" t="str">
         <v>Invite to JRM</v>
@@ -1540,15 +1537,15 @@
         <v>ofs</v>
       </c>
       <c r="G58">
-        <v>45408</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B59" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C59" t="str">
         <v>Invite to JRM</v>
@@ -1557,15 +1554,15 @@
         <v>ofs</v>
       </c>
       <c r="G59">
-        <v>45595</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B60" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C60" t="str">
         <v>Invite to JRM</v>
@@ -1574,15 +1571,15 @@
         <v>ofs</v>
       </c>
       <c r="G60">
-        <v>45392</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B61" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C61" t="str">
         <v>Invite to JRM</v>
@@ -1596,27 +1593,27 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B62" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C62" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E62" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G62">
-        <v>45411</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-18725</v>
       </c>
       <c r="B63" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>US Video System - Lenel to Genetec</v>
       </c>
       <c r="C63" t="str">
         <v>Invite to JRM</v>
@@ -1628,26 +1625,9 @@
         <v>45721</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="str">
-        <v>ENT-18725</v>
-      </c>
-      <c r="B64" t="str">
-        <v>US Video System - Lenel to Genetec</v>
-      </c>
-      <c r="C64" t="str">
-        <v>Invite to JRM</v>
-      </c>
-      <c r="E64" t="str">
-        <v>jrm</v>
-      </c>
-      <c r="G64">
-        <v>45721</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G64"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G63"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G62"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -429,16 +429,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>54354</v>
+        <v>123445</v>
       </c>
       <c r="B2" t="str">
-        <v>6546</v>
+        <v>1234</v>
       </c>
       <c r="C2" t="str">
-        <v>345</v>
+        <v>1234</v>
       </c>
       <c r="D2" t="str">
-        <v>6546</v>
+        <v>1234</v>
       </c>
       <c r="E2" t="str">
         <v>jrm</v>
@@ -452,10 +452,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>123445</v>
+        <v>1234</v>
       </c>
       <c r="B3" t="str">
-        <v>1234</v>
+        <v>1234123</v>
       </c>
       <c r="C3" t="str">
         <v>1234</v>
@@ -475,33 +475,30 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>1234</v>
+        <v>ENT-16949</v>
       </c>
       <c r="B4" t="str">
-        <v>1234123</v>
+        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
       </c>
       <c r="C4" t="str">
-        <v>1234</v>
+        <v>Invite to JRM</v>
       </c>
       <c r="D4" t="str">
-        <v>1234</v>
+        <v>FLCM</v>
       </c>
       <c r="E4" t="str">
-        <v>jrm</v>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v>2025-03-15</v>
+        <v>estimates</v>
+      </c>
+      <c r="G4">
+        <v>45531</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ENT-16949</v>
+        <v>ENT-16700</v>
       </c>
       <c r="B5" t="str">
-        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
+        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
       </c>
       <c r="C5" t="str">
         <v>Invite to JRM</v>
@@ -510,18 +507,18 @@
         <v>FLCM</v>
       </c>
       <c r="E5" t="str">
-        <v>estimates</v>
+        <v>jrm</v>
       </c>
       <c r="G5">
-        <v>45531</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ENT-16700</v>
+        <v>ENT-16621</v>
       </c>
       <c r="B6" t="str">
-        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
+        <v>CIW Data Products to PROD</v>
       </c>
       <c r="C6" t="str">
         <v>Invite to JRM</v>
@@ -530,18 +527,18 @@
         <v>FLCM</v>
       </c>
       <c r="E6" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G6">
-        <v>45523</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENT-16621</v>
+        <v>ENT-16374</v>
       </c>
       <c r="B7" t="str">
-        <v>CIW Data Products to PROD</v>
+        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
       </c>
       <c r="C7" t="str">
         <v>Invite to JRM</v>
@@ -550,18 +547,18 @@
         <v>FLCM</v>
       </c>
       <c r="E7" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G7">
-        <v>45596</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENT-16374</v>
+        <v>ENT-16031</v>
       </c>
       <c r="B8" t="str">
-        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
+        <v>Fraud - Notes generator</v>
       </c>
       <c r="C8" t="str">
         <v>Invite to JRM</v>
@@ -573,15 +570,15 @@
         <v>jrm</v>
       </c>
       <c r="G8">
-        <v>45455</v>
+        <v>45649</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-16031</v>
+        <v>ENT-15917</v>
       </c>
       <c r="B9" t="str">
-        <v>Fraud - Notes generator</v>
+        <v>REBO Bill Payment Investigation Requests</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -593,15 +590,15 @@
         <v>jrm</v>
       </c>
       <c r="G9">
-        <v>45649</v>
+        <v>45613</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-15917</v>
+        <v>ENT-17286</v>
       </c>
       <c r="B10" t="str">
-        <v>REBO Bill Payment Investigation Requests</v>
+        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -610,18 +607,18 @@
         <v>FLCM</v>
       </c>
       <c r="E10" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G10">
-        <v>45613</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-17286</v>
+        <v>ENT-17202</v>
       </c>
       <c r="B11" t="str">
-        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
+        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -630,18 +627,18 @@
         <v>FLCM</v>
       </c>
       <c r="E11" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G11">
-        <v>45699</v>
+        <v>45690</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-17202</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B12" t="str">
-        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -650,18 +647,21 @@
         <v>FLCM</v>
       </c>
       <c r="E12" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F12" t="str">
+        <v>PDF</v>
       </c>
       <c r="G12">
-        <v>45690</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B13" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -670,21 +670,18 @@
         <v>FLCM</v>
       </c>
       <c r="E13" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F13" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G13">
-        <v>45686</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B14" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -696,15 +693,15 @@
         <v>estimates</v>
       </c>
       <c r="G14">
-        <v>45700</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B15" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -716,15 +713,15 @@
         <v>estimates</v>
       </c>
       <c r="G15">
-        <v>45656</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B16" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -736,15 +733,15 @@
         <v>estimates</v>
       </c>
       <c r="G16">
-        <v>45588</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-17054</v>
       </c>
       <c r="B17" t="str">
-        <v>Data Source to EDGE</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -753,18 +750,21 @@
         <v>FLCM</v>
       </c>
       <c r="E17" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F17" t="str">
+        <v>PDF</v>
       </c>
       <c r="G17">
-        <v>45664</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ENT-17054</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B18" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
@@ -775,19 +775,16 @@
       <c r="E18" t="str">
         <v>approved</v>
       </c>
-      <c r="F18" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G18">
-        <v>45691</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-14372</v>
       </c>
       <c r="B19" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
@@ -798,16 +795,19 @@
       <c r="E19" t="str">
         <v>approved</v>
       </c>
+      <c r="F19" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G19">
-        <v>45299</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ENT-14372</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B20" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
@@ -822,58 +822,58 @@
         <v>PDF</v>
       </c>
       <c r="G20">
-        <v>45512</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B21" t="str">
-        <v>RAMP Phase 2</v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D21" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E21" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F21" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G21">
-        <v>45562</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B22" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D22" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E22" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F22" t="str">
+        <v>PDF</v>
       </c>
       <c r="G22">
-        <v>45695</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B23" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
@@ -888,15 +888,15 @@
         <v>PDF</v>
       </c>
       <c r="G23">
-        <v>45688</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B24" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
@@ -911,15 +911,15 @@
         <v>PDF</v>
       </c>
       <c r="G24">
-        <v>45701</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B25" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
@@ -930,19 +930,16 @@
       <c r="E25" t="str">
         <v>approved</v>
       </c>
-      <c r="F25" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G25">
-        <v>45695</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B26" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
@@ -951,138 +948,138 @@
         <v>FLCM</v>
       </c>
       <c r="E26" t="str">
-        <v>approved</v>
+        <v>estimates</v>
       </c>
       <c r="G26">
-        <v>45706</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B27" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D27" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E27" t="str">
         <v>estimates</v>
       </c>
       <c r="G27">
-        <v>45559</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B28" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D28" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E28" t="str">
         <v>estimates</v>
       </c>
       <c r="G28">
-        <v>45623</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B29" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>FLCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E29" t="str">
         <v>estimates</v>
       </c>
       <c r="G29">
-        <v>45355</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B30" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D30" t="str">
-        <v>CorpSec</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E30" t="str">
         <v>estimates</v>
       </c>
       <c r="G30">
-        <v>45446</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B31" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D31" t="str">
-        <v>BSCM/ESCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E31" t="str">
         <v>estimates</v>
       </c>
       <c r="G31">
-        <v>45477</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B32" t="str">
-        <v>CSDM Upgrade</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D32" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E32" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G32">
-        <v>45394</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B33" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
@@ -1094,15 +1091,15 @@
         <v>ofs</v>
       </c>
       <c r="G33">
-        <v>45531</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B34" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
@@ -1114,15 +1111,15 @@
         <v>ofs</v>
       </c>
       <c r="G34">
-        <v>45453</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B35" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
@@ -1131,98 +1128,95 @@
         <v>FLCM</v>
       </c>
       <c r="E35" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G35">
-        <v>45461</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B36" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D36" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E36" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G36">
-        <v>45714</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-15822</v>
       </c>
       <c r="B37" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D37" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E37" t="str">
         <v>estimates</v>
       </c>
       <c r="G37">
-        <v>45686</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ENT-15822</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B38" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D38" t="str">
-        <v>FLCM</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E38" t="str">
         <v>estimates</v>
       </c>
       <c r="G38">
-        <v>45650</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-17853</v>
       </c>
       <c r="B39" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
       </c>
-      <c r="D39" t="str">
-        <v>BSCM/ESCM</v>
-      </c>
       <c r="E39" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G39">
-        <v>45541</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENT-17853</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B40" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
@@ -1231,15 +1225,15 @@
         <v>ofs</v>
       </c>
       <c r="G40">
-        <v>45691</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B41" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1248,15 +1242,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45559</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B42" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1265,15 +1259,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45596</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B43" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1282,15 +1276,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45378</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B44" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1299,15 +1293,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45468</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B45" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1316,15 +1310,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45310</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B46" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1333,15 +1327,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45427</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B47" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1350,15 +1344,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45279</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B48" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1367,15 +1361,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45558</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B49" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1384,15 +1378,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45383</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B50" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1401,15 +1395,15 @@
         <v>ofs</v>
       </c>
       <c r="G50">
-        <v>45638</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B51" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1418,15 +1412,15 @@
         <v>ofs</v>
       </c>
       <c r="G51">
-        <v>45461</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B52" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1440,10 +1434,10 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B53" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1452,15 +1446,15 @@
         <v>ofs</v>
       </c>
       <c r="G53">
-        <v>45371</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B54" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1469,15 +1463,15 @@
         <v>ofs</v>
       </c>
       <c r="G54">
-        <v>45406</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B55" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1486,15 +1480,15 @@
         <v>ofs</v>
       </c>
       <c r="G55">
-        <v>45364</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B56" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1503,15 +1497,15 @@
         <v>ofs</v>
       </c>
       <c r="G56">
-        <v>45593</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B57" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
@@ -1520,15 +1514,15 @@
         <v>ofs</v>
       </c>
       <c r="G57">
-        <v>45408</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B58" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C58" t="str">
         <v>Invite to JRM</v>
@@ -1537,15 +1531,15 @@
         <v>ofs</v>
       </c>
       <c r="G58">
-        <v>45595</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B59" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C59" t="str">
         <v>Invite to JRM</v>
@@ -1554,15 +1548,15 @@
         <v>ofs</v>
       </c>
       <c r="G59">
-        <v>45392</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B60" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C60" t="str">
         <v>Invite to JRM</v>
@@ -1576,27 +1570,27 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B61" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C61" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E61" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G61">
-        <v>45411</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-18725</v>
       </c>
       <c r="B62" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>US Video System - Lenel to Genetec</v>
       </c>
       <c r="C62" t="str">
         <v>Invite to JRM</v>
@@ -1608,26 +1602,9 @@
         <v>45721</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="str">
-        <v>ENT-18725</v>
-      </c>
-      <c r="B63" t="str">
-        <v>US Video System - Lenel to Genetec</v>
-      </c>
-      <c r="C63" t="str">
-        <v>Invite to JRM</v>
-      </c>
-      <c r="E63" t="str">
-        <v>jrm</v>
-      </c>
-      <c r="G63">
-        <v>45721</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G63"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G62"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G61"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -429,10 +429,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>123445</v>
+        <v>1234</v>
       </c>
       <c r="B2" t="str">
-        <v>1234</v>
+        <v>1234123</v>
       </c>
       <c r="C2" t="str">
         <v>1234</v>
@@ -452,33 +452,30 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>1234</v>
+        <v>ENT-16949</v>
       </c>
       <c r="B3" t="str">
-        <v>1234123</v>
+        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
       </c>
       <c r="C3" t="str">
-        <v>1234</v>
+        <v>Invite to JRM</v>
       </c>
       <c r="D3" t="str">
-        <v>1234</v>
+        <v>FLCM</v>
       </c>
       <c r="E3" t="str">
-        <v>jrm</v>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v>2025-03-15</v>
+        <v>estimates</v>
+      </c>
+      <c r="G3">
+        <v>45531</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ENT-16949</v>
+        <v>ENT-16700</v>
       </c>
       <c r="B4" t="str">
-        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
+        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
       </c>
       <c r="C4" t="str">
         <v>Invite to JRM</v>
@@ -487,18 +484,18 @@
         <v>FLCM</v>
       </c>
       <c r="E4" t="str">
-        <v>estimates</v>
+        <v>jrm</v>
       </c>
       <c r="G4">
-        <v>45531</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ENT-16700</v>
+        <v>ENT-16621</v>
       </c>
       <c r="B5" t="str">
-        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
+        <v>CIW Data Products to PROD</v>
       </c>
       <c r="C5" t="str">
         <v>Invite to JRM</v>
@@ -507,18 +504,18 @@
         <v>FLCM</v>
       </c>
       <c r="E5" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G5">
-        <v>45523</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ENT-16621</v>
+        <v>ENT-16374</v>
       </c>
       <c r="B6" t="str">
-        <v>CIW Data Products to PROD</v>
+        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
       </c>
       <c r="C6" t="str">
         <v>Invite to JRM</v>
@@ -527,18 +524,18 @@
         <v>FLCM</v>
       </c>
       <c r="E6" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G6">
-        <v>45596</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENT-16374</v>
+        <v>ENT-16031</v>
       </c>
       <c r="B7" t="str">
-        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
+        <v>Fraud - Notes generator</v>
       </c>
       <c r="C7" t="str">
         <v>Invite to JRM</v>
@@ -550,15 +547,15 @@
         <v>jrm</v>
       </c>
       <c r="G7">
-        <v>45455</v>
+        <v>45649</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENT-16031</v>
+        <v>ENT-15917</v>
       </c>
       <c r="B8" t="str">
-        <v>Fraud - Notes generator</v>
+        <v>REBO Bill Payment Investigation Requests</v>
       </c>
       <c r="C8" t="str">
         <v>Invite to JRM</v>
@@ -570,15 +567,15 @@
         <v>jrm</v>
       </c>
       <c r="G8">
-        <v>45649</v>
+        <v>45613</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-15917</v>
+        <v>ENT-17286</v>
       </c>
       <c r="B9" t="str">
-        <v>REBO Bill Payment Investigation Requests</v>
+        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -587,18 +584,18 @@
         <v>FLCM</v>
       </c>
       <c r="E9" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G9">
-        <v>45613</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-17286</v>
+        <v>ENT-17202</v>
       </c>
       <c r="B10" t="str">
-        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
+        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -607,18 +604,18 @@
         <v>FLCM</v>
       </c>
       <c r="E10" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G10">
-        <v>45699</v>
+        <v>45690</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-17202</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B11" t="str">
-        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -627,18 +624,21 @@
         <v>FLCM</v>
       </c>
       <c r="E11" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F11" t="str">
+        <v>PDF</v>
       </c>
       <c r="G11">
-        <v>45690</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B12" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -647,21 +647,18 @@
         <v>FLCM</v>
       </c>
       <c r="E12" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F12" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G12">
-        <v>45686</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B13" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -673,15 +670,15 @@
         <v>estimates</v>
       </c>
       <c r="G13">
-        <v>45700</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B14" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -693,15 +690,15 @@
         <v>estimates</v>
       </c>
       <c r="G14">
-        <v>45656</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B15" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -713,15 +710,15 @@
         <v>estimates</v>
       </c>
       <c r="G15">
-        <v>45588</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-17054</v>
       </c>
       <c r="B16" t="str">
-        <v>Data Source to EDGE</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -730,18 +727,21 @@
         <v>FLCM</v>
       </c>
       <c r="E16" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F16" t="str">
+        <v>PDF</v>
       </c>
       <c r="G16">
-        <v>45664</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ENT-17054</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B17" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -752,19 +752,16 @@
       <c r="E17" t="str">
         <v>approved</v>
       </c>
-      <c r="F17" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G17">
-        <v>45691</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-14372</v>
       </c>
       <c r="B18" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
@@ -775,16 +772,19 @@
       <c r="E18" t="str">
         <v>approved</v>
       </c>
+      <c r="F18" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G18">
-        <v>45299</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ENT-14372</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B19" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
@@ -799,58 +799,58 @@
         <v>PDF</v>
       </c>
       <c r="G19">
-        <v>45512</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B20" t="str">
-        <v>RAMP Phase 2</v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D20" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E20" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F20" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G20">
-        <v>45562</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B21" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D21" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E21" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F21" t="str">
+        <v>PDF</v>
       </c>
       <c r="G21">
-        <v>45695</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B22" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
@@ -865,15 +865,15 @@
         <v>PDF</v>
       </c>
       <c r="G22">
-        <v>45688</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B23" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
@@ -888,15 +888,15 @@
         <v>PDF</v>
       </c>
       <c r="G23">
-        <v>45701</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B24" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
@@ -907,19 +907,16 @@
       <c r="E24" t="str">
         <v>approved</v>
       </c>
-      <c r="F24" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G24">
-        <v>45695</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B25" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
@@ -928,138 +925,138 @@
         <v>FLCM</v>
       </c>
       <c r="E25" t="str">
-        <v>approved</v>
+        <v>estimates</v>
       </c>
       <c r="G25">
-        <v>45706</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B26" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D26" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E26" t="str">
         <v>estimates</v>
       </c>
       <c r="G26">
-        <v>45559</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B27" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D27" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E27" t="str">
         <v>estimates</v>
       </c>
       <c r="G27">
-        <v>45623</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B28" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D28" t="str">
-        <v>FLCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E28" t="str">
         <v>estimates</v>
       </c>
       <c r="G28">
-        <v>45355</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B29" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>CorpSec</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E29" t="str">
         <v>estimates</v>
       </c>
       <c r="G29">
-        <v>45446</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B30" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D30" t="str">
-        <v>BSCM/ESCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E30" t="str">
         <v>estimates</v>
       </c>
       <c r="G30">
-        <v>45477</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B31" t="str">
-        <v>CSDM Upgrade</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D31" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E31" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G31">
-        <v>45394</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B32" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
@@ -1071,15 +1068,15 @@
         <v>ofs</v>
       </c>
       <c r="G32">
-        <v>45531</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B33" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
@@ -1091,15 +1088,15 @@
         <v>ofs</v>
       </c>
       <c r="G33">
-        <v>45453</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B34" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
@@ -1108,98 +1105,95 @@
         <v>FLCM</v>
       </c>
       <c r="E34" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G34">
-        <v>45461</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B35" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D35" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E35" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G35">
-        <v>45714</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-15822</v>
       </c>
       <c r="B36" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D36" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E36" t="str">
         <v>estimates</v>
       </c>
       <c r="G36">
-        <v>45686</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ENT-15822</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B37" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D37" t="str">
-        <v>FLCM</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E37" t="str">
         <v>estimates</v>
       </c>
       <c r="G37">
-        <v>45650</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-17853</v>
       </c>
       <c r="B38" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
       </c>
-      <c r="D38" t="str">
-        <v>BSCM/ESCM</v>
-      </c>
       <c r="E38" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G38">
-        <v>45541</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ENT-17853</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B39" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
@@ -1208,15 +1202,15 @@
         <v>ofs</v>
       </c>
       <c r="G39">
-        <v>45691</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B40" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
@@ -1225,15 +1219,15 @@
         <v>ofs</v>
       </c>
       <c r="G40">
-        <v>45559</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B41" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1242,15 +1236,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45596</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B42" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1259,15 +1253,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45378</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B43" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1276,15 +1270,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45468</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B44" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1293,15 +1287,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45310</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B45" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1310,15 +1304,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45427</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B46" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1327,15 +1321,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45279</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B47" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1344,15 +1338,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45558</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B48" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1361,15 +1355,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45383</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B49" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1378,15 +1372,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45638</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B50" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1395,15 +1389,15 @@
         <v>ofs</v>
       </c>
       <c r="G50">
-        <v>45461</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B51" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1417,10 +1411,10 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B52" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1429,15 +1423,15 @@
         <v>ofs</v>
       </c>
       <c r="G52">
-        <v>45371</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B53" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1446,15 +1440,15 @@
         <v>ofs</v>
       </c>
       <c r="G53">
-        <v>45406</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B54" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1463,15 +1457,15 @@
         <v>ofs</v>
       </c>
       <c r="G54">
-        <v>45364</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B55" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1480,15 +1474,15 @@
         <v>ofs</v>
       </c>
       <c r="G55">
-        <v>45593</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B56" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1497,15 +1491,15 @@
         <v>ofs</v>
       </c>
       <c r="G56">
-        <v>45408</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B57" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
@@ -1514,15 +1508,15 @@
         <v>ofs</v>
       </c>
       <c r="G57">
-        <v>45595</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B58" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C58" t="str">
         <v>Invite to JRM</v>
@@ -1531,15 +1525,15 @@
         <v>ofs</v>
       </c>
       <c r="G58">
-        <v>45392</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B59" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C59" t="str">
         <v>Invite to JRM</v>
@@ -1553,27 +1547,27 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B60" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C60" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E60" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G60">
-        <v>45411</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-18725</v>
       </c>
       <c r="B61" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>US Video System - Lenel to Genetec</v>
       </c>
       <c r="C61" t="str">
         <v>Invite to JRM</v>
@@ -1585,26 +1579,9 @@
         <v>45721</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="str">
-        <v>ENT-18725</v>
-      </c>
-      <c r="B62" t="str">
-        <v>US Video System - Lenel to Genetec</v>
-      </c>
-      <c r="C62" t="str">
-        <v>Invite to JRM</v>
-      </c>
-      <c r="E62" t="str">
-        <v>jrm</v>
-      </c>
-      <c r="G62">
-        <v>45721</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G62"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G61"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G60"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -472,10 +472,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ENT-16700</v>
+        <v>ENT-16621</v>
       </c>
       <c r="B4" t="str">
-        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
+        <v>CIW Data Products to PROD</v>
       </c>
       <c r="C4" t="str">
         <v>Invite to JRM</v>
@@ -484,18 +484,18 @@
         <v>FLCM</v>
       </c>
       <c r="E4" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G4">
-        <v>45523</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ENT-16621</v>
+        <v>ENT-16374</v>
       </c>
       <c r="B5" t="str">
-        <v>CIW Data Products to PROD</v>
+        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
       </c>
       <c r="C5" t="str">
         <v>Invite to JRM</v>
@@ -504,18 +504,18 @@
         <v>FLCM</v>
       </c>
       <c r="E5" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G5">
-        <v>45596</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ENT-16374</v>
+        <v>ENT-16031</v>
       </c>
       <c r="B6" t="str">
-        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
+        <v>Fraud - Notes generator</v>
       </c>
       <c r="C6" t="str">
         <v>Invite to JRM</v>
@@ -527,15 +527,15 @@
         <v>jrm</v>
       </c>
       <c r="G6">
-        <v>45455</v>
+        <v>45649</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENT-16031</v>
+        <v>ENT-15917</v>
       </c>
       <c r="B7" t="str">
-        <v>Fraud - Notes generator</v>
+        <v>REBO Bill Payment Investigation Requests</v>
       </c>
       <c r="C7" t="str">
         <v>Invite to JRM</v>
@@ -547,15 +547,15 @@
         <v>jrm</v>
       </c>
       <c r="G7">
-        <v>45649</v>
+        <v>45613</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENT-15917</v>
+        <v>ENT-17286</v>
       </c>
       <c r="B8" t="str">
-        <v>REBO Bill Payment Investigation Requests</v>
+        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
       </c>
       <c r="C8" t="str">
         <v>Invite to JRM</v>
@@ -564,18 +564,18 @@
         <v>FLCM</v>
       </c>
       <c r="E8" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G8">
-        <v>45613</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-17286</v>
+        <v>ENT-17202</v>
       </c>
       <c r="B9" t="str">
-        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
+        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -584,18 +584,18 @@
         <v>FLCM</v>
       </c>
       <c r="E9" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G9">
-        <v>45699</v>
+        <v>45690</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-17202</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B10" t="str">
-        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -604,18 +604,21 @@
         <v>FLCM</v>
       </c>
       <c r="E10" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F10" t="str">
+        <v>PDF</v>
       </c>
       <c r="G10">
-        <v>45690</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B11" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -624,21 +627,18 @@
         <v>FLCM</v>
       </c>
       <c r="E11" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F11" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G11">
-        <v>45686</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B12" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -650,15 +650,15 @@
         <v>estimates</v>
       </c>
       <c r="G12">
-        <v>45700</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B13" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -670,15 +670,15 @@
         <v>estimates</v>
       </c>
       <c r="G13">
-        <v>45656</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B14" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -690,15 +690,15 @@
         <v>estimates</v>
       </c>
       <c r="G14">
-        <v>45588</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-17054</v>
       </c>
       <c r="B15" t="str">
-        <v>Data Source to EDGE</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -707,18 +707,21 @@
         <v>FLCM</v>
       </c>
       <c r="E15" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F15" t="str">
+        <v>PDF</v>
       </c>
       <c r="G15">
-        <v>45664</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-17054</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B16" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -729,19 +732,16 @@
       <c r="E16" t="str">
         <v>approved</v>
       </c>
-      <c r="F16" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G16">
-        <v>45691</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-14372</v>
       </c>
       <c r="B17" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -752,16 +752,19 @@
       <c r="E17" t="str">
         <v>approved</v>
       </c>
+      <c r="F17" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G17">
-        <v>45299</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ENT-14372</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B18" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
@@ -776,58 +779,58 @@
         <v>PDF</v>
       </c>
       <c r="G18">
-        <v>45512</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B19" t="str">
-        <v>RAMP Phase 2</v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D19" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E19" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F19" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G19">
-        <v>45562</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B20" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D20" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E20" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F20" t="str">
+        <v>PDF</v>
       </c>
       <c r="G20">
-        <v>45695</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B21" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
@@ -842,15 +845,15 @@
         <v>PDF</v>
       </c>
       <c r="G21">
-        <v>45688</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B22" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
@@ -865,15 +868,15 @@
         <v>PDF</v>
       </c>
       <c r="G22">
-        <v>45701</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B23" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
@@ -884,19 +887,16 @@
       <c r="E23" t="str">
         <v>approved</v>
       </c>
-      <c r="F23" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G23">
-        <v>45695</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B24" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
@@ -905,138 +905,138 @@
         <v>FLCM</v>
       </c>
       <c r="E24" t="str">
-        <v>approved</v>
+        <v>estimates</v>
       </c>
       <c r="G24">
-        <v>45706</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B25" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D25" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E25" t="str">
         <v>estimates</v>
       </c>
       <c r="G25">
-        <v>45559</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B26" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D26" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E26" t="str">
         <v>estimates</v>
       </c>
       <c r="G26">
-        <v>45623</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B27" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D27" t="str">
-        <v>FLCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E27" t="str">
         <v>estimates</v>
       </c>
       <c r="G27">
-        <v>45355</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B28" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D28" t="str">
-        <v>CorpSec</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E28" t="str">
         <v>estimates</v>
       </c>
       <c r="G28">
-        <v>45446</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B29" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>BSCM/ESCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E29" t="str">
         <v>estimates</v>
       </c>
       <c r="G29">
-        <v>45477</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B30" t="str">
-        <v>CSDM Upgrade</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D30" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E30" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G30">
-        <v>45394</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B31" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
@@ -1048,15 +1048,15 @@
         <v>ofs</v>
       </c>
       <c r="G31">
-        <v>45531</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B32" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
@@ -1068,15 +1068,15 @@
         <v>ofs</v>
       </c>
       <c r="G32">
-        <v>45453</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B33" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
@@ -1085,98 +1085,95 @@
         <v>FLCM</v>
       </c>
       <c r="E33" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G33">
-        <v>45461</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B34" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D34" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E34" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G34">
-        <v>45714</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-15822</v>
       </c>
       <c r="B35" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D35" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E35" t="str">
         <v>estimates</v>
       </c>
       <c r="G35">
-        <v>45686</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-15822</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B36" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D36" t="str">
-        <v>FLCM</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E36" t="str">
         <v>estimates</v>
       </c>
       <c r="G36">
-        <v>45650</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-17853</v>
       </c>
       <c r="B37" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
       </c>
-      <c r="D37" t="str">
-        <v>BSCM/ESCM</v>
-      </c>
       <c r="E37" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G37">
-        <v>45541</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ENT-17853</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B38" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
@@ -1185,15 +1182,15 @@
         <v>ofs</v>
       </c>
       <c r="G38">
-        <v>45691</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B39" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
@@ -1202,15 +1199,15 @@
         <v>ofs</v>
       </c>
       <c r="G39">
-        <v>45559</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B40" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
@@ -1219,15 +1216,15 @@
         <v>ofs</v>
       </c>
       <c r="G40">
-        <v>45596</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B41" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1236,15 +1233,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45378</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B42" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1253,15 +1250,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45468</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B43" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1270,15 +1267,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45310</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B44" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1287,15 +1284,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45427</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B45" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1304,15 +1301,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45279</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B46" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1321,15 +1318,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45558</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B47" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1338,15 +1335,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45383</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B48" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1355,15 +1352,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45638</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B49" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1372,15 +1369,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45461</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B50" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1394,10 +1391,10 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B51" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1406,15 +1403,15 @@
         <v>ofs</v>
       </c>
       <c r="G51">
-        <v>45371</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B52" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1423,15 +1420,15 @@
         <v>ofs</v>
       </c>
       <c r="G52">
-        <v>45406</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B53" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1440,15 +1437,15 @@
         <v>ofs</v>
       </c>
       <c r="G53">
-        <v>45364</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B54" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1457,15 +1454,15 @@
         <v>ofs</v>
       </c>
       <c r="G54">
-        <v>45593</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B55" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1474,15 +1471,15 @@
         <v>ofs</v>
       </c>
       <c r="G55">
-        <v>45408</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B56" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1491,15 +1488,15 @@
         <v>ofs</v>
       </c>
       <c r="G56">
-        <v>45595</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B57" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
@@ -1508,15 +1505,15 @@
         <v>ofs</v>
       </c>
       <c r="G57">
-        <v>45392</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B58" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C58" t="str">
         <v>Invite to JRM</v>
@@ -1530,27 +1527,27 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B59" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C59" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E59" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G59">
-        <v>45411</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-18725</v>
       </c>
       <c r="B60" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>US Video System - Lenel to Genetec</v>
       </c>
       <c r="C60" t="str">
         <v>Invite to JRM</v>
@@ -1562,26 +1559,9 @@
         <v>45721</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="str">
-        <v>ENT-18725</v>
-      </c>
-      <c r="B61" t="str">
-        <v>US Video System - Lenel to Genetec</v>
-      </c>
-      <c r="C61" t="str">
-        <v>Invite to JRM</v>
-      </c>
-      <c r="E61" t="str">
-        <v>jrm</v>
-      </c>
-      <c r="G61">
-        <v>45721</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G60"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G59"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -492,10 +492,10 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ENT-16374</v>
+        <v>ENT-16031</v>
       </c>
       <c r="B5" t="str">
-        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
+        <v>Fraud - Notes generator</v>
       </c>
       <c r="C5" t="str">
         <v>Invite to JRM</v>
@@ -507,15 +507,15 @@
         <v>jrm</v>
       </c>
       <c r="G5">
-        <v>45455</v>
+        <v>45649</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ENT-16031</v>
+        <v>ENT-15917</v>
       </c>
       <c r="B6" t="str">
-        <v>Fraud - Notes generator</v>
+        <v>REBO Bill Payment Investigation Requests</v>
       </c>
       <c r="C6" t="str">
         <v>Invite to JRM</v>
@@ -527,15 +527,15 @@
         <v>jrm</v>
       </c>
       <c r="G6">
-        <v>45649</v>
+        <v>45613</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENT-15917</v>
+        <v>ENT-17286</v>
       </c>
       <c r="B7" t="str">
-        <v>REBO Bill Payment Investigation Requests</v>
+        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
       </c>
       <c r="C7" t="str">
         <v>Invite to JRM</v>
@@ -544,18 +544,18 @@
         <v>FLCM</v>
       </c>
       <c r="E7" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G7">
-        <v>45613</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENT-17286</v>
+        <v>ENT-17202</v>
       </c>
       <c r="B8" t="str">
-        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
+        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
       </c>
       <c r="C8" t="str">
         <v>Invite to JRM</v>
@@ -564,18 +564,18 @@
         <v>FLCM</v>
       </c>
       <c r="E8" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G8">
-        <v>45699</v>
+        <v>45690</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-17202</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B9" t="str">
-        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -584,18 +584,21 @@
         <v>FLCM</v>
       </c>
       <c r="E9" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F9" t="str">
+        <v>PDF</v>
       </c>
       <c r="G9">
-        <v>45690</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B10" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -604,21 +607,18 @@
         <v>FLCM</v>
       </c>
       <c r="E10" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F10" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G10">
-        <v>45686</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B11" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -630,15 +630,15 @@
         <v>estimates</v>
       </c>
       <c r="G11">
-        <v>45700</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B12" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -650,15 +650,15 @@
         <v>estimates</v>
       </c>
       <c r="G12">
-        <v>45656</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B13" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -670,15 +670,15 @@
         <v>estimates</v>
       </c>
       <c r="G13">
-        <v>45588</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-17054</v>
       </c>
       <c r="B14" t="str">
-        <v>Data Source to EDGE</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -687,18 +687,21 @@
         <v>FLCM</v>
       </c>
       <c r="E14" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F14" t="str">
+        <v>PDF</v>
       </c>
       <c r="G14">
-        <v>45664</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-17054</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B15" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -709,19 +712,16 @@
       <c r="E15" t="str">
         <v>approved</v>
       </c>
-      <c r="F15" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G15">
-        <v>45691</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-14372</v>
       </c>
       <c r="B16" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -732,16 +732,19 @@
       <c r="E16" t="str">
         <v>approved</v>
       </c>
+      <c r="F16" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G16">
-        <v>45299</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ENT-14372</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B17" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -756,58 +759,58 @@
         <v>PDF</v>
       </c>
       <c r="G17">
-        <v>45512</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B18" t="str">
-        <v>RAMP Phase 2</v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D18" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E18" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F18" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G18">
-        <v>45562</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B19" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D19" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E19" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F19" t="str">
+        <v>PDF</v>
       </c>
       <c r="G19">
-        <v>45695</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B20" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
@@ -822,15 +825,15 @@
         <v>PDF</v>
       </c>
       <c r="G20">
-        <v>45688</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B21" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
@@ -845,15 +848,15 @@
         <v>PDF</v>
       </c>
       <c r="G21">
-        <v>45701</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B22" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
@@ -864,19 +867,16 @@
       <c r="E22" t="str">
         <v>approved</v>
       </c>
-      <c r="F22" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G22">
-        <v>45695</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B23" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
@@ -885,138 +885,138 @@
         <v>FLCM</v>
       </c>
       <c r="E23" t="str">
-        <v>approved</v>
+        <v>estimates</v>
       </c>
       <c r="G23">
-        <v>45706</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B24" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D24" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E24" t="str">
         <v>estimates</v>
       </c>
       <c r="G24">
-        <v>45559</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B25" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D25" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E25" t="str">
         <v>estimates</v>
       </c>
       <c r="G25">
-        <v>45623</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B26" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D26" t="str">
-        <v>FLCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E26" t="str">
         <v>estimates</v>
       </c>
       <c r="G26">
-        <v>45355</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B27" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D27" t="str">
-        <v>CorpSec</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E27" t="str">
         <v>estimates</v>
       </c>
       <c r="G27">
-        <v>45446</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B28" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D28" t="str">
-        <v>BSCM/ESCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E28" t="str">
         <v>estimates</v>
       </c>
       <c r="G28">
-        <v>45477</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B29" t="str">
-        <v>CSDM Upgrade</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E29" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G29">
-        <v>45394</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B30" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
@@ -1028,15 +1028,15 @@
         <v>ofs</v>
       </c>
       <c r="G30">
-        <v>45531</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B31" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
@@ -1048,15 +1048,15 @@
         <v>ofs</v>
       </c>
       <c r="G31">
-        <v>45453</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B32" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
@@ -1065,98 +1065,95 @@
         <v>FLCM</v>
       </c>
       <c r="E32" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G32">
-        <v>45461</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B33" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D33" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E33" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G33">
-        <v>45714</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-15822</v>
       </c>
       <c r="B34" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D34" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E34" t="str">
         <v>estimates</v>
       </c>
       <c r="G34">
-        <v>45686</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-15822</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B35" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D35" t="str">
-        <v>FLCM</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E35" t="str">
         <v>estimates</v>
       </c>
       <c r="G35">
-        <v>45650</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-17853</v>
       </c>
       <c r="B36" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
       </c>
-      <c r="D36" t="str">
-        <v>BSCM/ESCM</v>
-      </c>
       <c r="E36" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G36">
-        <v>45541</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ENT-17853</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B37" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
@@ -1165,15 +1162,15 @@
         <v>ofs</v>
       </c>
       <c r="G37">
-        <v>45691</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B38" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
@@ -1182,15 +1179,15 @@
         <v>ofs</v>
       </c>
       <c r="G38">
-        <v>45559</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B39" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
@@ -1199,15 +1196,15 @@
         <v>ofs</v>
       </c>
       <c r="G39">
-        <v>45596</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B40" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
@@ -1216,15 +1213,15 @@
         <v>ofs</v>
       </c>
       <c r="G40">
-        <v>45378</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B41" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1233,15 +1230,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45468</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B42" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1250,15 +1247,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45310</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B43" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1267,15 +1264,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45427</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B44" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1284,15 +1281,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45279</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B45" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1301,15 +1298,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45558</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B46" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1318,15 +1315,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45383</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B47" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1335,15 +1332,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45638</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B48" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1352,15 +1349,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45461</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B49" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1374,10 +1371,10 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B50" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1386,15 +1383,15 @@
         <v>ofs</v>
       </c>
       <c r="G50">
-        <v>45371</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B51" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1403,15 +1400,15 @@
         <v>ofs</v>
       </c>
       <c r="G51">
-        <v>45406</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B52" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1420,15 +1417,15 @@
         <v>ofs</v>
       </c>
       <c r="G52">
-        <v>45364</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B53" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1437,15 +1434,15 @@
         <v>ofs</v>
       </c>
       <c r="G53">
-        <v>45593</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B54" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1454,15 +1451,15 @@
         <v>ofs</v>
       </c>
       <c r="G54">
-        <v>45408</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B55" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1471,15 +1468,15 @@
         <v>ofs</v>
       </c>
       <c r="G55">
-        <v>45595</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B56" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1488,15 +1485,15 @@
         <v>ofs</v>
       </c>
       <c r="G56">
-        <v>45392</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B57" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
@@ -1510,27 +1507,27 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B58" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C58" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E58" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G58">
-        <v>45411</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-18725</v>
       </c>
       <c r="B59" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>US Video System - Lenel to Genetec</v>
       </c>
       <c r="C59" t="str">
         <v>Invite to JRM</v>
@@ -1542,26 +1539,9 @@
         <v>45721</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="str">
-        <v>ENT-18725</v>
-      </c>
-      <c r="B60" t="str">
-        <v>US Video System - Lenel to Genetec</v>
-      </c>
-      <c r="C60" t="str">
-        <v>Invite to JRM</v>
-      </c>
-      <c r="E60" t="str">
-        <v>jrm</v>
-      </c>
-      <c r="G60">
-        <v>45721</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G60"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G59"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G58"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -452,10 +452,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ENT-16949</v>
+        <v>ENT-16621</v>
       </c>
       <c r="B3" t="str">
-        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
+        <v>CIW Data Products to PROD</v>
       </c>
       <c r="C3" t="str">
         <v>Invite to JRM</v>
@@ -464,18 +464,18 @@
         <v>FLCM</v>
       </c>
       <c r="E3" t="str">
-        <v>estimates</v>
+        <v>approved</v>
       </c>
       <c r="G3">
-        <v>45531</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ENT-16621</v>
+        <v>ENT-16031</v>
       </c>
       <c r="B4" t="str">
-        <v>CIW Data Products to PROD</v>
+        <v>Fraud - Notes generator</v>
       </c>
       <c r="C4" t="str">
         <v>Invite to JRM</v>
@@ -484,18 +484,18 @@
         <v>FLCM</v>
       </c>
       <c r="E4" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G4">
-        <v>45596</v>
+        <v>45649</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ENT-16031</v>
+        <v>ENT-15917</v>
       </c>
       <c r="B5" t="str">
-        <v>Fraud - Notes generator</v>
+        <v>REBO Bill Payment Investigation Requests</v>
       </c>
       <c r="C5" t="str">
         <v>Invite to JRM</v>
@@ -507,15 +507,15 @@
         <v>jrm</v>
       </c>
       <c r="G5">
-        <v>45649</v>
+        <v>45613</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ENT-15917</v>
+        <v>ENT-17286</v>
       </c>
       <c r="B6" t="str">
-        <v>REBO Bill Payment Investigation Requests</v>
+        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
       </c>
       <c r="C6" t="str">
         <v>Invite to JRM</v>
@@ -524,18 +524,18 @@
         <v>FLCM</v>
       </c>
       <c r="E6" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G6">
-        <v>45613</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENT-17286</v>
+        <v>ENT-17202</v>
       </c>
       <c r="B7" t="str">
-        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
+        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
       </c>
       <c r="C7" t="str">
         <v>Invite to JRM</v>
@@ -544,18 +544,18 @@
         <v>FLCM</v>
       </c>
       <c r="E7" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G7">
-        <v>45699</v>
+        <v>45690</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENT-17202</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B8" t="str">
-        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C8" t="str">
         <v>Invite to JRM</v>
@@ -564,18 +564,21 @@
         <v>FLCM</v>
       </c>
       <c r="E8" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F8" t="str">
+        <v>PDF</v>
       </c>
       <c r="G8">
-        <v>45690</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B9" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -584,21 +587,18 @@
         <v>FLCM</v>
       </c>
       <c r="E9" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F9" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G9">
-        <v>45686</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B10" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -610,15 +610,15 @@
         <v>estimates</v>
       </c>
       <c r="G10">
-        <v>45700</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B11" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -630,15 +630,15 @@
         <v>estimates</v>
       </c>
       <c r="G11">
-        <v>45656</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B12" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -650,15 +650,15 @@
         <v>estimates</v>
       </c>
       <c r="G12">
-        <v>45588</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-17054</v>
       </c>
       <c r="B13" t="str">
-        <v>Data Source to EDGE</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -667,18 +667,21 @@
         <v>FLCM</v>
       </c>
       <c r="E13" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F13" t="str">
+        <v>PDF</v>
       </c>
       <c r="G13">
-        <v>45664</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-17054</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B14" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -689,19 +692,16 @@
       <c r="E14" t="str">
         <v>approved</v>
       </c>
-      <c r="F14" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G14">
-        <v>45691</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-14372</v>
       </c>
       <c r="B15" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -712,16 +712,19 @@
       <c r="E15" t="str">
         <v>approved</v>
       </c>
+      <c r="F15" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G15">
-        <v>45299</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-14372</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B16" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -736,58 +739,58 @@
         <v>PDF</v>
       </c>
       <c r="G16">
-        <v>45512</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B17" t="str">
-        <v>RAMP Phase 2</v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D17" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E17" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F17" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G17">
-        <v>45562</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B18" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D18" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E18" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F18" t="str">
+        <v>PDF</v>
       </c>
       <c r="G18">
-        <v>45695</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B19" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
@@ -802,15 +805,15 @@
         <v>PDF</v>
       </c>
       <c r="G19">
-        <v>45688</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B20" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
@@ -825,15 +828,15 @@
         <v>PDF</v>
       </c>
       <c r="G20">
-        <v>45701</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B21" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
@@ -844,19 +847,16 @@
       <c r="E21" t="str">
         <v>approved</v>
       </c>
-      <c r="F21" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G21">
-        <v>45695</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B22" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
@@ -865,138 +865,138 @@
         <v>FLCM</v>
       </c>
       <c r="E22" t="str">
-        <v>approved</v>
+        <v>estimates</v>
       </c>
       <c r="G22">
-        <v>45706</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B23" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D23" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E23" t="str">
         <v>estimates</v>
       </c>
       <c r="G23">
-        <v>45559</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B24" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D24" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E24" t="str">
         <v>estimates</v>
       </c>
       <c r="G24">
-        <v>45623</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B25" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D25" t="str">
-        <v>FLCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E25" t="str">
         <v>estimates</v>
       </c>
       <c r="G25">
-        <v>45355</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B26" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D26" t="str">
-        <v>CorpSec</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E26" t="str">
         <v>estimates</v>
       </c>
       <c r="G26">
-        <v>45446</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B27" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D27" t="str">
-        <v>BSCM/ESCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E27" t="str">
         <v>estimates</v>
       </c>
       <c r="G27">
-        <v>45477</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B28" t="str">
-        <v>CSDM Upgrade</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D28" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E28" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G28">
-        <v>45394</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B29" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
@@ -1008,15 +1008,15 @@
         <v>ofs</v>
       </c>
       <c r="G29">
-        <v>45531</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B30" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
@@ -1028,15 +1028,15 @@
         <v>ofs</v>
       </c>
       <c r="G30">
-        <v>45453</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B31" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
@@ -1045,98 +1045,95 @@
         <v>FLCM</v>
       </c>
       <c r="E31" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G31">
-        <v>45461</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B32" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D32" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E32" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G32">
-        <v>45714</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-15822</v>
       </c>
       <c r="B33" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D33" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E33" t="str">
         <v>estimates</v>
       </c>
       <c r="G33">
-        <v>45686</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-15822</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B34" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D34" t="str">
-        <v>FLCM</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E34" t="str">
         <v>estimates</v>
       </c>
       <c r="G34">
-        <v>45650</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-17853</v>
       </c>
       <c r="B35" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
       </c>
-      <c r="D35" t="str">
-        <v>BSCM/ESCM</v>
-      </c>
       <c r="E35" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G35">
-        <v>45541</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-17853</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B36" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
@@ -1145,15 +1142,15 @@
         <v>ofs</v>
       </c>
       <c r="G36">
-        <v>45691</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B37" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
@@ -1162,15 +1159,15 @@
         <v>ofs</v>
       </c>
       <c r="G37">
-        <v>45559</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B38" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
@@ -1179,15 +1176,15 @@
         <v>ofs</v>
       </c>
       <c r="G38">
-        <v>45596</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B39" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
@@ -1196,15 +1193,15 @@
         <v>ofs</v>
       </c>
       <c r="G39">
-        <v>45378</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B40" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
@@ -1213,15 +1210,15 @@
         <v>ofs</v>
       </c>
       <c r="G40">
-        <v>45468</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B41" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1230,15 +1227,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45310</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B42" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1247,15 +1244,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45427</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B43" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1264,15 +1261,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45279</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B44" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1281,15 +1278,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45558</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B45" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1298,15 +1295,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45383</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B46" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1315,15 +1312,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45638</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B47" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1332,15 +1329,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45461</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B48" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1354,10 +1351,10 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B49" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1366,15 +1363,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45371</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B50" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1383,15 +1380,15 @@
         <v>ofs</v>
       </c>
       <c r="G50">
-        <v>45406</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B51" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1400,15 +1397,15 @@
         <v>ofs</v>
       </c>
       <c r="G51">
-        <v>45364</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B52" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1417,15 +1414,15 @@
         <v>ofs</v>
       </c>
       <c r="G52">
-        <v>45593</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B53" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1434,15 +1431,15 @@
         <v>ofs</v>
       </c>
       <c r="G53">
-        <v>45408</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B54" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1451,15 +1448,15 @@
         <v>ofs</v>
       </c>
       <c r="G54">
-        <v>45595</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B55" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1468,15 +1465,15 @@
         <v>ofs</v>
       </c>
       <c r="G55">
-        <v>45392</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B56" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1490,27 +1487,27 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B57" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E57" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G57">
-        <v>45411</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-18725</v>
       </c>
       <c r="B58" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>US Video System - Lenel to Genetec</v>
       </c>
       <c r="C58" t="str">
         <v>Invite to JRM</v>
@@ -1522,26 +1519,9 @@
         <v>45721</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="str">
-        <v>ENT-18725</v>
-      </c>
-      <c r="B59" t="str">
-        <v>US Video System - Lenel to Genetec</v>
-      </c>
-      <c r="C59" t="str">
-        <v>Invite to JRM</v>
-      </c>
-      <c r="E59" t="str">
-        <v>jrm</v>
-      </c>
-      <c r="G59">
-        <v>45721</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G59"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G58"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G57"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -429,33 +429,30 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>1234</v>
+        <v>ENT-16621</v>
       </c>
       <c r="B2" t="str">
-        <v>1234123</v>
+        <v>CIW Data Products to PROD</v>
       </c>
       <c r="C2" t="str">
-        <v>1234</v>
+        <v>Invite to JRM</v>
       </c>
       <c r="D2" t="str">
-        <v>1234</v>
+        <v>FLCM</v>
       </c>
       <c r="E2" t="str">
-        <v>jrm</v>
-      </c>
-      <c r="F2" t="str">
-        <v/>
-      </c>
-      <c r="G2" t="str">
-        <v>2025-03-15</v>
+        <v>approved</v>
+      </c>
+      <c r="G2">
+        <v>45596</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ENT-16621</v>
+        <v>ENT-16031</v>
       </c>
       <c r="B3" t="str">
-        <v>CIW Data Products to PROD</v>
+        <v>Fraud - Notes generator</v>
       </c>
       <c r="C3" t="str">
         <v>Invite to JRM</v>
@@ -464,18 +461,18 @@
         <v>FLCM</v>
       </c>
       <c r="E3" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G3">
-        <v>45596</v>
+        <v>45649</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ENT-16031</v>
+        <v>ENT-15917</v>
       </c>
       <c r="B4" t="str">
-        <v>Fraud - Notes generator</v>
+        <v>REBO Bill Payment Investigation Requests</v>
       </c>
       <c r="C4" t="str">
         <v>Invite to JRM</v>
@@ -487,15 +484,15 @@
         <v>jrm</v>
       </c>
       <c r="G4">
-        <v>45649</v>
+        <v>45613</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ENT-15917</v>
+        <v>ENT-17286</v>
       </c>
       <c r="B5" t="str">
-        <v>REBO Bill Payment Investigation Requests</v>
+        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
       </c>
       <c r="C5" t="str">
         <v>Invite to JRM</v>
@@ -504,18 +501,18 @@
         <v>FLCM</v>
       </c>
       <c r="E5" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G5">
-        <v>45613</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ENT-17286</v>
+        <v>ENT-17202</v>
       </c>
       <c r="B6" t="str">
-        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
+        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
       </c>
       <c r="C6" t="str">
         <v>Invite to JRM</v>
@@ -524,18 +521,18 @@
         <v>FLCM</v>
       </c>
       <c r="E6" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G6">
-        <v>45699</v>
+        <v>45690</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENT-17202</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B7" t="str">
-        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C7" t="str">
         <v>Invite to JRM</v>
@@ -544,18 +541,21 @@
         <v>FLCM</v>
       </c>
       <c r="E7" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F7" t="str">
+        <v>PDF</v>
       </c>
       <c r="G7">
-        <v>45690</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B8" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C8" t="str">
         <v>Invite to JRM</v>
@@ -564,21 +564,18 @@
         <v>FLCM</v>
       </c>
       <c r="E8" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F8" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G8">
-        <v>45686</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B9" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -590,15 +587,15 @@
         <v>estimates</v>
       </c>
       <c r="G9">
-        <v>45700</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B10" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -610,15 +607,15 @@
         <v>estimates</v>
       </c>
       <c r="G10">
-        <v>45656</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B11" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -630,15 +627,15 @@
         <v>estimates</v>
       </c>
       <c r="G11">
-        <v>45588</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-17054</v>
       </c>
       <c r="B12" t="str">
-        <v>Data Source to EDGE</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -647,18 +644,21 @@
         <v>FLCM</v>
       </c>
       <c r="E12" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F12" t="str">
+        <v>PDF</v>
       </c>
       <c r="G12">
-        <v>45664</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-17054</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B13" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -669,19 +669,16 @@
       <c r="E13" t="str">
         <v>approved</v>
       </c>
-      <c r="F13" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G13">
-        <v>45691</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-14372</v>
       </c>
       <c r="B14" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -692,16 +689,19 @@
       <c r="E14" t="str">
         <v>approved</v>
       </c>
+      <c r="F14" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G14">
-        <v>45299</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-14372</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B15" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -716,58 +716,58 @@
         <v>PDF</v>
       </c>
       <c r="G15">
-        <v>45512</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B16" t="str">
-        <v>RAMP Phase 2</v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D16" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E16" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F16" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G16">
-        <v>45562</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B17" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D17" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E17" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F17" t="str">
+        <v>PDF</v>
       </c>
       <c r="G17">
-        <v>45695</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B18" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
@@ -782,15 +782,15 @@
         <v>PDF</v>
       </c>
       <c r="G18">
-        <v>45688</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B19" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
@@ -805,15 +805,15 @@
         <v>PDF</v>
       </c>
       <c r="G19">
-        <v>45701</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B20" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
@@ -824,19 +824,16 @@
       <c r="E20" t="str">
         <v>approved</v>
       </c>
-      <c r="F20" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G20">
-        <v>45695</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B21" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
@@ -845,138 +842,138 @@
         <v>FLCM</v>
       </c>
       <c r="E21" t="str">
-        <v>approved</v>
+        <v>estimates</v>
       </c>
       <c r="G21">
-        <v>45706</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B22" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D22" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E22" t="str">
         <v>estimates</v>
       </c>
       <c r="G22">
-        <v>45559</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B23" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D23" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E23" t="str">
         <v>estimates</v>
       </c>
       <c r="G23">
-        <v>45623</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B24" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D24" t="str">
-        <v>FLCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E24" t="str">
         <v>estimates</v>
       </c>
       <c r="G24">
-        <v>45355</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B25" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D25" t="str">
-        <v>CorpSec</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E25" t="str">
         <v>estimates</v>
       </c>
       <c r="G25">
-        <v>45446</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B26" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D26" t="str">
-        <v>BSCM/ESCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E26" t="str">
         <v>estimates</v>
       </c>
       <c r="G26">
-        <v>45477</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B27" t="str">
-        <v>CSDM Upgrade</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D27" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E27" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G27">
-        <v>45394</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B28" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
@@ -988,15 +985,15 @@
         <v>ofs</v>
       </c>
       <c r="G28">
-        <v>45531</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B29" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
@@ -1008,15 +1005,15 @@
         <v>ofs</v>
       </c>
       <c r="G29">
-        <v>45453</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B30" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
@@ -1025,98 +1022,95 @@
         <v>FLCM</v>
       </c>
       <c r="E30" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G30">
-        <v>45461</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B31" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D31" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E31" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G31">
-        <v>45714</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-15822</v>
       </c>
       <c r="B32" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D32" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E32" t="str">
         <v>estimates</v>
       </c>
       <c r="G32">
-        <v>45686</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-15822</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B33" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D33" t="str">
-        <v>FLCM</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E33" t="str">
         <v>estimates</v>
       </c>
       <c r="G33">
-        <v>45650</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-17853</v>
       </c>
       <c r="B34" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
       </c>
-      <c r="D34" t="str">
-        <v>BSCM/ESCM</v>
-      </c>
       <c r="E34" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G34">
-        <v>45541</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-17853</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B35" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
@@ -1125,15 +1119,15 @@
         <v>ofs</v>
       </c>
       <c r="G35">
-        <v>45691</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B36" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
@@ -1142,15 +1136,15 @@
         <v>ofs</v>
       </c>
       <c r="G36">
-        <v>45559</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B37" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
@@ -1159,15 +1153,15 @@
         <v>ofs</v>
       </c>
       <c r="G37">
-        <v>45596</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B38" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
@@ -1176,15 +1170,15 @@
         <v>ofs</v>
       </c>
       <c r="G38">
-        <v>45378</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B39" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
@@ -1193,15 +1187,15 @@
         <v>ofs</v>
       </c>
       <c r="G39">
-        <v>45468</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B40" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
@@ -1210,15 +1204,15 @@
         <v>ofs</v>
       </c>
       <c r="G40">
-        <v>45310</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B41" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1227,15 +1221,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45427</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B42" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1244,15 +1238,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45279</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B43" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1261,15 +1255,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45558</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B44" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1278,15 +1272,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45383</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B45" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1295,15 +1289,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45638</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B46" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1312,15 +1306,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45461</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B47" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1334,10 +1328,10 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B48" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1346,15 +1340,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45371</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B49" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1363,15 +1357,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45406</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B50" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1380,15 +1374,15 @@
         <v>ofs</v>
       </c>
       <c r="G50">
-        <v>45364</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B51" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1397,15 +1391,15 @@
         <v>ofs</v>
       </c>
       <c r="G51">
-        <v>45593</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B52" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1414,15 +1408,15 @@
         <v>ofs</v>
       </c>
       <c r="G52">
-        <v>45408</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B53" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1431,15 +1425,15 @@
         <v>ofs</v>
       </c>
       <c r="G53">
-        <v>45595</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B54" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1448,15 +1442,15 @@
         <v>ofs</v>
       </c>
       <c r="G54">
-        <v>45392</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B55" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1470,27 +1464,27 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B56" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E56" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G56">
-        <v>45411</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-18725</v>
       </c>
       <c r="B57" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>US Video System - Lenel to Genetec</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
@@ -1502,26 +1496,9 @@
         <v>45721</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="str">
-        <v>ENT-18725</v>
-      </c>
-      <c r="B58" t="str">
-        <v>US Video System - Lenel to Genetec</v>
-      </c>
-      <c r="C58" t="str">
-        <v>Invite to JRM</v>
-      </c>
-      <c r="E58" t="str">
-        <v>jrm</v>
-      </c>
-      <c r="G58">
-        <v>45721</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G58"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G57"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G56"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -449,10 +449,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ENT-16031</v>
+        <v>ENT-15917</v>
       </c>
       <c r="B3" t="str">
-        <v>Fraud - Notes generator</v>
+        <v>REBO Bill Payment Investigation Requests</v>
       </c>
       <c r="C3" t="str">
         <v>Invite to JRM</v>
@@ -464,15 +464,15 @@
         <v>jrm</v>
       </c>
       <c r="G3">
-        <v>45649</v>
+        <v>45613</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ENT-15917</v>
+        <v>ENT-17286</v>
       </c>
       <c r="B4" t="str">
-        <v>REBO Bill Payment Investigation Requests</v>
+        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
       </c>
       <c r="C4" t="str">
         <v>Invite to JRM</v>
@@ -481,18 +481,18 @@
         <v>FLCM</v>
       </c>
       <c r="E4" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G4">
-        <v>45613</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ENT-17286</v>
+        <v>ENT-17202</v>
       </c>
       <c r="B5" t="str">
-        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
+        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
       </c>
       <c r="C5" t="str">
         <v>Invite to JRM</v>
@@ -501,18 +501,18 @@
         <v>FLCM</v>
       </c>
       <c r="E5" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G5">
-        <v>45699</v>
+        <v>45690</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ENT-17202</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B6" t="str">
-        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C6" t="str">
         <v>Invite to JRM</v>
@@ -521,18 +521,21 @@
         <v>FLCM</v>
       </c>
       <c r="E6" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F6" t="str">
+        <v>PDF</v>
       </c>
       <c r="G6">
-        <v>45690</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B7" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C7" t="str">
         <v>Invite to JRM</v>
@@ -541,21 +544,18 @@
         <v>FLCM</v>
       </c>
       <c r="E7" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F7" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G7">
-        <v>45686</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B8" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C8" t="str">
         <v>Invite to JRM</v>
@@ -567,15 +567,15 @@
         <v>estimates</v>
       </c>
       <c r="G8">
-        <v>45700</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B9" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -587,15 +587,15 @@
         <v>estimates</v>
       </c>
       <c r="G9">
-        <v>45656</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B10" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -607,15 +607,15 @@
         <v>estimates</v>
       </c>
       <c r="G10">
-        <v>45588</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-17054</v>
       </c>
       <c r="B11" t="str">
-        <v>Data Source to EDGE</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -624,18 +624,21 @@
         <v>FLCM</v>
       </c>
       <c r="E11" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F11" t="str">
+        <v>PDF</v>
       </c>
       <c r="G11">
-        <v>45664</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-17054</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B12" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -646,19 +649,16 @@
       <c r="E12" t="str">
         <v>approved</v>
       </c>
-      <c r="F12" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G12">
-        <v>45691</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-14372</v>
       </c>
       <c r="B13" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -669,16 +669,19 @@
       <c r="E13" t="str">
         <v>approved</v>
       </c>
+      <c r="F13" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G13">
-        <v>45299</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-14372</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B14" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -693,58 +696,58 @@
         <v>PDF</v>
       </c>
       <c r="G14">
-        <v>45512</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B15" t="str">
-        <v>RAMP Phase 2</v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D15" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E15" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F15" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G15">
-        <v>45562</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B16" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D16" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E16" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F16" t="str">
+        <v>PDF</v>
       </c>
       <c r="G16">
-        <v>45695</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B17" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -759,15 +762,15 @@
         <v>PDF</v>
       </c>
       <c r="G17">
-        <v>45688</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B18" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
@@ -782,15 +785,15 @@
         <v>PDF</v>
       </c>
       <c r="G18">
-        <v>45701</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B19" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
@@ -801,19 +804,16 @@
       <c r="E19" t="str">
         <v>approved</v>
       </c>
-      <c r="F19" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G19">
-        <v>45695</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B20" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
@@ -822,138 +822,138 @@
         <v>FLCM</v>
       </c>
       <c r="E20" t="str">
-        <v>approved</v>
+        <v>estimates</v>
       </c>
       <c r="G20">
-        <v>45706</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B21" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D21" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E21" t="str">
         <v>estimates</v>
       </c>
       <c r="G21">
-        <v>45559</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B22" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D22" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E22" t="str">
         <v>estimates</v>
       </c>
       <c r="G22">
-        <v>45623</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B23" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D23" t="str">
-        <v>FLCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E23" t="str">
         <v>estimates</v>
       </c>
       <c r="G23">
-        <v>45355</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B24" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D24" t="str">
-        <v>CorpSec</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E24" t="str">
         <v>estimates</v>
       </c>
       <c r="G24">
-        <v>45446</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B25" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D25" t="str">
-        <v>BSCM/ESCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E25" t="str">
         <v>estimates</v>
       </c>
       <c r="G25">
-        <v>45477</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B26" t="str">
-        <v>CSDM Upgrade</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D26" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E26" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G26">
-        <v>45394</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B27" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
@@ -965,15 +965,15 @@
         <v>ofs</v>
       </c>
       <c r="G27">
-        <v>45531</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B28" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
@@ -985,15 +985,15 @@
         <v>ofs</v>
       </c>
       <c r="G28">
-        <v>45453</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B29" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
@@ -1002,98 +1002,95 @@
         <v>FLCM</v>
       </c>
       <c r="E29" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G29">
-        <v>45461</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B30" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D30" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E30" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G30">
-        <v>45714</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-15822</v>
       </c>
       <c r="B31" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D31" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E31" t="str">
         <v>estimates</v>
       </c>
       <c r="G31">
-        <v>45686</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-15822</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B32" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D32" t="str">
-        <v>FLCM</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E32" t="str">
         <v>estimates</v>
       </c>
       <c r="G32">
-        <v>45650</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-17853</v>
       </c>
       <c r="B33" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
       </c>
-      <c r="D33" t="str">
-        <v>BSCM/ESCM</v>
-      </c>
       <c r="E33" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G33">
-        <v>45541</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-17853</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B34" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
@@ -1102,15 +1099,15 @@
         <v>ofs</v>
       </c>
       <c r="G34">
-        <v>45691</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B35" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
@@ -1119,15 +1116,15 @@
         <v>ofs</v>
       </c>
       <c r="G35">
-        <v>45559</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B36" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
@@ -1136,15 +1133,15 @@
         <v>ofs</v>
       </c>
       <c r="G36">
-        <v>45596</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B37" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
@@ -1153,15 +1150,15 @@
         <v>ofs</v>
       </c>
       <c r="G37">
-        <v>45378</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B38" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
@@ -1170,15 +1167,15 @@
         <v>ofs</v>
       </c>
       <c r="G38">
-        <v>45468</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B39" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
@@ -1187,15 +1184,15 @@
         <v>ofs</v>
       </c>
       <c r="G39">
-        <v>45310</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B40" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
@@ -1204,15 +1201,15 @@
         <v>ofs</v>
       </c>
       <c r="G40">
-        <v>45427</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B41" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1221,15 +1218,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45279</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B42" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1238,15 +1235,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45558</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B43" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1255,15 +1252,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45383</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B44" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1272,15 +1269,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45638</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B45" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1289,15 +1286,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45461</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B46" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1311,10 +1308,10 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B47" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1323,15 +1320,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45371</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B48" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1340,15 +1337,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45406</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B49" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1357,15 +1354,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45364</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B50" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1374,15 +1371,15 @@
         <v>ofs</v>
       </c>
       <c r="G50">
-        <v>45593</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B51" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1391,15 +1388,15 @@
         <v>ofs</v>
       </c>
       <c r="G51">
-        <v>45408</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B52" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1408,15 +1405,15 @@
         <v>ofs</v>
       </c>
       <c r="G52">
-        <v>45595</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B53" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1425,15 +1422,15 @@
         <v>ofs</v>
       </c>
       <c r="G53">
-        <v>45392</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B54" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1447,27 +1444,27 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B55" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E55" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G55">
-        <v>45411</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-18725</v>
       </c>
       <c r="B56" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>US Video System - Lenel to Genetec</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1479,26 +1476,9 @@
         <v>45721</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="str">
-        <v>ENT-18725</v>
-      </c>
-      <c r="B57" t="str">
-        <v>US Video System - Lenel to Genetec</v>
-      </c>
-      <c r="C57" t="str">
-        <v>Invite to JRM</v>
-      </c>
-      <c r="E57" t="str">
-        <v>jrm</v>
-      </c>
-      <c r="G57">
-        <v>45721</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G57"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G56"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G55"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -572,10 +572,10 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B9" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -587,15 +587,15 @@
         <v>estimates</v>
       </c>
       <c r="G9">
-        <v>45588</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-17054</v>
       </c>
       <c r="B10" t="str">
-        <v>Data Source to EDGE</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -604,18 +604,21 @@
         <v>FLCM</v>
       </c>
       <c r="E10" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F10" t="str">
+        <v>PDF</v>
       </c>
       <c r="G10">
-        <v>45664</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-17054</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B11" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -626,19 +629,16 @@
       <c r="E11" t="str">
         <v>approved</v>
       </c>
-      <c r="F11" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G11">
-        <v>45691</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-14372</v>
       </c>
       <c r="B12" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -649,16 +649,19 @@
       <c r="E12" t="str">
         <v>approved</v>
       </c>
+      <c r="F12" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G12">
-        <v>45299</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-14372</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B13" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -673,58 +676,58 @@
         <v>PDF</v>
       </c>
       <c r="G13">
-        <v>45512</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B14" t="str">
-        <v>RAMP Phase 2</v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D14" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E14" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F14" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G14">
-        <v>45562</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B15" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D15" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E15" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F15" t="str">
+        <v>PDF</v>
       </c>
       <c r="G15">
-        <v>45695</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B16" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -739,15 +742,15 @@
         <v>PDF</v>
       </c>
       <c r="G16">
-        <v>45688</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B17" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -762,15 +765,15 @@
         <v>PDF</v>
       </c>
       <c r="G17">
-        <v>45701</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B18" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
@@ -781,19 +784,16 @@
       <c r="E18" t="str">
         <v>approved</v>
       </c>
-      <c r="F18" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G18">
-        <v>45695</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B19" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
@@ -802,138 +802,138 @@
         <v>FLCM</v>
       </c>
       <c r="E19" t="str">
-        <v>approved</v>
+        <v>estimates</v>
       </c>
       <c r="G19">
-        <v>45706</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B20" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D20" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E20" t="str">
         <v>estimates</v>
       </c>
       <c r="G20">
-        <v>45559</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B21" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D21" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E21" t="str">
         <v>estimates</v>
       </c>
       <c r="G21">
-        <v>45623</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B22" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D22" t="str">
-        <v>FLCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E22" t="str">
         <v>estimates</v>
       </c>
       <c r="G22">
-        <v>45355</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B23" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D23" t="str">
-        <v>CorpSec</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E23" t="str">
         <v>estimates</v>
       </c>
       <c r="G23">
-        <v>45446</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B24" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D24" t="str">
-        <v>BSCM/ESCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E24" t="str">
         <v>estimates</v>
       </c>
       <c r="G24">
-        <v>45477</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B25" t="str">
-        <v>CSDM Upgrade</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D25" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E25" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G25">
-        <v>45394</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B26" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
@@ -945,15 +945,15 @@
         <v>ofs</v>
       </c>
       <c r="G26">
-        <v>45531</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B27" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
@@ -965,15 +965,15 @@
         <v>ofs</v>
       </c>
       <c r="G27">
-        <v>45453</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B28" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
@@ -982,98 +982,95 @@
         <v>FLCM</v>
       </c>
       <c r="E28" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G28">
-        <v>45461</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B29" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E29" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G29">
-        <v>45714</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-15822</v>
       </c>
       <c r="B30" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D30" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E30" t="str">
         <v>estimates</v>
       </c>
       <c r="G30">
-        <v>45686</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-15822</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B31" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D31" t="str">
-        <v>FLCM</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E31" t="str">
         <v>estimates</v>
       </c>
       <c r="G31">
-        <v>45650</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-17853</v>
       </c>
       <c r="B32" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
       </c>
-      <c r="D32" t="str">
-        <v>BSCM/ESCM</v>
-      </c>
       <c r="E32" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G32">
-        <v>45541</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-17853</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B33" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
@@ -1082,15 +1079,15 @@
         <v>ofs</v>
       </c>
       <c r="G33">
-        <v>45691</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B34" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
@@ -1099,15 +1096,15 @@
         <v>ofs</v>
       </c>
       <c r="G34">
-        <v>45559</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B35" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
@@ -1116,15 +1113,15 @@
         <v>ofs</v>
       </c>
       <c r="G35">
-        <v>45596</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B36" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
@@ -1133,15 +1130,15 @@
         <v>ofs</v>
       </c>
       <c r="G36">
-        <v>45378</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B37" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
@@ -1150,15 +1147,15 @@
         <v>ofs</v>
       </c>
       <c r="G37">
-        <v>45468</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B38" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
@@ -1167,15 +1164,15 @@
         <v>ofs</v>
       </c>
       <c r="G38">
-        <v>45310</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B39" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
@@ -1184,15 +1181,15 @@
         <v>ofs</v>
       </c>
       <c r="G39">
-        <v>45427</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B40" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
@@ -1201,15 +1198,15 @@
         <v>ofs</v>
       </c>
       <c r="G40">
-        <v>45279</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B41" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1218,15 +1215,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45558</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B42" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1235,15 +1232,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45383</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B43" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1252,15 +1249,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45638</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B44" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1269,15 +1266,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45461</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B45" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1291,10 +1288,10 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B46" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1303,15 +1300,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45371</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B47" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1320,15 +1317,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45406</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B48" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1337,15 +1334,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45364</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B49" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1354,15 +1351,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45593</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B50" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1371,15 +1368,15 @@
         <v>ofs</v>
       </c>
       <c r="G50">
-        <v>45408</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B51" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1388,15 +1385,15 @@
         <v>ofs</v>
       </c>
       <c r="G51">
-        <v>45595</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B52" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1405,15 +1402,15 @@
         <v>ofs</v>
       </c>
       <c r="G52">
-        <v>45392</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B53" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1427,27 +1424,27 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B54" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E54" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G54">
-        <v>45411</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-18725</v>
       </c>
       <c r="B55" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>US Video System - Lenel to Genetec</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1459,26 +1456,9 @@
         <v>45721</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="str">
-        <v>ENT-18725</v>
-      </c>
-      <c r="B56" t="str">
-        <v>US Video System - Lenel to Genetec</v>
-      </c>
-      <c r="C56" t="str">
-        <v>Invite to JRM</v>
-      </c>
-      <c r="E56" t="str">
-        <v>jrm</v>
-      </c>
-      <c r="G56">
-        <v>45721</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G56"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G55"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G54"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -790,130 +790,130 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B19" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D19" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E19" t="str">
         <v>estimates</v>
       </c>
       <c r="G19">
-        <v>45559</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B20" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D20" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E20" t="str">
         <v>estimates</v>
       </c>
       <c r="G20">
-        <v>45623</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B21" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D21" t="str">
-        <v>FLCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E21" t="str">
         <v>estimates</v>
       </c>
       <c r="G21">
-        <v>45355</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B22" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D22" t="str">
-        <v>CorpSec</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E22" t="str">
         <v>estimates</v>
       </c>
       <c r="G22">
-        <v>45446</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B23" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D23" t="str">
-        <v>BSCM/ESCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E23" t="str">
         <v>estimates</v>
       </c>
       <c r="G23">
-        <v>45477</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B24" t="str">
-        <v>CSDM Upgrade</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D24" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E24" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G24">
-        <v>45394</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B25" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
@@ -925,15 +925,15 @@
         <v>ofs</v>
       </c>
       <c r="G25">
-        <v>45531</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B26" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
@@ -945,15 +945,15 @@
         <v>ofs</v>
       </c>
       <c r="G26">
-        <v>45453</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B27" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
@@ -962,98 +962,95 @@
         <v>FLCM</v>
       </c>
       <c r="E27" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G27">
-        <v>45461</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B28" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D28" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E28" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G28">
-        <v>45714</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-15822</v>
       </c>
       <c r="B29" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E29" t="str">
         <v>estimates</v>
       </c>
       <c r="G29">
-        <v>45686</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-15822</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B30" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D30" t="str">
-        <v>FLCM</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E30" t="str">
         <v>estimates</v>
       </c>
       <c r="G30">
-        <v>45650</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-17853</v>
       </c>
       <c r="B31" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
       </c>
-      <c r="D31" t="str">
-        <v>BSCM/ESCM</v>
-      </c>
       <c r="E31" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G31">
-        <v>45541</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-17853</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B32" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
@@ -1062,15 +1059,15 @@
         <v>ofs</v>
       </c>
       <c r="G32">
-        <v>45691</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B33" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
@@ -1079,15 +1076,15 @@
         <v>ofs</v>
       </c>
       <c r="G33">
-        <v>45559</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B34" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
@@ -1096,15 +1093,15 @@
         <v>ofs</v>
       </c>
       <c r="G34">
-        <v>45596</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B35" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
@@ -1113,15 +1110,15 @@
         <v>ofs</v>
       </c>
       <c r="G35">
-        <v>45378</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B36" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
@@ -1130,15 +1127,15 @@
         <v>ofs</v>
       </c>
       <c r="G36">
-        <v>45468</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B37" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
@@ -1147,15 +1144,15 @@
         <v>ofs</v>
       </c>
       <c r="G37">
-        <v>45310</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B38" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
@@ -1164,15 +1161,15 @@
         <v>ofs</v>
       </c>
       <c r="G38">
-        <v>45427</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B39" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
@@ -1181,15 +1178,15 @@
         <v>ofs</v>
       </c>
       <c r="G39">
-        <v>45279</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B40" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
@@ -1198,15 +1195,15 @@
         <v>ofs</v>
       </c>
       <c r="G40">
-        <v>45558</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B41" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1215,15 +1212,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45383</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B42" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1232,15 +1229,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45638</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B43" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1249,15 +1246,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45461</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B44" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1271,10 +1268,10 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B45" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1283,15 +1280,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45371</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B46" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1300,15 +1297,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45406</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B47" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1317,15 +1314,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45364</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B48" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1334,15 +1331,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45593</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B49" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1351,15 +1348,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45408</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B50" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1368,15 +1365,15 @@
         <v>ofs</v>
       </c>
       <c r="G50">
-        <v>45595</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B51" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1385,15 +1382,15 @@
         <v>ofs</v>
       </c>
       <c r="G51">
-        <v>45392</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B52" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1407,27 +1404,27 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B53" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E53" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G53">
-        <v>45411</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-18725</v>
       </c>
       <c r="B54" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>US Video System - Lenel to Genetec</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1439,26 +1436,9 @@
         <v>45721</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="str">
-        <v>ENT-18725</v>
-      </c>
-      <c r="B55" t="str">
-        <v>US Video System - Lenel to Genetec</v>
-      </c>
-      <c r="C55" t="str">
-        <v>Invite to JRM</v>
-      </c>
-      <c r="E55" t="str">
-        <v>jrm</v>
-      </c>
-      <c r="G55">
-        <v>45721</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G55"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G54"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G53"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -449,10 +449,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ENT-15917</v>
+        <v>ENT-17286</v>
       </c>
       <c r="B3" t="str">
-        <v>REBO Bill Payment Investigation Requests</v>
+        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
       </c>
       <c r="C3" t="str">
         <v>Invite to JRM</v>
@@ -461,18 +461,18 @@
         <v>FLCM</v>
       </c>
       <c r="E3" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G3">
-        <v>45613</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ENT-17286</v>
+        <v>ENT-17202</v>
       </c>
       <c r="B4" t="str">
-        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
+        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
       </c>
       <c r="C4" t="str">
         <v>Invite to JRM</v>
@@ -481,18 +481,18 @@
         <v>FLCM</v>
       </c>
       <c r="E4" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G4">
-        <v>45699</v>
+        <v>45690</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ENT-17202</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B5" t="str">
-        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C5" t="str">
         <v>Invite to JRM</v>
@@ -501,18 +501,21 @@
         <v>FLCM</v>
       </c>
       <c r="E5" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F5" t="str">
+        <v>PDF</v>
       </c>
       <c r="G5">
-        <v>45690</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B6" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C6" t="str">
         <v>Invite to JRM</v>
@@ -521,21 +524,18 @@
         <v>FLCM</v>
       </c>
       <c r="E6" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F6" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G6">
-        <v>45686</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B7" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C7" t="str">
         <v>Invite to JRM</v>
@@ -547,15 +547,15 @@
         <v>estimates</v>
       </c>
       <c r="G7">
-        <v>45700</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B8" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C8" t="str">
         <v>Invite to JRM</v>
@@ -567,15 +567,15 @@
         <v>estimates</v>
       </c>
       <c r="G8">
-        <v>45656</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-17054</v>
       </c>
       <c r="B9" t="str">
-        <v>Data Source to EDGE</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -584,18 +584,21 @@
         <v>FLCM</v>
       </c>
       <c r="E9" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F9" t="str">
+        <v>PDF</v>
       </c>
       <c r="G9">
-        <v>45664</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-17054</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B10" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -606,19 +609,16 @@
       <c r="E10" t="str">
         <v>approved</v>
       </c>
-      <c r="F10" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G10">
-        <v>45691</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-14372</v>
       </c>
       <c r="B11" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -629,16 +629,19 @@
       <c r="E11" t="str">
         <v>approved</v>
       </c>
+      <c r="F11" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G11">
-        <v>45299</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-14372</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B12" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -653,58 +656,58 @@
         <v>PDF</v>
       </c>
       <c r="G12">
-        <v>45512</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B13" t="str">
-        <v>RAMP Phase 2</v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D13" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E13" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F13" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G13">
-        <v>45562</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B14" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D14" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E14" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F14" t="str">
+        <v>PDF</v>
       </c>
       <c r="G14">
-        <v>45695</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B15" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -719,15 +722,15 @@
         <v>PDF</v>
       </c>
       <c r="G15">
-        <v>45688</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B16" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -742,15 +745,15 @@
         <v>PDF</v>
       </c>
       <c r="G16">
-        <v>45701</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B17" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -761,139 +764,136 @@
       <c r="E17" t="str">
         <v>approved</v>
       </c>
-      <c r="F17" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G17">
-        <v>45695</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B18" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D18" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E18" t="str">
-        <v>approved</v>
+        <v>estimates</v>
       </c>
       <c r="G18">
-        <v>45706</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B19" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D19" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E19" t="str">
         <v>estimates</v>
       </c>
       <c r="G19">
-        <v>45623</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B20" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D20" t="str">
-        <v>FLCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E20" t="str">
         <v>estimates</v>
       </c>
       <c r="G20">
-        <v>45355</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B21" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D21" t="str">
-        <v>CorpSec</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E21" t="str">
         <v>estimates</v>
       </c>
       <c r="G21">
-        <v>45446</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B22" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D22" t="str">
-        <v>BSCM/ESCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E22" t="str">
         <v>estimates</v>
       </c>
       <c r="G22">
-        <v>45477</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B23" t="str">
-        <v>CSDM Upgrade</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D23" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E23" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G23">
-        <v>45394</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B24" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
@@ -905,15 +905,15 @@
         <v>ofs</v>
       </c>
       <c r="G24">
-        <v>45531</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B25" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
@@ -925,15 +925,15 @@
         <v>ofs</v>
       </c>
       <c r="G25">
-        <v>45453</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B26" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
@@ -942,98 +942,95 @@
         <v>FLCM</v>
       </c>
       <c r="E26" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G26">
-        <v>45461</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B27" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D27" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E27" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G27">
-        <v>45714</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-15822</v>
       </c>
       <c r="B28" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D28" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E28" t="str">
         <v>estimates</v>
       </c>
       <c r="G28">
-        <v>45686</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-15822</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B29" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>FLCM</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E29" t="str">
         <v>estimates</v>
       </c>
       <c r="G29">
-        <v>45650</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-17853</v>
       </c>
       <c r="B30" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
       </c>
-      <c r="D30" t="str">
-        <v>BSCM/ESCM</v>
-      </c>
       <c r="E30" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G30">
-        <v>45541</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-17853</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B31" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
@@ -1042,15 +1039,15 @@
         <v>ofs</v>
       </c>
       <c r="G31">
-        <v>45691</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B32" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
@@ -1059,15 +1056,15 @@
         <v>ofs</v>
       </c>
       <c r="G32">
-        <v>45559</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B33" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
@@ -1076,15 +1073,15 @@
         <v>ofs</v>
       </c>
       <c r="G33">
-        <v>45596</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B34" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
@@ -1093,15 +1090,15 @@
         <v>ofs</v>
       </c>
       <c r="G34">
-        <v>45378</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B35" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
@@ -1110,15 +1107,15 @@
         <v>ofs</v>
       </c>
       <c r="G35">
-        <v>45468</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B36" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
@@ -1127,15 +1124,15 @@
         <v>ofs</v>
       </c>
       <c r="G36">
-        <v>45310</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B37" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
@@ -1144,15 +1141,15 @@
         <v>ofs</v>
       </c>
       <c r="G37">
-        <v>45427</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B38" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
@@ -1161,15 +1158,15 @@
         <v>ofs</v>
       </c>
       <c r="G38">
-        <v>45279</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B39" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
@@ -1178,15 +1175,15 @@
         <v>ofs</v>
       </c>
       <c r="G39">
-        <v>45558</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B40" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
@@ -1195,15 +1192,15 @@
         <v>ofs</v>
       </c>
       <c r="G40">
-        <v>45383</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B41" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1212,15 +1209,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45638</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B42" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1229,15 +1226,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45461</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B43" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1251,10 +1248,10 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B44" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1263,15 +1260,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45371</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B45" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1280,15 +1277,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45406</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B46" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1297,15 +1294,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45364</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B47" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1314,15 +1311,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45593</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B48" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1331,15 +1328,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45408</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B49" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1348,15 +1345,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45595</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B50" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1365,15 +1362,15 @@
         <v>ofs</v>
       </c>
       <c r="G50">
-        <v>45392</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B51" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1387,27 +1384,27 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B52" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E52" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G52">
-        <v>45411</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-18725</v>
       </c>
       <c r="B53" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>US Video System - Lenel to Genetec</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1419,26 +1416,9 @@
         <v>45721</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="str">
-        <v>ENT-18725</v>
-      </c>
-      <c r="B54" t="str">
-        <v>US Video System - Lenel to Genetec</v>
-      </c>
-      <c r="C54" t="str">
-        <v>Invite to JRM</v>
-      </c>
-      <c r="E54" t="str">
-        <v>jrm</v>
-      </c>
-      <c r="G54">
-        <v>45721</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G54"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G53"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G52"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -469,10 +469,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ENT-17202</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B4" t="str">
-        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C4" t="str">
         <v>Invite to JRM</v>
@@ -481,18 +481,21 @@
         <v>FLCM</v>
       </c>
       <c r="E4" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F4" t="str">
+        <v>PDF</v>
       </c>
       <c r="G4">
-        <v>45690</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B5" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C5" t="str">
         <v>Invite to JRM</v>
@@ -501,21 +504,18 @@
         <v>FLCM</v>
       </c>
       <c r="E5" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F5" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G5">
-        <v>45686</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B6" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C6" t="str">
         <v>Invite to JRM</v>
@@ -527,15 +527,15 @@
         <v>estimates</v>
       </c>
       <c r="G6">
-        <v>45700</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B7" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C7" t="str">
         <v>Invite to JRM</v>
@@ -547,15 +547,15 @@
         <v>estimates</v>
       </c>
       <c r="G7">
-        <v>45656</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-17054</v>
       </c>
       <c r="B8" t="str">
-        <v>Data Source to EDGE</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C8" t="str">
         <v>Invite to JRM</v>
@@ -564,18 +564,21 @@
         <v>FLCM</v>
       </c>
       <c r="E8" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F8" t="str">
+        <v>PDF</v>
       </c>
       <c r="G8">
-        <v>45664</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-17054</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B9" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -586,19 +589,16 @@
       <c r="E9" t="str">
         <v>approved</v>
       </c>
-      <c r="F9" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G9">
-        <v>45691</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-14372</v>
       </c>
       <c r="B10" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -609,16 +609,19 @@
       <c r="E10" t="str">
         <v>approved</v>
       </c>
+      <c r="F10" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G10">
-        <v>45299</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-14372</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B11" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -633,58 +636,58 @@
         <v>PDF</v>
       </c>
       <c r="G11">
-        <v>45512</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B12" t="str">
-        <v>RAMP Phase 2</v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D12" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E12" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F12" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G12">
-        <v>45562</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B13" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D13" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E13" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F13" t="str">
+        <v>PDF</v>
       </c>
       <c r="G13">
-        <v>45695</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B14" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -699,15 +702,15 @@
         <v>PDF</v>
       </c>
       <c r="G14">
-        <v>45688</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B15" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -722,15 +725,15 @@
         <v>PDF</v>
       </c>
       <c r="G15">
-        <v>45701</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B16" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -741,139 +744,136 @@
       <c r="E16" t="str">
         <v>approved</v>
       </c>
-      <c r="F16" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G16">
-        <v>45695</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B17" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D17" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E17" t="str">
-        <v>approved</v>
+        <v>estimates</v>
       </c>
       <c r="G17">
-        <v>45706</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B18" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D18" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E18" t="str">
         <v>estimates</v>
       </c>
       <c r="G18">
-        <v>45623</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B19" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D19" t="str">
-        <v>FLCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E19" t="str">
         <v>estimates</v>
       </c>
       <c r="G19">
-        <v>45355</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B20" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D20" t="str">
-        <v>CorpSec</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E20" t="str">
         <v>estimates</v>
       </c>
       <c r="G20">
-        <v>45446</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B21" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D21" t="str">
-        <v>BSCM/ESCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E21" t="str">
         <v>estimates</v>
       </c>
       <c r="G21">
-        <v>45477</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B22" t="str">
-        <v>CSDM Upgrade</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D22" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E22" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G22">
-        <v>45394</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B23" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
@@ -885,15 +885,15 @@
         <v>ofs</v>
       </c>
       <c r="G23">
-        <v>45531</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B24" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
@@ -905,15 +905,15 @@
         <v>ofs</v>
       </c>
       <c r="G24">
-        <v>45453</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B25" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
@@ -922,98 +922,95 @@
         <v>FLCM</v>
       </c>
       <c r="E25" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G25">
-        <v>45461</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B26" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D26" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E26" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G26">
-        <v>45714</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-15822</v>
       </c>
       <c r="B27" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D27" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E27" t="str">
         <v>estimates</v>
       </c>
       <c r="G27">
-        <v>45686</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-15822</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B28" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D28" t="str">
-        <v>FLCM</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E28" t="str">
         <v>estimates</v>
       </c>
       <c r="G28">
-        <v>45650</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-17853</v>
       </c>
       <c r="B29" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
-      <c r="D29" t="str">
-        <v>BSCM/ESCM</v>
-      </c>
       <c r="E29" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G29">
-        <v>45541</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-17853</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B30" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
@@ -1022,15 +1019,15 @@
         <v>ofs</v>
       </c>
       <c r="G30">
-        <v>45691</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B31" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
@@ -1039,15 +1036,15 @@
         <v>ofs</v>
       </c>
       <c r="G31">
-        <v>45559</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B32" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
@@ -1056,15 +1053,15 @@
         <v>ofs</v>
       </c>
       <c r="G32">
-        <v>45596</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B33" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
@@ -1073,15 +1070,15 @@
         <v>ofs</v>
       </c>
       <c r="G33">
-        <v>45378</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B34" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
@@ -1090,15 +1087,15 @@
         <v>ofs</v>
       </c>
       <c r="G34">
-        <v>45468</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B35" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
@@ -1107,15 +1104,15 @@
         <v>ofs</v>
       </c>
       <c r="G35">
-        <v>45310</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B36" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
@@ -1124,15 +1121,15 @@
         <v>ofs</v>
       </c>
       <c r="G36">
-        <v>45427</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B37" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
@@ -1141,15 +1138,15 @@
         <v>ofs</v>
       </c>
       <c r="G37">
-        <v>45279</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B38" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
@@ -1158,15 +1155,15 @@
         <v>ofs</v>
       </c>
       <c r="G38">
-        <v>45558</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B39" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
@@ -1175,15 +1172,15 @@
         <v>ofs</v>
       </c>
       <c r="G39">
-        <v>45383</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B40" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
@@ -1192,15 +1189,15 @@
         <v>ofs</v>
       </c>
       <c r="G40">
-        <v>45638</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B41" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1209,15 +1206,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45461</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B42" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1231,10 +1228,10 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B43" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1243,15 +1240,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45371</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B44" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1260,15 +1257,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45406</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B45" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1277,15 +1274,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45364</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B46" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1294,15 +1291,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45593</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B47" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1311,15 +1308,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45408</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B48" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1328,15 +1325,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45595</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B49" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1345,15 +1342,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45392</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B50" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1367,27 +1364,27 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B51" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E51" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G51">
-        <v>45411</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-18725</v>
       </c>
       <c r="B52" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>US Video System - Lenel to Genetec</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1399,26 +1396,9 @@
         <v>45721</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="str">
-        <v>ENT-18725</v>
-      </c>
-      <c r="B53" t="str">
-        <v>US Video System - Lenel to Genetec</v>
-      </c>
-      <c r="C53" t="str">
-        <v>Invite to JRM</v>
-      </c>
-      <c r="E53" t="str">
-        <v>jrm</v>
-      </c>
-      <c r="G53">
-        <v>45721</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G53"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G52"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -2160,74 +2160,20 @@
       <c r="A8" t="str">
         <v>ENT-18364</v>
       </c>
-      <c r="B8">
-        <v>1384999</v>
-      </c>
-      <c r="C8">
-        <v>50000</v>
-      </c>
-      <c r="D8">
-        <v>1113047</v>
-      </c>
-      <c r="E8">
-        <v>992739</v>
-      </c>
-      <c r="F8">
-        <v>248185</v>
-      </c>
-      <c r="G8">
-        <v>375</v>
-      </c>
-      <c r="H8">
-        <v>372900</v>
-      </c>
-      <c r="I8">
-        <v>22.3</v>
-      </c>
-      <c r="J8">
-        <v>26</v>
-      </c>
-      <c r="K8">
-        <v>656</v>
-      </c>
-      <c r="L8">
-        <v>633844</v>
-      </c>
-      <c r="M8">
-        <v>39.1</v>
-      </c>
-      <c r="N8">
-        <v>44.2</v>
-      </c>
-      <c r="O8">
-        <v>488</v>
-      </c>
-      <c r="P8">
-        <v>234180</v>
-      </c>
-      <c r="Q8">
-        <v>29.1</v>
-      </c>
-      <c r="R8">
-        <v>16.3</v>
-      </c>
-      <c r="T8">
-        <v>50000</v>
-      </c>
-      <c r="V8">
-        <v>3</v>
-      </c>
-      <c r="W8">
+      <c r="B8" t="str">
+        <v>Control of the group</v>
+      </c>
+      <c r="C8" t="str">
         <v>159</v>
       </c>
-      <c r="X8">
-        <v>144075</v>
-      </c>
-      <c r="Y8">
-        <v>9.5</v>
-      </c>
-      <c r="Z8">
-        <v>10</v>
+      <c r="D8" t="str">
+        <v>$144075</v>
+      </c>
+      <c r="E8" t="str">
+        <v>9.50%</v>
+      </c>
+      <c r="F8" t="str">
+        <v>10.00%</v>
       </c>
     </row>
   </sheetData>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -2161,19 +2161,82 @@
         <v>ENT-18364</v>
       </c>
       <c r="B8" t="str">
-        <v>Control of the group</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C8" t="str">
-        <v>159</v>
+        <v>-</v>
       </c>
       <c r="D8" t="str">
-        <v>$144075</v>
+        <v>1609</v>
       </c>
       <c r="E8" t="str">
+        <v>-</v>
+      </c>
+      <c r="F8" t="str">
         <v>9.50%</v>
       </c>
-      <c r="F8" t="str">
+      <c r="G8" t="str">
         <v>10.00%</v>
+      </c>
+      <c r="H8" t="str">
+        <v>-</v>
+      </c>
+      <c r="I8" t="str">
+        <v>-</v>
+      </c>
+      <c r="J8" t="str">
+        <v>-</v>
+      </c>
+      <c r="K8" t="str">
+        <v>-</v>
+      </c>
+      <c r="L8" t="str">
+        <v>-</v>
+      </c>
+      <c r="M8" t="str">
+        <v>-</v>
+      </c>
+      <c r="N8" t="str">
+        <v>-</v>
+      </c>
+      <c r="O8" t="str">
+        <v>-</v>
+      </c>
+      <c r="P8" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q8" t="str">
+        <v>-</v>
+      </c>
+      <c r="R8" t="str">
+        <v>-</v>
+      </c>
+      <c r="S8" t="str">
+        <v>-</v>
+      </c>
+      <c r="T8" t="str">
+        <v>-</v>
+      </c>
+      <c r="U8" t="str">
+        <v>-</v>
+      </c>
+      <c r="V8" t="str">
+        <v>-</v>
+      </c>
+      <c r="W8" t="str">
+        <v>-</v>
+      </c>
+      <c r="X8" t="str">
+        <v>-</v>
+      </c>
+      <c r="Y8" t="str">
+        <v>-</v>
+      </c>
+      <c r="Z8" t="str">
+        <v>-</v>
+      </c>
+      <c r="AA8" t="str">
+        <v>-</v>
       </c>
     </row>
   </sheetData>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -2080,74 +2080,80 @@
       <c r="A7" t="str">
         <v>ENT-14372</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="str">
         <v>244153</v>
       </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
+      <c r="C7" t="str">
+        <v>-</v>
+      </c>
+      <c r="D7" t="str">
+        <v>-</v>
+      </c>
+      <c r="E7" t="str">
+        <v>-</v>
+      </c>
+      <c r="F7" t="str">
+        <v>-</v>
+      </c>
+      <c r="G7" t="str">
+        <v>-</v>
+      </c>
+      <c r="H7" t="str">
+        <v>-</v>
+      </c>
+      <c r="I7" t="str">
+        <v>-</v>
+      </c>
+      <c r="J7" t="str">
+        <v>-</v>
+      </c>
+      <c r="K7" t="str">
         <v>165</v>
       </c>
-      <c r="L7">
-        <v>127692</v>
-      </c>
-      <c r="M7">
-        <v>46.8</v>
-      </c>
-      <c r="N7">
-        <v>52.3</v>
-      </c>
-      <c r="O7">
+      <c r="L7" t="str">
+        <v>$127692</v>
+      </c>
+      <c r="M7" t="str">
+        <v>46.80%</v>
+      </c>
+      <c r="N7" t="str">
+        <v>52.30%</v>
+      </c>
+      <c r="O7" t="str">
         <v>147</v>
       </c>
-      <c r="P7">
-        <v>79763</v>
-      </c>
-      <c r="Q7">
-        <v>41.7</v>
-      </c>
-      <c r="R7">
-        <v>32.7</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
-      <c r="W7">
+      <c r="P7" t="str">
+        <v>$79763</v>
+      </c>
+      <c r="Q7" t="str">
+        <v>41.70%</v>
+      </c>
+      <c r="R7" t="str">
+        <v>32.70%</v>
+      </c>
+      <c r="S7" t="str">
+        <v>-</v>
+      </c>
+      <c r="T7" t="str">
+        <v>-</v>
+      </c>
+      <c r="U7" t="str">
+        <v>-</v>
+      </c>
+      <c r="V7" t="str">
+        <v>-</v>
+      </c>
+      <c r="W7" t="str">
         <v>41</v>
       </c>
-      <c r="X7">
-        <v>36698</v>
-      </c>
-      <c r="Y7">
-        <v>11.5</v>
-      </c>
-      <c r="Z7">
-        <v>15</v>
+      <c r="X7" t="str">
+        <v>$36698</v>
+      </c>
+      <c r="Y7" t="str">
+        <v>11.50%</v>
+      </c>
+      <c r="Z7" t="str">
+        <v>15.00%</v>
       </c>
     </row>
     <row r="8">

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -1778,77 +1778,80 @@
       <c r="A3" t="str">
         <v>ENT-17213</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="str">
         <v>703188</v>
       </c>
-      <c r="C3">
-        <v>67500</v>
-      </c>
-      <c r="E3">
-        <v>425495</v>
-      </c>
-      <c r="F3">
+      <c r="C3" t="str">
+        <v>1324</v>
+      </c>
+      <c r="D3" t="str">
+        <v>-</v>
+      </c>
+      <c r="E3" t="str">
+        <v>4324</v>
+      </c>
+      <c r="F3" t="str">
         <v>106374</v>
       </c>
-      <c r="G3">
+      <c r="G3" t="str">
         <v>159</v>
       </c>
-      <c r="H3">
-        <v>157861</v>
-      </c>
-      <c r="I3">
-        <v>14</v>
-      </c>
-      <c r="J3">
-        <v>20.5</v>
-      </c>
-      <c r="K3">
+      <c r="H3" t="str">
+        <v>$157861</v>
+      </c>
+      <c r="I3" t="str">
+        <v>120%</v>
+      </c>
+      <c r="J3" t="str">
+        <v>20.50%</v>
+      </c>
+      <c r="K3" t="str">
         <v>598</v>
       </c>
-      <c r="L3">
-        <v>308479</v>
-      </c>
-      <c r="M3">
-        <v>52.8</v>
-      </c>
-      <c r="N3">
-        <v>40</v>
-      </c>
-      <c r="O3">
+      <c r="L3" t="str">
+        <v>$308479</v>
+      </c>
+      <c r="M3" t="str">
+        <v>52.80%</v>
+      </c>
+      <c r="N3" t="str">
+        <v>40.00%</v>
+      </c>
+      <c r="O3" t="str">
         <v>303</v>
       </c>
-      <c r="P3">
-        <v>158200</v>
-      </c>
-      <c r="Q3">
-        <v>26.7</v>
-      </c>
-      <c r="R3">
-        <v>20.5</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>50000</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3">
-        <v>0</v>
-      </c>
-      <c r="W3">
+      <c r="P3" t="str">
+        <v>$158200</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>26.70%</v>
+      </c>
+      <c r="R3" t="str">
+        <v>20.50%</v>
+      </c>
+      <c r="S3" t="str">
+        <v>-</v>
+      </c>
+      <c r="T3" t="str">
+        <v>$50000</v>
+      </c>
+      <c r="U3" t="str">
+        <v>-</v>
+      </c>
+      <c r="V3" t="str">
+        <v>-</v>
+      </c>
+      <c r="W3" t="str">
         <v>73</v>
       </c>
-      <c r="X3">
-        <v>78648</v>
-      </c>
-      <c r="Y3">
-        <v>6.4</v>
-      </c>
-      <c r="Z3">
-        <v>10.2</v>
+      <c r="X3" t="str">
+        <v>$78648</v>
+      </c>
+      <c r="Y3" t="str">
+        <v>6.40%</v>
+      </c>
+      <c r="Z3" t="str">
+        <v>10.20%</v>
       </c>
     </row>
     <row r="4">

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -1791,13 +1791,13 @@
         <v>425495</v>
       </c>
       <c r="F3" t="str">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="G3" t="str">
-        <v>$157861</v>
+        <v>$14.00%</v>
       </c>
       <c r="H3" t="str">
-        <v>14.00%</v>
+        <v>20.50%</v>
       </c>
       <c r="I3" t="str">
         <v>20.50%</v>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -1791,10 +1791,10 @@
         <v>425495</v>
       </c>
       <c r="F3" t="str">
-        <v>200</v>
+        <v>-</v>
       </c>
       <c r="G3" t="str">
-        <v>$14.00%</v>
+        <v>123%</v>
       </c>
       <c r="H3" t="str">
         <v>20.50%</v>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -1794,10 +1794,10 @@
         <v>-</v>
       </c>
       <c r="G3" t="str">
-        <v>123%</v>
+        <v>$20.50</v>
       </c>
       <c r="H3" t="str">
-        <v>20.50%</v>
+        <v>1234%</v>
       </c>
       <c r="I3" t="str">
         <v>20.50%</v>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -1791,13 +1791,13 @@
         <v>425495</v>
       </c>
       <c r="F3" t="str">
-        <v>-</v>
+        <v>1234</v>
       </c>
       <c r="G3" t="str">
-        <v>$20.50</v>
+        <v>$12345</v>
       </c>
       <c r="H3" t="str">
-        <v>1234%</v>
+        <v>20.50%</v>
       </c>
       <c r="I3" t="str">
         <v>20.50%</v>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -1791,10 +1791,10 @@
         <v>425495</v>
       </c>
       <c r="F3" t="str">
-        <v>1234</v>
+        <v>-</v>
       </c>
       <c r="G3" t="str">
-        <v>$12345</v>
+        <v>$1234</v>
       </c>
       <c r="H3" t="str">
         <v>20.50%</v>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -1800,7 +1800,7 @@
         <v>14.00</v>
       </c>
       <c r="J3" t="str">
-        <v>20.50</v>
+        <v>200</v>
       </c>
       <c r="K3">
         <v>598</v>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -1791,7 +1791,7 @@
         <v>106374</v>
       </c>
       <c r="G3" t="str">
-        <v>160</v>
+        <v>700</v>
       </c>
       <c r="H3" t="str">
         <v>157861</v>
@@ -1800,7 +1800,7 @@
         <v>14.00</v>
       </c>
       <c r="J3" t="str">
-        <v>200</v>
+        <v>200.00</v>
       </c>
       <c r="K3">
         <v>598</v>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -1713,17 +1713,17 @@
       <c r="F2">
         <v>59466</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="str">
         <v>90</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="str">
         <v>83903</v>
       </c>
-      <c r="I2">
-        <v>38.7</v>
-      </c>
-      <c r="J2">
-        <v>46.4</v>
+      <c r="I2" t="str">
+        <v>38.70</v>
+      </c>
+      <c r="J2" t="str">
+        <v>46.40</v>
       </c>
       <c r="K2">
         <v>68</v>
@@ -1749,17 +1749,17 @@
       <c r="R2">
         <v>20.6</v>
       </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2">
+      <c r="S2" t="str">
+        <v>-</v>
+      </c>
+      <c r="T2" t="str">
         <v>2500</v>
       </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
-      <c r="V2">
-        <v>1</v>
+      <c r="U2" t="str">
+        <v>-</v>
+      </c>
+      <c r="V2" t="str">
+        <v>100.34</v>
       </c>
       <c r="W2">
         <v>0</v>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -1714,7 +1714,7 @@
         <v>59466</v>
       </c>
       <c r="G2" t="str">
-        <v>90</v>
+        <v>900</v>
       </c>
       <c r="H2" t="str">
         <v>83903</v>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G61"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -469,10 +469,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ENT-16881</v>
+        <v>ENT-16700</v>
       </c>
       <c r="B4" t="str">
-        <v>Split up Personal Overdraft P&amp;L</v>
+        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
       </c>
       <c r="C4" t="str">
         <v>Invite to JRM</v>
@@ -484,15 +484,15 @@
         <v>jrm</v>
       </c>
       <c r="G4">
-        <v>45929</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ENT-16700</v>
+        <v>ENT-16621</v>
       </c>
       <c r="B5" t="str">
-        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
+        <v>CIW Data Products to PROD</v>
       </c>
       <c r="C5" t="str">
         <v>Invite to JRM</v>
@@ -501,18 +501,18 @@
         <v>FLCM</v>
       </c>
       <c r="E5" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G5">
-        <v>45523</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ENT-16621</v>
+        <v>ENT-16374</v>
       </c>
       <c r="B6" t="str">
-        <v>CIW Data Products to PROD</v>
+        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
       </c>
       <c r="C6" t="str">
         <v>Invite to JRM</v>
@@ -521,18 +521,18 @@
         <v>FLCM</v>
       </c>
       <c r="E6" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G6">
-        <v>45596</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENT-16374</v>
+        <v>ENT-16031</v>
       </c>
       <c r="B7" t="str">
-        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
+        <v>Fraud - Notes generator</v>
       </c>
       <c r="C7" t="str">
         <v>Invite to JRM</v>
@@ -544,15 +544,15 @@
         <v>jrm</v>
       </c>
       <c r="G7">
-        <v>45455</v>
+        <v>45649</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENT-16031</v>
+        <v>ENT-15917</v>
       </c>
       <c r="B8" t="str">
-        <v>Fraud - Notes generator</v>
+        <v>REBO Bill Payment Investigation Requests</v>
       </c>
       <c r="C8" t="str">
         <v>Invite to JRM</v>
@@ -564,15 +564,15 @@
         <v>jrm</v>
       </c>
       <c r="G8">
-        <v>45649</v>
+        <v>45613</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-15917</v>
+        <v>ENT-17286</v>
       </c>
       <c r="B9" t="str">
-        <v>REBO Bill Payment Investigation Requests</v>
+        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -581,18 +581,18 @@
         <v>FLCM</v>
       </c>
       <c r="E9" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G9">
-        <v>45613</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-17286</v>
+        <v>ENT-17202</v>
       </c>
       <c r="B10" t="str">
-        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
+        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -601,18 +601,18 @@
         <v>FLCM</v>
       </c>
       <c r="E10" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G10">
-        <v>45699</v>
+        <v>45690</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-17202</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B11" t="str">
-        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -621,18 +621,21 @@
         <v>FLCM</v>
       </c>
       <c r="E11" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F11" t="str">
+        <v>PDF</v>
       </c>
       <c r="G11">
-        <v>45690</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B12" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -641,21 +644,18 @@
         <v>FLCM</v>
       </c>
       <c r="E12" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F12" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G12">
-        <v>45686</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B13" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -667,15 +667,15 @@
         <v>estimates</v>
       </c>
       <c r="G13">
-        <v>45700</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B14" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -687,15 +687,15 @@
         <v>estimates</v>
       </c>
       <c r="G14">
-        <v>45656</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B15" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -707,15 +707,15 @@
         <v>estimates</v>
       </c>
       <c r="G15">
-        <v>45588</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-17054</v>
       </c>
       <c r="B16" t="str">
-        <v>Data Source to EDGE</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -724,18 +724,21 @@
         <v>FLCM</v>
       </c>
       <c r="E16" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F16" t="str">
+        <v>PDF</v>
       </c>
       <c r="G16">
-        <v>45664</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ENT-17054</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B17" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -746,19 +749,16 @@
       <c r="E17" t="str">
         <v>approved</v>
       </c>
-      <c r="F17" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G17">
-        <v>45691</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-14372</v>
       </c>
       <c r="B18" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
@@ -769,16 +769,19 @@
       <c r="E18" t="str">
         <v>approved</v>
       </c>
+      <c r="F18" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G18">
-        <v>45299</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ENT-14372</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B19" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
@@ -793,58 +796,58 @@
         <v>PDF</v>
       </c>
       <c r="G19">
-        <v>45512</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B20" t="str">
-        <v>RAMP Phase 2</v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D20" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E20" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F20" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G20">
-        <v>45562</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B21" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D21" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E21" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F21" t="str">
+        <v>PDF</v>
       </c>
       <c r="G21">
-        <v>45695</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B22" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
@@ -859,15 +862,15 @@
         <v>PDF</v>
       </c>
       <c r="G22">
-        <v>45688</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B23" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
@@ -882,15 +885,15 @@
         <v>PDF</v>
       </c>
       <c r="G23">
-        <v>45701</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B24" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
@@ -901,19 +904,16 @@
       <c r="E24" t="str">
         <v>approved</v>
       </c>
-      <c r="F24" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G24">
-        <v>45695</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B25" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
@@ -922,138 +922,138 @@
         <v>FLCM</v>
       </c>
       <c r="E25" t="str">
-        <v>approved</v>
+        <v>estimates</v>
       </c>
       <c r="G25">
-        <v>45706</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B26" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D26" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E26" t="str">
         <v>estimates</v>
       </c>
       <c r="G26">
-        <v>45559</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B27" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D27" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E27" t="str">
         <v>estimates</v>
       </c>
       <c r="G27">
-        <v>45623</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B28" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D28" t="str">
-        <v>FLCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E28" t="str">
         <v>estimates</v>
       </c>
       <c r="G28">
-        <v>45355</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B29" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>CorpSec</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E29" t="str">
         <v>estimates</v>
       </c>
       <c r="G29">
-        <v>45446</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B30" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D30" t="str">
-        <v>BSCM/ESCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E30" t="str">
         <v>estimates</v>
       </c>
       <c r="G30">
-        <v>45477</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B31" t="str">
-        <v>CSDM Upgrade</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D31" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E31" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G31">
-        <v>45394</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B32" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
@@ -1065,15 +1065,15 @@
         <v>ofs</v>
       </c>
       <c r="G32">
-        <v>45531</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B33" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
@@ -1085,15 +1085,15 @@
         <v>ofs</v>
       </c>
       <c r="G33">
-        <v>45453</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B34" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
@@ -1102,98 +1102,95 @@
         <v>FLCM</v>
       </c>
       <c r="E34" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G34">
-        <v>45461</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B35" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D35" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E35" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G35">
-        <v>45714</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-15822</v>
       </c>
       <c r="B36" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D36" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E36" t="str">
         <v>estimates</v>
       </c>
       <c r="G36">
-        <v>45686</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ENT-15822</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B37" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D37" t="str">
-        <v>FLCM</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E37" t="str">
         <v>estimates</v>
       </c>
       <c r="G37">
-        <v>45650</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-17853</v>
       </c>
       <c r="B38" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
       </c>
-      <c r="D38" t="str">
-        <v>BSCM/ESCM</v>
-      </c>
       <c r="E38" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G38">
-        <v>45541</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ENT-17853</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B39" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
@@ -1202,15 +1199,15 @@
         <v>ofs</v>
       </c>
       <c r="G39">
-        <v>45691</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B40" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
@@ -1219,15 +1216,15 @@
         <v>ofs</v>
       </c>
       <c r="G40">
-        <v>45559</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B41" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1236,15 +1233,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45596</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B42" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1253,15 +1250,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45378</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B43" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1270,15 +1267,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45468</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B44" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1287,15 +1284,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45310</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B45" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1304,15 +1301,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45427</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B46" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1321,15 +1318,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45279</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B47" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1338,15 +1335,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45558</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B48" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1355,15 +1352,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45383</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B49" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1372,15 +1369,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45638</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B50" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1389,15 +1386,15 @@
         <v>ofs</v>
       </c>
       <c r="G50">
-        <v>45461</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B51" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1411,10 +1408,10 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B52" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1423,15 +1420,15 @@
         <v>ofs</v>
       </c>
       <c r="G52">
-        <v>45371</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B53" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1440,15 +1437,15 @@
         <v>ofs</v>
       </c>
       <c r="G53">
-        <v>45406</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B54" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1457,15 +1454,15 @@
         <v>ofs</v>
       </c>
       <c r="G54">
-        <v>45364</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B55" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1474,15 +1471,15 @@
         <v>ofs</v>
       </c>
       <c r="G55">
-        <v>45593</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B56" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1491,15 +1488,15 @@
         <v>ofs</v>
       </c>
       <c r="G56">
-        <v>45408</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B57" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
@@ -1508,15 +1505,15 @@
         <v>ofs</v>
       </c>
       <c r="G57">
-        <v>45595</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B58" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C58" t="str">
         <v>Invite to JRM</v>
@@ -1525,15 +1522,15 @@
         <v>ofs</v>
       </c>
       <c r="G58">
-        <v>45392</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B59" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C59" t="str">
         <v>Invite to JRM</v>
@@ -1547,27 +1544,27 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B60" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C60" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E60" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G60">
-        <v>45411</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-18725</v>
       </c>
       <c r="B61" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>US Video System - Lenel to Genetec</v>
       </c>
       <c r="C61" t="str">
         <v>Invite to JRM</v>
@@ -1579,36 +1576,9 @@
         <v>45721</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="str">
-        <v>ENT-18725</v>
-      </c>
-      <c r="B62" t="str">
-        <v>US Video System - Lenel to Genetec</v>
-      </c>
-      <c r="C62" t="str">
-        <v>Invite to JRM</v>
-      </c>
-      <c r="E62" t="str">
-        <v>jrm</v>
-      </c>
-      <c r="G62">
-        <v>45721</v>
-      </c>
-    </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="F12" r:id="rId1"/>
-    <hyperlink ref="F17" r:id="rId2"/>
-    <hyperlink ref="F19" r:id="rId3"/>
-    <hyperlink ref="F20" r:id="rId4"/>
-    <hyperlink ref="F22" r:id="rId5"/>
-    <hyperlink ref="F23" r:id="rId6"/>
-    <hyperlink ref="F24" r:id="rId7"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G62"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G61"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -1748,16 +1748,19 @@
       <c r="A3" t="str">
         <v>ENT-17213</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="str">
         <v>703188</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="str">
         <v>67500</v>
       </c>
-      <c r="E3">
+      <c r="D3" t="str">
+        <v>-</v>
+      </c>
+      <c r="E3" t="str">
         <v>425495</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="str">
         <v>106374</v>
       </c>
       <c r="G3" t="str">
@@ -1772,53 +1775,53 @@
       <c r="J3" t="str">
         <v>200.00</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="str">
         <v>598</v>
       </c>
-      <c r="L3">
+      <c r="L3" t="str">
         <v>308479</v>
       </c>
-      <c r="M3">
-        <v>52.8</v>
-      </c>
-      <c r="N3">
-        <v>40</v>
-      </c>
-      <c r="O3">
+      <c r="M3" t="str">
+        <v>52.80</v>
+      </c>
+      <c r="N3" t="str">
+        <v>40.00</v>
+      </c>
+      <c r="O3" t="str">
         <v>303</v>
       </c>
-      <c r="P3">
+      <c r="P3" t="str">
         <v>158200</v>
       </c>
-      <c r="Q3">
-        <v>26.7</v>
-      </c>
-      <c r="R3">
-        <v>20.5</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>50000</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3">
-        <v>0</v>
-      </c>
-      <c r="W3">
+      <c r="Q3" t="str">
+        <v>26.70</v>
+      </c>
+      <c r="R3" t="str">
+        <v>20.50</v>
+      </c>
+      <c r="S3" t="str">
+        <v>-</v>
+      </c>
+      <c r="T3" t="str">
+        <v>34</v>
+      </c>
+      <c r="U3" t="str">
+        <v>-</v>
+      </c>
+      <c r="V3" t="str">
+        <v>-</v>
+      </c>
+      <c r="W3" t="str">
         <v>73</v>
       </c>
-      <c r="X3">
+      <c r="X3" t="str">
         <v>78648</v>
       </c>
-      <c r="Y3">
-        <v>6.4</v>
-      </c>
-      <c r="Z3">
-        <v>10.2</v>
+      <c r="Y3" t="str">
+        <v>6.40</v>
+      </c>
+      <c r="Z3" t="str">
+        <v>10.20</v>
       </c>
     </row>
     <row r="4">

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G60"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -429,10 +429,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ENT-17062</v>
+        <v>ENT-16949</v>
       </c>
       <c r="B2" t="str">
-        <v>Account Open Enhancements and Outcome Orchestration</v>
+        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
       </c>
       <c r="C2" t="str">
         <v>Invite to JRM</v>
@@ -441,18 +441,18 @@
         <v>FLCM</v>
       </c>
       <c r="E2" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G2">
-        <v>45672</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ENT-16949</v>
+        <v>ENT-16700</v>
       </c>
       <c r="B3" t="str">
-        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
+        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
       </c>
       <c r="C3" t="str">
         <v>Invite to JRM</v>
@@ -461,18 +461,18 @@
         <v>FLCM</v>
       </c>
       <c r="E3" t="str">
-        <v>estimates</v>
+        <v>jrm</v>
       </c>
       <c r="G3">
-        <v>45531</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ENT-16700</v>
+        <v>ENT-16621</v>
       </c>
       <c r="B4" t="str">
-        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
+        <v>CIW Data Products to PROD</v>
       </c>
       <c r="C4" t="str">
         <v>Invite to JRM</v>
@@ -481,18 +481,18 @@
         <v>FLCM</v>
       </c>
       <c r="E4" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G4">
-        <v>45523</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ENT-16621</v>
+        <v>ENT-16374</v>
       </c>
       <c r="B5" t="str">
-        <v>CIW Data Products to PROD</v>
+        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
       </c>
       <c r="C5" t="str">
         <v>Invite to JRM</v>
@@ -501,18 +501,18 @@
         <v>FLCM</v>
       </c>
       <c r="E5" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G5">
-        <v>45596</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ENT-16374</v>
+        <v>ENT-16031</v>
       </c>
       <c r="B6" t="str">
-        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
+        <v>Fraud - Notes generator</v>
       </c>
       <c r="C6" t="str">
         <v>Invite to JRM</v>
@@ -524,15 +524,15 @@
         <v>jrm</v>
       </c>
       <c r="G6">
-        <v>45455</v>
+        <v>45649</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENT-16031</v>
+        <v>ENT-15917</v>
       </c>
       <c r="B7" t="str">
-        <v>Fraud - Notes generator</v>
+        <v>REBO Bill Payment Investigation Requests</v>
       </c>
       <c r="C7" t="str">
         <v>Invite to JRM</v>
@@ -544,15 +544,15 @@
         <v>jrm</v>
       </c>
       <c r="G7">
-        <v>45649</v>
+        <v>45613</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENT-15917</v>
+        <v>ENT-17286</v>
       </c>
       <c r="B8" t="str">
-        <v>REBO Bill Payment Investigation Requests</v>
+        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
       </c>
       <c r="C8" t="str">
         <v>Invite to JRM</v>
@@ -561,18 +561,18 @@
         <v>FLCM</v>
       </c>
       <c r="E8" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G8">
-        <v>45613</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-17286</v>
+        <v>ENT-17202</v>
       </c>
       <c r="B9" t="str">
-        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
+        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -581,18 +581,18 @@
         <v>FLCM</v>
       </c>
       <c r="E9" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G9">
-        <v>45699</v>
+        <v>45690</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-17202</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B10" t="str">
-        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -601,18 +601,21 @@
         <v>FLCM</v>
       </c>
       <c r="E10" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F10" t="str">
+        <v>PDF</v>
       </c>
       <c r="G10">
-        <v>45690</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B11" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -621,21 +624,18 @@
         <v>FLCM</v>
       </c>
       <c r="E11" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F11" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G11">
-        <v>45686</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B12" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -647,15 +647,15 @@
         <v>estimates</v>
       </c>
       <c r="G12">
-        <v>45700</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B13" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -667,15 +667,15 @@
         <v>estimates</v>
       </c>
       <c r="G13">
-        <v>45656</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B14" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -687,15 +687,15 @@
         <v>estimates</v>
       </c>
       <c r="G14">
-        <v>45588</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-17054</v>
       </c>
       <c r="B15" t="str">
-        <v>Data Source to EDGE</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -704,18 +704,21 @@
         <v>FLCM</v>
       </c>
       <c r="E15" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F15" t="str">
+        <v>PDF</v>
       </c>
       <c r="G15">
-        <v>45664</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-17054</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B16" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -726,19 +729,16 @@
       <c r="E16" t="str">
         <v>approved</v>
       </c>
-      <c r="F16" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G16">
-        <v>45691</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-14372</v>
       </c>
       <c r="B17" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -749,16 +749,19 @@
       <c r="E17" t="str">
         <v>approved</v>
       </c>
+      <c r="F17" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G17">
-        <v>45299</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ENT-14372</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B18" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
@@ -773,58 +776,58 @@
         <v>PDF</v>
       </c>
       <c r="G18">
-        <v>45512</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B19" t="str">
-        <v>RAMP Phase 2</v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D19" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E19" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F19" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G19">
-        <v>45562</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B20" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D20" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E20" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F20" t="str">
+        <v>PDF</v>
       </c>
       <c r="G20">
-        <v>45695</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B21" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
@@ -839,15 +842,15 @@
         <v>PDF</v>
       </c>
       <c r="G21">
-        <v>45688</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B22" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
@@ -862,15 +865,15 @@
         <v>PDF</v>
       </c>
       <c r="G22">
-        <v>45701</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B23" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
@@ -881,19 +884,16 @@
       <c r="E23" t="str">
         <v>approved</v>
       </c>
-      <c r="F23" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G23">
-        <v>45695</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B24" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
@@ -902,138 +902,138 @@
         <v>FLCM</v>
       </c>
       <c r="E24" t="str">
-        <v>approved</v>
+        <v>estimates</v>
       </c>
       <c r="G24">
-        <v>45706</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B25" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D25" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E25" t="str">
         <v>estimates</v>
       </c>
       <c r="G25">
-        <v>45559</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B26" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D26" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E26" t="str">
         <v>estimates</v>
       </c>
       <c r="G26">
-        <v>45623</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B27" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D27" t="str">
-        <v>FLCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E27" t="str">
         <v>estimates</v>
       </c>
       <c r="G27">
-        <v>45355</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B28" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D28" t="str">
-        <v>CorpSec</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E28" t="str">
         <v>estimates</v>
       </c>
       <c r="G28">
-        <v>45446</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B29" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>BSCM/ESCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E29" t="str">
         <v>estimates</v>
       </c>
       <c r="G29">
-        <v>45477</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B30" t="str">
-        <v>CSDM Upgrade</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D30" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E30" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G30">
-        <v>45394</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B31" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
@@ -1045,15 +1045,15 @@
         <v>ofs</v>
       </c>
       <c r="G31">
-        <v>45531</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B32" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
@@ -1065,15 +1065,15 @@
         <v>ofs</v>
       </c>
       <c r="G32">
-        <v>45453</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B33" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
@@ -1082,98 +1082,95 @@
         <v>FLCM</v>
       </c>
       <c r="E33" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G33">
-        <v>45461</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B34" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D34" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E34" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G34">
-        <v>45714</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-15822</v>
       </c>
       <c r="B35" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D35" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E35" t="str">
         <v>estimates</v>
       </c>
       <c r="G35">
-        <v>45686</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-15822</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B36" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D36" t="str">
-        <v>FLCM</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E36" t="str">
         <v>estimates</v>
       </c>
       <c r="G36">
-        <v>45650</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-17853</v>
       </c>
       <c r="B37" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
       </c>
-      <c r="D37" t="str">
-        <v>BSCM/ESCM</v>
-      </c>
       <c r="E37" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G37">
-        <v>45541</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ENT-17853</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B38" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
@@ -1182,15 +1179,15 @@
         <v>ofs</v>
       </c>
       <c r="G38">
-        <v>45691</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B39" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
@@ -1199,15 +1196,15 @@
         <v>ofs</v>
       </c>
       <c r="G39">
-        <v>45559</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B40" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
@@ -1216,15 +1213,15 @@
         <v>ofs</v>
       </c>
       <c r="G40">
-        <v>45596</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B41" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1233,15 +1230,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45378</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B42" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1250,15 +1247,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45468</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B43" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1267,15 +1264,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45310</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B44" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1284,15 +1281,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45427</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B45" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1301,15 +1298,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45279</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B46" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1318,15 +1315,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45558</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B47" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1335,15 +1332,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45383</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B48" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1352,15 +1349,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45638</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B49" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1369,15 +1366,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45461</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B50" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1391,10 +1388,10 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B51" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1403,15 +1400,15 @@
         <v>ofs</v>
       </c>
       <c r="G51">
-        <v>45371</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B52" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1420,15 +1417,15 @@
         <v>ofs</v>
       </c>
       <c r="G52">
-        <v>45406</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B53" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1437,15 +1434,15 @@
         <v>ofs</v>
       </c>
       <c r="G53">
-        <v>45364</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B54" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1454,15 +1451,15 @@
         <v>ofs</v>
       </c>
       <c r="G54">
-        <v>45593</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B55" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1471,15 +1468,15 @@
         <v>ofs</v>
       </c>
       <c r="G55">
-        <v>45408</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B56" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1488,15 +1485,15 @@
         <v>ofs</v>
       </c>
       <c r="G56">
-        <v>45595</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B57" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
@@ -1505,15 +1502,15 @@
         <v>ofs</v>
       </c>
       <c r="G57">
-        <v>45392</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B58" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C58" t="str">
         <v>Invite to JRM</v>
@@ -1527,27 +1524,27 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B59" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C59" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E59" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G59">
-        <v>45411</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-18725</v>
       </c>
       <c r="B60" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>US Video System - Lenel to Genetec</v>
       </c>
       <c r="C60" t="str">
         <v>Invite to JRM</v>
@@ -1559,26 +1556,9 @@
         <v>45721</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="str">
-        <v>ENT-18725</v>
-      </c>
-      <c r="B61" t="str">
-        <v>US Video System - Lenel to Genetec</v>
-      </c>
-      <c r="C61" t="str">
-        <v>Invite to JRM</v>
-      </c>
-      <c r="E61" t="str">
-        <v>jrm</v>
-      </c>
-      <c r="G61">
-        <v>45721</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G60"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G61"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -429,30 +429,33 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ENT-16949</v>
+        <v>23434</v>
       </c>
       <c r="B2" t="str">
-        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
+        <v>324234</v>
       </c>
       <c r="C2" t="str">
-        <v>Invite to JRM</v>
+        <v>324234</v>
       </c>
       <c r="D2" t="str">
-        <v>FLCM</v>
+        <v>324234</v>
       </c>
       <c r="E2" t="str">
-        <v>estimates</v>
-      </c>
-      <c r="G2">
-        <v>45531</v>
+        <v>jrm</v>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v>2025-03-15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ENT-16700</v>
+        <v>ENT-16949</v>
       </c>
       <c r="B3" t="str">
-        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
+        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
       </c>
       <c r="C3" t="str">
         <v>Invite to JRM</v>
@@ -461,18 +464,18 @@
         <v>FLCM</v>
       </c>
       <c r="E3" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G3">
-        <v>45523</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ENT-16621</v>
+        <v>ENT-16700</v>
       </c>
       <c r="B4" t="str">
-        <v>CIW Data Products to PROD</v>
+        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
       </c>
       <c r="C4" t="str">
         <v>Invite to JRM</v>
@@ -481,18 +484,18 @@
         <v>FLCM</v>
       </c>
       <c r="E4" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G4">
-        <v>45596</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ENT-16374</v>
+        <v>ENT-16621</v>
       </c>
       <c r="B5" t="str">
-        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
+        <v>CIW Data Products to PROD</v>
       </c>
       <c r="C5" t="str">
         <v>Invite to JRM</v>
@@ -501,18 +504,18 @@
         <v>FLCM</v>
       </c>
       <c r="E5" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G5">
-        <v>45455</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ENT-16031</v>
+        <v>ENT-16374</v>
       </c>
       <c r="B6" t="str">
-        <v>Fraud - Notes generator</v>
+        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
       </c>
       <c r="C6" t="str">
         <v>Invite to JRM</v>
@@ -524,15 +527,15 @@
         <v>jrm</v>
       </c>
       <c r="G6">
-        <v>45649</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENT-15917</v>
+        <v>ENT-16031</v>
       </c>
       <c r="B7" t="str">
-        <v>REBO Bill Payment Investigation Requests</v>
+        <v>Fraud - Notes generator</v>
       </c>
       <c r="C7" t="str">
         <v>Invite to JRM</v>
@@ -544,15 +547,15 @@
         <v>jrm</v>
       </c>
       <c r="G7">
-        <v>45613</v>
+        <v>45649</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENT-17286</v>
+        <v>ENT-15917</v>
       </c>
       <c r="B8" t="str">
-        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
+        <v>REBO Bill Payment Investigation Requests</v>
       </c>
       <c r="C8" t="str">
         <v>Invite to JRM</v>
@@ -561,18 +564,18 @@
         <v>FLCM</v>
       </c>
       <c r="E8" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G8">
-        <v>45699</v>
+        <v>45613</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-17202</v>
+        <v>ENT-17286</v>
       </c>
       <c r="B9" t="str">
-        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
+        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -581,18 +584,18 @@
         <v>FLCM</v>
       </c>
       <c r="E9" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G9">
-        <v>45690</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17202</v>
       </c>
       <c r="B10" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -601,21 +604,18 @@
         <v>FLCM</v>
       </c>
       <c r="E10" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F10" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G10">
-        <v>45686</v>
+        <v>45690</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B11" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -624,18 +624,21 @@
         <v>FLCM</v>
       </c>
       <c r="E11" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F11" t="str">
+        <v>PDF</v>
       </c>
       <c r="G11">
-        <v>45700</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B12" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -647,15 +650,15 @@
         <v>estimates</v>
       </c>
       <c r="G12">
-        <v>45656</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B13" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -667,15 +670,15 @@
         <v>estimates</v>
       </c>
       <c r="G13">
-        <v>45588</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B14" t="str">
-        <v>Data Source to EDGE</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -687,15 +690,15 @@
         <v>estimates</v>
       </c>
       <c r="G14">
-        <v>45664</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-17054</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B15" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -704,21 +707,18 @@
         <v>FLCM</v>
       </c>
       <c r="E15" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F15" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G15">
-        <v>45691</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-17054</v>
       </c>
       <c r="B16" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -729,16 +729,19 @@
       <c r="E16" t="str">
         <v>approved</v>
       </c>
+      <c r="F16" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G16">
-        <v>45299</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ENT-14372</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B17" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -749,19 +752,16 @@
       <c r="E17" t="str">
         <v>approved</v>
       </c>
-      <c r="F17" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G17">
-        <v>45512</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-14372</v>
       </c>
       <c r="B18" t="str">
-        <v>RAMP Phase 2</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
@@ -776,58 +776,58 @@
         <v>PDF</v>
       </c>
       <c r="G18">
-        <v>45562</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B19" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D19" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E19" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F19" t="str">
+        <v>PDF</v>
       </c>
       <c r="G19">
-        <v>45695</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B20" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D20" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E20" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F20" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G20">
-        <v>45688</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B21" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
@@ -842,15 +842,15 @@
         <v>PDF</v>
       </c>
       <c r="G21">
-        <v>45701</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B22" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
@@ -865,15 +865,15 @@
         <v>PDF</v>
       </c>
       <c r="G22">
-        <v>45695</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B23" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
@@ -884,16 +884,19 @@
       <c r="E23" t="str">
         <v>approved</v>
       </c>
+      <c r="F23" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G23">
-        <v>45706</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B24" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
@@ -902,138 +905,138 @@
         <v>FLCM</v>
       </c>
       <c r="E24" t="str">
-        <v>estimates</v>
+        <v>approved</v>
       </c>
       <c r="G24">
-        <v>45559</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B25" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D25" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E25" t="str">
         <v>estimates</v>
       </c>
       <c r="G25">
-        <v>45623</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B26" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D26" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E26" t="str">
         <v>estimates</v>
       </c>
       <c r="G26">
-        <v>45355</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B27" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D27" t="str">
-        <v>CorpSec</v>
+        <v>FLCM</v>
       </c>
       <c r="E27" t="str">
         <v>estimates</v>
       </c>
       <c r="G27">
-        <v>45446</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B28" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D28" t="str">
-        <v>BSCM/ESCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E28" t="str">
         <v>estimates</v>
       </c>
       <c r="G28">
-        <v>45477</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B29" t="str">
-        <v>CSDM Upgrade</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E29" t="str">
         <v>estimates</v>
       </c>
       <c r="G29">
-        <v>45394</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B30" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D30" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E30" t="str">
-        <v>ofs</v>
+        <v>estimates</v>
       </c>
       <c r="G30">
-        <v>45531</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B31" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
@@ -1045,15 +1048,15 @@
         <v>ofs</v>
       </c>
       <c r="G31">
-        <v>45453</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B32" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
@@ -1065,15 +1068,15 @@
         <v>ofs</v>
       </c>
       <c r="G32">
-        <v>45461</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B33" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
@@ -1082,95 +1085,98 @@
         <v>FLCM</v>
       </c>
       <c r="E33" t="str">
-        <v>jrm</v>
+        <v>ofs</v>
       </c>
       <c r="G33">
-        <v>45714</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B34" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D34" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E34" t="str">
-        <v>estimates</v>
+        <v>jrm</v>
       </c>
       <c r="G34">
-        <v>45686</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-15822</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B35" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D35" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E35" t="str">
         <v>estimates</v>
       </c>
       <c r="G35">
-        <v>45650</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-15822</v>
       </c>
       <c r="B36" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D36" t="str">
-        <v>BSCM/ESCM</v>
+        <v>FLCM</v>
       </c>
       <c r="E36" t="str">
         <v>estimates</v>
       </c>
       <c r="G36">
-        <v>45541</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ENT-17853</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B37" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
       </c>
+      <c r="D37" t="str">
+        <v>BSCM/ESCM</v>
+      </c>
       <c r="E37" t="str">
-        <v>ofs</v>
+        <v>estimates</v>
       </c>
       <c r="G37">
-        <v>45691</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-17853</v>
       </c>
       <c r="B38" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
@@ -1179,15 +1185,15 @@
         <v>ofs</v>
       </c>
       <c r="G38">
-        <v>45559</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B39" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
@@ -1196,15 +1202,15 @@
         <v>ofs</v>
       </c>
       <c r="G39">
-        <v>45596</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B40" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
@@ -1213,15 +1219,15 @@
         <v>ofs</v>
       </c>
       <c r="G40">
-        <v>45378</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B41" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1230,15 +1236,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45468</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B42" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1247,15 +1253,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45310</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B43" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1264,15 +1270,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45427</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B44" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1281,15 +1287,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45279</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B45" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1298,15 +1304,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45558</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B46" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1315,15 +1321,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45383</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B47" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1332,15 +1338,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45638</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B48" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1349,15 +1355,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45461</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B49" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1366,15 +1372,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45371</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B50" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1388,10 +1394,10 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B51" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1400,15 +1406,15 @@
         <v>ofs</v>
       </c>
       <c r="G51">
-        <v>45406</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B52" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1417,15 +1423,15 @@
         <v>ofs</v>
       </c>
       <c r="G52">
-        <v>45364</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B53" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1434,15 +1440,15 @@
         <v>ofs</v>
       </c>
       <c r="G53">
-        <v>45593</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B54" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1451,15 +1457,15 @@
         <v>ofs</v>
       </c>
       <c r="G54">
-        <v>45408</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B55" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1468,15 +1474,15 @@
         <v>ofs</v>
       </c>
       <c r="G55">
-        <v>45595</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B56" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1485,15 +1491,15 @@
         <v>ofs</v>
       </c>
       <c r="G56">
-        <v>45392</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B57" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
@@ -1502,15 +1508,15 @@
         <v>ofs</v>
       </c>
       <c r="G57">
-        <v>45411</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B58" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C58" t="str">
         <v>Invite to JRM</v>
@@ -1524,27 +1530,27 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B59" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C59" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E59" t="str">
-        <v>jrm</v>
+        <v>ofs</v>
       </c>
       <c r="G59">
-        <v>45721</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ENT-18725</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B60" t="str">
-        <v>US Video System - Lenel to Genetec</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C60" t="str">
         <v>Invite to JRM</v>
@@ -1556,9 +1562,26 @@
         <v>45721</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>ENT-18725</v>
+      </c>
+      <c r="B61" t="str">
+        <v>US Video System - Lenel to Genetec</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Invite to JRM</v>
+      </c>
+      <c r="E61" t="str">
+        <v>jrm</v>
+      </c>
+      <c r="G61">
+        <v>45721</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G60"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G61"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G60"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -429,33 +429,30 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>23434</v>
+        <v>ENT-16949</v>
       </c>
       <c r="B2" t="str">
-        <v>324234</v>
+        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
       </c>
       <c r="C2" t="str">
-        <v>324234</v>
+        <v>Invite to JRM</v>
       </c>
       <c r="D2" t="str">
-        <v>324234</v>
+        <v>FLCM</v>
       </c>
       <c r="E2" t="str">
-        <v>jrm</v>
-      </c>
-      <c r="F2" t="str">
-        <v/>
-      </c>
-      <c r="G2" t="str">
-        <v>2025-03-15</v>
+        <v>estimates</v>
+      </c>
+      <c r="G2">
+        <v>45531</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ENT-16949</v>
+        <v>ENT-16700</v>
       </c>
       <c r="B3" t="str">
-        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
+        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
       </c>
       <c r="C3" t="str">
         <v>Invite to JRM</v>
@@ -464,18 +461,18 @@
         <v>FLCM</v>
       </c>
       <c r="E3" t="str">
-        <v>estimates</v>
+        <v>jrm</v>
       </c>
       <c r="G3">
-        <v>45531</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ENT-16700</v>
+        <v>ENT-16621</v>
       </c>
       <c r="B4" t="str">
-        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
+        <v>CIW Data Products to PROD</v>
       </c>
       <c r="C4" t="str">
         <v>Invite to JRM</v>
@@ -484,18 +481,18 @@
         <v>FLCM</v>
       </c>
       <c r="E4" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G4">
-        <v>45523</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ENT-16621</v>
+        <v>ENT-16374</v>
       </c>
       <c r="B5" t="str">
-        <v>CIW Data Products to PROD</v>
+        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
       </c>
       <c r="C5" t="str">
         <v>Invite to JRM</v>
@@ -504,18 +501,18 @@
         <v>FLCM</v>
       </c>
       <c r="E5" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G5">
-        <v>45596</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ENT-16374</v>
+        <v>ENT-16031</v>
       </c>
       <c r="B6" t="str">
-        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
+        <v>Fraud - Notes generator</v>
       </c>
       <c r="C6" t="str">
         <v>Invite to JRM</v>
@@ -527,15 +524,15 @@
         <v>jrm</v>
       </c>
       <c r="G6">
-        <v>45455</v>
+        <v>45649</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENT-16031</v>
+        <v>ENT-15917</v>
       </c>
       <c r="B7" t="str">
-        <v>Fraud - Notes generator</v>
+        <v>REBO Bill Payment Investigation Requests</v>
       </c>
       <c r="C7" t="str">
         <v>Invite to JRM</v>
@@ -547,15 +544,15 @@
         <v>jrm</v>
       </c>
       <c r="G7">
-        <v>45649</v>
+        <v>45613</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENT-15917</v>
+        <v>ENT-17286</v>
       </c>
       <c r="B8" t="str">
-        <v>REBO Bill Payment Investigation Requests</v>
+        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
       </c>
       <c r="C8" t="str">
         <v>Invite to JRM</v>
@@ -564,18 +561,18 @@
         <v>FLCM</v>
       </c>
       <c r="E8" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G8">
-        <v>45613</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-17286</v>
+        <v>ENT-17202</v>
       </c>
       <c r="B9" t="str">
-        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
+        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -584,18 +581,18 @@
         <v>FLCM</v>
       </c>
       <c r="E9" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G9">
-        <v>45699</v>
+        <v>45690</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-17202</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B10" t="str">
-        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -604,18 +601,21 @@
         <v>FLCM</v>
       </c>
       <c r="E10" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F10" t="str">
+        <v>PDF</v>
       </c>
       <c r="G10">
-        <v>45690</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B11" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -624,21 +624,18 @@
         <v>FLCM</v>
       </c>
       <c r="E11" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F11" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G11">
-        <v>45686</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B12" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -650,15 +647,15 @@
         <v>estimates</v>
       </c>
       <c r="G12">
-        <v>45700</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B13" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -670,15 +667,15 @@
         <v>estimates</v>
       </c>
       <c r="G13">
-        <v>45656</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B14" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -690,15 +687,15 @@
         <v>estimates</v>
       </c>
       <c r="G14">
-        <v>45588</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-17054</v>
       </c>
       <c r="B15" t="str">
-        <v>Data Source to EDGE</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -707,18 +704,21 @@
         <v>FLCM</v>
       </c>
       <c r="E15" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F15" t="str">
+        <v>PDF</v>
       </c>
       <c r="G15">
-        <v>45664</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-17054</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B16" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -729,19 +729,16 @@
       <c r="E16" t="str">
         <v>approved</v>
       </c>
-      <c r="F16" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G16">
-        <v>45691</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-14372</v>
       </c>
       <c r="B17" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -752,16 +749,19 @@
       <c r="E17" t="str">
         <v>approved</v>
       </c>
+      <c r="F17" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G17">
-        <v>45299</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ENT-14372</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B18" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
@@ -776,58 +776,58 @@
         <v>PDF</v>
       </c>
       <c r="G18">
-        <v>45512</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B19" t="str">
-        <v>RAMP Phase 2</v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D19" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E19" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F19" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G19">
-        <v>45562</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B20" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D20" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E20" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F20" t="str">
+        <v>PDF</v>
       </c>
       <c r="G20">
-        <v>45695</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B21" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
@@ -842,15 +842,15 @@
         <v>PDF</v>
       </c>
       <c r="G21">
-        <v>45688</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B22" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
@@ -865,15 +865,15 @@
         <v>PDF</v>
       </c>
       <c r="G22">
-        <v>45701</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B23" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
@@ -884,19 +884,16 @@
       <c r="E23" t="str">
         <v>approved</v>
       </c>
-      <c r="F23" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G23">
-        <v>45695</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B24" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
@@ -905,138 +902,138 @@
         <v>FLCM</v>
       </c>
       <c r="E24" t="str">
-        <v>approved</v>
+        <v>estimates</v>
       </c>
       <c r="G24">
-        <v>45706</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B25" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D25" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E25" t="str">
         <v>estimates</v>
       </c>
       <c r="G25">
-        <v>45559</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B26" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D26" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E26" t="str">
         <v>estimates</v>
       </c>
       <c r="G26">
-        <v>45623</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B27" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D27" t="str">
-        <v>FLCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E27" t="str">
         <v>estimates</v>
       </c>
       <c r="G27">
-        <v>45355</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B28" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D28" t="str">
-        <v>CorpSec</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E28" t="str">
         <v>estimates</v>
       </c>
       <c r="G28">
-        <v>45446</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B29" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>BSCM/ESCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E29" t="str">
         <v>estimates</v>
       </c>
       <c r="G29">
-        <v>45477</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B30" t="str">
-        <v>CSDM Upgrade</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D30" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E30" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G30">
-        <v>45394</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B31" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
@@ -1048,15 +1045,15 @@
         <v>ofs</v>
       </c>
       <c r="G31">
-        <v>45531</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B32" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
@@ -1068,15 +1065,15 @@
         <v>ofs</v>
       </c>
       <c r="G32">
-        <v>45453</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B33" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
@@ -1085,98 +1082,95 @@
         <v>FLCM</v>
       </c>
       <c r="E33" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G33">
-        <v>45461</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B34" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D34" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E34" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G34">
-        <v>45714</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-15822</v>
       </c>
       <c r="B35" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D35" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E35" t="str">
         <v>estimates</v>
       </c>
       <c r="G35">
-        <v>45686</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-15822</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B36" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D36" t="str">
-        <v>FLCM</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E36" t="str">
         <v>estimates</v>
       </c>
       <c r="G36">
-        <v>45650</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-17853</v>
       </c>
       <c r="B37" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
       </c>
-      <c r="D37" t="str">
-        <v>BSCM/ESCM</v>
-      </c>
       <c r="E37" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G37">
-        <v>45541</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ENT-17853</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B38" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
@@ -1185,15 +1179,15 @@
         <v>ofs</v>
       </c>
       <c r="G38">
-        <v>45691</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B39" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
@@ -1202,15 +1196,15 @@
         <v>ofs</v>
       </c>
       <c r="G39">
-        <v>45559</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B40" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
@@ -1219,15 +1213,15 @@
         <v>ofs</v>
       </c>
       <c r="G40">
-        <v>45596</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B41" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1236,15 +1230,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45378</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B42" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1253,15 +1247,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45468</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B43" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1270,15 +1264,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45310</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B44" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1287,15 +1281,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45427</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B45" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1304,15 +1298,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45279</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B46" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1321,15 +1315,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45558</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B47" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1338,15 +1332,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45383</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B48" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1355,15 +1349,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45638</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B49" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1372,15 +1366,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45461</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B50" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1394,10 +1388,10 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B51" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1406,15 +1400,15 @@
         <v>ofs</v>
       </c>
       <c r="G51">
-        <v>45371</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B52" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1423,15 +1417,15 @@
         <v>ofs</v>
       </c>
       <c r="G52">
-        <v>45406</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B53" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1440,15 +1434,15 @@
         <v>ofs</v>
       </c>
       <c r="G53">
-        <v>45364</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B54" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1457,15 +1451,15 @@
         <v>ofs</v>
       </c>
       <c r="G54">
-        <v>45593</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B55" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1474,15 +1468,15 @@
         <v>ofs</v>
       </c>
       <c r="G55">
-        <v>45408</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B56" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1491,15 +1485,15 @@
         <v>ofs</v>
       </c>
       <c r="G56">
-        <v>45595</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B57" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
@@ -1508,15 +1502,15 @@
         <v>ofs</v>
       </c>
       <c r="G57">
-        <v>45392</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B58" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C58" t="str">
         <v>Invite to JRM</v>
@@ -1530,27 +1524,27 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B59" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C59" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E59" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G59">
-        <v>45411</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-18725</v>
       </c>
       <c r="B60" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>US Video System - Lenel to Genetec</v>
       </c>
       <c r="C60" t="str">
         <v>Invite to JRM</v>
@@ -1562,26 +1556,9 @@
         <v>45721</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="str">
-        <v>ENT-18725</v>
-      </c>
-      <c r="B61" t="str">
-        <v>US Video System - Lenel to Genetec</v>
-      </c>
-      <c r="C61" t="str">
-        <v>Invite to JRM</v>
-      </c>
-      <c r="E61" t="str">
-        <v>jrm</v>
-      </c>
-      <c r="G61">
-        <v>45721</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G60"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -1651,16 +1651,19 @@
       <c r="A2" t="str">
         <v>ENT-17054</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="str">
         <v>178399</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="str">
         <v>2500</v>
       </c>
-      <c r="E2">
+      <c r="D2" t="str">
+        <v>-</v>
+      </c>
+      <c r="E2" t="str">
         <v>118933</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="str">
         <v>59466</v>
       </c>
       <c r="G2" t="str">
@@ -1675,29 +1678,29 @@
       <c r="J2" t="str">
         <v>46.40</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="str">
         <v>68</v>
       </c>
-      <c r="L2">
+      <c r="L2" t="str">
         <v>57206</v>
       </c>
-      <c r="M2">
-        <v>29</v>
-      </c>
-      <c r="N2">
-        <v>31.6</v>
-      </c>
-      <c r="O2">
+      <c r="M2" t="str">
+        <v>29.00</v>
+      </c>
+      <c r="N2" t="str">
+        <v>31.60</v>
+      </c>
+      <c r="O2" t="str">
         <v>75</v>
       </c>
-      <c r="P2">
-        <v>37290</v>
-      </c>
-      <c r="Q2">
-        <v>32.3</v>
-      </c>
-      <c r="R2">
-        <v>20.6</v>
+      <c r="P2" t="str">
+        <v>3729</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>32.30</v>
+      </c>
+      <c r="R2" t="str">
+        <v>20.60</v>
       </c>
       <c r="S2" t="str">
         <v>-</v>
@@ -1711,17 +1714,17 @@
       <c r="V2" t="str">
         <v>100.34</v>
       </c>
-      <c r="W2">
-        <v>0</v>
-      </c>
-      <c r="X2">
-        <v>0</v>
-      </c>
-      <c r="Y2">
-        <v>0</v>
-      </c>
-      <c r="Z2">
-        <v>0</v>
+      <c r="W2" t="str">
+        <v>-</v>
+      </c>
+      <c r="X2" t="str">
+        <v>-</v>
+      </c>
+      <c r="Y2" t="str">
+        <v>-</v>
+      </c>
+      <c r="Z2" t="str">
+        <v>-</v>
       </c>
     </row>
     <row r="3">

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -1713,17 +1713,17 @@
       <c r="F2">
         <v>59466</v>
       </c>
-      <c r="G2">
-        <v>90</v>
-      </c>
-      <c r="H2">
+      <c r="G2" t="str">
+        <v>900</v>
+      </c>
+      <c r="H2" t="str">
         <v>83903</v>
       </c>
-      <c r="I2">
-        <v>38.7</v>
-      </c>
-      <c r="J2">
-        <v>46.4</v>
+      <c r="I2" t="str">
+        <v>38.70</v>
+      </c>
+      <c r="J2" t="str">
+        <v>46.40</v>
       </c>
       <c r="K2">
         <v>68</v>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G63"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -429,30 +429,33 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ENT-17062</v>
+        <v>17062</v>
       </c>
       <c r="B2" t="str">
-        <v>Account Open Enhancements and Outcome Orchestration</v>
+        <v>123</v>
       </c>
       <c r="C2" t="str">
-        <v>Invite to JRM</v>
+        <v>123</v>
       </c>
       <c r="D2" t="str">
-        <v>FLCM</v>
+        <v>123</v>
       </c>
       <c r="E2" t="str">
         <v>jrm</v>
       </c>
-      <c r="G2">
-        <v>45672</v>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v>2025-03-15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ENT-16949</v>
+        <v>ENT-17062</v>
       </c>
       <c r="B3" t="str">
-        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
+        <v>Account Open Enhancements and Outcome Orchestration</v>
       </c>
       <c r="C3" t="str">
         <v>Invite to JRM</v>
@@ -461,18 +464,18 @@
         <v>FLCM</v>
       </c>
       <c r="E3" t="str">
-        <v>estimates</v>
+        <v>jrm</v>
       </c>
       <c r="G3">
-        <v>45531</v>
+        <v>45672</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ENT-16881</v>
+        <v>ENT-16949</v>
       </c>
       <c r="B4" t="str">
-        <v>Split up Personal Overdraft P&amp;L</v>
+        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
       </c>
       <c r="C4" t="str">
         <v>Invite to JRM</v>
@@ -481,18 +484,18 @@
         <v>FLCM</v>
       </c>
       <c r="E4" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G4">
-        <v>45929</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ENT-16700</v>
+        <v>ENT-16881</v>
       </c>
       <c r="B5" t="str">
-        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
+        <v>Split up Personal Overdraft P&amp;L</v>
       </c>
       <c r="C5" t="str">
         <v>Invite to JRM</v>
@@ -504,15 +507,15 @@
         <v>jrm</v>
       </c>
       <c r="G5">
-        <v>45523</v>
+        <v>45929</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ENT-16621</v>
+        <v>ENT-16700</v>
       </c>
       <c r="B6" t="str">
-        <v>CIW Data Products to PROD</v>
+        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
       </c>
       <c r="C6" t="str">
         <v>Invite to JRM</v>
@@ -521,18 +524,18 @@
         <v>FLCM</v>
       </c>
       <c r="E6" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G6">
-        <v>45596</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENT-16374</v>
+        <v>ENT-16621</v>
       </c>
       <c r="B7" t="str">
-        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
+        <v>CIW Data Products to PROD</v>
       </c>
       <c r="C7" t="str">
         <v>Invite to JRM</v>
@@ -541,18 +544,18 @@
         <v>FLCM</v>
       </c>
       <c r="E7" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G7">
-        <v>45455</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENT-16031</v>
+        <v>ENT-16374</v>
       </c>
       <c r="B8" t="str">
-        <v>Fraud - Notes generator</v>
+        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
       </c>
       <c r="C8" t="str">
         <v>Invite to JRM</v>
@@ -564,15 +567,15 @@
         <v>jrm</v>
       </c>
       <c r="G8">
-        <v>45649</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-15917</v>
+        <v>ENT-16031</v>
       </c>
       <c r="B9" t="str">
-        <v>REBO Bill Payment Investigation Requests</v>
+        <v>Fraud - Notes generator</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -584,15 +587,15 @@
         <v>jrm</v>
       </c>
       <c r="G9">
-        <v>45613</v>
+        <v>45649</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-17286</v>
+        <v>ENT-15917</v>
       </c>
       <c r="B10" t="str">
-        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
+        <v>REBO Bill Payment Investigation Requests</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -601,18 +604,18 @@
         <v>FLCM</v>
       </c>
       <c r="E10" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G10">
-        <v>45699</v>
+        <v>45613</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-17202</v>
+        <v>ENT-17286</v>
       </c>
       <c r="B11" t="str">
-        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
+        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -621,18 +624,18 @@
         <v>FLCM</v>
       </c>
       <c r="E11" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G11">
-        <v>45690</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17202</v>
       </c>
       <c r="B12" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -641,21 +644,18 @@
         <v>FLCM</v>
       </c>
       <c r="E12" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F12" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G12">
-        <v>45686</v>
+        <v>45690</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B13" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -664,18 +664,21 @@
         <v>FLCM</v>
       </c>
       <c r="E13" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F13" t="str">
+        <v>PDF</v>
       </c>
       <c r="G13">
-        <v>45700</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B14" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -687,15 +690,15 @@
         <v>estimates</v>
       </c>
       <c r="G14">
-        <v>45656</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B15" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -707,15 +710,15 @@
         <v>estimates</v>
       </c>
       <c r="G15">
-        <v>45588</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B16" t="str">
-        <v>Data Source to EDGE</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -727,15 +730,15 @@
         <v>estimates</v>
       </c>
       <c r="G16">
-        <v>45664</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ENT-17054</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B17" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -744,21 +747,18 @@
         <v>FLCM</v>
       </c>
       <c r="E17" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F17" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G17">
-        <v>45691</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-17054</v>
       </c>
       <c r="B18" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
@@ -769,16 +769,19 @@
       <c r="E18" t="str">
         <v>approved</v>
       </c>
+      <c r="F18" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G18">
-        <v>45299</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ENT-14372</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B19" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
@@ -789,19 +792,16 @@
       <c r="E19" t="str">
         <v>approved</v>
       </c>
-      <c r="F19" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G19">
-        <v>45512</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-14372</v>
       </c>
       <c r="B20" t="str">
-        <v>RAMP Phase 2</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
@@ -816,58 +816,58 @@
         <v>PDF</v>
       </c>
       <c r="G20">
-        <v>45562</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B21" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D21" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E21" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F21" t="str">
+        <v>PDF</v>
       </c>
       <c r="G21">
-        <v>45695</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B22" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D22" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E22" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F22" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G22">
-        <v>45688</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B23" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
@@ -882,15 +882,15 @@
         <v>PDF</v>
       </c>
       <c r="G23">
-        <v>45701</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B24" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
@@ -905,15 +905,15 @@
         <v>PDF</v>
       </c>
       <c r="G24">
-        <v>45695</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B25" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
@@ -924,16 +924,19 @@
       <c r="E25" t="str">
         <v>approved</v>
       </c>
+      <c r="F25" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G25">
-        <v>45706</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B26" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
@@ -942,138 +945,138 @@
         <v>FLCM</v>
       </c>
       <c r="E26" t="str">
-        <v>estimates</v>
+        <v>approved</v>
       </c>
       <c r="G26">
-        <v>45559</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B27" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D27" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E27" t="str">
         <v>estimates</v>
       </c>
       <c r="G27">
-        <v>45623</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B28" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D28" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E28" t="str">
         <v>estimates</v>
       </c>
       <c r="G28">
-        <v>45355</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B29" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>CorpSec</v>
+        <v>FLCM</v>
       </c>
       <c r="E29" t="str">
         <v>estimates</v>
       </c>
       <c r="G29">
-        <v>45446</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B30" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D30" t="str">
-        <v>BSCM/ESCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E30" t="str">
         <v>estimates</v>
       </c>
       <c r="G30">
-        <v>45477</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B31" t="str">
-        <v>CSDM Upgrade</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D31" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E31" t="str">
         <v>estimates</v>
       </c>
       <c r="G31">
-        <v>45394</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B32" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D32" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E32" t="str">
-        <v>ofs</v>
+        <v>estimates</v>
       </c>
       <c r="G32">
-        <v>45531</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B33" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
@@ -1085,15 +1088,15 @@
         <v>ofs</v>
       </c>
       <c r="G33">
-        <v>45453</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B34" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
@@ -1105,15 +1108,15 @@
         <v>ofs</v>
       </c>
       <c r="G34">
-        <v>45461</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B35" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
@@ -1122,95 +1125,98 @@
         <v>FLCM</v>
       </c>
       <c r="E35" t="str">
-        <v>jrm</v>
+        <v>ofs</v>
       </c>
       <c r="G35">
-        <v>45714</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B36" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D36" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E36" t="str">
-        <v>estimates</v>
+        <v>jrm</v>
       </c>
       <c r="G36">
-        <v>45686</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ENT-15822</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B37" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D37" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E37" t="str">
         <v>estimates</v>
       </c>
       <c r="G37">
-        <v>45650</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-15822</v>
       </c>
       <c r="B38" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D38" t="str">
-        <v>BSCM/ESCM</v>
+        <v>FLCM</v>
       </c>
       <c r="E38" t="str">
         <v>estimates</v>
       </c>
       <c r="G38">
-        <v>45541</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ENT-17853</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B39" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
       </c>
+      <c r="D39" t="str">
+        <v>BSCM/ESCM</v>
+      </c>
       <c r="E39" t="str">
-        <v>ofs</v>
+        <v>estimates</v>
       </c>
       <c r="G39">
-        <v>45691</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-17853</v>
       </c>
       <c r="B40" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
@@ -1219,15 +1225,15 @@
         <v>ofs</v>
       </c>
       <c r="G40">
-        <v>45559</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B41" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1236,15 +1242,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45596</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B42" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1253,15 +1259,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45378</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B43" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1270,15 +1276,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45468</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B44" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1287,15 +1293,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45310</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B45" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1304,15 +1310,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45427</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B46" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1321,15 +1327,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45279</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B47" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1338,15 +1344,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45558</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B48" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1355,15 +1361,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45383</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B49" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1372,15 +1378,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45638</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B50" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1389,15 +1395,15 @@
         <v>ofs</v>
       </c>
       <c r="G50">
-        <v>45461</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B51" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1406,15 +1412,15 @@
         <v>ofs</v>
       </c>
       <c r="G51">
-        <v>45371</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B52" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1428,10 +1434,10 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B53" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1440,15 +1446,15 @@
         <v>ofs</v>
       </c>
       <c r="G53">
-        <v>45406</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B54" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1457,15 +1463,15 @@
         <v>ofs</v>
       </c>
       <c r="G54">
-        <v>45364</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B55" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1474,15 +1480,15 @@
         <v>ofs</v>
       </c>
       <c r="G55">
-        <v>45593</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B56" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1491,15 +1497,15 @@
         <v>ofs</v>
       </c>
       <c r="G56">
-        <v>45408</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B57" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
@@ -1508,15 +1514,15 @@
         <v>ofs</v>
       </c>
       <c r="G57">
-        <v>45595</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B58" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C58" t="str">
         <v>Invite to JRM</v>
@@ -1525,15 +1531,15 @@
         <v>ofs</v>
       </c>
       <c r="G58">
-        <v>45392</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B59" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C59" t="str">
         <v>Invite to JRM</v>
@@ -1542,15 +1548,15 @@
         <v>ofs</v>
       </c>
       <c r="G59">
-        <v>45411</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B60" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C60" t="str">
         <v>Invite to JRM</v>
@@ -1564,27 +1570,27 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B61" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C61" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E61" t="str">
-        <v>jrm</v>
+        <v>ofs</v>
       </c>
       <c r="G61">
-        <v>45721</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>ENT-18725</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B62" t="str">
-        <v>US Video System - Lenel to Genetec</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C62" t="str">
         <v>Invite to JRM</v>
@@ -1596,19 +1602,26 @@
         <v>45721</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>ENT-18725</v>
+      </c>
+      <c r="B63" t="str">
+        <v>US Video System - Lenel to Genetec</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Invite to JRM</v>
+      </c>
+      <c r="E63" t="str">
+        <v>jrm</v>
+      </c>
+      <c r="G63">
+        <v>45721</v>
+      </c>
+    </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="F12" r:id="rId1"/>
-    <hyperlink ref="F17" r:id="rId2"/>
-    <hyperlink ref="F19" r:id="rId3"/>
-    <hyperlink ref="F20" r:id="rId4"/>
-    <hyperlink ref="F22" r:id="rId5"/>
-    <hyperlink ref="F23" r:id="rId6"/>
-    <hyperlink ref="F24" r:id="rId7"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G62"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G63"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G64"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -429,10 +429,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>17062</v>
+        <v>ENT-168812</v>
       </c>
       <c r="B2" t="str">
-        <v>123</v>
+        <v>terw</v>
       </c>
       <c r="C2" t="str">
         <v>123</v>
@@ -452,30 +452,33 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ENT-17062</v>
+        <v>17062</v>
       </c>
       <c r="B3" t="str">
-        <v>Account Open Enhancements and Outcome Orchestration</v>
+        <v>123</v>
       </c>
       <c r="C3" t="str">
-        <v>Invite to JRM</v>
+        <v>123</v>
       </c>
       <c r="D3" t="str">
-        <v>FLCM</v>
+        <v>123</v>
       </c>
       <c r="E3" t="str">
         <v>jrm</v>
       </c>
-      <c r="G3">
-        <v>45672</v>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v>2025-03-15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ENT-16949</v>
+        <v>ENT-17062</v>
       </c>
       <c r="B4" t="str">
-        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
+        <v>Account Open Enhancements and Outcome Orchestration</v>
       </c>
       <c r="C4" t="str">
         <v>Invite to JRM</v>
@@ -484,18 +487,18 @@
         <v>FLCM</v>
       </c>
       <c r="E4" t="str">
-        <v>estimates</v>
+        <v>jrm</v>
       </c>
       <c r="G4">
-        <v>45531</v>
+        <v>45672</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ENT-16881</v>
+        <v>ENT-16949</v>
       </c>
       <c r="B5" t="str">
-        <v>Split up Personal Overdraft P&amp;L</v>
+        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
       </c>
       <c r="C5" t="str">
         <v>Invite to JRM</v>
@@ -504,18 +507,18 @@
         <v>FLCM</v>
       </c>
       <c r="E5" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G5">
-        <v>45929</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ENT-16700</v>
+        <v>ENT-16881</v>
       </c>
       <c r="B6" t="str">
-        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
+        <v>Split up Personal Overdraft P&amp;L</v>
       </c>
       <c r="C6" t="str">
         <v>Invite to JRM</v>
@@ -527,15 +530,15 @@
         <v>jrm</v>
       </c>
       <c r="G6">
-        <v>45523</v>
+        <v>45929</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENT-16621</v>
+        <v>ENT-16700</v>
       </c>
       <c r="B7" t="str">
-        <v>CIW Data Products to PROD</v>
+        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
       </c>
       <c r="C7" t="str">
         <v>Invite to JRM</v>
@@ -544,18 +547,18 @@
         <v>FLCM</v>
       </c>
       <c r="E7" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G7">
-        <v>45596</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENT-16374</v>
+        <v>ENT-16621</v>
       </c>
       <c r="B8" t="str">
-        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
+        <v>CIW Data Products to PROD</v>
       </c>
       <c r="C8" t="str">
         <v>Invite to JRM</v>
@@ -564,18 +567,18 @@
         <v>FLCM</v>
       </c>
       <c r="E8" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G8">
-        <v>45455</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-16031</v>
+        <v>ENT-16374</v>
       </c>
       <c r="B9" t="str">
-        <v>Fraud - Notes generator</v>
+        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -587,15 +590,15 @@
         <v>jrm</v>
       </c>
       <c r="G9">
-        <v>45649</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-15917</v>
+        <v>ENT-16031</v>
       </c>
       <c r="B10" t="str">
-        <v>REBO Bill Payment Investigation Requests</v>
+        <v>Fraud - Notes generator</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -607,15 +610,15 @@
         <v>jrm</v>
       </c>
       <c r="G10">
-        <v>45613</v>
+        <v>45649</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-17286</v>
+        <v>ENT-15917</v>
       </c>
       <c r="B11" t="str">
-        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
+        <v>REBO Bill Payment Investigation Requests</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -624,18 +627,18 @@
         <v>FLCM</v>
       </c>
       <c r="E11" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G11">
-        <v>45699</v>
+        <v>45613</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-17202</v>
+        <v>ENT-17286</v>
       </c>
       <c r="B12" t="str">
-        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
+        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -644,18 +647,18 @@
         <v>FLCM</v>
       </c>
       <c r="E12" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G12">
-        <v>45690</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17202</v>
       </c>
       <c r="B13" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -664,21 +667,18 @@
         <v>FLCM</v>
       </c>
       <c r="E13" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F13" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G13">
-        <v>45686</v>
+        <v>45690</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B14" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -687,18 +687,21 @@
         <v>FLCM</v>
       </c>
       <c r="E14" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F14" t="str">
+        <v>PDF</v>
       </c>
       <c r="G14">
-        <v>45700</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B15" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -710,15 +713,15 @@
         <v>estimates</v>
       </c>
       <c r="G15">
-        <v>45656</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B16" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -730,15 +733,15 @@
         <v>estimates</v>
       </c>
       <c r="G16">
-        <v>45588</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B17" t="str">
-        <v>Data Source to EDGE</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -750,15 +753,15 @@
         <v>estimates</v>
       </c>
       <c r="G17">
-        <v>45664</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ENT-17054</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B18" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
@@ -767,21 +770,18 @@
         <v>FLCM</v>
       </c>
       <c r="E18" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F18" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G18">
-        <v>45691</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-17054</v>
       </c>
       <c r="B19" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
@@ -792,16 +792,19 @@
       <c r="E19" t="str">
         <v>approved</v>
       </c>
+      <c r="F19" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G19">
-        <v>45299</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ENT-14372</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B20" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
@@ -812,19 +815,16 @@
       <c r="E20" t="str">
         <v>approved</v>
       </c>
-      <c r="F20" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G20">
-        <v>45512</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-14372</v>
       </c>
       <c r="B21" t="str">
-        <v>RAMP Phase 2</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
@@ -839,58 +839,58 @@
         <v>PDF</v>
       </c>
       <c r="G21">
-        <v>45562</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B22" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D22" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E22" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F22" t="str">
+        <v>PDF</v>
       </c>
       <c r="G22">
-        <v>45695</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B23" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D23" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E23" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F23" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G23">
-        <v>45688</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B24" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
@@ -905,15 +905,15 @@
         <v>PDF</v>
       </c>
       <c r="G24">
-        <v>45701</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B25" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
@@ -928,15 +928,15 @@
         <v>PDF</v>
       </c>
       <c r="G25">
-        <v>45695</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B26" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
@@ -947,16 +947,19 @@
       <c r="E26" t="str">
         <v>approved</v>
       </c>
+      <c r="F26" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G26">
-        <v>45706</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B27" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
@@ -965,138 +968,138 @@
         <v>FLCM</v>
       </c>
       <c r="E27" t="str">
-        <v>estimates</v>
+        <v>approved</v>
       </c>
       <c r="G27">
-        <v>45559</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B28" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D28" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E28" t="str">
         <v>estimates</v>
       </c>
       <c r="G28">
-        <v>45623</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B29" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E29" t="str">
         <v>estimates</v>
       </c>
       <c r="G29">
-        <v>45355</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B30" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D30" t="str">
-        <v>CorpSec</v>
+        <v>FLCM</v>
       </c>
       <c r="E30" t="str">
         <v>estimates</v>
       </c>
       <c r="G30">
-        <v>45446</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B31" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D31" t="str">
-        <v>BSCM/ESCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E31" t="str">
         <v>estimates</v>
       </c>
       <c r="G31">
-        <v>45477</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B32" t="str">
-        <v>CSDM Upgrade</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D32" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E32" t="str">
         <v>estimates</v>
       </c>
       <c r="G32">
-        <v>45394</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B33" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D33" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E33" t="str">
-        <v>ofs</v>
+        <v>estimates</v>
       </c>
       <c r="G33">
-        <v>45531</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B34" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
@@ -1108,15 +1111,15 @@
         <v>ofs</v>
       </c>
       <c r="G34">
-        <v>45453</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B35" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
@@ -1128,15 +1131,15 @@
         <v>ofs</v>
       </c>
       <c r="G35">
-        <v>45461</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B36" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
@@ -1145,95 +1148,98 @@
         <v>FLCM</v>
       </c>
       <c r="E36" t="str">
-        <v>jrm</v>
+        <v>ofs</v>
       </c>
       <c r="G36">
-        <v>45714</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B37" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D37" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E37" t="str">
-        <v>estimates</v>
+        <v>jrm</v>
       </c>
       <c r="G37">
-        <v>45686</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ENT-15822</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B38" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D38" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E38" t="str">
         <v>estimates</v>
       </c>
       <c r="G38">
-        <v>45650</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-15822</v>
       </c>
       <c r="B39" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D39" t="str">
-        <v>BSCM/ESCM</v>
+        <v>FLCM</v>
       </c>
       <c r="E39" t="str">
         <v>estimates</v>
       </c>
       <c r="G39">
-        <v>45541</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENT-17853</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B40" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
       </c>
+      <c r="D40" t="str">
+        <v>BSCM/ESCM</v>
+      </c>
       <c r="E40" t="str">
-        <v>ofs</v>
+        <v>estimates</v>
       </c>
       <c r="G40">
-        <v>45691</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-17853</v>
       </c>
       <c r="B41" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1242,15 +1248,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45559</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B42" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1259,15 +1265,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45596</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B43" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1276,15 +1282,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45378</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B44" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1293,15 +1299,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45468</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B45" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1310,15 +1316,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45310</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B46" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1327,15 +1333,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45427</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B47" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1344,15 +1350,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45279</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B48" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1361,15 +1367,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45558</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B49" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1378,15 +1384,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45383</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B50" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1395,15 +1401,15 @@
         <v>ofs</v>
       </c>
       <c r="G50">
-        <v>45638</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B51" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1412,15 +1418,15 @@
         <v>ofs</v>
       </c>
       <c r="G51">
-        <v>45461</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B52" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1429,15 +1435,15 @@
         <v>ofs</v>
       </c>
       <c r="G52">
-        <v>45371</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B53" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1451,10 +1457,10 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B54" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1463,15 +1469,15 @@
         <v>ofs</v>
       </c>
       <c r="G54">
-        <v>45406</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B55" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1480,15 +1486,15 @@
         <v>ofs</v>
       </c>
       <c r="G55">
-        <v>45364</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B56" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1497,15 +1503,15 @@
         <v>ofs</v>
       </c>
       <c r="G56">
-        <v>45593</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B57" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
@@ -1514,15 +1520,15 @@
         <v>ofs</v>
       </c>
       <c r="G57">
-        <v>45408</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B58" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C58" t="str">
         <v>Invite to JRM</v>
@@ -1531,15 +1537,15 @@
         <v>ofs</v>
       </c>
       <c r="G58">
-        <v>45595</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B59" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C59" t="str">
         <v>Invite to JRM</v>
@@ -1548,15 +1554,15 @@
         <v>ofs</v>
       </c>
       <c r="G59">
-        <v>45392</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B60" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C60" t="str">
         <v>Invite to JRM</v>
@@ -1565,15 +1571,15 @@
         <v>ofs</v>
       </c>
       <c r="G60">
-        <v>45411</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B61" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C61" t="str">
         <v>Invite to JRM</v>
@@ -1587,27 +1593,27 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B62" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C62" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E62" t="str">
-        <v>jrm</v>
+        <v>ofs</v>
       </c>
       <c r="G62">
-        <v>45721</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>ENT-18725</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B63" t="str">
-        <v>US Video System - Lenel to Genetec</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C63" t="str">
         <v>Invite to JRM</v>
@@ -1619,9 +1625,26 @@
         <v>45721</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>ENT-18725</v>
+      </c>
+      <c r="B64" t="str">
+        <v>US Video System - Lenel to Genetec</v>
+      </c>
+      <c r="C64" t="str">
+        <v>Invite to JRM</v>
+      </c>
+      <c r="E64" t="str">
+        <v>jrm</v>
+      </c>
+      <c r="G64">
+        <v>45721</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G63"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G64"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G65"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -429,16 +429,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ENT-168812</v>
+        <v>ENT-168843</v>
       </c>
       <c r="B2" t="str">
-        <v>terw</v>
+        <v>qwe</v>
       </c>
       <c r="C2" t="str">
-        <v>123</v>
+        <v>qwe</v>
       </c>
       <c r="D2" t="str">
-        <v>123</v>
+        <v>qwe</v>
       </c>
       <c r="E2" t="str">
         <v>jrm</v>
@@ -452,10 +452,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>17062</v>
+        <v>ENT-168812</v>
       </c>
       <c r="B3" t="str">
-        <v>123</v>
+        <v>terw</v>
       </c>
       <c r="C3" t="str">
         <v>123</v>
@@ -475,30 +475,33 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ENT-17062</v>
+        <v>17062</v>
       </c>
       <c r="B4" t="str">
-        <v>Account Open Enhancements and Outcome Orchestration</v>
+        <v>123</v>
       </c>
       <c r="C4" t="str">
-        <v>Invite to JRM</v>
+        <v>123</v>
       </c>
       <c r="D4" t="str">
-        <v>FLCM</v>
+        <v>123</v>
       </c>
       <c r="E4" t="str">
         <v>jrm</v>
       </c>
-      <c r="G4">
-        <v>45672</v>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v>2025-03-15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ENT-16949</v>
+        <v>ENT-17062</v>
       </c>
       <c r="B5" t="str">
-        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
+        <v>Account Open Enhancements and Outcome Orchestration</v>
       </c>
       <c r="C5" t="str">
         <v>Invite to JRM</v>
@@ -507,18 +510,18 @@
         <v>FLCM</v>
       </c>
       <c r="E5" t="str">
-        <v>estimates</v>
+        <v>jrm</v>
       </c>
       <c r="G5">
-        <v>45531</v>
+        <v>45672</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ENT-16881</v>
+        <v>ENT-16949</v>
       </c>
       <c r="B6" t="str">
-        <v>Split up Personal Overdraft P&amp;L</v>
+        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
       </c>
       <c r="C6" t="str">
         <v>Invite to JRM</v>
@@ -527,18 +530,18 @@
         <v>FLCM</v>
       </c>
       <c r="E6" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G6">
-        <v>45929</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENT-16700</v>
+        <v>ENT-16881</v>
       </c>
       <c r="B7" t="str">
-        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
+        <v>Split up Personal Overdraft P&amp;L</v>
       </c>
       <c r="C7" t="str">
         <v>Invite to JRM</v>
@@ -550,15 +553,15 @@
         <v>jrm</v>
       </c>
       <c r="G7">
-        <v>45523</v>
+        <v>45929</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENT-16621</v>
+        <v>ENT-16700</v>
       </c>
       <c r="B8" t="str">
-        <v>CIW Data Products to PROD</v>
+        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
       </c>
       <c r="C8" t="str">
         <v>Invite to JRM</v>
@@ -567,18 +570,18 @@
         <v>FLCM</v>
       </c>
       <c r="E8" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G8">
-        <v>45596</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-16374</v>
+        <v>ENT-16621</v>
       </c>
       <c r="B9" t="str">
-        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
+        <v>CIW Data Products to PROD</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -587,18 +590,18 @@
         <v>FLCM</v>
       </c>
       <c r="E9" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G9">
-        <v>45455</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-16031</v>
+        <v>ENT-16374</v>
       </c>
       <c r="B10" t="str">
-        <v>Fraud - Notes generator</v>
+        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -610,15 +613,15 @@
         <v>jrm</v>
       </c>
       <c r="G10">
-        <v>45649</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-15917</v>
+        <v>ENT-16031</v>
       </c>
       <c r="B11" t="str">
-        <v>REBO Bill Payment Investigation Requests</v>
+        <v>Fraud - Notes generator</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -630,15 +633,15 @@
         <v>jrm</v>
       </c>
       <c r="G11">
-        <v>45613</v>
+        <v>45649</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-17286</v>
+        <v>ENT-15917</v>
       </c>
       <c r="B12" t="str">
-        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
+        <v>REBO Bill Payment Investigation Requests</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -647,18 +650,18 @@
         <v>FLCM</v>
       </c>
       <c r="E12" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G12">
-        <v>45699</v>
+        <v>45613</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-17202</v>
+        <v>ENT-17286</v>
       </c>
       <c r="B13" t="str">
-        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
+        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -667,18 +670,18 @@
         <v>FLCM</v>
       </c>
       <c r="E13" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G13">
-        <v>45690</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17202</v>
       </c>
       <c r="B14" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -687,21 +690,18 @@
         <v>FLCM</v>
       </c>
       <c r="E14" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F14" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G14">
-        <v>45686</v>
+        <v>45690</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B15" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -710,18 +710,21 @@
         <v>FLCM</v>
       </c>
       <c r="E15" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F15" t="str">
+        <v>PDF</v>
       </c>
       <c r="G15">
-        <v>45700</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B16" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -733,15 +736,15 @@
         <v>estimates</v>
       </c>
       <c r="G16">
-        <v>45656</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B17" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -753,15 +756,15 @@
         <v>estimates</v>
       </c>
       <c r="G17">
-        <v>45588</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B18" t="str">
-        <v>Data Source to EDGE</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
@@ -773,15 +776,15 @@
         <v>estimates</v>
       </c>
       <c r="G18">
-        <v>45664</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ENT-17054</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B19" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
@@ -790,21 +793,18 @@
         <v>FLCM</v>
       </c>
       <c r="E19" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F19" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G19">
-        <v>45691</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-17054</v>
       </c>
       <c r="B20" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
@@ -815,16 +815,19 @@
       <c r="E20" t="str">
         <v>approved</v>
       </c>
+      <c r="F20" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G20">
-        <v>45299</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-14372</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B21" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
@@ -835,19 +838,16 @@
       <c r="E21" t="str">
         <v>approved</v>
       </c>
-      <c r="F21" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G21">
-        <v>45512</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-14372</v>
       </c>
       <c r="B22" t="str">
-        <v>RAMP Phase 2</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
@@ -862,58 +862,58 @@
         <v>PDF</v>
       </c>
       <c r="G22">
-        <v>45562</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B23" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D23" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E23" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F23" t="str">
+        <v>PDF</v>
       </c>
       <c r="G23">
-        <v>45695</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B24" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D24" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E24" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F24" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G24">
-        <v>45688</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B25" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
@@ -928,15 +928,15 @@
         <v>PDF</v>
       </c>
       <c r="G25">
-        <v>45701</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B26" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
@@ -951,15 +951,15 @@
         <v>PDF</v>
       </c>
       <c r="G26">
-        <v>45695</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B27" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
@@ -970,16 +970,19 @@
       <c r="E27" t="str">
         <v>approved</v>
       </c>
+      <c r="F27" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G27">
-        <v>45706</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B28" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
@@ -988,138 +991,138 @@
         <v>FLCM</v>
       </c>
       <c r="E28" t="str">
-        <v>estimates</v>
+        <v>approved</v>
       </c>
       <c r="G28">
-        <v>45559</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B29" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E29" t="str">
         <v>estimates</v>
       </c>
       <c r="G29">
-        <v>45623</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B30" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D30" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E30" t="str">
         <v>estimates</v>
       </c>
       <c r="G30">
-        <v>45355</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B31" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D31" t="str">
-        <v>CorpSec</v>
+        <v>FLCM</v>
       </c>
       <c r="E31" t="str">
         <v>estimates</v>
       </c>
       <c r="G31">
-        <v>45446</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B32" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D32" t="str">
-        <v>BSCM/ESCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E32" t="str">
         <v>estimates</v>
       </c>
       <c r="G32">
-        <v>45477</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B33" t="str">
-        <v>CSDM Upgrade</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D33" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E33" t="str">
         <v>estimates</v>
       </c>
       <c r="G33">
-        <v>45394</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B34" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D34" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E34" t="str">
-        <v>ofs</v>
+        <v>estimates</v>
       </c>
       <c r="G34">
-        <v>45531</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B35" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
@@ -1131,15 +1134,15 @@
         <v>ofs</v>
       </c>
       <c r="G35">
-        <v>45453</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B36" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
@@ -1151,15 +1154,15 @@
         <v>ofs</v>
       </c>
       <c r="G36">
-        <v>45461</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B37" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
@@ -1168,95 +1171,98 @@
         <v>FLCM</v>
       </c>
       <c r="E37" t="str">
-        <v>jrm</v>
+        <v>ofs</v>
       </c>
       <c r="G37">
-        <v>45714</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B38" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D38" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E38" t="str">
-        <v>estimates</v>
+        <v>jrm</v>
       </c>
       <c r="G38">
-        <v>45686</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ENT-15822</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B39" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D39" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E39" t="str">
         <v>estimates</v>
       </c>
       <c r="G39">
-        <v>45650</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-15822</v>
       </c>
       <c r="B40" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D40" t="str">
-        <v>BSCM/ESCM</v>
+        <v>FLCM</v>
       </c>
       <c r="E40" t="str">
         <v>estimates</v>
       </c>
       <c r="G40">
-        <v>45541</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-17853</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B41" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
       </c>
+      <c r="D41" t="str">
+        <v>BSCM/ESCM</v>
+      </c>
       <c r="E41" t="str">
-        <v>ofs</v>
+        <v>estimates</v>
       </c>
       <c r="G41">
-        <v>45691</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-17853</v>
       </c>
       <c r="B42" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1265,15 +1271,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45559</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B43" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1282,15 +1288,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45596</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B44" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1299,15 +1305,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45378</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B45" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1316,15 +1322,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45468</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B46" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1333,15 +1339,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45310</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B47" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1350,15 +1356,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45427</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B48" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1367,15 +1373,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45279</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B49" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1384,15 +1390,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45558</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B50" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1401,15 +1407,15 @@
         <v>ofs</v>
       </c>
       <c r="G50">
-        <v>45383</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B51" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1418,15 +1424,15 @@
         <v>ofs</v>
       </c>
       <c r="G51">
-        <v>45638</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B52" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1435,15 +1441,15 @@
         <v>ofs</v>
       </c>
       <c r="G52">
-        <v>45461</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B53" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1452,15 +1458,15 @@
         <v>ofs</v>
       </c>
       <c r="G53">
-        <v>45371</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B54" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1474,10 +1480,10 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B55" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1486,15 +1492,15 @@
         <v>ofs</v>
       </c>
       <c r="G55">
-        <v>45406</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B56" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1503,15 +1509,15 @@
         <v>ofs</v>
       </c>
       <c r="G56">
-        <v>45364</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B57" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
@@ -1520,15 +1526,15 @@
         <v>ofs</v>
       </c>
       <c r="G57">
-        <v>45593</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B58" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C58" t="str">
         <v>Invite to JRM</v>
@@ -1537,15 +1543,15 @@
         <v>ofs</v>
       </c>
       <c r="G58">
-        <v>45408</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B59" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C59" t="str">
         <v>Invite to JRM</v>
@@ -1554,15 +1560,15 @@
         <v>ofs</v>
       </c>
       <c r="G59">
-        <v>45595</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B60" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C60" t="str">
         <v>Invite to JRM</v>
@@ -1571,15 +1577,15 @@
         <v>ofs</v>
       </c>
       <c r="G60">
-        <v>45392</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B61" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C61" t="str">
         <v>Invite to JRM</v>
@@ -1588,15 +1594,15 @@
         <v>ofs</v>
       </c>
       <c r="G61">
-        <v>45411</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B62" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C62" t="str">
         <v>Invite to JRM</v>
@@ -1610,27 +1616,27 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B63" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C63" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E63" t="str">
-        <v>jrm</v>
+        <v>ofs</v>
       </c>
       <c r="G63">
-        <v>45721</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>ENT-18725</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B64" t="str">
-        <v>US Video System - Lenel to Genetec</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C64" t="str">
         <v>Invite to JRM</v>
@@ -1642,9 +1648,26 @@
         <v>45721</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>ENT-18725</v>
+      </c>
+      <c r="B65" t="str">
+        <v>US Video System - Lenel to Genetec</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Invite to JRM</v>
+      </c>
+      <c r="E65" t="str">
+        <v>jrm</v>
+      </c>
+      <c r="G65">
+        <v>45721</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G64"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G65"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G64"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -429,16 +429,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ENT-168843</v>
+        <v>ENT-168812</v>
       </c>
       <c r="B2" t="str">
-        <v>qwe</v>
+        <v>terw</v>
       </c>
       <c r="C2" t="str">
-        <v>qwe</v>
+        <v>123</v>
       </c>
       <c r="D2" t="str">
-        <v>qwe</v>
+        <v>123</v>
       </c>
       <c r="E2" t="str">
         <v>jrm</v>
@@ -452,10 +452,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ENT-168812</v>
+        <v>17062</v>
       </c>
       <c r="B3" t="str">
-        <v>terw</v>
+        <v>123</v>
       </c>
       <c r="C3" t="str">
         <v>123</v>
@@ -475,33 +475,30 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>17062</v>
+        <v>ENT-17062</v>
       </c>
       <c r="B4" t="str">
-        <v>123</v>
+        <v>Account Open Enhancements and Outcome Orchestration</v>
       </c>
       <c r="C4" t="str">
-        <v>123</v>
+        <v>Invite to JRM</v>
       </c>
       <c r="D4" t="str">
-        <v>123</v>
+        <v>FLCM</v>
       </c>
       <c r="E4" t="str">
         <v>jrm</v>
       </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v>2025-03-15</v>
+      <c r="G4">
+        <v>45672</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ENT-17062</v>
+        <v>ENT-16949</v>
       </c>
       <c r="B5" t="str">
-        <v>Account Open Enhancements and Outcome Orchestration</v>
+        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
       </c>
       <c r="C5" t="str">
         <v>Invite to JRM</v>
@@ -510,18 +507,18 @@
         <v>FLCM</v>
       </c>
       <c r="E5" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G5">
-        <v>45672</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ENT-16949</v>
+        <v>ENT-16881</v>
       </c>
       <c r="B6" t="str">
-        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
+        <v>Split up Personal Overdraft P&amp;L</v>
       </c>
       <c r="C6" t="str">
         <v>Invite to JRM</v>
@@ -530,18 +527,18 @@
         <v>FLCM</v>
       </c>
       <c r="E6" t="str">
-        <v>estimates</v>
+        <v>jrm</v>
       </c>
       <c r="G6">
-        <v>45531</v>
+        <v>45929</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENT-16881</v>
+        <v>ENT-16700</v>
       </c>
       <c r="B7" t="str">
-        <v>Split up Personal Overdraft P&amp;L</v>
+        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
       </c>
       <c r="C7" t="str">
         <v>Invite to JRM</v>
@@ -553,15 +550,15 @@
         <v>jrm</v>
       </c>
       <c r="G7">
-        <v>45929</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENT-16700</v>
+        <v>ENT-16621</v>
       </c>
       <c r="B8" t="str">
-        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
+        <v>CIW Data Products to PROD</v>
       </c>
       <c r="C8" t="str">
         <v>Invite to JRM</v>
@@ -570,18 +567,18 @@
         <v>FLCM</v>
       </c>
       <c r="E8" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G8">
-        <v>45523</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-16621</v>
+        <v>ENT-16374</v>
       </c>
       <c r="B9" t="str">
-        <v>CIW Data Products to PROD</v>
+        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -590,18 +587,18 @@
         <v>FLCM</v>
       </c>
       <c r="E9" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G9">
-        <v>45596</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-16374</v>
+        <v>ENT-16031</v>
       </c>
       <c r="B10" t="str">
-        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
+        <v>Fraud - Notes generator</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -613,15 +610,15 @@
         <v>jrm</v>
       </c>
       <c r="G10">
-        <v>45455</v>
+        <v>45649</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-16031</v>
+        <v>ENT-15917</v>
       </c>
       <c r="B11" t="str">
-        <v>Fraud - Notes generator</v>
+        <v>REBO Bill Payment Investigation Requests</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -633,15 +630,15 @@
         <v>jrm</v>
       </c>
       <c r="G11">
-        <v>45649</v>
+        <v>45613</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-15917</v>
+        <v>ENT-17286</v>
       </c>
       <c r="B12" t="str">
-        <v>REBO Bill Payment Investigation Requests</v>
+        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -650,18 +647,18 @@
         <v>FLCM</v>
       </c>
       <c r="E12" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G12">
-        <v>45613</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-17286</v>
+        <v>ENT-17202</v>
       </c>
       <c r="B13" t="str">
-        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
+        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -670,18 +667,18 @@
         <v>FLCM</v>
       </c>
       <c r="E13" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G13">
-        <v>45699</v>
+        <v>45690</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-17202</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B14" t="str">
-        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -690,18 +687,21 @@
         <v>FLCM</v>
       </c>
       <c r="E14" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F14" t="str">
+        <v>PDF</v>
       </c>
       <c r="G14">
-        <v>45690</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B15" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -710,21 +710,18 @@
         <v>FLCM</v>
       </c>
       <c r="E15" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F15" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G15">
-        <v>45686</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B16" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -736,15 +733,15 @@
         <v>estimates</v>
       </c>
       <c r="G16">
-        <v>45700</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B17" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -756,15 +753,15 @@
         <v>estimates</v>
       </c>
       <c r="G17">
-        <v>45656</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B18" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
@@ -776,15 +773,15 @@
         <v>estimates</v>
       </c>
       <c r="G18">
-        <v>45588</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-17054</v>
       </c>
       <c r="B19" t="str">
-        <v>Data Source to EDGE</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
@@ -793,18 +790,21 @@
         <v>FLCM</v>
       </c>
       <c r="E19" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F19" t="str">
+        <v>PDF</v>
       </c>
       <c r="G19">
-        <v>45664</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ENT-17054</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B20" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
@@ -815,19 +815,16 @@
       <c r="E20" t="str">
         <v>approved</v>
       </c>
-      <c r="F20" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G20">
-        <v>45691</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-14372</v>
       </c>
       <c r="B21" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
@@ -838,16 +835,19 @@
       <c r="E21" t="str">
         <v>approved</v>
       </c>
+      <c r="F21" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G21">
-        <v>45299</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-14372</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B22" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
@@ -862,58 +862,58 @@
         <v>PDF</v>
       </c>
       <c r="G22">
-        <v>45512</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B23" t="str">
-        <v>RAMP Phase 2</v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D23" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E23" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F23" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G23">
-        <v>45562</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B24" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D24" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E24" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F24" t="str">
+        <v>PDF</v>
       </c>
       <c r="G24">
-        <v>45695</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B25" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
@@ -928,15 +928,15 @@
         <v>PDF</v>
       </c>
       <c r="G25">
-        <v>45688</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B26" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
@@ -951,15 +951,15 @@
         <v>PDF</v>
       </c>
       <c r="G26">
-        <v>45701</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B27" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
@@ -970,19 +970,16 @@
       <c r="E27" t="str">
         <v>approved</v>
       </c>
-      <c r="F27" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G27">
-        <v>45695</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B28" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
@@ -991,138 +988,138 @@
         <v>FLCM</v>
       </c>
       <c r="E28" t="str">
-        <v>approved</v>
+        <v>estimates</v>
       </c>
       <c r="G28">
-        <v>45706</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B29" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E29" t="str">
         <v>estimates</v>
       </c>
       <c r="G29">
-        <v>45559</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B30" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D30" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E30" t="str">
         <v>estimates</v>
       </c>
       <c r="G30">
-        <v>45623</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B31" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D31" t="str">
-        <v>FLCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E31" t="str">
         <v>estimates</v>
       </c>
       <c r="G31">
-        <v>45355</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B32" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D32" t="str">
-        <v>CorpSec</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E32" t="str">
         <v>estimates</v>
       </c>
       <c r="G32">
-        <v>45446</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B33" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D33" t="str">
-        <v>BSCM/ESCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E33" t="str">
         <v>estimates</v>
       </c>
       <c r="G33">
-        <v>45477</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B34" t="str">
-        <v>CSDM Upgrade</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D34" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E34" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G34">
-        <v>45394</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B35" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
@@ -1134,15 +1131,15 @@
         <v>ofs</v>
       </c>
       <c r="G35">
-        <v>45531</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B36" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
@@ -1154,15 +1151,15 @@
         <v>ofs</v>
       </c>
       <c r="G36">
-        <v>45453</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B37" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
@@ -1171,98 +1168,95 @@
         <v>FLCM</v>
       </c>
       <c r="E37" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G37">
-        <v>45461</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B38" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D38" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E38" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G38">
-        <v>45714</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-15822</v>
       </c>
       <c r="B39" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D39" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E39" t="str">
         <v>estimates</v>
       </c>
       <c r="G39">
-        <v>45686</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENT-15822</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B40" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D40" t="str">
-        <v>FLCM</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E40" t="str">
         <v>estimates</v>
       </c>
       <c r="G40">
-        <v>45650</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-17853</v>
       </c>
       <c r="B41" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
       </c>
-      <c r="D41" t="str">
-        <v>BSCM/ESCM</v>
-      </c>
       <c r="E41" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45541</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-17853</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B42" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1271,15 +1265,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45691</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B43" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1288,15 +1282,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45559</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B44" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1305,15 +1299,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45596</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B45" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1322,15 +1316,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45378</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B46" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1339,15 +1333,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45468</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B47" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1356,15 +1350,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45310</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B48" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1373,15 +1367,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45427</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B49" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1390,15 +1384,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45279</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B50" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1407,15 +1401,15 @@
         <v>ofs</v>
       </c>
       <c r="G50">
-        <v>45558</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B51" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1424,15 +1418,15 @@
         <v>ofs</v>
       </c>
       <c r="G51">
-        <v>45383</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B52" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1441,15 +1435,15 @@
         <v>ofs</v>
       </c>
       <c r="G52">
-        <v>45638</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B53" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1458,15 +1452,15 @@
         <v>ofs</v>
       </c>
       <c r="G53">
-        <v>45461</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B54" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1480,10 +1474,10 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B55" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1492,15 +1486,15 @@
         <v>ofs</v>
       </c>
       <c r="G55">
-        <v>45371</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B56" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1509,15 +1503,15 @@
         <v>ofs</v>
       </c>
       <c r="G56">
-        <v>45406</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B57" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
@@ -1526,15 +1520,15 @@
         <v>ofs</v>
       </c>
       <c r="G57">
-        <v>45364</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B58" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C58" t="str">
         <v>Invite to JRM</v>
@@ -1543,15 +1537,15 @@
         <v>ofs</v>
       </c>
       <c r="G58">
-        <v>45593</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B59" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C59" t="str">
         <v>Invite to JRM</v>
@@ -1560,15 +1554,15 @@
         <v>ofs</v>
       </c>
       <c r="G59">
-        <v>45408</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B60" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C60" t="str">
         <v>Invite to JRM</v>
@@ -1577,15 +1571,15 @@
         <v>ofs</v>
       </c>
       <c r="G60">
-        <v>45595</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B61" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C61" t="str">
         <v>Invite to JRM</v>
@@ -1594,15 +1588,15 @@
         <v>ofs</v>
       </c>
       <c r="G61">
-        <v>45392</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B62" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C62" t="str">
         <v>Invite to JRM</v>
@@ -1616,27 +1610,27 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B63" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C63" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E63" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G63">
-        <v>45411</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-18725</v>
       </c>
       <c r="B64" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>US Video System - Lenel to Genetec</v>
       </c>
       <c r="C64" t="str">
         <v>Invite to JRM</v>
@@ -1648,26 +1642,9 @@
         <v>45721</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="str">
-        <v>ENT-18725</v>
-      </c>
-      <c r="B65" t="str">
-        <v>US Video System - Lenel to Genetec</v>
-      </c>
-      <c r="C65" t="str">
-        <v>Invite to JRM</v>
-      </c>
-      <c r="E65" t="str">
-        <v>jrm</v>
-      </c>
-      <c r="G65">
-        <v>45721</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G65"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G64"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G65"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -429,16 +429,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ENT-168812</v>
+        <v>234234</v>
       </c>
       <c r="B2" t="str">
-        <v>terw</v>
+        <v>5345</v>
       </c>
       <c r="C2" t="str">
-        <v>123</v>
+        <v>345</v>
       </c>
       <c r="D2" t="str">
-        <v>123</v>
+        <v>345345</v>
       </c>
       <c r="E2" t="str">
         <v>jrm</v>
@@ -447,15 +447,15 @@
         <v/>
       </c>
       <c r="G2" t="str">
-        <v>2025-03-15</v>
+        <v>2025-03-16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>17062</v>
+        <v>ENT-168812</v>
       </c>
       <c r="B3" t="str">
-        <v>123</v>
+        <v>terw</v>
       </c>
       <c r="C3" t="str">
         <v>123</v>
@@ -475,30 +475,33 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ENT-17062</v>
+        <v>17062</v>
       </c>
       <c r="B4" t="str">
-        <v>Account Open Enhancements and Outcome Orchestration</v>
+        <v>123</v>
       </c>
       <c r="C4" t="str">
-        <v>Invite to JRM</v>
+        <v>123</v>
       </c>
       <c r="D4" t="str">
-        <v>FLCM</v>
+        <v>123</v>
       </c>
       <c r="E4" t="str">
         <v>jrm</v>
       </c>
-      <c r="G4">
-        <v>45672</v>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v>2025-03-15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ENT-16949</v>
+        <v>ENT-17062</v>
       </c>
       <c r="B5" t="str">
-        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
+        <v>Account Open Enhancements and Outcome Orchestration</v>
       </c>
       <c r="C5" t="str">
         <v>Invite to JRM</v>
@@ -507,18 +510,18 @@
         <v>FLCM</v>
       </c>
       <c r="E5" t="str">
-        <v>estimates</v>
+        <v>jrm</v>
       </c>
       <c r="G5">
-        <v>45531</v>
+        <v>45672</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ENT-16881</v>
+        <v>ENT-16949</v>
       </c>
       <c r="B6" t="str">
-        <v>Split up Personal Overdraft P&amp;L</v>
+        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
       </c>
       <c r="C6" t="str">
         <v>Invite to JRM</v>
@@ -527,18 +530,18 @@
         <v>FLCM</v>
       </c>
       <c r="E6" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G6">
-        <v>45929</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENT-16700</v>
+        <v>ENT-16881</v>
       </c>
       <c r="B7" t="str">
-        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
+        <v>Split up Personal Overdraft P&amp;L</v>
       </c>
       <c r="C7" t="str">
         <v>Invite to JRM</v>
@@ -550,15 +553,15 @@
         <v>jrm</v>
       </c>
       <c r="G7">
-        <v>45523</v>
+        <v>45929</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENT-16621</v>
+        <v>ENT-16700</v>
       </c>
       <c r="B8" t="str">
-        <v>CIW Data Products to PROD</v>
+        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
       </c>
       <c r="C8" t="str">
         <v>Invite to JRM</v>
@@ -567,18 +570,18 @@
         <v>FLCM</v>
       </c>
       <c r="E8" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G8">
-        <v>45596</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-16374</v>
+        <v>ENT-16621</v>
       </c>
       <c r="B9" t="str">
-        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
+        <v>CIW Data Products to PROD</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -587,18 +590,18 @@
         <v>FLCM</v>
       </c>
       <c r="E9" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G9">
-        <v>45455</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-16031</v>
+        <v>ENT-16374</v>
       </c>
       <c r="B10" t="str">
-        <v>Fraud - Notes generator</v>
+        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -610,15 +613,15 @@
         <v>jrm</v>
       </c>
       <c r="G10">
-        <v>45649</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-15917</v>
+        <v>ENT-16031</v>
       </c>
       <c r="B11" t="str">
-        <v>REBO Bill Payment Investigation Requests</v>
+        <v>Fraud - Notes generator</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -630,15 +633,15 @@
         <v>jrm</v>
       </c>
       <c r="G11">
-        <v>45613</v>
+        <v>45649</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-17286</v>
+        <v>ENT-15917</v>
       </c>
       <c r="B12" t="str">
-        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
+        <v>REBO Bill Payment Investigation Requests</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -647,18 +650,18 @@
         <v>FLCM</v>
       </c>
       <c r="E12" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G12">
-        <v>45699</v>
+        <v>45613</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-17202</v>
+        <v>ENT-17286</v>
       </c>
       <c r="B13" t="str">
-        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
+        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -667,18 +670,18 @@
         <v>FLCM</v>
       </c>
       <c r="E13" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G13">
-        <v>45690</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17202</v>
       </c>
       <c r="B14" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -687,21 +690,18 @@
         <v>FLCM</v>
       </c>
       <c r="E14" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F14" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G14">
-        <v>45686</v>
+        <v>45690</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B15" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -710,18 +710,21 @@
         <v>FLCM</v>
       </c>
       <c r="E15" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F15" t="str">
+        <v>PDF</v>
       </c>
       <c r="G15">
-        <v>45700</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B16" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -733,15 +736,15 @@
         <v>estimates</v>
       </c>
       <c r="G16">
-        <v>45656</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B17" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -753,15 +756,15 @@
         <v>estimates</v>
       </c>
       <c r="G17">
-        <v>45588</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B18" t="str">
-        <v>Data Source to EDGE</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
@@ -773,15 +776,15 @@
         <v>estimates</v>
       </c>
       <c r="G18">
-        <v>45664</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ENT-17054</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B19" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
@@ -790,21 +793,18 @@
         <v>FLCM</v>
       </c>
       <c r="E19" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F19" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G19">
-        <v>45691</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-17054</v>
       </c>
       <c r="B20" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
@@ -815,16 +815,19 @@
       <c r="E20" t="str">
         <v>approved</v>
       </c>
+      <c r="F20" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G20">
-        <v>45299</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-14372</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B21" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
@@ -835,19 +838,16 @@
       <c r="E21" t="str">
         <v>approved</v>
       </c>
-      <c r="F21" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G21">
-        <v>45512</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-14372</v>
       </c>
       <c r="B22" t="str">
-        <v>RAMP Phase 2</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
@@ -862,58 +862,58 @@
         <v>PDF</v>
       </c>
       <c r="G22">
-        <v>45562</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B23" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D23" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E23" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F23" t="str">
+        <v>PDF</v>
       </c>
       <c r="G23">
-        <v>45695</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B24" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D24" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E24" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F24" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G24">
-        <v>45688</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B25" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
@@ -928,15 +928,15 @@
         <v>PDF</v>
       </c>
       <c r="G25">
-        <v>45701</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B26" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
@@ -951,15 +951,15 @@
         <v>PDF</v>
       </c>
       <c r="G26">
-        <v>45695</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B27" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
@@ -970,16 +970,19 @@
       <c r="E27" t="str">
         <v>approved</v>
       </c>
+      <c r="F27" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G27">
-        <v>45706</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B28" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
@@ -988,138 +991,138 @@
         <v>FLCM</v>
       </c>
       <c r="E28" t="str">
-        <v>estimates</v>
+        <v>approved</v>
       </c>
       <c r="G28">
-        <v>45559</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B29" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E29" t="str">
         <v>estimates</v>
       </c>
       <c r="G29">
-        <v>45623</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B30" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D30" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E30" t="str">
         <v>estimates</v>
       </c>
       <c r="G30">
-        <v>45355</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B31" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D31" t="str">
-        <v>CorpSec</v>
+        <v>FLCM</v>
       </c>
       <c r="E31" t="str">
         <v>estimates</v>
       </c>
       <c r="G31">
-        <v>45446</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B32" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D32" t="str">
-        <v>BSCM/ESCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E32" t="str">
         <v>estimates</v>
       </c>
       <c r="G32">
-        <v>45477</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B33" t="str">
-        <v>CSDM Upgrade</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D33" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E33" t="str">
         <v>estimates</v>
       </c>
       <c r="G33">
-        <v>45394</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B34" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D34" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E34" t="str">
-        <v>ofs</v>
+        <v>estimates</v>
       </c>
       <c r="G34">
-        <v>45531</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B35" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
@@ -1131,15 +1134,15 @@
         <v>ofs</v>
       </c>
       <c r="G35">
-        <v>45453</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B36" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
@@ -1151,15 +1154,15 @@
         <v>ofs</v>
       </c>
       <c r="G36">
-        <v>45461</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B37" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
@@ -1168,95 +1171,98 @@
         <v>FLCM</v>
       </c>
       <c r="E37" t="str">
-        <v>jrm</v>
+        <v>ofs</v>
       </c>
       <c r="G37">
-        <v>45714</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B38" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D38" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E38" t="str">
-        <v>estimates</v>
+        <v>jrm</v>
       </c>
       <c r="G38">
-        <v>45686</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ENT-15822</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B39" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D39" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E39" t="str">
         <v>estimates</v>
       </c>
       <c r="G39">
-        <v>45650</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-15822</v>
       </c>
       <c r="B40" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D40" t="str">
-        <v>BSCM/ESCM</v>
+        <v>FLCM</v>
       </c>
       <c r="E40" t="str">
         <v>estimates</v>
       </c>
       <c r="G40">
-        <v>45541</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-17853</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B41" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
       </c>
+      <c r="D41" t="str">
+        <v>BSCM/ESCM</v>
+      </c>
       <c r="E41" t="str">
-        <v>ofs</v>
+        <v>estimates</v>
       </c>
       <c r="G41">
-        <v>45691</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-17853</v>
       </c>
       <c r="B42" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1265,15 +1271,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45559</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B43" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1282,15 +1288,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45596</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B44" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1299,15 +1305,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45378</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B45" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1316,15 +1322,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45468</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B46" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1333,15 +1339,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45310</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B47" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1350,15 +1356,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45427</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B48" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1367,15 +1373,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45279</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B49" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1384,15 +1390,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45558</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B50" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1401,15 +1407,15 @@
         <v>ofs</v>
       </c>
       <c r="G50">
-        <v>45383</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B51" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1418,15 +1424,15 @@
         <v>ofs</v>
       </c>
       <c r="G51">
-        <v>45638</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B52" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1435,15 +1441,15 @@
         <v>ofs</v>
       </c>
       <c r="G52">
-        <v>45461</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B53" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1452,15 +1458,15 @@
         <v>ofs</v>
       </c>
       <c r="G53">
-        <v>45371</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B54" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1474,10 +1480,10 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B55" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1486,15 +1492,15 @@
         <v>ofs</v>
       </c>
       <c r="G55">
-        <v>45406</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B56" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1503,15 +1509,15 @@
         <v>ofs</v>
       </c>
       <c r="G56">
-        <v>45364</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B57" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
@@ -1520,15 +1526,15 @@
         <v>ofs</v>
       </c>
       <c r="G57">
-        <v>45593</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B58" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C58" t="str">
         <v>Invite to JRM</v>
@@ -1537,15 +1543,15 @@
         <v>ofs</v>
       </c>
       <c r="G58">
-        <v>45408</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B59" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C59" t="str">
         <v>Invite to JRM</v>
@@ -1554,15 +1560,15 @@
         <v>ofs</v>
       </c>
       <c r="G59">
-        <v>45595</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B60" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C60" t="str">
         <v>Invite to JRM</v>
@@ -1571,15 +1577,15 @@
         <v>ofs</v>
       </c>
       <c r="G60">
-        <v>45392</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B61" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C61" t="str">
         <v>Invite to JRM</v>
@@ -1588,15 +1594,15 @@
         <v>ofs</v>
       </c>
       <c r="G61">
-        <v>45411</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B62" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C62" t="str">
         <v>Invite to JRM</v>
@@ -1610,27 +1616,27 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B63" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C63" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E63" t="str">
-        <v>jrm</v>
+        <v>ofs</v>
       </c>
       <c r="G63">
-        <v>45721</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>ENT-18725</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B64" t="str">
-        <v>US Video System - Lenel to Genetec</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C64" t="str">
         <v>Invite to JRM</v>
@@ -1642,9 +1648,26 @@
         <v>45721</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>ENT-18725</v>
+      </c>
+      <c r="B65" t="str">
+        <v>US Video System - Lenel to Genetec</v>
+      </c>
+      <c r="C65" t="str">
+        <v>Invite to JRM</v>
+      </c>
+      <c r="E65" t="str">
+        <v>jrm</v>
+      </c>
+      <c r="G65">
+        <v>45721</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G64"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G65"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G64"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -452,10 +452,10 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ENT-168812</v>
+        <v>17062</v>
       </c>
       <c r="B3" t="str">
-        <v>terw</v>
+        <v>123</v>
       </c>
       <c r="C3" t="str">
         <v>123</v>
@@ -475,33 +475,30 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>17062</v>
+        <v>ENT-17062</v>
       </c>
       <c r="B4" t="str">
-        <v>123</v>
+        <v>Account Open Enhancements and Outcome Orchestration</v>
       </c>
       <c r="C4" t="str">
-        <v>123</v>
+        <v>Invite to JRM</v>
       </c>
       <c r="D4" t="str">
-        <v>123</v>
+        <v>FLCM</v>
       </c>
       <c r="E4" t="str">
         <v>jrm</v>
       </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v>2025-03-15</v>
+      <c r="G4">
+        <v>45672</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ENT-17062</v>
+        <v>ENT-16949</v>
       </c>
       <c r="B5" t="str">
-        <v>Account Open Enhancements and Outcome Orchestration</v>
+        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
       </c>
       <c r="C5" t="str">
         <v>Invite to JRM</v>
@@ -510,18 +507,18 @@
         <v>FLCM</v>
       </c>
       <c r="E5" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G5">
-        <v>45672</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ENT-16949</v>
+        <v>ENT-16881</v>
       </c>
       <c r="B6" t="str">
-        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
+        <v>Split up Personal Overdraft P&amp;L</v>
       </c>
       <c r="C6" t="str">
         <v>Invite to JRM</v>
@@ -530,18 +527,18 @@
         <v>FLCM</v>
       </c>
       <c r="E6" t="str">
-        <v>estimates</v>
+        <v>jrm</v>
       </c>
       <c r="G6">
-        <v>45531</v>
+        <v>45929</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENT-16881</v>
+        <v>ENT-16700</v>
       </c>
       <c r="B7" t="str">
-        <v>Split up Personal Overdraft P&amp;L</v>
+        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
       </c>
       <c r="C7" t="str">
         <v>Invite to JRM</v>
@@ -553,15 +550,15 @@
         <v>jrm</v>
       </c>
       <c r="G7">
-        <v>45929</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENT-16700</v>
+        <v>ENT-16621</v>
       </c>
       <c r="B8" t="str">
-        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
+        <v>CIW Data Products to PROD</v>
       </c>
       <c r="C8" t="str">
         <v>Invite to JRM</v>
@@ -570,18 +567,18 @@
         <v>FLCM</v>
       </c>
       <c r="E8" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G8">
-        <v>45523</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-16621</v>
+        <v>ENT-16374</v>
       </c>
       <c r="B9" t="str">
-        <v>CIW Data Products to PROD</v>
+        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -590,18 +587,18 @@
         <v>FLCM</v>
       </c>
       <c r="E9" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G9">
-        <v>45596</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-16374</v>
+        <v>ENT-16031</v>
       </c>
       <c r="B10" t="str">
-        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
+        <v>Fraud - Notes generator</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -613,15 +610,15 @@
         <v>jrm</v>
       </c>
       <c r="G10">
-        <v>45455</v>
+        <v>45649</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-16031</v>
+        <v>ENT-15917</v>
       </c>
       <c r="B11" t="str">
-        <v>Fraud - Notes generator</v>
+        <v>REBO Bill Payment Investigation Requests</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -633,15 +630,15 @@
         <v>jrm</v>
       </c>
       <c r="G11">
-        <v>45649</v>
+        <v>45613</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-15917</v>
+        <v>ENT-17286</v>
       </c>
       <c r="B12" t="str">
-        <v>REBO Bill Payment Investigation Requests</v>
+        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -650,18 +647,18 @@
         <v>FLCM</v>
       </c>
       <c r="E12" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G12">
-        <v>45613</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-17286</v>
+        <v>ENT-17202</v>
       </c>
       <c r="B13" t="str">
-        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
+        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -670,18 +667,18 @@
         <v>FLCM</v>
       </c>
       <c r="E13" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G13">
-        <v>45699</v>
+        <v>45690</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-17202</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B14" t="str">
-        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -690,18 +687,21 @@
         <v>FLCM</v>
       </c>
       <c r="E14" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F14" t="str">
+        <v>PDF</v>
       </c>
       <c r="G14">
-        <v>45690</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B15" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -710,21 +710,18 @@
         <v>FLCM</v>
       </c>
       <c r="E15" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F15" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G15">
-        <v>45686</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B16" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -736,15 +733,15 @@
         <v>estimates</v>
       </c>
       <c r="G16">
-        <v>45700</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B17" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -756,15 +753,15 @@
         <v>estimates</v>
       </c>
       <c r="G17">
-        <v>45656</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B18" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
@@ -776,15 +773,15 @@
         <v>estimates</v>
       </c>
       <c r="G18">
-        <v>45588</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-17054</v>
       </c>
       <c r="B19" t="str">
-        <v>Data Source to EDGE</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
@@ -793,18 +790,21 @@
         <v>FLCM</v>
       </c>
       <c r="E19" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F19" t="str">
+        <v>PDF</v>
       </c>
       <c r="G19">
-        <v>45664</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ENT-17054</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B20" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
@@ -815,19 +815,16 @@
       <c r="E20" t="str">
         <v>approved</v>
       </c>
-      <c r="F20" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G20">
-        <v>45691</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-14372</v>
       </c>
       <c r="B21" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
@@ -838,16 +835,19 @@
       <c r="E21" t="str">
         <v>approved</v>
       </c>
+      <c r="F21" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G21">
-        <v>45299</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-14372</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B22" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
@@ -862,58 +862,58 @@
         <v>PDF</v>
       </c>
       <c r="G22">
-        <v>45512</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B23" t="str">
-        <v>RAMP Phase 2</v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D23" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E23" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F23" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G23">
-        <v>45562</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B24" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D24" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E24" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F24" t="str">
+        <v>PDF</v>
       </c>
       <c r="G24">
-        <v>45695</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B25" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
@@ -928,15 +928,15 @@
         <v>PDF</v>
       </c>
       <c r="G25">
-        <v>45688</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B26" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
@@ -951,15 +951,15 @@
         <v>PDF</v>
       </c>
       <c r="G26">
-        <v>45701</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B27" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
@@ -970,19 +970,16 @@
       <c r="E27" t="str">
         <v>approved</v>
       </c>
-      <c r="F27" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G27">
-        <v>45695</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B28" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
@@ -991,138 +988,138 @@
         <v>FLCM</v>
       </c>
       <c r="E28" t="str">
-        <v>approved</v>
+        <v>estimates</v>
       </c>
       <c r="G28">
-        <v>45706</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B29" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E29" t="str">
         <v>estimates</v>
       </c>
       <c r="G29">
-        <v>45559</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B30" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D30" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E30" t="str">
         <v>estimates</v>
       </c>
       <c r="G30">
-        <v>45623</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B31" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D31" t="str">
-        <v>FLCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E31" t="str">
         <v>estimates</v>
       </c>
       <c r="G31">
-        <v>45355</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B32" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D32" t="str">
-        <v>CorpSec</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E32" t="str">
         <v>estimates</v>
       </c>
       <c r="G32">
-        <v>45446</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B33" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D33" t="str">
-        <v>BSCM/ESCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E33" t="str">
         <v>estimates</v>
       </c>
       <c r="G33">
-        <v>45477</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B34" t="str">
-        <v>CSDM Upgrade</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D34" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E34" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G34">
-        <v>45394</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B35" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
@@ -1134,15 +1131,15 @@
         <v>ofs</v>
       </c>
       <c r="G35">
-        <v>45531</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B36" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
@@ -1154,15 +1151,15 @@
         <v>ofs</v>
       </c>
       <c r="G36">
-        <v>45453</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B37" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
@@ -1171,98 +1168,95 @@
         <v>FLCM</v>
       </c>
       <c r="E37" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G37">
-        <v>45461</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B38" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D38" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E38" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G38">
-        <v>45714</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-15822</v>
       </c>
       <c r="B39" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D39" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E39" t="str">
         <v>estimates</v>
       </c>
       <c r="G39">
-        <v>45686</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENT-15822</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B40" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D40" t="str">
-        <v>FLCM</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E40" t="str">
         <v>estimates</v>
       </c>
       <c r="G40">
-        <v>45650</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-17853</v>
       </c>
       <c r="B41" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
       </c>
-      <c r="D41" t="str">
-        <v>BSCM/ESCM</v>
-      </c>
       <c r="E41" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45541</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-17853</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B42" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1271,15 +1265,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45691</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B43" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1288,15 +1282,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45559</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B44" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1305,15 +1299,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45596</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B45" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1322,15 +1316,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45378</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B46" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1339,15 +1333,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45468</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B47" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1356,15 +1350,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45310</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B48" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1373,15 +1367,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45427</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B49" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1390,15 +1384,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45279</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B50" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1407,15 +1401,15 @@
         <v>ofs</v>
       </c>
       <c r="G50">
-        <v>45558</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B51" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1424,15 +1418,15 @@
         <v>ofs</v>
       </c>
       <c r="G51">
-        <v>45383</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B52" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1441,15 +1435,15 @@
         <v>ofs</v>
       </c>
       <c r="G52">
-        <v>45638</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B53" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1458,15 +1452,15 @@
         <v>ofs</v>
       </c>
       <c r="G53">
-        <v>45461</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B54" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1480,10 +1474,10 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B55" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1492,15 +1486,15 @@
         <v>ofs</v>
       </c>
       <c r="G55">
-        <v>45371</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B56" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1509,15 +1503,15 @@
         <v>ofs</v>
       </c>
       <c r="G56">
-        <v>45406</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B57" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
@@ -1526,15 +1520,15 @@
         <v>ofs</v>
       </c>
       <c r="G57">
-        <v>45364</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B58" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C58" t="str">
         <v>Invite to JRM</v>
@@ -1543,15 +1537,15 @@
         <v>ofs</v>
       </c>
       <c r="G58">
-        <v>45593</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B59" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C59" t="str">
         <v>Invite to JRM</v>
@@ -1560,15 +1554,15 @@
         <v>ofs</v>
       </c>
       <c r="G59">
-        <v>45408</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B60" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C60" t="str">
         <v>Invite to JRM</v>
@@ -1577,15 +1571,15 @@
         <v>ofs</v>
       </c>
       <c r="G60">
-        <v>45595</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B61" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C61" t="str">
         <v>Invite to JRM</v>
@@ -1594,15 +1588,15 @@
         <v>ofs</v>
       </c>
       <c r="G61">
-        <v>45392</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B62" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C62" t="str">
         <v>Invite to JRM</v>
@@ -1616,27 +1610,27 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B63" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C63" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E63" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G63">
-        <v>45411</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-18725</v>
       </c>
       <c r="B64" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>US Video System - Lenel to Genetec</v>
       </c>
       <c r="C64" t="str">
         <v>Invite to JRM</v>
@@ -1648,26 +1642,9 @@
         <v>45721</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="str">
-        <v>ENT-18725</v>
-      </c>
-      <c r="B65" t="str">
-        <v>US Video System - Lenel to Genetec</v>
-      </c>
-      <c r="C65" t="str">
-        <v>Invite to JRM</v>
-      </c>
-      <c r="E65" t="str">
-        <v>jrm</v>
-      </c>
-      <c r="G65">
-        <v>45721</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G65"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G64"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G63"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -429,16 +429,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>234234</v>
+        <v>17062</v>
       </c>
       <c r="B2" t="str">
-        <v>5345</v>
+        <v>123</v>
       </c>
       <c r="C2" t="str">
-        <v>345</v>
+        <v>123</v>
       </c>
       <c r="D2" t="str">
-        <v>345345</v>
+        <v>123</v>
       </c>
       <c r="E2" t="str">
         <v>jrm</v>
@@ -447,38 +447,35 @@
         <v/>
       </c>
       <c r="G2" t="str">
-        <v>2025-03-16</v>
+        <v>2025-03-15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>17062</v>
+        <v>ENT-17062</v>
       </c>
       <c r="B3" t="str">
-        <v>123</v>
+        <v>Account Open Enhancements and Outcome Orchestration</v>
       </c>
       <c r="C3" t="str">
-        <v>123</v>
+        <v>Invite to JRM</v>
       </c>
       <c r="D3" t="str">
-        <v>123</v>
+        <v>FLCM</v>
       </c>
       <c r="E3" t="str">
         <v>jrm</v>
       </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v>2025-03-15</v>
+      <c r="G3">
+        <v>45672</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ENT-17062</v>
+        <v>ENT-16949</v>
       </c>
       <c r="B4" t="str">
-        <v>Account Open Enhancements and Outcome Orchestration</v>
+        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
       </c>
       <c r="C4" t="str">
         <v>Invite to JRM</v>
@@ -487,18 +484,18 @@
         <v>FLCM</v>
       </c>
       <c r="E4" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G4">
-        <v>45672</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ENT-16949</v>
+        <v>ENT-16881</v>
       </c>
       <c r="B5" t="str">
-        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
+        <v>Split up Personal Overdraft P&amp;L</v>
       </c>
       <c r="C5" t="str">
         <v>Invite to JRM</v>
@@ -507,18 +504,18 @@
         <v>FLCM</v>
       </c>
       <c r="E5" t="str">
-        <v>estimates</v>
+        <v>jrm</v>
       </c>
       <c r="G5">
-        <v>45531</v>
+        <v>45929</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ENT-16881</v>
+        <v>ENT-16700</v>
       </c>
       <c r="B6" t="str">
-        <v>Split up Personal Overdraft P&amp;L</v>
+        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
       </c>
       <c r="C6" t="str">
         <v>Invite to JRM</v>
@@ -530,15 +527,15 @@
         <v>jrm</v>
       </c>
       <c r="G6">
-        <v>45929</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENT-16700</v>
+        <v>ENT-16621</v>
       </c>
       <c r="B7" t="str">
-        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
+        <v>CIW Data Products to PROD</v>
       </c>
       <c r="C7" t="str">
         <v>Invite to JRM</v>
@@ -547,18 +544,18 @@
         <v>FLCM</v>
       </c>
       <c r="E7" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G7">
-        <v>45523</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENT-16621</v>
+        <v>ENT-16374</v>
       </c>
       <c r="B8" t="str">
-        <v>CIW Data Products to PROD</v>
+        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
       </c>
       <c r="C8" t="str">
         <v>Invite to JRM</v>
@@ -567,18 +564,18 @@
         <v>FLCM</v>
       </c>
       <c r="E8" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G8">
-        <v>45596</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-16374</v>
+        <v>ENT-16031</v>
       </c>
       <c r="B9" t="str">
-        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
+        <v>Fraud - Notes generator</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -590,15 +587,15 @@
         <v>jrm</v>
       </c>
       <c r="G9">
-        <v>45455</v>
+        <v>45649</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-16031</v>
+        <v>ENT-15917</v>
       </c>
       <c r="B10" t="str">
-        <v>Fraud - Notes generator</v>
+        <v>REBO Bill Payment Investigation Requests</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -610,15 +607,15 @@
         <v>jrm</v>
       </c>
       <c r="G10">
-        <v>45649</v>
+        <v>45613</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-15917</v>
+        <v>ENT-17286</v>
       </c>
       <c r="B11" t="str">
-        <v>REBO Bill Payment Investigation Requests</v>
+        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -627,18 +624,18 @@
         <v>FLCM</v>
       </c>
       <c r="E11" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G11">
-        <v>45613</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-17286</v>
+        <v>ENT-17202</v>
       </c>
       <c r="B12" t="str">
-        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
+        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -647,18 +644,18 @@
         <v>FLCM</v>
       </c>
       <c r="E12" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G12">
-        <v>45699</v>
+        <v>45690</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-17202</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B13" t="str">
-        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -667,18 +664,21 @@
         <v>FLCM</v>
       </c>
       <c r="E13" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F13" t="str">
+        <v>PDF</v>
       </c>
       <c r="G13">
-        <v>45690</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B14" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -687,21 +687,18 @@
         <v>FLCM</v>
       </c>
       <c r="E14" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F14" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G14">
-        <v>45686</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B15" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -713,15 +710,15 @@
         <v>estimates</v>
       </c>
       <c r="G15">
-        <v>45700</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B16" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -733,15 +730,15 @@
         <v>estimates</v>
       </c>
       <c r="G16">
-        <v>45656</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B17" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -753,15 +750,15 @@
         <v>estimates</v>
       </c>
       <c r="G17">
-        <v>45588</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-17054</v>
       </c>
       <c r="B18" t="str">
-        <v>Data Source to EDGE</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
@@ -770,18 +767,21 @@
         <v>FLCM</v>
       </c>
       <c r="E18" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F18" t="str">
+        <v>PDF</v>
       </c>
       <c r="G18">
-        <v>45664</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ENT-17054</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B19" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
@@ -792,19 +792,16 @@
       <c r="E19" t="str">
         <v>approved</v>
       </c>
-      <c r="F19" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G19">
-        <v>45691</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-14372</v>
       </c>
       <c r="B20" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
@@ -815,16 +812,19 @@
       <c r="E20" t="str">
         <v>approved</v>
       </c>
+      <c r="F20" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G20">
-        <v>45299</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-14372</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B21" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
@@ -839,58 +839,58 @@
         <v>PDF</v>
       </c>
       <c r="G21">
-        <v>45512</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B22" t="str">
-        <v>RAMP Phase 2</v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D22" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E22" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F22" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G22">
-        <v>45562</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B23" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D23" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E23" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F23" t="str">
+        <v>PDF</v>
       </c>
       <c r="G23">
-        <v>45695</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B24" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
@@ -905,15 +905,15 @@
         <v>PDF</v>
       </c>
       <c r="G24">
-        <v>45688</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B25" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
@@ -928,15 +928,15 @@
         <v>PDF</v>
       </c>
       <c r="G25">
-        <v>45701</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B26" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
@@ -947,19 +947,16 @@
       <c r="E26" t="str">
         <v>approved</v>
       </c>
-      <c r="F26" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G26">
-        <v>45695</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B27" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
@@ -968,138 +965,138 @@
         <v>FLCM</v>
       </c>
       <c r="E27" t="str">
-        <v>approved</v>
+        <v>estimates</v>
       </c>
       <c r="G27">
-        <v>45706</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B28" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D28" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E28" t="str">
         <v>estimates</v>
       </c>
       <c r="G28">
-        <v>45559</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B29" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E29" t="str">
         <v>estimates</v>
       </c>
       <c r="G29">
-        <v>45623</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B30" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D30" t="str">
-        <v>FLCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E30" t="str">
         <v>estimates</v>
       </c>
       <c r="G30">
-        <v>45355</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B31" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D31" t="str">
-        <v>CorpSec</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E31" t="str">
         <v>estimates</v>
       </c>
       <c r="G31">
-        <v>45446</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B32" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D32" t="str">
-        <v>BSCM/ESCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E32" t="str">
         <v>estimates</v>
       </c>
       <c r="G32">
-        <v>45477</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B33" t="str">
-        <v>CSDM Upgrade</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D33" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E33" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G33">
-        <v>45394</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B34" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
@@ -1111,15 +1108,15 @@
         <v>ofs</v>
       </c>
       <c r="G34">
-        <v>45531</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B35" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
@@ -1131,15 +1128,15 @@
         <v>ofs</v>
       </c>
       <c r="G35">
-        <v>45453</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B36" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
@@ -1148,98 +1145,95 @@
         <v>FLCM</v>
       </c>
       <c r="E36" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G36">
-        <v>45461</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B37" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D37" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E37" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G37">
-        <v>45714</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-15822</v>
       </c>
       <c r="B38" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D38" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E38" t="str">
         <v>estimates</v>
       </c>
       <c r="G38">
-        <v>45686</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ENT-15822</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B39" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D39" t="str">
-        <v>FLCM</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E39" t="str">
         <v>estimates</v>
       </c>
       <c r="G39">
-        <v>45650</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-17853</v>
       </c>
       <c r="B40" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
       </c>
-      <c r="D40" t="str">
-        <v>BSCM/ESCM</v>
-      </c>
       <c r="E40" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G40">
-        <v>45541</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-17853</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B41" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1248,15 +1242,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45691</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B42" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1265,15 +1259,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45559</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B43" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1282,15 +1276,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45596</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B44" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1299,15 +1293,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45378</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B45" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1316,15 +1310,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45468</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B46" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1333,15 +1327,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45310</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B47" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1350,15 +1344,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45427</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B48" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1367,15 +1361,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45279</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B49" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1384,15 +1378,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45558</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B50" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1401,15 +1395,15 @@
         <v>ofs</v>
       </c>
       <c r="G50">
-        <v>45383</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B51" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1418,15 +1412,15 @@
         <v>ofs</v>
       </c>
       <c r="G51">
-        <v>45638</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B52" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1435,15 +1429,15 @@
         <v>ofs</v>
       </c>
       <c r="G52">
-        <v>45461</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B53" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1457,10 +1451,10 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B54" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1469,15 +1463,15 @@
         <v>ofs</v>
       </c>
       <c r="G54">
-        <v>45371</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B55" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1486,15 +1480,15 @@
         <v>ofs</v>
       </c>
       <c r="G55">
-        <v>45406</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B56" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1503,15 +1497,15 @@
         <v>ofs</v>
       </c>
       <c r="G56">
-        <v>45364</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B57" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
@@ -1520,15 +1514,15 @@
         <v>ofs</v>
       </c>
       <c r="G57">
-        <v>45593</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B58" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C58" t="str">
         <v>Invite to JRM</v>
@@ -1537,15 +1531,15 @@
         <v>ofs</v>
       </c>
       <c r="G58">
-        <v>45408</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B59" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C59" t="str">
         <v>Invite to JRM</v>
@@ -1554,15 +1548,15 @@
         <v>ofs</v>
       </c>
       <c r="G59">
-        <v>45595</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B60" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C60" t="str">
         <v>Invite to JRM</v>
@@ -1571,15 +1565,15 @@
         <v>ofs</v>
       </c>
       <c r="G60">
-        <v>45392</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B61" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C61" t="str">
         <v>Invite to JRM</v>
@@ -1593,27 +1587,27 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B62" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C62" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E62" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G62">
-        <v>45411</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-18725</v>
       </c>
       <c r="B63" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>US Video System - Lenel to Genetec</v>
       </c>
       <c r="C63" t="str">
         <v>Invite to JRM</v>
@@ -1625,26 +1619,9 @@
         <v>45721</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="str">
-        <v>ENT-18725</v>
-      </c>
-      <c r="B64" t="str">
-        <v>US Video System - Lenel to Genetec</v>
-      </c>
-      <c r="C64" t="str">
-        <v>Invite to JRM</v>
-      </c>
-      <c r="E64" t="str">
-        <v>jrm</v>
-      </c>
-      <c r="G64">
-        <v>45721</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G64"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G63"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G62"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -429,33 +429,30 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>17062</v>
+        <v>ENT-17062</v>
       </c>
       <c r="B2" t="str">
-        <v>123</v>
+        <v>Account Open Enhancements and Outcome Orchestration</v>
       </c>
       <c r="C2" t="str">
-        <v>123</v>
+        <v>Invite to JRM</v>
       </c>
       <c r="D2" t="str">
-        <v>123</v>
+        <v>FLCM</v>
       </c>
       <c r="E2" t="str">
         <v>jrm</v>
       </c>
-      <c r="F2" t="str">
-        <v/>
-      </c>
-      <c r="G2" t="str">
-        <v>2025-03-15</v>
+      <c r="G2">
+        <v>45672</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ENT-17062</v>
+        <v>ENT-16949</v>
       </c>
       <c r="B3" t="str">
-        <v>Account Open Enhancements and Outcome Orchestration</v>
+        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
       </c>
       <c r="C3" t="str">
         <v>Invite to JRM</v>
@@ -464,18 +461,18 @@
         <v>FLCM</v>
       </c>
       <c r="E3" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G3">
-        <v>45672</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ENT-16949</v>
+        <v>ENT-16881</v>
       </c>
       <c r="B4" t="str">
-        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
+        <v>Split up Personal Overdraft P&amp;L</v>
       </c>
       <c r="C4" t="str">
         <v>Invite to JRM</v>
@@ -484,18 +481,18 @@
         <v>FLCM</v>
       </c>
       <c r="E4" t="str">
-        <v>estimates</v>
+        <v>jrm</v>
       </c>
       <c r="G4">
-        <v>45531</v>
+        <v>45929</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ENT-16881</v>
+        <v>ENT-16700</v>
       </c>
       <c r="B5" t="str">
-        <v>Split up Personal Overdraft P&amp;L</v>
+        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
       </c>
       <c r="C5" t="str">
         <v>Invite to JRM</v>
@@ -507,15 +504,15 @@
         <v>jrm</v>
       </c>
       <c r="G5">
-        <v>45929</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ENT-16700</v>
+        <v>ENT-16621</v>
       </c>
       <c r="B6" t="str">
-        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
+        <v>CIW Data Products to PROD</v>
       </c>
       <c r="C6" t="str">
         <v>Invite to JRM</v>
@@ -524,18 +521,18 @@
         <v>FLCM</v>
       </c>
       <c r="E6" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G6">
-        <v>45523</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENT-16621</v>
+        <v>ENT-16374</v>
       </c>
       <c r="B7" t="str">
-        <v>CIW Data Products to PROD</v>
+        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
       </c>
       <c r="C7" t="str">
         <v>Invite to JRM</v>
@@ -544,18 +541,18 @@
         <v>FLCM</v>
       </c>
       <c r="E7" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G7">
-        <v>45596</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENT-16374</v>
+        <v>ENT-16031</v>
       </c>
       <c r="B8" t="str">
-        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
+        <v>Fraud - Notes generator</v>
       </c>
       <c r="C8" t="str">
         <v>Invite to JRM</v>
@@ -567,15 +564,15 @@
         <v>jrm</v>
       </c>
       <c r="G8">
-        <v>45455</v>
+        <v>45649</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-16031</v>
+        <v>ENT-15917</v>
       </c>
       <c r="B9" t="str">
-        <v>Fraud - Notes generator</v>
+        <v>REBO Bill Payment Investigation Requests</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -587,15 +584,15 @@
         <v>jrm</v>
       </c>
       <c r="G9">
-        <v>45649</v>
+        <v>45613</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-15917</v>
+        <v>ENT-17286</v>
       </c>
       <c r="B10" t="str">
-        <v>REBO Bill Payment Investigation Requests</v>
+        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -604,18 +601,18 @@
         <v>FLCM</v>
       </c>
       <c r="E10" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G10">
-        <v>45613</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-17286</v>
+        <v>ENT-17202</v>
       </c>
       <c r="B11" t="str">
-        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
+        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -624,18 +621,18 @@
         <v>FLCM</v>
       </c>
       <c r="E11" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G11">
-        <v>45699</v>
+        <v>45690</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-17202</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B12" t="str">
-        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -644,18 +641,21 @@
         <v>FLCM</v>
       </c>
       <c r="E12" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F12" t="str">
+        <v>PDF</v>
       </c>
       <c r="G12">
-        <v>45690</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B13" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -664,21 +664,18 @@
         <v>FLCM</v>
       </c>
       <c r="E13" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F13" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G13">
-        <v>45686</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B14" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -690,15 +687,15 @@
         <v>estimates</v>
       </c>
       <c r="G14">
-        <v>45700</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B15" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -710,15 +707,15 @@
         <v>estimates</v>
       </c>
       <c r="G15">
-        <v>45656</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B16" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -730,15 +727,15 @@
         <v>estimates</v>
       </c>
       <c r="G16">
-        <v>45588</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-17054</v>
       </c>
       <c r="B17" t="str">
-        <v>Data Source to EDGE</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -747,18 +744,21 @@
         <v>FLCM</v>
       </c>
       <c r="E17" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F17" t="str">
+        <v>PDF</v>
       </c>
       <c r="G17">
-        <v>45664</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ENT-17054</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B18" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
@@ -769,19 +769,16 @@
       <c r="E18" t="str">
         <v>approved</v>
       </c>
-      <c r="F18" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G18">
-        <v>45691</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-14372</v>
       </c>
       <c r="B19" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
@@ -792,16 +789,19 @@
       <c r="E19" t="str">
         <v>approved</v>
       </c>
+      <c r="F19" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G19">
-        <v>45299</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ENT-14372</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B20" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
@@ -816,58 +816,58 @@
         <v>PDF</v>
       </c>
       <c r="G20">
-        <v>45512</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B21" t="str">
-        <v>RAMP Phase 2</v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D21" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E21" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F21" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G21">
-        <v>45562</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B22" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D22" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E22" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F22" t="str">
+        <v>PDF</v>
       </c>
       <c r="G22">
-        <v>45695</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B23" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
@@ -882,15 +882,15 @@
         <v>PDF</v>
       </c>
       <c r="G23">
-        <v>45688</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B24" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
@@ -905,15 +905,15 @@
         <v>PDF</v>
       </c>
       <c r="G24">
-        <v>45701</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B25" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
@@ -924,19 +924,16 @@
       <c r="E25" t="str">
         <v>approved</v>
       </c>
-      <c r="F25" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G25">
-        <v>45695</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B26" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
@@ -945,138 +942,138 @@
         <v>FLCM</v>
       </c>
       <c r="E26" t="str">
-        <v>approved</v>
+        <v>estimates</v>
       </c>
       <c r="G26">
-        <v>45706</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B27" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D27" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E27" t="str">
         <v>estimates</v>
       </c>
       <c r="G27">
-        <v>45559</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B28" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D28" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E28" t="str">
         <v>estimates</v>
       </c>
       <c r="G28">
-        <v>45623</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B29" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>FLCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E29" t="str">
         <v>estimates</v>
       </c>
       <c r="G29">
-        <v>45355</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B30" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D30" t="str">
-        <v>CorpSec</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E30" t="str">
         <v>estimates</v>
       </c>
       <c r="G30">
-        <v>45446</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B31" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D31" t="str">
-        <v>BSCM/ESCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E31" t="str">
         <v>estimates</v>
       </c>
       <c r="G31">
-        <v>45477</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B32" t="str">
-        <v>CSDM Upgrade</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D32" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E32" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G32">
-        <v>45394</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B33" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
@@ -1088,15 +1085,15 @@
         <v>ofs</v>
       </c>
       <c r="G33">
-        <v>45531</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B34" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
@@ -1108,15 +1105,15 @@
         <v>ofs</v>
       </c>
       <c r="G34">
-        <v>45453</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B35" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
@@ -1125,98 +1122,95 @@
         <v>FLCM</v>
       </c>
       <c r="E35" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G35">
-        <v>45461</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B36" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D36" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E36" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G36">
-        <v>45714</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-15822</v>
       </c>
       <c r="B37" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D37" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E37" t="str">
         <v>estimates</v>
       </c>
       <c r="G37">
-        <v>45686</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ENT-15822</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B38" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D38" t="str">
-        <v>FLCM</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E38" t="str">
         <v>estimates</v>
       </c>
       <c r="G38">
-        <v>45650</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-17853</v>
       </c>
       <c r="B39" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
       </c>
-      <c r="D39" t="str">
-        <v>BSCM/ESCM</v>
-      </c>
       <c r="E39" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G39">
-        <v>45541</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENT-17853</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B40" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
@@ -1225,15 +1219,15 @@
         <v>ofs</v>
       </c>
       <c r="G40">
-        <v>45691</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B41" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1242,15 +1236,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45559</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B42" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1259,15 +1253,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45596</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B43" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1276,15 +1270,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45378</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B44" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1293,15 +1287,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45468</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B45" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1310,15 +1304,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45310</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B46" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1327,15 +1321,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45427</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B47" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1344,15 +1338,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45279</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B48" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1361,15 +1355,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45558</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B49" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1378,15 +1372,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45383</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B50" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1395,15 +1389,15 @@
         <v>ofs</v>
       </c>
       <c r="G50">
-        <v>45638</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B51" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1412,15 +1406,15 @@
         <v>ofs</v>
       </c>
       <c r="G51">
-        <v>45461</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B52" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1434,10 +1428,10 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B53" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1446,15 +1440,15 @@
         <v>ofs</v>
       </c>
       <c r="G53">
-        <v>45371</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B54" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1463,15 +1457,15 @@
         <v>ofs</v>
       </c>
       <c r="G54">
-        <v>45406</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B55" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1480,15 +1474,15 @@
         <v>ofs</v>
       </c>
       <c r="G55">
-        <v>45364</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B56" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1497,15 +1491,15 @@
         <v>ofs</v>
       </c>
       <c r="G56">
-        <v>45593</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B57" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
@@ -1514,15 +1508,15 @@
         <v>ofs</v>
       </c>
       <c r="G57">
-        <v>45408</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B58" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C58" t="str">
         <v>Invite to JRM</v>
@@ -1531,15 +1525,15 @@
         <v>ofs</v>
       </c>
       <c r="G58">
-        <v>45595</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B59" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C59" t="str">
         <v>Invite to JRM</v>
@@ -1548,15 +1542,15 @@
         <v>ofs</v>
       </c>
       <c r="G59">
-        <v>45392</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B60" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C60" t="str">
         <v>Invite to JRM</v>
@@ -1570,27 +1564,27 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B61" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C61" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E61" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G61">
-        <v>45411</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-18725</v>
       </c>
       <c r="B62" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>US Video System - Lenel to Genetec</v>
       </c>
       <c r="C62" t="str">
         <v>Invite to JRM</v>
@@ -1602,26 +1596,9 @@
         <v>45721</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="str">
-        <v>ENT-18725</v>
-      </c>
-      <c r="B63" t="str">
-        <v>US Video System - Lenel to Genetec</v>
-      </c>
-      <c r="C63" t="str">
-        <v>Invite to JRM</v>
-      </c>
-      <c r="E63" t="str">
-        <v>jrm</v>
-      </c>
-      <c r="G63">
-        <v>45721</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G63"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G62"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -1769,7 +1769,7 @@
         <v>ENT-17213</v>
       </c>
       <c r="B3" t="str">
-        <v>703188</v>
+        <v>1000000</v>
       </c>
       <c r="C3" t="str">
         <v>67500</v>
@@ -1790,10 +1790,10 @@
         <v>157861</v>
       </c>
       <c r="I3" t="str">
-        <v>14.00</v>
+        <v>14</v>
       </c>
       <c r="J3" t="str">
-        <v>20.50</v>
+        <v>20.5</v>
       </c>
       <c r="K3" t="str">
         <v>598</v>
@@ -1802,10 +1802,10 @@
         <v>308479</v>
       </c>
       <c r="M3" t="str">
-        <v>52.80</v>
+        <v>52.8</v>
       </c>
       <c r="N3" t="str">
-        <v>40.00</v>
+        <v>40</v>
       </c>
       <c r="O3" t="str">
         <v>303</v>
@@ -1814,7 +1814,7 @@
         <v>158200</v>
       </c>
       <c r="Q3" t="str">
-        <v>26.70</v>
+        <v>26.7</v>
       </c>
       <c r="R3" t="str">
         <v>23</v>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -1691,23 +1691,26 @@
       <c r="A2" t="str">
         <v>ENT-17054</v>
       </c>
-      <c r="B2">
-        <v>178399</v>
-      </c>
-      <c r="C2">
-        <v>2500</v>
-      </c>
-      <c r="E2">
-        <v>118933</v>
-      </c>
-      <c r="F2">
-        <v>59466</v>
+      <c r="B2" t="str">
+        <v>178399.00</v>
+      </c>
+      <c r="C2" t="str">
+        <v>2500.00</v>
+      </c>
+      <c r="D2" t="str">
+        <v>-</v>
+      </c>
+      <c r="E2" t="str">
+        <v>118933.00</v>
+      </c>
+      <c r="F2" t="str">
+        <v>59466.00</v>
       </c>
       <c r="G2" t="str">
         <v>900</v>
       </c>
       <c r="H2" t="str">
-        <v>83903</v>
+        <v>83903.00</v>
       </c>
       <c r="I2" t="str">
         <v>38.70</v>
@@ -1715,53 +1718,53 @@
       <c r="J2" t="str">
         <v>46.40</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="str">
         <v>68</v>
       </c>
-      <c r="L2">
-        <v>57206</v>
-      </c>
-      <c r="M2">
-        <v>29</v>
-      </c>
-      <c r="N2">
-        <v>31.6</v>
-      </c>
-      <c r="O2">
+      <c r="L2" t="str">
+        <v>57206.00</v>
+      </c>
+      <c r="M2" t="str">
+        <v>29.00</v>
+      </c>
+      <c r="N2" t="str">
+        <v>31.60</v>
+      </c>
+      <c r="O2" t="str">
         <v>75</v>
       </c>
-      <c r="P2">
-        <v>37290</v>
-      </c>
-      <c r="Q2">
-        <v>32.3</v>
-      </c>
-      <c r="R2">
-        <v>20.6</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <v>2500</v>
-      </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
-      <c r="V2">
-        <v>1</v>
-      </c>
-      <c r="W2">
-        <v>0</v>
-      </c>
-      <c r="X2">
-        <v>0</v>
-      </c>
-      <c r="Y2">
-        <v>0</v>
-      </c>
-      <c r="Z2">
-        <v>0</v>
+      <c r="P2" t="str">
+        <v>37290.00</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>32.30</v>
+      </c>
+      <c r="R2" t="str">
+        <v>20.60</v>
+      </c>
+      <c r="S2" t="str">
+        <v>-</v>
+      </c>
+      <c r="T2" t="str">
+        <v>2500.00</v>
+      </c>
+      <c r="U2" t="str">
+        <v>-</v>
+      </c>
+      <c r="V2" t="str">
+        <v>-</v>
+      </c>
+      <c r="W2" t="str">
+        <v>-</v>
+      </c>
+      <c r="X2" t="str">
+        <v>-</v>
+      </c>
+      <c r="Y2" t="str">
+        <v>-</v>
+      </c>
+      <c r="Z2" t="str">
+        <v>-</v>
       </c>
     </row>
     <row r="3">

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -1999,17 +1999,20 @@
       <c r="A6" t="str">
         <v>ENT-17705</v>
       </c>
-      <c r="B6">
-        <v>46433</v>
-      </c>
-      <c r="C6">
-        <v>5000</v>
-      </c>
-      <c r="E6">
-        <v>30962</v>
-      </c>
-      <c r="F6">
-        <v>15481</v>
+      <c r="B6" t="str">
+        <v>46433.00</v>
+      </c>
+      <c r="C6" t="str">
+        <v>5000.00</v>
+      </c>
+      <c r="D6" t="str">
+        <v>-</v>
+      </c>
+      <c r="E6" t="str">
+        <v>30962.00</v>
+      </c>
+      <c r="F6" t="str">
+        <v>4234234</v>
       </c>
       <c r="G6">
         <v>23</v>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -441,7 +441,7 @@
         <v>FLCM</v>
       </c>
       <c r="E2" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G2">
         <v>45672</v>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -521,7 +521,7 @@
         <v>FLCM</v>
       </c>
       <c r="E6" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G6">
         <v>45596</v>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -481,7 +481,7 @@
         <v>FLCM</v>
       </c>
       <c r="E4" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G4">
         <v>45929</v>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -501,7 +501,7 @@
         <v>FLCM</v>
       </c>
       <c r="E5" t="str">
-        <v>jrm</v>
+        <v>ofs</v>
       </c>
       <c r="G5">
         <v>45523</v>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G63"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -429,30 +429,33 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ENT-17062</v>
+        <v>435</v>
       </c>
       <c r="B2" t="str">
-        <v>Account Open Enhancements and Outcome Orchestration</v>
+        <v>345</v>
       </c>
       <c r="C2" t="str">
-        <v>Invite to JRM</v>
+        <v>345</v>
       </c>
       <c r="D2" t="str">
-        <v>FLCM</v>
+        <v>345345</v>
       </c>
       <c r="E2" t="str">
-        <v>estimates</v>
-      </c>
-      <c r="G2">
-        <v>45672</v>
+        <v>jrm</v>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v>2025-03-01</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ENT-16949</v>
+        <v>ENT-17062</v>
       </c>
       <c r="B3" t="str">
-        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
+        <v>Account Open Enhancements and Outcome Orchestration</v>
       </c>
       <c r="C3" t="str">
         <v>Invite to JRM</v>
@@ -464,15 +467,15 @@
         <v>estimates</v>
       </c>
       <c r="G3">
-        <v>45531</v>
+        <v>45672</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ENT-16881</v>
+        <v>ENT-16949</v>
       </c>
       <c r="B4" t="str">
-        <v>Split up Personal Overdraft P&amp;L</v>
+        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
       </c>
       <c r="C4" t="str">
         <v>Invite to JRM</v>
@@ -481,18 +484,18 @@
         <v>FLCM</v>
       </c>
       <c r="E4" t="str">
-        <v>approved</v>
+        <v>estimates</v>
       </c>
       <c r="G4">
-        <v>45929</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ENT-16700</v>
+        <v>ENT-16881</v>
       </c>
       <c r="B5" t="str">
-        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
+        <v>Split up Personal Overdraft P&amp;L</v>
       </c>
       <c r="C5" t="str">
         <v>Invite to JRM</v>
@@ -501,18 +504,18 @@
         <v>FLCM</v>
       </c>
       <c r="E5" t="str">
-        <v>ofs</v>
+        <v>approved</v>
       </c>
       <c r="G5">
-        <v>45523</v>
+        <v>45929</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ENT-16621</v>
+        <v>ENT-16700</v>
       </c>
       <c r="B6" t="str">
-        <v>CIW Data Products to PROD</v>
+        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
       </c>
       <c r="C6" t="str">
         <v>Invite to JRM</v>
@@ -521,18 +524,18 @@
         <v>FLCM</v>
       </c>
       <c r="E6" t="str">
-        <v>jrm</v>
+        <v>ofs</v>
       </c>
       <c r="G6">
-        <v>45596</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENT-16374</v>
+        <v>ENT-16621</v>
       </c>
       <c r="B7" t="str">
-        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
+        <v>CIW Data Products to PROD</v>
       </c>
       <c r="C7" t="str">
         <v>Invite to JRM</v>
@@ -544,15 +547,15 @@
         <v>jrm</v>
       </c>
       <c r="G7">
-        <v>45455</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENT-16031</v>
+        <v>ENT-16374</v>
       </c>
       <c r="B8" t="str">
-        <v>Fraud - Notes generator</v>
+        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
       </c>
       <c r="C8" t="str">
         <v>Invite to JRM</v>
@@ -564,15 +567,15 @@
         <v>jrm</v>
       </c>
       <c r="G8">
-        <v>45649</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-15917</v>
+        <v>ENT-16031</v>
       </c>
       <c r="B9" t="str">
-        <v>REBO Bill Payment Investigation Requests</v>
+        <v>Fraud - Notes generator</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -584,15 +587,15 @@
         <v>jrm</v>
       </c>
       <c r="G9">
-        <v>45613</v>
+        <v>45649</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-17286</v>
+        <v>ENT-15917</v>
       </c>
       <c r="B10" t="str">
-        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
+        <v>REBO Bill Payment Investigation Requests</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -601,18 +604,18 @@
         <v>FLCM</v>
       </c>
       <c r="E10" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G10">
-        <v>45699</v>
+        <v>45613</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-17202</v>
+        <v>ENT-17286</v>
       </c>
       <c r="B11" t="str">
-        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
+        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -621,18 +624,18 @@
         <v>FLCM</v>
       </c>
       <c r="E11" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G11">
-        <v>45690</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17202</v>
       </c>
       <c r="B12" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -641,21 +644,18 @@
         <v>FLCM</v>
       </c>
       <c r="E12" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F12" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G12">
-        <v>45686</v>
+        <v>45690</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B13" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -664,18 +664,21 @@
         <v>FLCM</v>
       </c>
       <c r="E13" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F13" t="str">
+        <v>PDF</v>
       </c>
       <c r="G13">
-        <v>45700</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B14" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -687,15 +690,15 @@
         <v>estimates</v>
       </c>
       <c r="G14">
-        <v>45656</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B15" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -707,15 +710,15 @@
         <v>estimates</v>
       </c>
       <c r="G15">
-        <v>45588</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B16" t="str">
-        <v>Data Source to EDGE</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -727,15 +730,15 @@
         <v>estimates</v>
       </c>
       <c r="G16">
-        <v>45664</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ENT-17054</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B17" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -744,21 +747,18 @@
         <v>FLCM</v>
       </c>
       <c r="E17" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F17" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G17">
-        <v>45691</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-17054</v>
       </c>
       <c r="B18" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
@@ -769,16 +769,19 @@
       <c r="E18" t="str">
         <v>approved</v>
       </c>
+      <c r="F18" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G18">
-        <v>45299</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ENT-14372</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B19" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
@@ -789,19 +792,16 @@
       <c r="E19" t="str">
         <v>approved</v>
       </c>
-      <c r="F19" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G19">
-        <v>45512</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-14372</v>
       </c>
       <c r="B20" t="str">
-        <v>RAMP Phase 2</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
@@ -816,58 +816,58 @@
         <v>PDF</v>
       </c>
       <c r="G20">
-        <v>45562</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B21" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D21" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E21" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F21" t="str">
+        <v>PDF</v>
       </c>
       <c r="G21">
-        <v>45695</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B22" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D22" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E22" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F22" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G22">
-        <v>45688</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B23" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
@@ -882,15 +882,15 @@
         <v>PDF</v>
       </c>
       <c r="G23">
-        <v>45701</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B24" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
@@ -905,15 +905,15 @@
         <v>PDF</v>
       </c>
       <c r="G24">
-        <v>45695</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B25" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
@@ -924,16 +924,19 @@
       <c r="E25" t="str">
         <v>approved</v>
       </c>
+      <c r="F25" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G25">
-        <v>45706</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B26" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
@@ -942,138 +945,138 @@
         <v>FLCM</v>
       </c>
       <c r="E26" t="str">
-        <v>estimates</v>
+        <v>approved</v>
       </c>
       <c r="G26">
-        <v>45559</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B27" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D27" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E27" t="str">
         <v>estimates</v>
       </c>
       <c r="G27">
-        <v>45623</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B28" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D28" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E28" t="str">
         <v>estimates</v>
       </c>
       <c r="G28">
-        <v>45355</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B29" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>CorpSec</v>
+        <v>FLCM</v>
       </c>
       <c r="E29" t="str">
         <v>estimates</v>
       </c>
       <c r="G29">
-        <v>45446</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B30" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D30" t="str">
-        <v>BSCM/ESCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E30" t="str">
         <v>estimates</v>
       </c>
       <c r="G30">
-        <v>45477</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B31" t="str">
-        <v>CSDM Upgrade</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D31" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E31" t="str">
         <v>estimates</v>
       </c>
       <c r="G31">
-        <v>45394</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B32" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D32" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E32" t="str">
-        <v>ofs</v>
+        <v>estimates</v>
       </c>
       <c r="G32">
-        <v>45531</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B33" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
@@ -1085,15 +1088,15 @@
         <v>ofs</v>
       </c>
       <c r="G33">
-        <v>45453</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B34" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
@@ -1105,15 +1108,15 @@
         <v>ofs</v>
       </c>
       <c r="G34">
-        <v>45461</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B35" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
@@ -1122,95 +1125,98 @@
         <v>FLCM</v>
       </c>
       <c r="E35" t="str">
-        <v>jrm</v>
+        <v>ofs</v>
       </c>
       <c r="G35">
-        <v>45714</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B36" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D36" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E36" t="str">
-        <v>estimates</v>
+        <v>jrm</v>
       </c>
       <c r="G36">
-        <v>45686</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ENT-15822</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B37" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D37" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E37" t="str">
         <v>estimates</v>
       </c>
       <c r="G37">
-        <v>45650</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-15822</v>
       </c>
       <c r="B38" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D38" t="str">
-        <v>BSCM/ESCM</v>
+        <v>FLCM</v>
       </c>
       <c r="E38" t="str">
         <v>estimates</v>
       </c>
       <c r="G38">
-        <v>45541</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ENT-17853</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B39" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
       </c>
+      <c r="D39" t="str">
+        <v>BSCM/ESCM</v>
+      </c>
       <c r="E39" t="str">
-        <v>ofs</v>
+        <v>estimates</v>
       </c>
       <c r="G39">
-        <v>45691</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-17853</v>
       </c>
       <c r="B40" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
@@ -1219,15 +1225,15 @@
         <v>ofs</v>
       </c>
       <c r="G40">
-        <v>45559</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B41" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1236,15 +1242,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45596</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B42" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1253,15 +1259,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45378</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B43" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1270,15 +1276,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45468</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B44" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1287,15 +1293,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45310</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B45" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1304,15 +1310,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45427</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B46" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1321,15 +1327,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45279</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B47" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1338,15 +1344,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45558</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B48" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1355,15 +1361,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45383</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B49" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1372,15 +1378,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45638</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B50" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1389,15 +1395,15 @@
         <v>ofs</v>
       </c>
       <c r="G50">
-        <v>45461</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B51" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1406,15 +1412,15 @@
         <v>ofs</v>
       </c>
       <c r="G51">
-        <v>45371</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B52" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1428,10 +1434,10 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B53" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1440,15 +1446,15 @@
         <v>ofs</v>
       </c>
       <c r="G53">
-        <v>45406</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B54" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1457,15 +1463,15 @@
         <v>ofs</v>
       </c>
       <c r="G54">
-        <v>45364</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B55" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1474,15 +1480,15 @@
         <v>ofs</v>
       </c>
       <c r="G55">
-        <v>45593</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B56" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1491,15 +1497,15 @@
         <v>ofs</v>
       </c>
       <c r="G56">
-        <v>45408</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B57" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
@@ -1508,15 +1514,15 @@
         <v>ofs</v>
       </c>
       <c r="G57">
-        <v>45595</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B58" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C58" t="str">
         <v>Invite to JRM</v>
@@ -1525,15 +1531,15 @@
         <v>ofs</v>
       </c>
       <c r="G58">
-        <v>45392</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B59" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C59" t="str">
         <v>Invite to JRM</v>
@@ -1542,15 +1548,15 @@
         <v>ofs</v>
       </c>
       <c r="G59">
-        <v>45411</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B60" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C60" t="str">
         <v>Invite to JRM</v>
@@ -1564,27 +1570,27 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B61" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C61" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E61" t="str">
-        <v>jrm</v>
+        <v>ofs</v>
       </c>
       <c r="G61">
-        <v>45721</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>ENT-18725</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B62" t="str">
-        <v>US Video System - Lenel to Genetec</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C62" t="str">
         <v>Invite to JRM</v>
@@ -1596,9 +1602,26 @@
         <v>45721</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>ENT-18725</v>
+      </c>
+      <c r="B63" t="str">
+        <v>US Video System - Lenel to Genetec</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Invite to JRM</v>
+      </c>
+      <c r="E63" t="str">
+        <v>jrm</v>
+      </c>
+      <c r="G63">
+        <v>45721</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G62"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G63"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -441,7 +441,7 @@
         <v>345345</v>
       </c>
       <c r="E2" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="F2" t="str">
         <v/>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -544,7 +544,7 @@
         <v>FLCM</v>
       </c>
       <c r="E7" t="str">
-        <v>jrm</v>
+        <v>ofs</v>
       </c>
       <c r="G7">
         <v>45596</v>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -564,7 +564,7 @@
         <v>FLCM</v>
       </c>
       <c r="E8" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G8">
         <v>45455</v>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G62"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -572,10 +572,10 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-16031</v>
+        <v>ENT-15917</v>
       </c>
       <c r="B9" t="str">
-        <v>Fraud - Notes generator</v>
+        <v>REBO Bill Payment Investigation Requests</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -587,15 +587,15 @@
         <v>jrm</v>
       </c>
       <c r="G9">
-        <v>45649</v>
+        <v>45613</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-15917</v>
+        <v>ENT-17286</v>
       </c>
       <c r="B10" t="str">
-        <v>REBO Bill Payment Investigation Requests</v>
+        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -604,18 +604,18 @@
         <v>FLCM</v>
       </c>
       <c r="E10" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G10">
-        <v>45613</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-17286</v>
+        <v>ENT-17202</v>
       </c>
       <c r="B11" t="str">
-        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
+        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -624,18 +624,18 @@
         <v>FLCM</v>
       </c>
       <c r="E11" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G11">
-        <v>45699</v>
+        <v>45690</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-17202</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B12" t="str">
-        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -644,18 +644,21 @@
         <v>FLCM</v>
       </c>
       <c r="E12" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F12" t="str">
+        <v>PDF</v>
       </c>
       <c r="G12">
-        <v>45690</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B13" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -664,21 +667,18 @@
         <v>FLCM</v>
       </c>
       <c r="E13" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F13" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G13">
-        <v>45686</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B14" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -690,15 +690,15 @@
         <v>estimates</v>
       </c>
       <c r="G14">
-        <v>45700</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B15" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -710,15 +710,15 @@
         <v>estimates</v>
       </c>
       <c r="G15">
-        <v>45656</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B16" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -730,15 +730,15 @@
         <v>estimates</v>
       </c>
       <c r="G16">
-        <v>45588</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-17054</v>
       </c>
       <c r="B17" t="str">
-        <v>Data Source to EDGE</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -747,18 +747,21 @@
         <v>FLCM</v>
       </c>
       <c r="E17" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F17" t="str">
+        <v>PDF</v>
       </c>
       <c r="G17">
-        <v>45664</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ENT-17054</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B18" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
@@ -769,19 +772,16 @@
       <c r="E18" t="str">
         <v>approved</v>
       </c>
-      <c r="F18" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G18">
-        <v>45691</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-14372</v>
       </c>
       <c r="B19" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
@@ -792,16 +792,19 @@
       <c r="E19" t="str">
         <v>approved</v>
       </c>
+      <c r="F19" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G19">
-        <v>45299</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ENT-14372</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B20" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
@@ -816,58 +819,58 @@
         <v>PDF</v>
       </c>
       <c r="G20">
-        <v>45512</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B21" t="str">
-        <v>RAMP Phase 2</v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D21" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E21" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F21" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G21">
-        <v>45562</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B22" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D22" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E22" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F22" t="str">
+        <v>PDF</v>
       </c>
       <c r="G22">
-        <v>45695</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B23" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
@@ -882,15 +885,15 @@
         <v>PDF</v>
       </c>
       <c r="G23">
-        <v>45688</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B24" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
@@ -905,15 +908,15 @@
         <v>PDF</v>
       </c>
       <c r="G24">
-        <v>45701</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B25" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
@@ -924,19 +927,16 @@
       <c r="E25" t="str">
         <v>approved</v>
       </c>
-      <c r="F25" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G25">
-        <v>45695</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B26" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
@@ -945,138 +945,138 @@
         <v>FLCM</v>
       </c>
       <c r="E26" t="str">
-        <v>approved</v>
+        <v>estimates</v>
       </c>
       <c r="G26">
-        <v>45706</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B27" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D27" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E27" t="str">
         <v>estimates</v>
       </c>
       <c r="G27">
-        <v>45559</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B28" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D28" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E28" t="str">
         <v>estimates</v>
       </c>
       <c r="G28">
-        <v>45623</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B29" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>FLCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E29" t="str">
         <v>estimates</v>
       </c>
       <c r="G29">
-        <v>45355</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B30" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D30" t="str">
-        <v>CorpSec</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E30" t="str">
         <v>estimates</v>
       </c>
       <c r="G30">
-        <v>45446</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B31" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D31" t="str">
-        <v>BSCM/ESCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E31" t="str">
         <v>estimates</v>
       </c>
       <c r="G31">
-        <v>45477</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B32" t="str">
-        <v>CSDM Upgrade</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D32" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E32" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G32">
-        <v>45394</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B33" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
@@ -1088,15 +1088,15 @@
         <v>ofs</v>
       </c>
       <c r="G33">
-        <v>45531</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B34" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
@@ -1108,15 +1108,15 @@
         <v>ofs</v>
       </c>
       <c r="G34">
-        <v>45453</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B35" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
@@ -1125,98 +1125,95 @@
         <v>FLCM</v>
       </c>
       <c r="E35" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G35">
-        <v>45461</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B36" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D36" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E36" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G36">
-        <v>45714</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-15822</v>
       </c>
       <c r="B37" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D37" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E37" t="str">
         <v>estimates</v>
       </c>
       <c r="G37">
-        <v>45686</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ENT-15822</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B38" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D38" t="str">
-        <v>FLCM</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E38" t="str">
         <v>estimates</v>
       </c>
       <c r="G38">
-        <v>45650</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-17853</v>
       </c>
       <c r="B39" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
       </c>
-      <c r="D39" t="str">
-        <v>BSCM/ESCM</v>
-      </c>
       <c r="E39" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G39">
-        <v>45541</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENT-17853</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B40" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
@@ -1225,15 +1222,15 @@
         <v>ofs</v>
       </c>
       <c r="G40">
-        <v>45691</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B41" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1242,15 +1239,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45559</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B42" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1259,15 +1256,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45596</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B43" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1276,15 +1273,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45378</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B44" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1293,15 +1290,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45468</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B45" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1310,15 +1307,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45310</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B46" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1327,15 +1324,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45427</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B47" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1344,15 +1341,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45279</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B48" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1361,15 +1358,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45558</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B49" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1378,15 +1375,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45383</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B50" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1395,15 +1392,15 @@
         <v>ofs</v>
       </c>
       <c r="G50">
-        <v>45638</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B51" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1412,15 +1409,15 @@
         <v>ofs</v>
       </c>
       <c r="G51">
-        <v>45461</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B52" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1434,10 +1431,10 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B53" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1446,15 +1443,15 @@
         <v>ofs</v>
       </c>
       <c r="G53">
-        <v>45371</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B54" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1463,15 +1460,15 @@
         <v>ofs</v>
       </c>
       <c r="G54">
-        <v>45406</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B55" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1480,15 +1477,15 @@
         <v>ofs</v>
       </c>
       <c r="G55">
-        <v>45364</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B56" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1497,15 +1494,15 @@
         <v>ofs</v>
       </c>
       <c r="G56">
-        <v>45593</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B57" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
@@ -1514,15 +1511,15 @@
         <v>ofs</v>
       </c>
       <c r="G57">
-        <v>45408</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B58" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C58" t="str">
         <v>Invite to JRM</v>
@@ -1531,15 +1528,15 @@
         <v>ofs</v>
       </c>
       <c r="G58">
-        <v>45595</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B59" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C59" t="str">
         <v>Invite to JRM</v>
@@ -1548,15 +1545,15 @@
         <v>ofs</v>
       </c>
       <c r="G59">
-        <v>45392</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B60" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C60" t="str">
         <v>Invite to JRM</v>
@@ -1570,27 +1567,27 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B61" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C61" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E61" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G61">
-        <v>45411</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-18725</v>
       </c>
       <c r="B62" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>US Video System - Lenel to Genetec</v>
       </c>
       <c r="C62" t="str">
         <v>Invite to JRM</v>
@@ -1602,26 +1599,9 @@
         <v>45721</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="str">
-        <v>ENT-18725</v>
-      </c>
-      <c r="B63" t="str">
-        <v>US Video System - Lenel to Genetec</v>
-      </c>
-      <c r="C63" t="str">
-        <v>Invite to JRM</v>
-      </c>
-      <c r="E63" t="str">
-        <v>jrm</v>
-      </c>
-      <c r="G63">
-        <v>45721</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G63"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G62"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G63"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -429,53 +429,56 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>435</v>
+        <v>16031</v>
       </c>
       <c r="B2" t="str">
-        <v>345</v>
+        <v>qweqwe</v>
       </c>
       <c r="C2" t="str">
-        <v>345</v>
+        <v>qweqwe</v>
       </c>
       <c r="D2" t="str">
-        <v>345345</v>
+        <v>qweqwe</v>
       </c>
       <c r="E2" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="F2" t="str">
         <v/>
       </c>
       <c r="G2" t="str">
-        <v>2025-03-01</v>
+        <v>2025-03-04</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ENT-17062</v>
+        <v>435</v>
       </c>
       <c r="B3" t="str">
-        <v>Account Open Enhancements and Outcome Orchestration</v>
+        <v>345</v>
       </c>
       <c r="C3" t="str">
-        <v>Invite to JRM</v>
+        <v>345</v>
       </c>
       <c r="D3" t="str">
-        <v>FLCM</v>
+        <v>345345</v>
       </c>
       <c r="E3" t="str">
-        <v>estimates</v>
-      </c>
-      <c r="G3">
-        <v>45672</v>
+        <v>approved</v>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v>2025-03-01</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ENT-16949</v>
+        <v>ENT-17062</v>
       </c>
       <c r="B4" t="str">
-        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
+        <v>Account Open Enhancements and Outcome Orchestration</v>
       </c>
       <c r="C4" t="str">
         <v>Invite to JRM</v>
@@ -487,15 +490,15 @@
         <v>estimates</v>
       </c>
       <c r="G4">
-        <v>45531</v>
+        <v>45672</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ENT-16881</v>
+        <v>ENT-16949</v>
       </c>
       <c r="B5" t="str">
-        <v>Split up Personal Overdraft P&amp;L</v>
+        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
       </c>
       <c r="C5" t="str">
         <v>Invite to JRM</v>
@@ -504,18 +507,18 @@
         <v>FLCM</v>
       </c>
       <c r="E5" t="str">
-        <v>approved</v>
+        <v>estimates</v>
       </c>
       <c r="G5">
-        <v>45929</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ENT-16700</v>
+        <v>ENT-16881</v>
       </c>
       <c r="B6" t="str">
-        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
+        <v>Split up Personal Overdraft P&amp;L</v>
       </c>
       <c r="C6" t="str">
         <v>Invite to JRM</v>
@@ -524,18 +527,18 @@
         <v>FLCM</v>
       </c>
       <c r="E6" t="str">
-        <v>ofs</v>
+        <v>approved</v>
       </c>
       <c r="G6">
-        <v>45523</v>
+        <v>45929</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENT-16621</v>
+        <v>ENT-16700</v>
       </c>
       <c r="B7" t="str">
-        <v>CIW Data Products to PROD</v>
+        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
       </c>
       <c r="C7" t="str">
         <v>Invite to JRM</v>
@@ -547,15 +550,15 @@
         <v>ofs</v>
       </c>
       <c r="G7">
-        <v>45596</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENT-16374</v>
+        <v>ENT-16621</v>
       </c>
       <c r="B8" t="str">
-        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
+        <v>CIW Data Products to PROD</v>
       </c>
       <c r="C8" t="str">
         <v>Invite to JRM</v>
@@ -564,18 +567,18 @@
         <v>FLCM</v>
       </c>
       <c r="E8" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G8">
-        <v>45455</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-15917</v>
+        <v>ENT-16374</v>
       </c>
       <c r="B9" t="str">
-        <v>REBO Bill Payment Investigation Requests</v>
+        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -584,18 +587,18 @@
         <v>FLCM</v>
       </c>
       <c r="E9" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G9">
-        <v>45613</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-17286</v>
+        <v>ENT-15917</v>
       </c>
       <c r="B10" t="str">
-        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
+        <v>REBO Bill Payment Investigation Requests</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -604,18 +607,18 @@
         <v>FLCM</v>
       </c>
       <c r="E10" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G10">
-        <v>45699</v>
+        <v>45613</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-17202</v>
+        <v>ENT-17286</v>
       </c>
       <c r="B11" t="str">
-        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
+        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -624,18 +627,18 @@
         <v>FLCM</v>
       </c>
       <c r="E11" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G11">
-        <v>45690</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17202</v>
       </c>
       <c r="B12" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -644,21 +647,18 @@
         <v>FLCM</v>
       </c>
       <c r="E12" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F12" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G12">
-        <v>45686</v>
+        <v>45690</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B13" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -667,18 +667,21 @@
         <v>FLCM</v>
       </c>
       <c r="E13" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F13" t="str">
+        <v>PDF</v>
       </c>
       <c r="G13">
-        <v>45700</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B14" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -690,15 +693,15 @@
         <v>estimates</v>
       </c>
       <c r="G14">
-        <v>45656</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B15" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -710,15 +713,15 @@
         <v>estimates</v>
       </c>
       <c r="G15">
-        <v>45588</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B16" t="str">
-        <v>Data Source to EDGE</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -730,15 +733,15 @@
         <v>estimates</v>
       </c>
       <c r="G16">
-        <v>45664</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ENT-17054</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B17" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -747,21 +750,18 @@
         <v>FLCM</v>
       </c>
       <c r="E17" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F17" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G17">
-        <v>45691</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-17054</v>
       </c>
       <c r="B18" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
@@ -772,16 +772,19 @@
       <c r="E18" t="str">
         <v>approved</v>
       </c>
+      <c r="F18" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G18">
-        <v>45299</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ENT-14372</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B19" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
@@ -792,19 +795,16 @@
       <c r="E19" t="str">
         <v>approved</v>
       </c>
-      <c r="F19" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G19">
-        <v>45512</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-14372</v>
       </c>
       <c r="B20" t="str">
-        <v>RAMP Phase 2</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
@@ -819,58 +819,58 @@
         <v>PDF</v>
       </c>
       <c r="G20">
-        <v>45562</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B21" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D21" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E21" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F21" t="str">
+        <v>PDF</v>
       </c>
       <c r="G21">
-        <v>45695</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B22" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D22" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E22" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F22" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G22">
-        <v>45688</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B23" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
@@ -885,15 +885,15 @@
         <v>PDF</v>
       </c>
       <c r="G23">
-        <v>45701</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B24" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
@@ -908,15 +908,15 @@
         <v>PDF</v>
       </c>
       <c r="G24">
-        <v>45695</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B25" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
@@ -927,16 +927,19 @@
       <c r="E25" t="str">
         <v>approved</v>
       </c>
+      <c r="F25" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G25">
-        <v>45706</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B26" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
@@ -945,138 +948,138 @@
         <v>FLCM</v>
       </c>
       <c r="E26" t="str">
-        <v>estimates</v>
+        <v>approved</v>
       </c>
       <c r="G26">
-        <v>45559</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B27" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D27" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E27" t="str">
         <v>estimates</v>
       </c>
       <c r="G27">
-        <v>45623</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B28" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D28" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E28" t="str">
         <v>estimates</v>
       </c>
       <c r="G28">
-        <v>45355</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B29" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>CorpSec</v>
+        <v>FLCM</v>
       </c>
       <c r="E29" t="str">
         <v>estimates</v>
       </c>
       <c r="G29">
-        <v>45446</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B30" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D30" t="str">
-        <v>BSCM/ESCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E30" t="str">
         <v>estimates</v>
       </c>
       <c r="G30">
-        <v>45477</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B31" t="str">
-        <v>CSDM Upgrade</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D31" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E31" t="str">
         <v>estimates</v>
       </c>
       <c r="G31">
-        <v>45394</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B32" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D32" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E32" t="str">
-        <v>ofs</v>
+        <v>estimates</v>
       </c>
       <c r="G32">
-        <v>45531</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B33" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
@@ -1088,15 +1091,15 @@
         <v>ofs</v>
       </c>
       <c r="G33">
-        <v>45453</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B34" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
@@ -1108,15 +1111,15 @@
         <v>ofs</v>
       </c>
       <c r="G34">
-        <v>45461</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B35" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
@@ -1125,95 +1128,98 @@
         <v>FLCM</v>
       </c>
       <c r="E35" t="str">
-        <v>jrm</v>
+        <v>ofs</v>
       </c>
       <c r="G35">
-        <v>45714</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B36" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D36" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E36" t="str">
-        <v>estimates</v>
+        <v>jrm</v>
       </c>
       <c r="G36">
-        <v>45686</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ENT-15822</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B37" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D37" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E37" t="str">
         <v>estimates</v>
       </c>
       <c r="G37">
-        <v>45650</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-15822</v>
       </c>
       <c r="B38" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D38" t="str">
-        <v>BSCM/ESCM</v>
+        <v>FLCM</v>
       </c>
       <c r="E38" t="str">
         <v>estimates</v>
       </c>
       <c r="G38">
-        <v>45541</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ENT-17853</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B39" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
       </c>
+      <c r="D39" t="str">
+        <v>BSCM/ESCM</v>
+      </c>
       <c r="E39" t="str">
-        <v>ofs</v>
+        <v>estimates</v>
       </c>
       <c r="G39">
-        <v>45691</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-17853</v>
       </c>
       <c r="B40" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
@@ -1222,15 +1228,15 @@
         <v>ofs</v>
       </c>
       <c r="G40">
-        <v>45559</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B41" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1239,15 +1245,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45596</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B42" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1256,15 +1262,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45378</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B43" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1273,15 +1279,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45468</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B44" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1290,15 +1296,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45310</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B45" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1307,15 +1313,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45427</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B46" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1324,15 +1330,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45279</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B47" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1341,15 +1347,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45558</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B48" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1358,15 +1364,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45383</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B49" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1375,15 +1381,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45638</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B50" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1392,15 +1398,15 @@
         <v>ofs</v>
       </c>
       <c r="G50">
-        <v>45461</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B51" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1409,15 +1415,15 @@
         <v>ofs</v>
       </c>
       <c r="G51">
-        <v>45371</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B52" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1431,10 +1437,10 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B53" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1443,15 +1449,15 @@
         <v>ofs</v>
       </c>
       <c r="G53">
-        <v>45406</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B54" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1460,15 +1466,15 @@
         <v>ofs</v>
       </c>
       <c r="G54">
-        <v>45364</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B55" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1477,15 +1483,15 @@
         <v>ofs</v>
       </c>
       <c r="G55">
-        <v>45593</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B56" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1494,15 +1500,15 @@
         <v>ofs</v>
       </c>
       <c r="G56">
-        <v>45408</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B57" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
@@ -1511,15 +1517,15 @@
         <v>ofs</v>
       </c>
       <c r="G57">
-        <v>45595</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B58" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C58" t="str">
         <v>Invite to JRM</v>
@@ -1528,15 +1534,15 @@
         <v>ofs</v>
       </c>
       <c r="G58">
-        <v>45392</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B59" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C59" t="str">
         <v>Invite to JRM</v>
@@ -1545,15 +1551,15 @@
         <v>ofs</v>
       </c>
       <c r="G59">
-        <v>45411</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B60" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C60" t="str">
         <v>Invite to JRM</v>
@@ -1567,27 +1573,27 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B61" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C61" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E61" t="str">
-        <v>jrm</v>
+        <v>ofs</v>
       </c>
       <c r="G61">
-        <v>45721</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>ENT-18725</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B62" t="str">
-        <v>US Video System - Lenel to Genetec</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C62" t="str">
         <v>Invite to JRM</v>
@@ -1599,9 +1605,26 @@
         <v>45721</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>ENT-18725</v>
+      </c>
+      <c r="B63" t="str">
+        <v>US Video System - Lenel to Genetec</v>
+      </c>
+      <c r="C63" t="str">
+        <v>Invite to JRM</v>
+      </c>
+      <c r="E63" t="str">
+        <v>jrm</v>
+      </c>
+      <c r="G63">
+        <v>45721</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G62"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G63"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -441,7 +441,7 @@
         <v>qweqwe</v>
       </c>
       <c r="E2" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="F2" t="str">
         <v/>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G62"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -452,33 +452,30 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>435</v>
+        <v>ENT-17062</v>
       </c>
       <c r="B3" t="str">
-        <v>345</v>
+        <v>Account Open Enhancements and Outcome Orchestration</v>
       </c>
       <c r="C3" t="str">
-        <v>345</v>
+        <v>Invite to JRM</v>
       </c>
       <c r="D3" t="str">
-        <v>345345</v>
+        <v>FLCM</v>
       </c>
       <c r="E3" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v>2025-03-01</v>
+        <v>estimates</v>
+      </c>
+      <c r="G3">
+        <v>45672</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ENT-17062</v>
+        <v>ENT-16949</v>
       </c>
       <c r="B4" t="str">
-        <v>Account Open Enhancements and Outcome Orchestration</v>
+        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
       </c>
       <c r="C4" t="str">
         <v>Invite to JRM</v>
@@ -490,15 +487,15 @@
         <v>estimates</v>
       </c>
       <c r="G4">
-        <v>45672</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ENT-16949</v>
+        <v>ENT-16881</v>
       </c>
       <c r="B5" t="str">
-        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
+        <v>Split up Personal Overdraft P&amp;L</v>
       </c>
       <c r="C5" t="str">
         <v>Invite to JRM</v>
@@ -507,18 +504,18 @@
         <v>FLCM</v>
       </c>
       <c r="E5" t="str">
-        <v>estimates</v>
+        <v>approved</v>
       </c>
       <c r="G5">
-        <v>45531</v>
+        <v>45929</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ENT-16881</v>
+        <v>ENT-16700</v>
       </c>
       <c r="B6" t="str">
-        <v>Split up Personal Overdraft P&amp;L</v>
+        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
       </c>
       <c r="C6" t="str">
         <v>Invite to JRM</v>
@@ -527,18 +524,18 @@
         <v>FLCM</v>
       </c>
       <c r="E6" t="str">
-        <v>approved</v>
+        <v>ofs</v>
       </c>
       <c r="G6">
-        <v>45929</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENT-16700</v>
+        <v>ENT-16621</v>
       </c>
       <c r="B7" t="str">
-        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
+        <v>CIW Data Products to PROD</v>
       </c>
       <c r="C7" t="str">
         <v>Invite to JRM</v>
@@ -550,15 +547,15 @@
         <v>ofs</v>
       </c>
       <c r="G7">
-        <v>45523</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENT-16621</v>
+        <v>ENT-16374</v>
       </c>
       <c r="B8" t="str">
-        <v>CIW Data Products to PROD</v>
+        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
       </c>
       <c r="C8" t="str">
         <v>Invite to JRM</v>
@@ -567,18 +564,18 @@
         <v>FLCM</v>
       </c>
       <c r="E8" t="str">
-        <v>ofs</v>
+        <v>estimates</v>
       </c>
       <c r="G8">
-        <v>45596</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-16374</v>
+        <v>ENT-15917</v>
       </c>
       <c r="B9" t="str">
-        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
+        <v>REBO Bill Payment Investigation Requests</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -587,18 +584,18 @@
         <v>FLCM</v>
       </c>
       <c r="E9" t="str">
-        <v>estimates</v>
+        <v>jrm</v>
       </c>
       <c r="G9">
-        <v>45455</v>
+        <v>45613</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-15917</v>
+        <v>ENT-17286</v>
       </c>
       <c r="B10" t="str">
-        <v>REBO Bill Payment Investigation Requests</v>
+        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -607,18 +604,18 @@
         <v>FLCM</v>
       </c>
       <c r="E10" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G10">
-        <v>45613</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-17286</v>
+        <v>ENT-17202</v>
       </c>
       <c r="B11" t="str">
-        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
+        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -627,18 +624,18 @@
         <v>FLCM</v>
       </c>
       <c r="E11" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G11">
-        <v>45699</v>
+        <v>45690</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-17202</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B12" t="str">
-        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -647,18 +644,21 @@
         <v>FLCM</v>
       </c>
       <c r="E12" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F12" t="str">
+        <v>PDF</v>
       </c>
       <c r="G12">
-        <v>45690</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B13" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -667,21 +667,18 @@
         <v>FLCM</v>
       </c>
       <c r="E13" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F13" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G13">
-        <v>45686</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B14" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -693,15 +690,15 @@
         <v>estimates</v>
       </c>
       <c r="G14">
-        <v>45700</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B15" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -713,15 +710,15 @@
         <v>estimates</v>
       </c>
       <c r="G15">
-        <v>45656</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B16" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -733,15 +730,15 @@
         <v>estimates</v>
       </c>
       <c r="G16">
-        <v>45588</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-17054</v>
       </c>
       <c r="B17" t="str">
-        <v>Data Source to EDGE</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -750,18 +747,21 @@
         <v>FLCM</v>
       </c>
       <c r="E17" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F17" t="str">
+        <v>PDF</v>
       </c>
       <c r="G17">
-        <v>45664</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ENT-17054</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B18" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
@@ -772,19 +772,16 @@
       <c r="E18" t="str">
         <v>approved</v>
       </c>
-      <c r="F18" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G18">
-        <v>45691</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-14372</v>
       </c>
       <c r="B19" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
@@ -795,16 +792,19 @@
       <c r="E19" t="str">
         <v>approved</v>
       </c>
+      <c r="F19" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G19">
-        <v>45299</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ENT-14372</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B20" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
@@ -819,58 +819,58 @@
         <v>PDF</v>
       </c>
       <c r="G20">
-        <v>45512</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B21" t="str">
-        <v>RAMP Phase 2</v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D21" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E21" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F21" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G21">
-        <v>45562</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B22" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D22" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E22" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F22" t="str">
+        <v>PDF</v>
       </c>
       <c r="G22">
-        <v>45695</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B23" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
@@ -885,15 +885,15 @@
         <v>PDF</v>
       </c>
       <c r="G23">
-        <v>45688</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B24" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
@@ -908,15 +908,15 @@
         <v>PDF</v>
       </c>
       <c r="G24">
-        <v>45701</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B25" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
@@ -927,19 +927,16 @@
       <c r="E25" t="str">
         <v>approved</v>
       </c>
-      <c r="F25" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G25">
-        <v>45695</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B26" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
@@ -948,138 +945,138 @@
         <v>FLCM</v>
       </c>
       <c r="E26" t="str">
-        <v>approved</v>
+        <v>estimates</v>
       </c>
       <c r="G26">
-        <v>45706</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B27" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D27" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E27" t="str">
         <v>estimates</v>
       </c>
       <c r="G27">
-        <v>45559</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B28" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D28" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E28" t="str">
         <v>estimates</v>
       </c>
       <c r="G28">
-        <v>45623</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B29" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>FLCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E29" t="str">
         <v>estimates</v>
       </c>
       <c r="G29">
-        <v>45355</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B30" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D30" t="str">
-        <v>CorpSec</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E30" t="str">
         <v>estimates</v>
       </c>
       <c r="G30">
-        <v>45446</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B31" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D31" t="str">
-        <v>BSCM/ESCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E31" t="str">
         <v>estimates</v>
       </c>
       <c r="G31">
-        <v>45477</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B32" t="str">
-        <v>CSDM Upgrade</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D32" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E32" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G32">
-        <v>45394</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B33" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
@@ -1091,15 +1088,15 @@
         <v>ofs</v>
       </c>
       <c r="G33">
-        <v>45531</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B34" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
@@ -1111,15 +1108,15 @@
         <v>ofs</v>
       </c>
       <c r="G34">
-        <v>45453</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B35" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
@@ -1128,98 +1125,95 @@
         <v>FLCM</v>
       </c>
       <c r="E35" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G35">
-        <v>45461</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B36" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D36" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E36" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G36">
-        <v>45714</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-15822</v>
       </c>
       <c r="B37" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D37" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E37" t="str">
         <v>estimates</v>
       </c>
       <c r="G37">
-        <v>45686</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ENT-15822</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B38" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D38" t="str">
-        <v>FLCM</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E38" t="str">
         <v>estimates</v>
       </c>
       <c r="G38">
-        <v>45650</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-17853</v>
       </c>
       <c r="B39" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
       </c>
-      <c r="D39" t="str">
-        <v>BSCM/ESCM</v>
-      </c>
       <c r="E39" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G39">
-        <v>45541</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENT-17853</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B40" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
@@ -1228,15 +1222,15 @@
         <v>ofs</v>
       </c>
       <c r="G40">
-        <v>45691</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B41" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1245,15 +1239,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45559</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B42" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1262,15 +1256,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45596</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B43" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1279,15 +1273,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45378</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B44" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1296,15 +1290,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45468</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B45" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1313,15 +1307,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45310</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B46" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1330,15 +1324,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45427</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B47" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1347,15 +1341,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45279</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B48" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1364,15 +1358,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45558</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B49" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1381,15 +1375,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45383</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B50" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1398,15 +1392,15 @@
         <v>ofs</v>
       </c>
       <c r="G50">
-        <v>45638</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B51" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1415,15 +1409,15 @@
         <v>ofs</v>
       </c>
       <c r="G51">
-        <v>45461</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B52" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1437,10 +1431,10 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B53" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1449,15 +1443,15 @@
         <v>ofs</v>
       </c>
       <c r="G53">
-        <v>45371</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B54" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1466,15 +1460,15 @@
         <v>ofs</v>
       </c>
       <c r="G54">
-        <v>45406</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B55" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1483,15 +1477,15 @@
         <v>ofs</v>
       </c>
       <c r="G55">
-        <v>45364</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B56" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1500,15 +1494,15 @@
         <v>ofs</v>
       </c>
       <c r="G56">
-        <v>45593</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B57" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
@@ -1517,15 +1511,15 @@
         <v>ofs</v>
       </c>
       <c r="G57">
-        <v>45408</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B58" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C58" t="str">
         <v>Invite to JRM</v>
@@ -1534,15 +1528,15 @@
         <v>ofs</v>
       </c>
       <c r="G58">
-        <v>45595</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B59" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C59" t="str">
         <v>Invite to JRM</v>
@@ -1551,15 +1545,15 @@
         <v>ofs</v>
       </c>
       <c r="G59">
-        <v>45392</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B60" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C60" t="str">
         <v>Invite to JRM</v>
@@ -1573,27 +1567,27 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B61" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C61" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E61" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G61">
-        <v>45411</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-18725</v>
       </c>
       <c r="B62" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>US Video System - Lenel to Genetec</v>
       </c>
       <c r="C62" t="str">
         <v>Invite to JRM</v>
@@ -1605,26 +1599,9 @@
         <v>45721</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="str">
-        <v>ENT-18725</v>
-      </c>
-      <c r="B63" t="str">
-        <v>US Video System - Lenel to Genetec</v>
-      </c>
-      <c r="C63" t="str">
-        <v>Invite to JRM</v>
-      </c>
-      <c r="E63" t="str">
-        <v>jrm</v>
-      </c>
-      <c r="G63">
-        <v>45721</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G63"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G62"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G61"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -612,10 +612,10 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-17202</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B11" t="str">
-        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -624,18 +624,21 @@
         <v>FLCM</v>
       </c>
       <c r="E11" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F11" t="str">
+        <v>PDF</v>
       </c>
       <c r="G11">
-        <v>45690</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B12" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -644,21 +647,18 @@
         <v>FLCM</v>
       </c>
       <c r="E12" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F12" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G12">
-        <v>45686</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B13" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -670,15 +670,15 @@
         <v>estimates</v>
       </c>
       <c r="G13">
-        <v>45700</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B14" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -690,15 +690,15 @@
         <v>estimates</v>
       </c>
       <c r="G14">
-        <v>45656</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B15" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -710,15 +710,15 @@
         <v>estimates</v>
       </c>
       <c r="G15">
-        <v>45588</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-17054</v>
       </c>
       <c r="B16" t="str">
-        <v>Data Source to EDGE</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -727,18 +727,21 @@
         <v>FLCM</v>
       </c>
       <c r="E16" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F16" t="str">
+        <v>PDF</v>
       </c>
       <c r="G16">
-        <v>45664</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ENT-17054</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B17" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -749,19 +752,16 @@
       <c r="E17" t="str">
         <v>approved</v>
       </c>
-      <c r="F17" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G17">
-        <v>45691</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-14372</v>
       </c>
       <c r="B18" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
@@ -772,16 +772,19 @@
       <c r="E18" t="str">
         <v>approved</v>
       </c>
+      <c r="F18" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G18">
-        <v>45299</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ENT-14372</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B19" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
@@ -796,58 +799,58 @@
         <v>PDF</v>
       </c>
       <c r="G19">
-        <v>45512</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B20" t="str">
-        <v>RAMP Phase 2</v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D20" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E20" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F20" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G20">
-        <v>45562</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B21" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D21" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E21" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F21" t="str">
+        <v>PDF</v>
       </c>
       <c r="G21">
-        <v>45695</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B22" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
@@ -862,15 +865,15 @@
         <v>PDF</v>
       </c>
       <c r="G22">
-        <v>45688</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B23" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
@@ -885,15 +888,15 @@
         <v>PDF</v>
       </c>
       <c r="G23">
-        <v>45701</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B24" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
@@ -904,19 +907,16 @@
       <c r="E24" t="str">
         <v>approved</v>
       </c>
-      <c r="F24" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G24">
-        <v>45695</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B25" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
@@ -925,138 +925,138 @@
         <v>FLCM</v>
       </c>
       <c r="E25" t="str">
-        <v>approved</v>
+        <v>estimates</v>
       </c>
       <c r="G25">
-        <v>45706</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B26" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D26" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E26" t="str">
         <v>estimates</v>
       </c>
       <c r="G26">
-        <v>45559</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B27" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D27" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E27" t="str">
         <v>estimates</v>
       </c>
       <c r="G27">
-        <v>45623</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B28" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D28" t="str">
-        <v>FLCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E28" t="str">
         <v>estimates</v>
       </c>
       <c r="G28">
-        <v>45355</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B29" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>CorpSec</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E29" t="str">
         <v>estimates</v>
       </c>
       <c r="G29">
-        <v>45446</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B30" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D30" t="str">
-        <v>BSCM/ESCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E30" t="str">
         <v>estimates</v>
       </c>
       <c r="G30">
-        <v>45477</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B31" t="str">
-        <v>CSDM Upgrade</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D31" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E31" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G31">
-        <v>45394</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B32" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
@@ -1068,15 +1068,15 @@
         <v>ofs</v>
       </c>
       <c r="G32">
-        <v>45531</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B33" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
@@ -1088,15 +1088,15 @@
         <v>ofs</v>
       </c>
       <c r="G33">
-        <v>45453</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B34" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
@@ -1105,98 +1105,95 @@
         <v>FLCM</v>
       </c>
       <c r="E34" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G34">
-        <v>45461</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B35" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D35" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E35" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G35">
-        <v>45714</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-15822</v>
       </c>
       <c r="B36" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D36" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E36" t="str">
         <v>estimates</v>
       </c>
       <c r="G36">
-        <v>45686</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ENT-15822</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B37" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D37" t="str">
-        <v>FLCM</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E37" t="str">
         <v>estimates</v>
       </c>
       <c r="G37">
-        <v>45650</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-17853</v>
       </c>
       <c r="B38" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
       </c>
-      <c r="D38" t="str">
-        <v>BSCM/ESCM</v>
-      </c>
       <c r="E38" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G38">
-        <v>45541</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ENT-17853</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B39" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
@@ -1205,15 +1202,15 @@
         <v>ofs</v>
       </c>
       <c r="G39">
-        <v>45691</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B40" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
@@ -1222,15 +1219,15 @@
         <v>ofs</v>
       </c>
       <c r="G40">
-        <v>45559</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B41" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1239,15 +1236,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45596</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B42" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1256,15 +1253,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45378</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B43" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1273,15 +1270,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45468</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B44" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1290,15 +1287,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45310</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B45" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1307,15 +1304,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45427</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B46" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1324,15 +1321,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45279</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B47" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1341,15 +1338,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45558</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B48" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1358,15 +1355,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45383</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B49" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1375,15 +1372,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45638</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B50" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1392,15 +1389,15 @@
         <v>ofs</v>
       </c>
       <c r="G50">
-        <v>45461</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B51" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1414,10 +1411,10 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B52" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1426,15 +1423,15 @@
         <v>ofs</v>
       </c>
       <c r="G52">
-        <v>45371</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B53" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1443,15 +1440,15 @@
         <v>ofs</v>
       </c>
       <c r="G53">
-        <v>45406</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B54" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1460,15 +1457,15 @@
         <v>ofs</v>
       </c>
       <c r="G54">
-        <v>45364</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B55" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1477,15 +1474,15 @@
         <v>ofs</v>
       </c>
       <c r="G55">
-        <v>45593</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B56" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1494,15 +1491,15 @@
         <v>ofs</v>
       </c>
       <c r="G56">
-        <v>45408</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B57" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
@@ -1511,15 +1508,15 @@
         <v>ofs</v>
       </c>
       <c r="G57">
-        <v>45595</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B58" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C58" t="str">
         <v>Invite to JRM</v>
@@ -1528,15 +1525,15 @@
         <v>ofs</v>
       </c>
       <c r="G58">
-        <v>45392</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B59" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C59" t="str">
         <v>Invite to JRM</v>
@@ -1550,27 +1547,27 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B60" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C60" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E60" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G60">
-        <v>45411</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-18725</v>
       </c>
       <c r="B61" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>US Video System - Lenel to Genetec</v>
       </c>
       <c r="C61" t="str">
         <v>Invite to JRM</v>
@@ -1582,26 +1579,9 @@
         <v>45721</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="str">
-        <v>ENT-18725</v>
-      </c>
-      <c r="B62" t="str">
-        <v>US Video System - Lenel to Genetec</v>
-      </c>
-      <c r="C62" t="str">
-        <v>Invite to JRM</v>
-      </c>
-      <c r="E62" t="str">
-        <v>jrm</v>
-      </c>
-      <c r="G62">
-        <v>45721</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G62"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G61"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G62"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -429,53 +429,56 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>16031</v>
+        <v>2123</v>
       </c>
       <c r="B2" t="str">
-        <v>qweqwe</v>
+        <v>234234</v>
       </c>
       <c r="C2" t="str">
-        <v>qweqwe</v>
+        <v>234234</v>
       </c>
       <c r="D2" t="str">
-        <v>qweqwe</v>
+        <v>234234</v>
       </c>
       <c r="E2" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="F2" t="str">
         <v/>
       </c>
       <c r="G2" t="str">
-        <v>2025-03-04</v>
+        <v>2025-02-26</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ENT-17062</v>
+        <v>16031</v>
       </c>
       <c r="B3" t="str">
-        <v>Account Open Enhancements and Outcome Orchestration</v>
+        <v>qweqwe</v>
       </c>
       <c r="C3" t="str">
-        <v>Invite to JRM</v>
+        <v>qweqwe</v>
       </c>
       <c r="D3" t="str">
-        <v>FLCM</v>
+        <v>qweqwe</v>
       </c>
       <c r="E3" t="str">
-        <v>estimates</v>
-      </c>
-      <c r="G3">
-        <v>45672</v>
+        <v>approved</v>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v>2025-03-04</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ENT-16949</v>
+        <v>ENT-17062</v>
       </c>
       <c r="B4" t="str">
-        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
+        <v>Account Open Enhancements and Outcome Orchestration</v>
       </c>
       <c r="C4" t="str">
         <v>Invite to JRM</v>
@@ -487,15 +490,15 @@
         <v>estimates</v>
       </c>
       <c r="G4">
-        <v>45531</v>
+        <v>45672</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ENT-16881</v>
+        <v>ENT-16949</v>
       </c>
       <c r="B5" t="str">
-        <v>Split up Personal Overdraft P&amp;L</v>
+        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
       </c>
       <c r="C5" t="str">
         <v>Invite to JRM</v>
@@ -504,18 +507,18 @@
         <v>FLCM</v>
       </c>
       <c r="E5" t="str">
-        <v>approved</v>
+        <v>estimates</v>
       </c>
       <c r="G5">
-        <v>45929</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ENT-16700</v>
+        <v>ENT-16881</v>
       </c>
       <c r="B6" t="str">
-        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
+        <v>Split up Personal Overdraft P&amp;L</v>
       </c>
       <c r="C6" t="str">
         <v>Invite to JRM</v>
@@ -524,18 +527,18 @@
         <v>FLCM</v>
       </c>
       <c r="E6" t="str">
-        <v>ofs</v>
+        <v>approved</v>
       </c>
       <c r="G6">
-        <v>45523</v>
+        <v>45929</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENT-16621</v>
+        <v>ENT-16700</v>
       </c>
       <c r="B7" t="str">
-        <v>CIW Data Products to PROD</v>
+        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
       </c>
       <c r="C7" t="str">
         <v>Invite to JRM</v>
@@ -547,15 +550,15 @@
         <v>ofs</v>
       </c>
       <c r="G7">
-        <v>45596</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENT-16374</v>
+        <v>ENT-16621</v>
       </c>
       <c r="B8" t="str">
-        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
+        <v>CIW Data Products to PROD</v>
       </c>
       <c r="C8" t="str">
         <v>Invite to JRM</v>
@@ -564,18 +567,18 @@
         <v>FLCM</v>
       </c>
       <c r="E8" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G8">
-        <v>45455</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-15917</v>
+        <v>ENT-16374</v>
       </c>
       <c r="B9" t="str">
-        <v>REBO Bill Payment Investigation Requests</v>
+        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -584,18 +587,18 @@
         <v>FLCM</v>
       </c>
       <c r="E9" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G9">
-        <v>45613</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-17286</v>
+        <v>ENT-15917</v>
       </c>
       <c r="B10" t="str">
-        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
+        <v>REBO Bill Payment Investigation Requests</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -604,18 +607,18 @@
         <v>FLCM</v>
       </c>
       <c r="E10" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G10">
-        <v>45699</v>
+        <v>45613</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17286</v>
       </c>
       <c r="B11" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -626,19 +629,16 @@
       <c r="E11" t="str">
         <v>approved</v>
       </c>
-      <c r="F11" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G11">
-        <v>45686</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B12" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -647,18 +647,21 @@
         <v>FLCM</v>
       </c>
       <c r="E12" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F12" t="str">
+        <v>PDF</v>
       </c>
       <c r="G12">
-        <v>45700</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B13" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -670,15 +673,15 @@
         <v>estimates</v>
       </c>
       <c r="G13">
-        <v>45656</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B14" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -690,15 +693,15 @@
         <v>estimates</v>
       </c>
       <c r="G14">
-        <v>45588</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B15" t="str">
-        <v>Data Source to EDGE</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -710,15 +713,15 @@
         <v>estimates</v>
       </c>
       <c r="G15">
-        <v>45664</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-17054</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B16" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -727,21 +730,18 @@
         <v>FLCM</v>
       </c>
       <c r="E16" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F16" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G16">
-        <v>45691</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-17054</v>
       </c>
       <c r="B17" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -752,16 +752,19 @@
       <c r="E17" t="str">
         <v>approved</v>
       </c>
+      <c r="F17" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G17">
-        <v>45299</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ENT-14372</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B18" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
@@ -772,19 +775,16 @@
       <c r="E18" t="str">
         <v>approved</v>
       </c>
-      <c r="F18" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G18">
-        <v>45512</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-14372</v>
       </c>
       <c r="B19" t="str">
-        <v>RAMP Phase 2</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
@@ -799,58 +799,58 @@
         <v>PDF</v>
       </c>
       <c r="G19">
-        <v>45562</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B20" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D20" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E20" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F20" t="str">
+        <v>PDF</v>
       </c>
       <c r="G20">
-        <v>45695</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B21" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D21" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E21" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F21" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G21">
-        <v>45688</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B22" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
@@ -865,15 +865,15 @@
         <v>PDF</v>
       </c>
       <c r="G22">
-        <v>45701</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B23" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
@@ -888,15 +888,15 @@
         <v>PDF</v>
       </c>
       <c r="G23">
-        <v>45695</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B24" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
@@ -907,16 +907,19 @@
       <c r="E24" t="str">
         <v>approved</v>
       </c>
+      <c r="F24" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G24">
-        <v>45706</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B25" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
@@ -925,138 +928,138 @@
         <v>FLCM</v>
       </c>
       <c r="E25" t="str">
-        <v>estimates</v>
+        <v>approved</v>
       </c>
       <c r="G25">
-        <v>45559</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B26" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D26" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E26" t="str">
         <v>estimates</v>
       </c>
       <c r="G26">
-        <v>45623</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B27" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D27" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E27" t="str">
         <v>estimates</v>
       </c>
       <c r="G27">
-        <v>45355</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B28" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D28" t="str">
-        <v>CorpSec</v>
+        <v>FLCM</v>
       </c>
       <c r="E28" t="str">
         <v>estimates</v>
       </c>
       <c r="G28">
-        <v>45446</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B29" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>BSCM/ESCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E29" t="str">
         <v>estimates</v>
       </c>
       <c r="G29">
-        <v>45477</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B30" t="str">
-        <v>CSDM Upgrade</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D30" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E30" t="str">
         <v>estimates</v>
       </c>
       <c r="G30">
-        <v>45394</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B31" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D31" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E31" t="str">
-        <v>ofs</v>
+        <v>estimates</v>
       </c>
       <c r="G31">
-        <v>45531</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B32" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
@@ -1068,15 +1071,15 @@
         <v>ofs</v>
       </c>
       <c r="G32">
-        <v>45453</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B33" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
@@ -1088,15 +1091,15 @@
         <v>ofs</v>
       </c>
       <c r="G33">
-        <v>45461</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B34" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
@@ -1105,95 +1108,98 @@
         <v>FLCM</v>
       </c>
       <c r="E34" t="str">
-        <v>jrm</v>
+        <v>ofs</v>
       </c>
       <c r="G34">
-        <v>45714</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B35" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D35" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E35" t="str">
-        <v>estimates</v>
+        <v>jrm</v>
       </c>
       <c r="G35">
-        <v>45686</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-15822</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B36" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D36" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E36" t="str">
         <v>estimates</v>
       </c>
       <c r="G36">
-        <v>45650</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-15822</v>
       </c>
       <c r="B37" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D37" t="str">
-        <v>BSCM/ESCM</v>
+        <v>FLCM</v>
       </c>
       <c r="E37" t="str">
         <v>estimates</v>
       </c>
       <c r="G37">
-        <v>45541</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ENT-17853</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B38" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
       </c>
+      <c r="D38" t="str">
+        <v>BSCM/ESCM</v>
+      </c>
       <c r="E38" t="str">
-        <v>ofs</v>
+        <v>estimates</v>
       </c>
       <c r="G38">
-        <v>45691</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-17853</v>
       </c>
       <c r="B39" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
@@ -1202,15 +1208,15 @@
         <v>ofs</v>
       </c>
       <c r="G39">
-        <v>45559</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B40" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
@@ -1219,15 +1225,15 @@
         <v>ofs</v>
       </c>
       <c r="G40">
-        <v>45596</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B41" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1236,15 +1242,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45378</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B42" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1253,15 +1259,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45468</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B43" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1270,15 +1276,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45310</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B44" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1287,15 +1293,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45427</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B45" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1304,15 +1310,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45279</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B46" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1321,15 +1327,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45558</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B47" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1338,15 +1344,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45383</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B48" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1355,15 +1361,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45638</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B49" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1372,15 +1378,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45461</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B50" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1389,15 +1395,15 @@
         <v>ofs</v>
       </c>
       <c r="G50">
-        <v>45371</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B51" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1411,10 +1417,10 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B52" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1423,15 +1429,15 @@
         <v>ofs</v>
       </c>
       <c r="G52">
-        <v>45406</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B53" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1440,15 +1446,15 @@
         <v>ofs</v>
       </c>
       <c r="G53">
-        <v>45364</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B54" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1457,15 +1463,15 @@
         <v>ofs</v>
       </c>
       <c r="G54">
-        <v>45593</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B55" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1474,15 +1480,15 @@
         <v>ofs</v>
       </c>
       <c r="G55">
-        <v>45408</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B56" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1491,15 +1497,15 @@
         <v>ofs</v>
       </c>
       <c r="G56">
-        <v>45595</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B57" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
@@ -1508,15 +1514,15 @@
         <v>ofs</v>
       </c>
       <c r="G57">
-        <v>45392</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B58" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C58" t="str">
         <v>Invite to JRM</v>
@@ -1525,15 +1531,15 @@
         <v>ofs</v>
       </c>
       <c r="G58">
-        <v>45411</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B59" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C59" t="str">
         <v>Invite to JRM</v>
@@ -1547,27 +1553,27 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B60" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C60" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E60" t="str">
-        <v>jrm</v>
+        <v>ofs</v>
       </c>
       <c r="G60">
-        <v>45721</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ENT-18725</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B61" t="str">
-        <v>US Video System - Lenel to Genetec</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C61" t="str">
         <v>Invite to JRM</v>
@@ -1579,9 +1585,26 @@
         <v>45721</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>ENT-18725</v>
+      </c>
+      <c r="B62" t="str">
+        <v>US Video System - Lenel to Genetec</v>
+      </c>
+      <c r="C62" t="str">
+        <v>Invite to JRM</v>
+      </c>
+      <c r="E62" t="str">
+        <v>jrm</v>
+      </c>
+      <c r="G62">
+        <v>45721</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G62"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -1701,7 +1701,7 @@
         <v>178399.00</v>
       </c>
       <c r="C2" t="str">
-        <v>2500.00</v>
+        <v>234324</v>
       </c>
       <c r="D2" t="str">
         <v>-</v>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -1701,7 +1701,7 @@
         <v>178399.00</v>
       </c>
       <c r="C2" t="str">
-        <v>234324</v>
+        <v>abdc</v>
       </c>
       <c r="D2" t="str">
         <v>-</v>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G61"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -429,56 +429,53 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2123</v>
+        <v>16031</v>
       </c>
       <c r="B2" t="str">
-        <v>234234</v>
+        <v>qweqwe</v>
       </c>
       <c r="C2" t="str">
-        <v>234234</v>
+        <v>qweqwe</v>
       </c>
       <c r="D2" t="str">
-        <v>234234</v>
+        <v>qweqwe</v>
       </c>
       <c r="E2" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="F2" t="str">
         <v/>
       </c>
       <c r="G2" t="str">
-        <v>2025-02-26</v>
+        <v>2025-03-04</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>16031</v>
+        <v>ENT-17062</v>
       </c>
       <c r="B3" t="str">
-        <v>qweqwe</v>
+        <v>Account Open Enhancements and Outcome Orchestration</v>
       </c>
       <c r="C3" t="str">
-        <v>qweqwe</v>
+        <v>Invite to JRM</v>
       </c>
       <c r="D3" t="str">
-        <v>qweqwe</v>
+        <v>FLCM</v>
       </c>
       <c r="E3" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v>2025-03-04</v>
+        <v>estimates</v>
+      </c>
+      <c r="G3">
+        <v>45672</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ENT-17062</v>
+        <v>ENT-16949</v>
       </c>
       <c r="B4" t="str">
-        <v>Account Open Enhancements and Outcome Orchestration</v>
+        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
       </c>
       <c r="C4" t="str">
         <v>Invite to JRM</v>
@@ -490,15 +487,15 @@
         <v>estimates</v>
       </c>
       <c r="G4">
-        <v>45672</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ENT-16949</v>
+        <v>ENT-16881</v>
       </c>
       <c r="B5" t="str">
-        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
+        <v>Split up Personal Overdraft P&amp;L</v>
       </c>
       <c r="C5" t="str">
         <v>Invite to JRM</v>
@@ -507,18 +504,18 @@
         <v>FLCM</v>
       </c>
       <c r="E5" t="str">
-        <v>estimates</v>
+        <v>approved</v>
       </c>
       <c r="G5">
-        <v>45531</v>
+        <v>45929</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ENT-16881</v>
+        <v>ENT-16700</v>
       </c>
       <c r="B6" t="str">
-        <v>Split up Personal Overdraft P&amp;L</v>
+        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
       </c>
       <c r="C6" t="str">
         <v>Invite to JRM</v>
@@ -527,18 +524,18 @@
         <v>FLCM</v>
       </c>
       <c r="E6" t="str">
-        <v>approved</v>
+        <v>ofs</v>
       </c>
       <c r="G6">
-        <v>45929</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENT-16700</v>
+        <v>ENT-16621</v>
       </c>
       <c r="B7" t="str">
-        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
+        <v>CIW Data Products to PROD</v>
       </c>
       <c r="C7" t="str">
         <v>Invite to JRM</v>
@@ -550,15 +547,15 @@
         <v>ofs</v>
       </c>
       <c r="G7">
-        <v>45523</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENT-16621</v>
+        <v>ENT-16374</v>
       </c>
       <c r="B8" t="str">
-        <v>CIW Data Products to PROD</v>
+        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
       </c>
       <c r="C8" t="str">
         <v>Invite to JRM</v>
@@ -567,18 +564,18 @@
         <v>FLCM</v>
       </c>
       <c r="E8" t="str">
-        <v>ofs</v>
+        <v>estimates</v>
       </c>
       <c r="G8">
-        <v>45596</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-16374</v>
+        <v>ENT-15917</v>
       </c>
       <c r="B9" t="str">
-        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
+        <v>REBO Bill Payment Investigation Requests</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -587,18 +584,18 @@
         <v>FLCM</v>
       </c>
       <c r="E9" t="str">
-        <v>estimates</v>
+        <v>jrm</v>
       </c>
       <c r="G9">
-        <v>45455</v>
+        <v>45613</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-15917</v>
+        <v>ENT-17286</v>
       </c>
       <c r="B10" t="str">
-        <v>REBO Bill Payment Investigation Requests</v>
+        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -607,18 +604,18 @@
         <v>FLCM</v>
       </c>
       <c r="E10" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G10">
-        <v>45613</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-17286</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B11" t="str">
-        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -629,16 +626,19 @@
       <c r="E11" t="str">
         <v>approved</v>
       </c>
+      <c r="F11" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G11">
-        <v>45699</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B12" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -647,21 +647,18 @@
         <v>FLCM</v>
       </c>
       <c r="E12" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F12" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G12">
-        <v>45686</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B13" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -673,15 +670,15 @@
         <v>estimates</v>
       </c>
       <c r="G13">
-        <v>45700</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B14" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -693,15 +690,15 @@
         <v>estimates</v>
       </c>
       <c r="G14">
-        <v>45656</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B15" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -713,15 +710,15 @@
         <v>estimates</v>
       </c>
       <c r="G15">
-        <v>45588</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-17054</v>
       </c>
       <c r="B16" t="str">
-        <v>Data Source to EDGE</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -730,18 +727,21 @@
         <v>FLCM</v>
       </c>
       <c r="E16" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F16" t="str">
+        <v>PDF</v>
       </c>
       <c r="G16">
-        <v>45664</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ENT-17054</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B17" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -752,19 +752,16 @@
       <c r="E17" t="str">
         <v>approved</v>
       </c>
-      <c r="F17" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G17">
-        <v>45691</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-14372</v>
       </c>
       <c r="B18" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
@@ -775,16 +772,19 @@
       <c r="E18" t="str">
         <v>approved</v>
       </c>
+      <c r="F18" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G18">
-        <v>45299</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ENT-14372</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B19" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
@@ -799,58 +799,58 @@
         <v>PDF</v>
       </c>
       <c r="G19">
-        <v>45512</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B20" t="str">
-        <v>RAMP Phase 2</v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D20" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E20" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F20" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G20">
-        <v>45562</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B21" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D21" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E21" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F21" t="str">
+        <v>PDF</v>
       </c>
       <c r="G21">
-        <v>45695</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B22" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
@@ -865,15 +865,15 @@
         <v>PDF</v>
       </c>
       <c r="G22">
-        <v>45688</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B23" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
@@ -888,15 +888,15 @@
         <v>PDF</v>
       </c>
       <c r="G23">
-        <v>45701</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B24" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
@@ -907,19 +907,16 @@
       <c r="E24" t="str">
         <v>approved</v>
       </c>
-      <c r="F24" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G24">
-        <v>45695</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B25" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
@@ -928,138 +925,138 @@
         <v>FLCM</v>
       </c>
       <c r="E25" t="str">
-        <v>approved</v>
+        <v>estimates</v>
       </c>
       <c r="G25">
-        <v>45706</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B26" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D26" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E26" t="str">
         <v>estimates</v>
       </c>
       <c r="G26">
-        <v>45559</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B27" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D27" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E27" t="str">
         <v>estimates</v>
       </c>
       <c r="G27">
-        <v>45623</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B28" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D28" t="str">
-        <v>FLCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E28" t="str">
         <v>estimates</v>
       </c>
       <c r="G28">
-        <v>45355</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B29" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>CorpSec</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E29" t="str">
         <v>estimates</v>
       </c>
       <c r="G29">
-        <v>45446</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B30" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D30" t="str">
-        <v>BSCM/ESCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E30" t="str">
         <v>estimates</v>
       </c>
       <c r="G30">
-        <v>45477</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B31" t="str">
-        <v>CSDM Upgrade</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D31" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E31" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G31">
-        <v>45394</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B32" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
@@ -1071,15 +1068,15 @@
         <v>ofs</v>
       </c>
       <c r="G32">
-        <v>45531</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B33" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
@@ -1091,15 +1088,15 @@
         <v>ofs</v>
       </c>
       <c r="G33">
-        <v>45453</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B34" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
@@ -1108,98 +1105,95 @@
         <v>FLCM</v>
       </c>
       <c r="E34" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G34">
-        <v>45461</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B35" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D35" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E35" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G35">
-        <v>45714</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-15822</v>
       </c>
       <c r="B36" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D36" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E36" t="str">
         <v>estimates</v>
       </c>
       <c r="G36">
-        <v>45686</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ENT-15822</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B37" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D37" t="str">
-        <v>FLCM</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E37" t="str">
         <v>estimates</v>
       </c>
       <c r="G37">
-        <v>45650</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-17853</v>
       </c>
       <c r="B38" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
       </c>
-      <c r="D38" t="str">
-        <v>BSCM/ESCM</v>
-      </c>
       <c r="E38" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G38">
-        <v>45541</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ENT-17853</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B39" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
@@ -1208,15 +1202,15 @@
         <v>ofs</v>
       </c>
       <c r="G39">
-        <v>45691</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B40" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
@@ -1225,15 +1219,15 @@
         <v>ofs</v>
       </c>
       <c r="G40">
-        <v>45559</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B41" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1242,15 +1236,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45596</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B42" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1259,15 +1253,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45378</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B43" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1276,15 +1270,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45468</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B44" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1293,15 +1287,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45310</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B45" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1310,15 +1304,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45427</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B46" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1327,15 +1321,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45279</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B47" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1344,15 +1338,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45558</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B48" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1361,15 +1355,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45383</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B49" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1378,15 +1372,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45638</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B50" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1395,15 +1389,15 @@
         <v>ofs</v>
       </c>
       <c r="G50">
-        <v>45461</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B51" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1417,10 +1411,10 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B52" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1429,15 +1423,15 @@
         <v>ofs</v>
       </c>
       <c r="G52">
-        <v>45371</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B53" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1446,15 +1440,15 @@
         <v>ofs</v>
       </c>
       <c r="G53">
-        <v>45406</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B54" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1463,15 +1457,15 @@
         <v>ofs</v>
       </c>
       <c r="G54">
-        <v>45364</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B55" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1480,15 +1474,15 @@
         <v>ofs</v>
       </c>
       <c r="G55">
-        <v>45593</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B56" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1497,15 +1491,15 @@
         <v>ofs</v>
       </c>
       <c r="G56">
-        <v>45408</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B57" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
@@ -1514,15 +1508,15 @@
         <v>ofs</v>
       </c>
       <c r="G57">
-        <v>45595</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B58" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C58" t="str">
         <v>Invite to JRM</v>
@@ -1531,15 +1525,15 @@
         <v>ofs</v>
       </c>
       <c r="G58">
-        <v>45392</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B59" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C59" t="str">
         <v>Invite to JRM</v>
@@ -1553,27 +1547,27 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B60" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C60" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E60" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G60">
-        <v>45411</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-18725</v>
       </c>
       <c r="B61" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>US Video System - Lenel to Genetec</v>
       </c>
       <c r="C61" t="str">
         <v>Invite to JRM</v>
@@ -1585,26 +1579,9 @@
         <v>45721</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="str">
-        <v>ENT-18725</v>
-      </c>
-      <c r="B62" t="str">
-        <v>US Video System - Lenel to Genetec</v>
-      </c>
-      <c r="C62" t="str">
-        <v>Invite to JRM</v>
-      </c>
-      <c r="E62" t="str">
-        <v>jrm</v>
-      </c>
-      <c r="G62">
-        <v>45721</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G62"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G61"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -584,7 +584,7 @@
         <v>FLCM</v>
       </c>
       <c r="E9" t="str">
-        <v>jrm</v>
+        <v>ofs</v>
       </c>
       <c r="G9">
         <v>45613</v>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G62"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -429,53 +429,56 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>16031</v>
+        <v>18472</v>
       </c>
       <c r="B2" t="str">
-        <v>qweqwe</v>
+        <v>12321</v>
       </c>
       <c r="C2" t="str">
-        <v>qweqwe</v>
+        <v>123123</v>
       </c>
       <c r="D2" t="str">
-        <v>qweqwe</v>
+        <v>123123</v>
       </c>
       <c r="E2" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="F2" t="str">
         <v/>
       </c>
       <c r="G2" t="str">
-        <v>2025-03-04</v>
+        <v>2025-03-10</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ENT-17062</v>
+        <v>16031</v>
       </c>
       <c r="B3" t="str">
-        <v>Account Open Enhancements and Outcome Orchestration</v>
+        <v>qweqwe</v>
       </c>
       <c r="C3" t="str">
-        <v>Invite to JRM</v>
+        <v>qweqwe</v>
       </c>
       <c r="D3" t="str">
-        <v>FLCM</v>
+        <v>qweqwe</v>
       </c>
       <c r="E3" t="str">
-        <v>estimates</v>
-      </c>
-      <c r="G3">
-        <v>45672</v>
+        <v>approved</v>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v>2025-03-04</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ENT-16949</v>
+        <v>ENT-17062</v>
       </c>
       <c r="B4" t="str">
-        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
+        <v>Account Open Enhancements and Outcome Orchestration</v>
       </c>
       <c r="C4" t="str">
         <v>Invite to JRM</v>
@@ -487,15 +490,15 @@
         <v>estimates</v>
       </c>
       <c r="G4">
-        <v>45531</v>
+        <v>45672</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ENT-16881</v>
+        <v>ENT-16949</v>
       </c>
       <c r="B5" t="str">
-        <v>Split up Personal Overdraft P&amp;L</v>
+        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
       </c>
       <c r="C5" t="str">
         <v>Invite to JRM</v>
@@ -504,18 +507,18 @@
         <v>FLCM</v>
       </c>
       <c r="E5" t="str">
-        <v>approved</v>
+        <v>estimates</v>
       </c>
       <c r="G5">
-        <v>45929</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ENT-16700</v>
+        <v>ENT-16881</v>
       </c>
       <c r="B6" t="str">
-        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
+        <v>Split up Personal Overdraft P&amp;L</v>
       </c>
       <c r="C6" t="str">
         <v>Invite to JRM</v>
@@ -524,18 +527,18 @@
         <v>FLCM</v>
       </c>
       <c r="E6" t="str">
-        <v>ofs</v>
+        <v>approved</v>
       </c>
       <c r="G6">
-        <v>45523</v>
+        <v>45929</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENT-16621</v>
+        <v>ENT-16700</v>
       </c>
       <c r="B7" t="str">
-        <v>CIW Data Products to PROD</v>
+        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
       </c>
       <c r="C7" t="str">
         <v>Invite to JRM</v>
@@ -547,15 +550,15 @@
         <v>ofs</v>
       </c>
       <c r="G7">
-        <v>45596</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENT-16374</v>
+        <v>ENT-16621</v>
       </c>
       <c r="B8" t="str">
-        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
+        <v>CIW Data Products to PROD</v>
       </c>
       <c r="C8" t="str">
         <v>Invite to JRM</v>
@@ -564,18 +567,18 @@
         <v>FLCM</v>
       </c>
       <c r="E8" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G8">
-        <v>45455</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-15917</v>
+        <v>ENT-16374</v>
       </c>
       <c r="B9" t="str">
-        <v>REBO Bill Payment Investigation Requests</v>
+        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -584,18 +587,18 @@
         <v>FLCM</v>
       </c>
       <c r="E9" t="str">
-        <v>ofs</v>
+        <v>estimates</v>
       </c>
       <c r="G9">
-        <v>45613</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-17286</v>
+        <v>ENT-15917</v>
       </c>
       <c r="B10" t="str">
-        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
+        <v>REBO Bill Payment Investigation Requests</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -604,18 +607,18 @@
         <v>FLCM</v>
       </c>
       <c r="E10" t="str">
-        <v>approved</v>
+        <v>ofs</v>
       </c>
       <c r="G10">
-        <v>45699</v>
+        <v>45613</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17286</v>
       </c>
       <c r="B11" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -626,19 +629,16 @@
       <c r="E11" t="str">
         <v>approved</v>
       </c>
-      <c r="F11" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G11">
-        <v>45686</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B12" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -647,18 +647,21 @@
         <v>FLCM</v>
       </c>
       <c r="E12" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F12" t="str">
+        <v>PDF</v>
       </c>
       <c r="G12">
-        <v>45700</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B13" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -670,15 +673,15 @@
         <v>estimates</v>
       </c>
       <c r="G13">
-        <v>45656</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B14" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -690,15 +693,15 @@
         <v>estimates</v>
       </c>
       <c r="G14">
-        <v>45588</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B15" t="str">
-        <v>Data Source to EDGE</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -710,15 +713,15 @@
         <v>estimates</v>
       </c>
       <c r="G15">
-        <v>45664</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-17054</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B16" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -727,21 +730,18 @@
         <v>FLCM</v>
       </c>
       <c r="E16" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F16" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G16">
-        <v>45691</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-17054</v>
       </c>
       <c r="B17" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -752,16 +752,19 @@
       <c r="E17" t="str">
         <v>approved</v>
       </c>
+      <c r="F17" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G17">
-        <v>45299</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ENT-14372</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B18" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
@@ -772,19 +775,16 @@
       <c r="E18" t="str">
         <v>approved</v>
       </c>
-      <c r="F18" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G18">
-        <v>45512</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-14372</v>
       </c>
       <c r="B19" t="str">
-        <v>RAMP Phase 2</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
@@ -799,58 +799,58 @@
         <v>PDF</v>
       </c>
       <c r="G19">
-        <v>45562</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B20" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D20" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E20" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F20" t="str">
+        <v>PDF</v>
       </c>
       <c r="G20">
-        <v>45695</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B21" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D21" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E21" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F21" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G21">
-        <v>45688</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B22" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
@@ -865,15 +865,15 @@
         <v>PDF</v>
       </c>
       <c r="G22">
-        <v>45701</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B23" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
@@ -888,15 +888,15 @@
         <v>PDF</v>
       </c>
       <c r="G23">
-        <v>45695</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B24" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
@@ -907,16 +907,19 @@
       <c r="E24" t="str">
         <v>approved</v>
       </c>
+      <c r="F24" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G24">
-        <v>45706</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B25" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
@@ -925,138 +928,138 @@
         <v>FLCM</v>
       </c>
       <c r="E25" t="str">
-        <v>estimates</v>
+        <v>approved</v>
       </c>
       <c r="G25">
-        <v>45559</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B26" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D26" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E26" t="str">
         <v>estimates</v>
       </c>
       <c r="G26">
-        <v>45623</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B27" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D27" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E27" t="str">
         <v>estimates</v>
       </c>
       <c r="G27">
-        <v>45355</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B28" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D28" t="str">
-        <v>CorpSec</v>
+        <v>FLCM</v>
       </c>
       <c r="E28" t="str">
         <v>estimates</v>
       </c>
       <c r="G28">
-        <v>45446</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B29" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>BSCM/ESCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E29" t="str">
         <v>estimates</v>
       </c>
       <c r="G29">
-        <v>45477</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B30" t="str">
-        <v>CSDM Upgrade</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D30" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E30" t="str">
         <v>estimates</v>
       </c>
       <c r="G30">
-        <v>45394</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B31" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D31" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E31" t="str">
-        <v>ofs</v>
+        <v>estimates</v>
       </c>
       <c r="G31">
-        <v>45531</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B32" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
@@ -1068,15 +1071,15 @@
         <v>ofs</v>
       </c>
       <c r="G32">
-        <v>45453</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B33" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
@@ -1088,15 +1091,15 @@
         <v>ofs</v>
       </c>
       <c r="G33">
-        <v>45461</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B34" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
@@ -1105,95 +1108,98 @@
         <v>FLCM</v>
       </c>
       <c r="E34" t="str">
-        <v>jrm</v>
+        <v>ofs</v>
       </c>
       <c r="G34">
-        <v>45714</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B35" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D35" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E35" t="str">
-        <v>estimates</v>
+        <v>jrm</v>
       </c>
       <c r="G35">
-        <v>45686</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-15822</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B36" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D36" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E36" t="str">
         <v>estimates</v>
       </c>
       <c r="G36">
-        <v>45650</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-15822</v>
       </c>
       <c r="B37" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D37" t="str">
-        <v>BSCM/ESCM</v>
+        <v>FLCM</v>
       </c>
       <c r="E37" t="str">
         <v>estimates</v>
       </c>
       <c r="G37">
-        <v>45541</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ENT-17853</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B38" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
       </c>
+      <c r="D38" t="str">
+        <v>BSCM/ESCM</v>
+      </c>
       <c r="E38" t="str">
-        <v>ofs</v>
+        <v>estimates</v>
       </c>
       <c r="G38">
-        <v>45691</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-17853</v>
       </c>
       <c r="B39" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
@@ -1202,15 +1208,15 @@
         <v>ofs</v>
       </c>
       <c r="G39">
-        <v>45559</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B40" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
@@ -1219,15 +1225,15 @@
         <v>ofs</v>
       </c>
       <c r="G40">
-        <v>45596</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B41" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1236,15 +1242,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45378</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B42" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1253,15 +1259,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45468</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B43" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1270,15 +1276,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45310</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B44" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1287,15 +1293,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45427</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B45" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1304,15 +1310,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45279</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B46" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1321,15 +1327,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45558</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B47" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1338,15 +1344,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45383</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B48" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1355,15 +1361,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45638</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B49" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1372,15 +1378,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45461</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B50" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1389,15 +1395,15 @@
         <v>ofs</v>
       </c>
       <c r="G50">
-        <v>45371</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B51" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1411,10 +1417,10 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B52" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1423,15 +1429,15 @@
         <v>ofs</v>
       </c>
       <c r="G52">
-        <v>45406</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B53" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1440,15 +1446,15 @@
         <v>ofs</v>
       </c>
       <c r="G53">
-        <v>45364</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B54" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1457,15 +1463,15 @@
         <v>ofs</v>
       </c>
       <c r="G54">
-        <v>45593</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B55" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1474,15 +1480,15 @@
         <v>ofs</v>
       </c>
       <c r="G55">
-        <v>45408</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B56" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1491,15 +1497,15 @@
         <v>ofs</v>
       </c>
       <c r="G56">
-        <v>45595</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B57" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
@@ -1508,15 +1514,15 @@
         <v>ofs</v>
       </c>
       <c r="G57">
-        <v>45392</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B58" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C58" t="str">
         <v>Invite to JRM</v>
@@ -1525,15 +1531,15 @@
         <v>ofs</v>
       </c>
       <c r="G58">
-        <v>45411</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B59" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C59" t="str">
         <v>Invite to JRM</v>
@@ -1547,27 +1553,27 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B60" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C60" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E60" t="str">
-        <v>jrm</v>
+        <v>ofs</v>
       </c>
       <c r="G60">
-        <v>45721</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ENT-18725</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B61" t="str">
-        <v>US Video System - Lenel to Genetec</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C61" t="str">
         <v>Invite to JRM</v>
@@ -1579,9 +1585,26 @@
         <v>45721</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>ENT-18725</v>
+      </c>
+      <c r="B62" t="str">
+        <v>US Video System - Lenel to Genetec</v>
+      </c>
+      <c r="C62" t="str">
+        <v>Invite to JRM</v>
+      </c>
+      <c r="E62" t="str">
+        <v>jrm</v>
+      </c>
+      <c r="G62">
+        <v>45721</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G62"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -1778,19 +1778,19 @@
         <v>ENT-17213</v>
       </c>
       <c r="B3" t="str">
-        <v>1000000</v>
+        <v>1000000.00</v>
       </c>
       <c r="C3" t="str">
-        <v>67500</v>
+        <v>324</v>
       </c>
       <c r="D3" t="str">
         <v>-</v>
       </c>
       <c r="E3" t="str">
-        <v>425495</v>
+        <v>425495.00</v>
       </c>
       <c r="F3" t="str">
-        <v>106374</v>
+        <v>106374.00</v>
       </c>
       <c r="G3" t="str">
         <v>159</v>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G61"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -429,56 +429,53 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>18472</v>
+        <v>16031</v>
       </c>
       <c r="B2" t="str">
-        <v>12321</v>
+        <v>qweqwe</v>
       </c>
       <c r="C2" t="str">
-        <v>123123</v>
+        <v>qweqwe</v>
       </c>
       <c r="D2" t="str">
-        <v>123123</v>
+        <v>qweqwe</v>
       </c>
       <c r="E2" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="F2" t="str">
         <v/>
       </c>
       <c r="G2" t="str">
-        <v>2025-03-10</v>
+        <v>2025-03-04</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>16031</v>
+        <v>ENT-17062</v>
       </c>
       <c r="B3" t="str">
-        <v>qweqwe</v>
+        <v>Account Open Enhancements and Outcome Orchestration</v>
       </c>
       <c r="C3" t="str">
-        <v>qweqwe</v>
+        <v>Invite to JRM</v>
       </c>
       <c r="D3" t="str">
-        <v>qweqwe</v>
+        <v>FLCM</v>
       </c>
       <c r="E3" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v>2025-03-04</v>
+        <v>estimates</v>
+      </c>
+      <c r="G3">
+        <v>45672</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ENT-17062</v>
+        <v>ENT-16949</v>
       </c>
       <c r="B4" t="str">
-        <v>Account Open Enhancements and Outcome Orchestration</v>
+        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
       </c>
       <c r="C4" t="str">
         <v>Invite to JRM</v>
@@ -490,15 +487,15 @@
         <v>estimates</v>
       </c>
       <c r="G4">
-        <v>45672</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ENT-16949</v>
+        <v>ENT-16881</v>
       </c>
       <c r="B5" t="str">
-        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
+        <v>Split up Personal Overdraft P&amp;L</v>
       </c>
       <c r="C5" t="str">
         <v>Invite to JRM</v>
@@ -507,18 +504,18 @@
         <v>FLCM</v>
       </c>
       <c r="E5" t="str">
-        <v>estimates</v>
+        <v>approved</v>
       </c>
       <c r="G5">
-        <v>45531</v>
+        <v>45929</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ENT-16881</v>
+        <v>ENT-16700</v>
       </c>
       <c r="B6" t="str">
-        <v>Split up Personal Overdraft P&amp;L</v>
+        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
       </c>
       <c r="C6" t="str">
         <v>Invite to JRM</v>
@@ -527,18 +524,18 @@
         <v>FLCM</v>
       </c>
       <c r="E6" t="str">
-        <v>approved</v>
+        <v>ofs</v>
       </c>
       <c r="G6">
-        <v>45929</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENT-16700</v>
+        <v>ENT-16621</v>
       </c>
       <c r="B7" t="str">
-        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
+        <v>CIW Data Products to PROD</v>
       </c>
       <c r="C7" t="str">
         <v>Invite to JRM</v>
@@ -550,15 +547,15 @@
         <v>ofs</v>
       </c>
       <c r="G7">
-        <v>45523</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENT-16621</v>
+        <v>ENT-16374</v>
       </c>
       <c r="B8" t="str">
-        <v>CIW Data Products to PROD</v>
+        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
       </c>
       <c r="C8" t="str">
         <v>Invite to JRM</v>
@@ -567,18 +564,18 @@
         <v>FLCM</v>
       </c>
       <c r="E8" t="str">
-        <v>ofs</v>
+        <v>estimates</v>
       </c>
       <c r="G8">
-        <v>45596</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-16374</v>
+        <v>ENT-15917</v>
       </c>
       <c r="B9" t="str">
-        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
+        <v>REBO Bill Payment Investigation Requests</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -587,18 +584,18 @@
         <v>FLCM</v>
       </c>
       <c r="E9" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G9">
-        <v>45455</v>
+        <v>45613</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-15917</v>
+        <v>ENT-17286</v>
       </c>
       <c r="B10" t="str">
-        <v>REBO Bill Payment Investigation Requests</v>
+        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -607,18 +604,18 @@
         <v>FLCM</v>
       </c>
       <c r="E10" t="str">
-        <v>ofs</v>
+        <v>approved</v>
       </c>
       <c r="G10">
-        <v>45613</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-17286</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B11" t="str">
-        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -629,16 +626,19 @@
       <c r="E11" t="str">
         <v>approved</v>
       </c>
+      <c r="F11" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G11">
-        <v>45699</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B12" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -647,21 +647,18 @@
         <v>FLCM</v>
       </c>
       <c r="E12" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F12" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G12">
-        <v>45686</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B13" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -673,15 +670,15 @@
         <v>estimates</v>
       </c>
       <c r="G13">
-        <v>45700</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B14" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -693,15 +690,15 @@
         <v>estimates</v>
       </c>
       <c r="G14">
-        <v>45656</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B15" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -713,15 +710,15 @@
         <v>estimates</v>
       </c>
       <c r="G15">
-        <v>45588</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-17054</v>
       </c>
       <c r="B16" t="str">
-        <v>Data Source to EDGE</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -730,18 +727,21 @@
         <v>FLCM</v>
       </c>
       <c r="E16" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F16" t="str">
+        <v>PDF</v>
       </c>
       <c r="G16">
-        <v>45664</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ENT-17054</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B17" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -752,19 +752,16 @@
       <c r="E17" t="str">
         <v>approved</v>
       </c>
-      <c r="F17" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G17">
-        <v>45691</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-14372</v>
       </c>
       <c r="B18" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
@@ -775,16 +772,19 @@
       <c r="E18" t="str">
         <v>approved</v>
       </c>
+      <c r="F18" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G18">
-        <v>45299</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ENT-14372</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B19" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
@@ -799,58 +799,58 @@
         <v>PDF</v>
       </c>
       <c r="G19">
-        <v>45512</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B20" t="str">
-        <v>RAMP Phase 2</v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D20" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E20" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F20" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G20">
-        <v>45562</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B21" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D21" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E21" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F21" t="str">
+        <v>PDF</v>
       </c>
       <c r="G21">
-        <v>45695</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B22" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
@@ -865,15 +865,15 @@
         <v>PDF</v>
       </c>
       <c r="G22">
-        <v>45688</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B23" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
@@ -888,15 +888,15 @@
         <v>PDF</v>
       </c>
       <c r="G23">
-        <v>45701</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B24" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
@@ -907,19 +907,16 @@
       <c r="E24" t="str">
         <v>approved</v>
       </c>
-      <c r="F24" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G24">
-        <v>45695</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B25" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
@@ -928,138 +925,138 @@
         <v>FLCM</v>
       </c>
       <c r="E25" t="str">
-        <v>approved</v>
+        <v>estimates</v>
       </c>
       <c r="G25">
-        <v>45706</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B26" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D26" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E26" t="str">
         <v>estimates</v>
       </c>
       <c r="G26">
-        <v>45559</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B27" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D27" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E27" t="str">
         <v>estimates</v>
       </c>
       <c r="G27">
-        <v>45623</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B28" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D28" t="str">
-        <v>FLCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E28" t="str">
         <v>estimates</v>
       </c>
       <c r="G28">
-        <v>45355</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B29" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>CorpSec</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E29" t="str">
         <v>estimates</v>
       </c>
       <c r="G29">
-        <v>45446</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B30" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D30" t="str">
-        <v>BSCM/ESCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E30" t="str">
         <v>estimates</v>
       </c>
       <c r="G30">
-        <v>45477</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B31" t="str">
-        <v>CSDM Upgrade</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D31" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E31" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G31">
-        <v>45394</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B32" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
@@ -1071,15 +1068,15 @@
         <v>ofs</v>
       </c>
       <c r="G32">
-        <v>45531</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B33" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
@@ -1091,15 +1088,15 @@
         <v>ofs</v>
       </c>
       <c r="G33">
-        <v>45453</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B34" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
@@ -1108,98 +1105,95 @@
         <v>FLCM</v>
       </c>
       <c r="E34" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G34">
-        <v>45461</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B35" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D35" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E35" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G35">
-        <v>45714</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-15822</v>
       </c>
       <c r="B36" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D36" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E36" t="str">
         <v>estimates</v>
       </c>
       <c r="G36">
-        <v>45686</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ENT-15822</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B37" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D37" t="str">
-        <v>FLCM</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E37" t="str">
         <v>estimates</v>
       </c>
       <c r="G37">
-        <v>45650</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-17853</v>
       </c>
       <c r="B38" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
       </c>
-      <c r="D38" t="str">
-        <v>BSCM/ESCM</v>
-      </c>
       <c r="E38" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G38">
-        <v>45541</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ENT-17853</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B39" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
@@ -1208,15 +1202,15 @@
         <v>ofs</v>
       </c>
       <c r="G39">
-        <v>45691</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B40" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
@@ -1225,15 +1219,15 @@
         <v>ofs</v>
       </c>
       <c r="G40">
-        <v>45559</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B41" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1242,15 +1236,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45596</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B42" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1259,15 +1253,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45378</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B43" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1276,15 +1270,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45468</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B44" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1293,15 +1287,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45310</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B45" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1310,15 +1304,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45427</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B46" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1327,15 +1321,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45279</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B47" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1344,15 +1338,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45558</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B48" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1361,15 +1355,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45383</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B49" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1378,15 +1372,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45638</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B50" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1395,15 +1389,15 @@
         <v>ofs</v>
       </c>
       <c r="G50">
-        <v>45461</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B51" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1417,10 +1411,10 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B52" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1429,15 +1423,15 @@
         <v>ofs</v>
       </c>
       <c r="G52">
-        <v>45371</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B53" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1446,15 +1440,15 @@
         <v>ofs</v>
       </c>
       <c r="G53">
-        <v>45406</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B54" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1463,15 +1457,15 @@
         <v>ofs</v>
       </c>
       <c r="G54">
-        <v>45364</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B55" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1480,15 +1474,15 @@
         <v>ofs</v>
       </c>
       <c r="G55">
-        <v>45593</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B56" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1497,15 +1491,15 @@
         <v>ofs</v>
       </c>
       <c r="G56">
-        <v>45408</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B57" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
@@ -1514,15 +1508,15 @@
         <v>ofs</v>
       </c>
       <c r="G57">
-        <v>45595</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B58" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C58" t="str">
         <v>Invite to JRM</v>
@@ -1531,15 +1525,15 @@
         <v>ofs</v>
       </c>
       <c r="G58">
-        <v>45392</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B59" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C59" t="str">
         <v>Invite to JRM</v>
@@ -1553,27 +1547,27 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B60" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C60" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E60" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G60">
-        <v>45411</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-18725</v>
       </c>
       <c r="B61" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>US Video System - Lenel to Genetec</v>
       </c>
       <c r="C61" t="str">
         <v>Invite to JRM</v>
@@ -1585,26 +1579,9 @@
         <v>45721</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="str">
-        <v>ENT-18725</v>
-      </c>
-      <c r="B62" t="str">
-        <v>US Video System - Lenel to Genetec</v>
-      </c>
-      <c r="C62" t="str">
-        <v>Invite to JRM</v>
-      </c>
-      <c r="E62" t="str">
-        <v>jrm</v>
-      </c>
-      <c r="G62">
-        <v>45721</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G62"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G61"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -816,7 +816,7 @@
         <v>FIQM</v>
       </c>
       <c r="E20" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G20">
         <v>45695</v>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G60"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -429,33 +429,30 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>16031</v>
+        <v>ENT-17062</v>
       </c>
       <c r="B2" t="str">
-        <v>qweqwe</v>
+        <v>Account Open Enhancements and Outcome Orchestration</v>
       </c>
       <c r="C2" t="str">
-        <v>qweqwe</v>
+        <v>Invite to JRM</v>
       </c>
       <c r="D2" t="str">
-        <v>qweqwe</v>
+        <v>FLCM</v>
       </c>
       <c r="E2" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F2" t="str">
-        <v/>
-      </c>
-      <c r="G2" t="str">
-        <v>2025-03-04</v>
+        <v>estimates</v>
+      </c>
+      <c r="G2">
+        <v>45672</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ENT-17062</v>
+        <v>ENT-16949</v>
       </c>
       <c r="B3" t="str">
-        <v>Account Open Enhancements and Outcome Orchestration</v>
+        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
       </c>
       <c r="C3" t="str">
         <v>Invite to JRM</v>
@@ -467,15 +464,15 @@
         <v>estimates</v>
       </c>
       <c r="G3">
-        <v>45672</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ENT-16949</v>
+        <v>ENT-16881</v>
       </c>
       <c r="B4" t="str">
-        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
+        <v>Split up Personal Overdraft P&amp;L</v>
       </c>
       <c r="C4" t="str">
         <v>Invite to JRM</v>
@@ -484,18 +481,18 @@
         <v>FLCM</v>
       </c>
       <c r="E4" t="str">
-        <v>estimates</v>
+        <v>approved</v>
       </c>
       <c r="G4">
-        <v>45531</v>
+        <v>45929</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ENT-16881</v>
+        <v>ENT-16700</v>
       </c>
       <c r="B5" t="str">
-        <v>Split up Personal Overdraft P&amp;L</v>
+        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
       </c>
       <c r="C5" t="str">
         <v>Invite to JRM</v>
@@ -504,18 +501,18 @@
         <v>FLCM</v>
       </c>
       <c r="E5" t="str">
-        <v>approved</v>
+        <v>ofs</v>
       </c>
       <c r="G5">
-        <v>45929</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ENT-16700</v>
+        <v>ENT-16621</v>
       </c>
       <c r="B6" t="str">
-        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
+        <v>CIW Data Products to PROD</v>
       </c>
       <c r="C6" t="str">
         <v>Invite to JRM</v>
@@ -527,15 +524,15 @@
         <v>ofs</v>
       </c>
       <c r="G6">
-        <v>45523</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENT-16621</v>
+        <v>ENT-16374</v>
       </c>
       <c r="B7" t="str">
-        <v>CIW Data Products to PROD</v>
+        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
       </c>
       <c r="C7" t="str">
         <v>Invite to JRM</v>
@@ -544,18 +541,18 @@
         <v>FLCM</v>
       </c>
       <c r="E7" t="str">
-        <v>ofs</v>
+        <v>estimates</v>
       </c>
       <c r="G7">
-        <v>45596</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENT-16374</v>
+        <v>ENT-15917</v>
       </c>
       <c r="B8" t="str">
-        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
+        <v>REBO Bill Payment Investigation Requests</v>
       </c>
       <c r="C8" t="str">
         <v>Invite to JRM</v>
@@ -564,18 +561,18 @@
         <v>FLCM</v>
       </c>
       <c r="E8" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G8">
-        <v>45455</v>
+        <v>45613</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-15917</v>
+        <v>ENT-17286</v>
       </c>
       <c r="B9" t="str">
-        <v>REBO Bill Payment Investigation Requests</v>
+        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -584,18 +581,18 @@
         <v>FLCM</v>
       </c>
       <c r="E9" t="str">
-        <v>ofs</v>
+        <v>approved</v>
       </c>
       <c r="G9">
-        <v>45613</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-17286</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B10" t="str">
-        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -606,16 +603,19 @@
       <c r="E10" t="str">
         <v>approved</v>
       </c>
+      <c r="F10" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G10">
-        <v>45699</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B11" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -624,21 +624,18 @@
         <v>FLCM</v>
       </c>
       <c r="E11" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F11" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G11">
-        <v>45686</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B12" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -650,15 +647,15 @@
         <v>estimates</v>
       </c>
       <c r="G12">
-        <v>45700</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B13" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -670,15 +667,15 @@
         <v>estimates</v>
       </c>
       <c r="G13">
-        <v>45656</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B14" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -690,15 +687,15 @@
         <v>estimates</v>
       </c>
       <c r="G14">
-        <v>45588</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-17054</v>
       </c>
       <c r="B15" t="str">
-        <v>Data Source to EDGE</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -707,18 +704,21 @@
         <v>FLCM</v>
       </c>
       <c r="E15" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F15" t="str">
+        <v>PDF</v>
       </c>
       <c r="G15">
-        <v>45664</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-17054</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B16" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -729,19 +729,16 @@
       <c r="E16" t="str">
         <v>approved</v>
       </c>
-      <c r="F16" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G16">
-        <v>45691</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-14372</v>
       </c>
       <c r="B17" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -752,16 +749,19 @@
       <c r="E17" t="str">
         <v>approved</v>
       </c>
+      <c r="F17" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G17">
-        <v>45299</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ENT-14372</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B18" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
@@ -776,58 +776,58 @@
         <v>PDF</v>
       </c>
       <c r="G18">
-        <v>45512</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B19" t="str">
-        <v>RAMP Phase 2</v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D19" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E19" t="str">
         <v>approved</v>
       </c>
-      <c r="F19" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G19">
-        <v>45562</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B20" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D20" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E20" t="str">
         <v>approved</v>
       </c>
+      <c r="F20" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G20">
-        <v>45695</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B21" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
@@ -842,15 +842,15 @@
         <v>PDF</v>
       </c>
       <c r="G21">
-        <v>45688</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B22" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
@@ -865,15 +865,15 @@
         <v>PDF</v>
       </c>
       <c r="G22">
-        <v>45701</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B23" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
@@ -884,19 +884,16 @@
       <c r="E23" t="str">
         <v>approved</v>
       </c>
-      <c r="F23" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G23">
-        <v>45695</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B24" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
@@ -905,138 +902,138 @@
         <v>FLCM</v>
       </c>
       <c r="E24" t="str">
-        <v>approved</v>
+        <v>estimates</v>
       </c>
       <c r="G24">
-        <v>45706</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B25" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D25" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E25" t="str">
         <v>estimates</v>
       </c>
       <c r="G25">
-        <v>45559</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B26" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D26" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E26" t="str">
         <v>estimates</v>
       </c>
       <c r="G26">
-        <v>45623</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B27" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D27" t="str">
-        <v>FLCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E27" t="str">
         <v>estimates</v>
       </c>
       <c r="G27">
-        <v>45355</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B28" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D28" t="str">
-        <v>CorpSec</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E28" t="str">
         <v>estimates</v>
       </c>
       <c r="G28">
-        <v>45446</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B29" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>BSCM/ESCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E29" t="str">
         <v>estimates</v>
       </c>
       <c r="G29">
-        <v>45477</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B30" t="str">
-        <v>CSDM Upgrade</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D30" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E30" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G30">
-        <v>45394</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B31" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
@@ -1048,15 +1045,15 @@
         <v>ofs</v>
       </c>
       <c r="G31">
-        <v>45531</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B32" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
@@ -1068,15 +1065,15 @@
         <v>ofs</v>
       </c>
       <c r="G32">
-        <v>45453</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B33" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
@@ -1085,98 +1082,95 @@
         <v>FLCM</v>
       </c>
       <c r="E33" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G33">
-        <v>45461</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B34" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D34" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E34" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G34">
-        <v>45714</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-15822</v>
       </c>
       <c r="B35" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D35" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E35" t="str">
         <v>estimates</v>
       </c>
       <c r="G35">
-        <v>45686</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-15822</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B36" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D36" t="str">
-        <v>FLCM</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E36" t="str">
         <v>estimates</v>
       </c>
       <c r="G36">
-        <v>45650</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-17853</v>
       </c>
       <c r="B37" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
       </c>
-      <c r="D37" t="str">
-        <v>BSCM/ESCM</v>
-      </c>
       <c r="E37" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G37">
-        <v>45541</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ENT-17853</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B38" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
@@ -1185,15 +1179,15 @@
         <v>ofs</v>
       </c>
       <c r="G38">
-        <v>45691</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B39" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
@@ -1202,15 +1196,15 @@
         <v>ofs</v>
       </c>
       <c r="G39">
-        <v>45559</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B40" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
@@ -1219,15 +1213,15 @@
         <v>ofs</v>
       </c>
       <c r="G40">
-        <v>45596</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B41" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1236,15 +1230,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45378</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B42" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1253,15 +1247,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45468</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B43" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1270,15 +1264,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45310</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B44" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1287,15 +1281,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45427</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B45" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1304,15 +1298,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45279</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B46" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1321,15 +1315,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45558</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B47" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1338,15 +1332,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45383</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B48" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1355,15 +1349,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45638</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B49" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1372,15 +1366,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45461</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B50" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1394,10 +1388,10 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B51" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1406,15 +1400,15 @@
         <v>ofs</v>
       </c>
       <c r="G51">
-        <v>45371</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B52" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1423,15 +1417,15 @@
         <v>ofs</v>
       </c>
       <c r="G52">
-        <v>45406</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B53" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1440,15 +1434,15 @@
         <v>ofs</v>
       </c>
       <c r="G53">
-        <v>45364</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B54" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1457,15 +1451,15 @@
         <v>ofs</v>
       </c>
       <c r="G54">
-        <v>45593</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B55" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1474,15 +1468,15 @@
         <v>ofs</v>
       </c>
       <c r="G55">
-        <v>45408</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B56" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1491,15 +1485,15 @@
         <v>ofs</v>
       </c>
       <c r="G56">
-        <v>45595</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B57" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
@@ -1508,15 +1502,15 @@
         <v>ofs</v>
       </c>
       <c r="G57">
-        <v>45392</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B58" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C58" t="str">
         <v>Invite to JRM</v>
@@ -1530,27 +1524,27 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B59" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C59" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E59" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G59">
-        <v>45411</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-18725</v>
       </c>
       <c r="B60" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>US Video System - Lenel to Genetec</v>
       </c>
       <c r="C60" t="str">
         <v>Invite to JRM</v>
@@ -1562,26 +1556,9 @@
         <v>45721</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="str">
-        <v>ENT-18725</v>
-      </c>
-      <c r="B61" t="str">
-        <v>US Video System - Lenel to Genetec</v>
-      </c>
-      <c r="C61" t="str">
-        <v>Invite to JRM</v>
-      </c>
-      <c r="E61" t="str">
-        <v>jrm</v>
-      </c>
-      <c r="G61">
-        <v>45721</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G60"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -1082,7 +1082,7 @@
         <v>FLCM</v>
       </c>
       <c r="E33" t="str">
-        <v>jrm</v>
+        <v>ofs</v>
       </c>
       <c r="G33">
         <v>45714</v>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G59"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -429,10 +429,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ENT-17062</v>
+        <v>ENT-16949</v>
       </c>
       <c r="B2" t="str">
-        <v>Account Open Enhancements and Outcome Orchestration</v>
+        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
       </c>
       <c r="C2" t="str">
         <v>Invite to JRM</v>
@@ -444,15 +444,15 @@
         <v>estimates</v>
       </c>
       <c r="G2">
-        <v>45672</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ENT-16949</v>
+        <v>ENT-16881</v>
       </c>
       <c r="B3" t="str">
-        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
+        <v>Split up Personal Overdraft P&amp;L</v>
       </c>
       <c r="C3" t="str">
         <v>Invite to JRM</v>
@@ -461,18 +461,18 @@
         <v>FLCM</v>
       </c>
       <c r="E3" t="str">
-        <v>estimates</v>
+        <v>approved</v>
       </c>
       <c r="G3">
-        <v>45531</v>
+        <v>45929</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ENT-16881</v>
+        <v>ENT-16700</v>
       </c>
       <c r="B4" t="str">
-        <v>Split up Personal Overdraft P&amp;L</v>
+        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
       </c>
       <c r="C4" t="str">
         <v>Invite to JRM</v>
@@ -481,18 +481,18 @@
         <v>FLCM</v>
       </c>
       <c r="E4" t="str">
-        <v>approved</v>
+        <v>ofs</v>
       </c>
       <c r="G4">
-        <v>45929</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ENT-16700</v>
+        <v>ENT-16621</v>
       </c>
       <c r="B5" t="str">
-        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
+        <v>CIW Data Products to PROD</v>
       </c>
       <c r="C5" t="str">
         <v>Invite to JRM</v>
@@ -504,15 +504,15 @@
         <v>ofs</v>
       </c>
       <c r="G5">
-        <v>45523</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ENT-16621</v>
+        <v>ENT-16374</v>
       </c>
       <c r="B6" t="str">
-        <v>CIW Data Products to PROD</v>
+        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
       </c>
       <c r="C6" t="str">
         <v>Invite to JRM</v>
@@ -521,18 +521,18 @@
         <v>FLCM</v>
       </c>
       <c r="E6" t="str">
-        <v>ofs</v>
+        <v>estimates</v>
       </c>
       <c r="G6">
-        <v>45596</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENT-16374</v>
+        <v>ENT-15917</v>
       </c>
       <c r="B7" t="str">
-        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
+        <v>REBO Bill Payment Investigation Requests</v>
       </c>
       <c r="C7" t="str">
         <v>Invite to JRM</v>
@@ -541,18 +541,18 @@
         <v>FLCM</v>
       </c>
       <c r="E7" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G7">
-        <v>45455</v>
+        <v>45613</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENT-15917</v>
+        <v>ENT-17286</v>
       </c>
       <c r="B8" t="str">
-        <v>REBO Bill Payment Investigation Requests</v>
+        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
       </c>
       <c r="C8" t="str">
         <v>Invite to JRM</v>
@@ -561,18 +561,18 @@
         <v>FLCM</v>
       </c>
       <c r="E8" t="str">
-        <v>ofs</v>
+        <v>approved</v>
       </c>
       <c r="G8">
-        <v>45613</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-17286</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B9" t="str">
-        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -583,16 +583,19 @@
       <c r="E9" t="str">
         <v>approved</v>
       </c>
+      <c r="F9" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G9">
-        <v>45699</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B10" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -601,21 +604,18 @@
         <v>FLCM</v>
       </c>
       <c r="E10" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F10" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G10">
-        <v>45686</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B11" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -627,15 +627,15 @@
         <v>estimates</v>
       </c>
       <c r="G11">
-        <v>45700</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B12" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -647,15 +647,15 @@
         <v>estimates</v>
       </c>
       <c r="G12">
-        <v>45656</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B13" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -667,15 +667,15 @@
         <v>estimates</v>
       </c>
       <c r="G13">
-        <v>45588</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-17054</v>
       </c>
       <c r="B14" t="str">
-        <v>Data Source to EDGE</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -684,18 +684,21 @@
         <v>FLCM</v>
       </c>
       <c r="E14" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F14" t="str">
+        <v>PDF</v>
       </c>
       <c r="G14">
-        <v>45664</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-17054</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B15" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -706,19 +709,16 @@
       <c r="E15" t="str">
         <v>approved</v>
       </c>
-      <c r="F15" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G15">
-        <v>45691</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-14372</v>
       </c>
       <c r="B16" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -729,16 +729,19 @@
       <c r="E16" t="str">
         <v>approved</v>
       </c>
+      <c r="F16" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G16">
-        <v>45299</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ENT-14372</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B17" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -753,58 +756,58 @@
         <v>PDF</v>
       </c>
       <c r="G17">
-        <v>45512</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B18" t="str">
-        <v>RAMP Phase 2</v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D18" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E18" t="str">
         <v>approved</v>
       </c>
-      <c r="F18" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G18">
-        <v>45562</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B19" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D19" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E19" t="str">
         <v>approved</v>
       </c>
+      <c r="F19" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G19">
-        <v>45695</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B20" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
@@ -819,15 +822,15 @@
         <v>PDF</v>
       </c>
       <c r="G20">
-        <v>45688</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B21" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
@@ -842,15 +845,15 @@
         <v>PDF</v>
       </c>
       <c r="G21">
-        <v>45701</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B22" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
@@ -861,19 +864,16 @@
       <c r="E22" t="str">
         <v>approved</v>
       </c>
-      <c r="F22" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G22">
-        <v>45695</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B23" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
@@ -882,138 +882,138 @@
         <v>FLCM</v>
       </c>
       <c r="E23" t="str">
-        <v>approved</v>
+        <v>estimates</v>
       </c>
       <c r="G23">
-        <v>45706</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B24" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D24" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E24" t="str">
         <v>estimates</v>
       </c>
       <c r="G24">
-        <v>45559</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B25" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D25" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E25" t="str">
         <v>estimates</v>
       </c>
       <c r="G25">
-        <v>45623</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B26" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D26" t="str">
-        <v>FLCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E26" t="str">
         <v>estimates</v>
       </c>
       <c r="G26">
-        <v>45355</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B27" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D27" t="str">
-        <v>CorpSec</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E27" t="str">
         <v>estimates</v>
       </c>
       <c r="G27">
-        <v>45446</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B28" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D28" t="str">
-        <v>BSCM/ESCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E28" t="str">
         <v>estimates</v>
       </c>
       <c r="G28">
-        <v>45477</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B29" t="str">
-        <v>CSDM Upgrade</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E29" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G29">
-        <v>45394</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B30" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
@@ -1025,15 +1025,15 @@
         <v>ofs</v>
       </c>
       <c r="G30">
-        <v>45531</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B31" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
@@ -1045,15 +1045,15 @@
         <v>ofs</v>
       </c>
       <c r="G31">
-        <v>45453</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B32" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
@@ -1065,95 +1065,92 @@
         <v>ofs</v>
       </c>
       <c r="G32">
-        <v>45461</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B33" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D33" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E33" t="str">
-        <v>ofs</v>
+        <v>estimates</v>
       </c>
       <c r="G33">
-        <v>45714</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-15822</v>
       </c>
       <c r="B34" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D34" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E34" t="str">
         <v>estimates</v>
       </c>
       <c r="G34">
-        <v>45686</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-15822</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B35" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D35" t="str">
-        <v>FLCM</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E35" t="str">
         <v>estimates</v>
       </c>
       <c r="G35">
-        <v>45650</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-17853</v>
       </c>
       <c r="B36" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
       </c>
-      <c r="D36" t="str">
-        <v>BSCM/ESCM</v>
-      </c>
       <c r="E36" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G36">
-        <v>45541</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ENT-17853</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B37" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
@@ -1162,15 +1159,15 @@
         <v>ofs</v>
       </c>
       <c r="G37">
-        <v>45691</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B38" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
@@ -1179,15 +1176,15 @@
         <v>ofs</v>
       </c>
       <c r="G38">
-        <v>45559</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B39" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
@@ -1196,15 +1193,15 @@
         <v>ofs</v>
       </c>
       <c r="G39">
-        <v>45596</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B40" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
@@ -1213,15 +1210,15 @@
         <v>ofs</v>
       </c>
       <c r="G40">
-        <v>45378</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B41" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1230,15 +1227,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45468</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B42" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1247,15 +1244,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45310</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B43" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1264,15 +1261,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45427</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B44" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1281,15 +1278,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45279</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B45" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1298,15 +1295,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45558</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B46" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1315,15 +1312,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45383</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B47" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1332,15 +1329,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45638</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B48" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1349,15 +1346,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45461</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B49" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1371,10 +1368,10 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B50" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1383,15 +1380,15 @@
         <v>ofs</v>
       </c>
       <c r="G50">
-        <v>45371</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B51" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1400,15 +1397,15 @@
         <v>ofs</v>
       </c>
       <c r="G51">
-        <v>45406</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B52" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1417,15 +1414,15 @@
         <v>ofs</v>
       </c>
       <c r="G52">
-        <v>45364</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B53" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1434,15 +1431,15 @@
         <v>ofs</v>
       </c>
       <c r="G53">
-        <v>45593</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B54" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1451,15 +1448,15 @@
         <v>ofs</v>
       </c>
       <c r="G54">
-        <v>45408</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B55" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1468,15 +1465,15 @@
         <v>ofs</v>
       </c>
       <c r="G55">
-        <v>45595</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B56" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1485,15 +1482,15 @@
         <v>ofs</v>
       </c>
       <c r="G56">
-        <v>45392</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B57" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
@@ -1507,27 +1504,27 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B58" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C58" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E58" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G58">
-        <v>45411</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-18725</v>
       </c>
       <c r="B59" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>US Video System - Lenel to Genetec</v>
       </c>
       <c r="C59" t="str">
         <v>Invite to JRM</v>
@@ -1539,26 +1536,9 @@
         <v>45721</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="str">
-        <v>ENT-18725</v>
-      </c>
-      <c r="B60" t="str">
-        <v>US Video System - Lenel to Genetec</v>
-      </c>
-      <c r="C60" t="str">
-        <v>Invite to JRM</v>
-      </c>
-      <c r="E60" t="str">
-        <v>jrm</v>
-      </c>
-      <c r="G60">
-        <v>45721</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G60"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G59"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -1513,7 +1513,7 @@
         <v>Invite to JRM</v>
       </c>
       <c r="E58" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G58">
         <v>45721</v>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -1635,10 +1635,10 @@
         <v>178399.00</v>
       </c>
       <c r="C2" t="str">
-        <v>abdc</v>
+        <v>123123</v>
       </c>
       <c r="D2" t="str">
-        <v>-</v>
+        <v>123123</v>
       </c>
       <c r="E2" t="str">
         <v>118933.00</v>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -902,7 +902,7 @@
         <v>MinIO/DreamIO</v>
       </c>
       <c r="E24" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G24">
         <v>45623</v>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G58"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -429,10 +429,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ENT-16949</v>
+        <v>ENT-16881</v>
       </c>
       <c r="B2" t="str">
-        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
+        <v>Split up Personal Overdraft P&amp;L</v>
       </c>
       <c r="C2" t="str">
         <v>Invite to JRM</v>
@@ -441,18 +441,18 @@
         <v>FLCM</v>
       </c>
       <c r="E2" t="str">
-        <v>estimates</v>
+        <v>approved</v>
       </c>
       <c r="G2">
-        <v>45531</v>
+        <v>45929</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ENT-16881</v>
+        <v>ENT-16700</v>
       </c>
       <c r="B3" t="str">
-        <v>Split up Personal Overdraft P&amp;L</v>
+        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
       </c>
       <c r="C3" t="str">
         <v>Invite to JRM</v>
@@ -461,18 +461,18 @@
         <v>FLCM</v>
       </c>
       <c r="E3" t="str">
-        <v>approved</v>
+        <v>ofs</v>
       </c>
       <c r="G3">
-        <v>45929</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ENT-16700</v>
+        <v>ENT-16621</v>
       </c>
       <c r="B4" t="str">
-        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
+        <v>CIW Data Products to PROD</v>
       </c>
       <c r="C4" t="str">
         <v>Invite to JRM</v>
@@ -484,15 +484,15 @@
         <v>ofs</v>
       </c>
       <c r="G4">
-        <v>45523</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ENT-16621</v>
+        <v>ENT-16374</v>
       </c>
       <c r="B5" t="str">
-        <v>CIW Data Products to PROD</v>
+        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
       </c>
       <c r="C5" t="str">
         <v>Invite to JRM</v>
@@ -501,18 +501,18 @@
         <v>FLCM</v>
       </c>
       <c r="E5" t="str">
-        <v>ofs</v>
+        <v>estimates</v>
       </c>
       <c r="G5">
-        <v>45596</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ENT-16374</v>
+        <v>ENT-15917</v>
       </c>
       <c r="B6" t="str">
-        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
+        <v>REBO Bill Payment Investigation Requests</v>
       </c>
       <c r="C6" t="str">
         <v>Invite to JRM</v>
@@ -521,18 +521,18 @@
         <v>FLCM</v>
       </c>
       <c r="E6" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G6">
-        <v>45455</v>
+        <v>45613</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENT-15917</v>
+        <v>ENT-17286</v>
       </c>
       <c r="B7" t="str">
-        <v>REBO Bill Payment Investigation Requests</v>
+        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
       </c>
       <c r="C7" t="str">
         <v>Invite to JRM</v>
@@ -541,18 +541,18 @@
         <v>FLCM</v>
       </c>
       <c r="E7" t="str">
-        <v>ofs</v>
+        <v>approved</v>
       </c>
       <c r="G7">
-        <v>45613</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENT-17286</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B8" t="str">
-        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C8" t="str">
         <v>Invite to JRM</v>
@@ -563,16 +563,19 @@
       <c r="E8" t="str">
         <v>approved</v>
       </c>
+      <c r="F8" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G8">
-        <v>45699</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B9" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -581,21 +584,18 @@
         <v>FLCM</v>
       </c>
       <c r="E9" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F9" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G9">
-        <v>45686</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B10" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -607,15 +607,15 @@
         <v>estimates</v>
       </c>
       <c r="G10">
-        <v>45700</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B11" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -627,15 +627,15 @@
         <v>estimates</v>
       </c>
       <c r="G11">
-        <v>45656</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B12" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -647,15 +647,15 @@
         <v>estimates</v>
       </c>
       <c r="G12">
-        <v>45588</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-17054</v>
       </c>
       <c r="B13" t="str">
-        <v>Data Source to EDGE</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -664,18 +664,21 @@
         <v>FLCM</v>
       </c>
       <c r="E13" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F13" t="str">
+        <v>PDF</v>
       </c>
       <c r="G13">
-        <v>45664</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-17054</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B14" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -686,19 +689,16 @@
       <c r="E14" t="str">
         <v>approved</v>
       </c>
-      <c r="F14" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G14">
-        <v>45691</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-14372</v>
       </c>
       <c r="B15" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -709,16 +709,19 @@
       <c r="E15" t="str">
         <v>approved</v>
       </c>
+      <c r="F15" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G15">
-        <v>45299</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-14372</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B16" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -733,58 +736,58 @@
         <v>PDF</v>
       </c>
       <c r="G16">
-        <v>45512</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B17" t="str">
-        <v>RAMP Phase 2</v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D17" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E17" t="str">
         <v>approved</v>
       </c>
-      <c r="F17" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G17">
-        <v>45562</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B18" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D18" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E18" t="str">
         <v>approved</v>
       </c>
+      <c r="F18" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G18">
-        <v>45695</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B19" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
@@ -799,15 +802,15 @@
         <v>PDF</v>
       </c>
       <c r="G19">
-        <v>45688</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B20" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
@@ -822,15 +825,15 @@
         <v>PDF</v>
       </c>
       <c r="G20">
-        <v>45701</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B21" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
@@ -841,19 +844,16 @@
       <c r="E21" t="str">
         <v>approved</v>
       </c>
-      <c r="F21" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G21">
-        <v>45695</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B22" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
@@ -862,138 +862,138 @@
         <v>FLCM</v>
       </c>
       <c r="E22" t="str">
-        <v>approved</v>
+        <v>estimates</v>
       </c>
       <c r="G22">
-        <v>45706</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B23" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D23" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E23" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G23">
-        <v>45559</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B24" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D24" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E24" t="str">
-        <v>ofs</v>
+        <v>estimates</v>
       </c>
       <c r="G24">
-        <v>45623</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B25" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D25" t="str">
-        <v>FLCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E25" t="str">
         <v>estimates</v>
       </c>
       <c r="G25">
-        <v>45355</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B26" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D26" t="str">
-        <v>CorpSec</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E26" t="str">
         <v>estimates</v>
       </c>
       <c r="G26">
-        <v>45446</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B27" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D27" t="str">
-        <v>BSCM/ESCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E27" t="str">
         <v>estimates</v>
       </c>
       <c r="G27">
-        <v>45477</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B28" t="str">
-        <v>CSDM Upgrade</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D28" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E28" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G28">
-        <v>45394</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B29" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
@@ -1005,15 +1005,15 @@
         <v>ofs</v>
       </c>
       <c r="G29">
-        <v>45531</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B30" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
@@ -1025,15 +1025,15 @@
         <v>ofs</v>
       </c>
       <c r="G30">
-        <v>45453</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B31" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
@@ -1045,95 +1045,92 @@
         <v>ofs</v>
       </c>
       <c r="G31">
-        <v>45461</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B32" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D32" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E32" t="str">
-        <v>ofs</v>
+        <v>estimates</v>
       </c>
       <c r="G32">
-        <v>45714</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-15822</v>
       </c>
       <c r="B33" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D33" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E33" t="str">
         <v>estimates</v>
       </c>
       <c r="G33">
-        <v>45686</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-15822</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B34" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D34" t="str">
-        <v>FLCM</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E34" t="str">
         <v>estimates</v>
       </c>
       <c r="G34">
-        <v>45650</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-17853</v>
       </c>
       <c r="B35" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
       </c>
-      <c r="D35" t="str">
-        <v>BSCM/ESCM</v>
-      </c>
       <c r="E35" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G35">
-        <v>45541</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-17853</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B36" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
@@ -1142,15 +1139,15 @@
         <v>ofs</v>
       </c>
       <c r="G36">
-        <v>45691</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B37" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
@@ -1159,15 +1156,15 @@
         <v>ofs</v>
       </c>
       <c r="G37">
-        <v>45559</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B38" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
@@ -1176,15 +1173,15 @@
         <v>ofs</v>
       </c>
       <c r="G38">
-        <v>45596</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B39" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
@@ -1193,15 +1190,15 @@
         <v>ofs</v>
       </c>
       <c r="G39">
-        <v>45378</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B40" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
@@ -1210,15 +1207,15 @@
         <v>ofs</v>
       </c>
       <c r="G40">
-        <v>45468</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B41" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1227,15 +1224,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45310</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B42" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1244,15 +1241,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45427</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B43" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1261,15 +1258,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45279</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B44" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1278,15 +1275,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45558</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B45" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1295,15 +1292,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45383</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B46" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1312,15 +1309,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45638</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B47" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1329,15 +1326,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45461</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B48" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1351,10 +1348,10 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B49" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1363,15 +1360,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45371</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B50" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1380,15 +1377,15 @@
         <v>ofs</v>
       </c>
       <c r="G50">
-        <v>45406</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B51" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1397,15 +1394,15 @@
         <v>ofs</v>
       </c>
       <c r="G51">
-        <v>45364</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B52" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1414,15 +1411,15 @@
         <v>ofs</v>
       </c>
       <c r="G52">
-        <v>45593</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B53" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1431,15 +1428,15 @@
         <v>ofs</v>
       </c>
       <c r="G53">
-        <v>45408</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B54" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1448,15 +1445,15 @@
         <v>ofs</v>
       </c>
       <c r="G54">
-        <v>45595</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B55" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1465,15 +1462,15 @@
         <v>ofs</v>
       </c>
       <c r="G55">
-        <v>45392</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B56" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1487,58 +1484,41 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B57" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E57" t="str">
-        <v>ofs</v>
+        <v>estimates</v>
       </c>
       <c r="G57">
-        <v>45411</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-18725</v>
       </c>
       <c r="B58" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>US Video System - Lenel to Genetec</v>
       </c>
       <c r="C58" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E58" t="str">
-        <v>estimates</v>
+        <v>jrm</v>
       </c>
       <c r="G58">
         <v>45721</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="str">
-        <v>ENT-18725</v>
-      </c>
-      <c r="B59" t="str">
-        <v>US Video System - Lenel to Genetec</v>
-      </c>
-      <c r="C59" t="str">
-        <v>Invite to JRM</v>
-      </c>
-      <c r="E59" t="str">
-        <v>jrm</v>
-      </c>
-      <c r="G59">
-        <v>45721</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G59"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G58"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -461,7 +461,7 @@
         <v>FLCM</v>
       </c>
       <c r="E3" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G3">
         <v>45929</v>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -481,7 +481,7 @@
         <v>FLCM</v>
       </c>
       <c r="E4" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G4">
         <v>45523</v>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G62"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -429,30 +429,33 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ENT-16949</v>
+        <v>12344</v>
       </c>
       <c r="B2" t="str">
-        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
+        <v>324</v>
       </c>
       <c r="C2" t="str">
-        <v>Invite to JRM</v>
+        <v>234234</v>
       </c>
       <c r="D2" t="str">
-        <v>FLCM</v>
+        <v>234234</v>
       </c>
       <c r="E2" t="str">
-        <v>estimates</v>
-      </c>
-      <c r="G2">
-        <v>45531</v>
+        <v>jrm</v>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v>2025-03-10</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ENT-16881</v>
+        <v>ENT-16949</v>
       </c>
       <c r="B3" t="str">
-        <v>Split up Personal Overdraft P&amp;L</v>
+        <v>Fusion: CSP Cards Status Frequency Update-RBSSINTK-9334</v>
       </c>
       <c r="C3" t="str">
         <v>Invite to JRM</v>
@@ -461,18 +464,18 @@
         <v>FLCM</v>
       </c>
       <c r="E3" t="str">
-        <v>approved</v>
+        <v>estimates</v>
       </c>
       <c r="G3">
-        <v>45929</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ENT-16700</v>
+        <v>ENT-16881</v>
       </c>
       <c r="B4" t="str">
-        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
+        <v>Split up Personal Overdraft P&amp;L</v>
       </c>
       <c r="C4" t="str">
         <v>Invite to JRM</v>
@@ -484,15 +487,15 @@
         <v>approved</v>
       </c>
       <c r="G4">
-        <v>45523</v>
+        <v>45929</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ENT-16621</v>
+        <v>ENT-16700</v>
       </c>
       <c r="B5" t="str">
-        <v>CIW Data Products to PROD</v>
+        <v>Simplii Debit Mastercard (Debit Card) MCC Block Removal</v>
       </c>
       <c r="C5" t="str">
         <v>Invite to JRM</v>
@@ -504,15 +507,15 @@
         <v>approved</v>
       </c>
       <c r="G5">
-        <v>45596</v>
+        <v>45523</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ENT-16374</v>
+        <v>ENT-16621</v>
       </c>
       <c r="B6" t="str">
-        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
+        <v>CIW Data Products to PROD</v>
       </c>
       <c r="C6" t="str">
         <v>Invite to JRM</v>
@@ -521,18 +524,18 @@
         <v>FLCM</v>
       </c>
       <c r="E6" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G6">
-        <v>45455</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENT-16031</v>
+        <v>ENT-16374</v>
       </c>
       <c r="B7" t="str">
-        <v>Fraud - Notes generator</v>
+        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
       </c>
       <c r="C7" t="str">
         <v>Invite to JRM</v>
@@ -544,15 +547,15 @@
         <v>jrm</v>
       </c>
       <c r="G7">
-        <v>45649</v>
+        <v>45455</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENT-15917</v>
+        <v>ENT-16031</v>
       </c>
       <c r="B8" t="str">
-        <v>REBO Bill Payment Investigation Requests</v>
+        <v>Fraud - Notes generator</v>
       </c>
       <c r="C8" t="str">
         <v>Invite to JRM</v>
@@ -564,15 +567,15 @@
         <v>jrm</v>
       </c>
       <c r="G8">
-        <v>45613</v>
+        <v>45649</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-17286</v>
+        <v>ENT-15917</v>
       </c>
       <c r="B9" t="str">
-        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
+        <v>REBO Bill Payment Investigation Requests</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -581,18 +584,18 @@
         <v>FLCM</v>
       </c>
       <c r="E9" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G9">
-        <v>45699</v>
+        <v>45613</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-17202</v>
+        <v>ENT-17286</v>
       </c>
       <c r="B10" t="str">
-        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
+        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -601,18 +604,18 @@
         <v>FLCM</v>
       </c>
       <c r="E10" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G10">
-        <v>45690</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17202</v>
       </c>
       <c r="B11" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -621,21 +624,18 @@
         <v>FLCM</v>
       </c>
       <c r="E11" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F11" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G11">
-        <v>45686</v>
+        <v>45690</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B12" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -644,18 +644,21 @@
         <v>FLCM</v>
       </c>
       <c r="E12" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F12" t="str">
+        <v>PDF</v>
       </c>
       <c r="G12">
-        <v>45700</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B13" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -667,15 +670,15 @@
         <v>estimates</v>
       </c>
       <c r="G13">
-        <v>45656</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B14" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -687,15 +690,15 @@
         <v>estimates</v>
       </c>
       <c r="G14">
-        <v>45588</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B15" t="str">
-        <v>Data Source to EDGE</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -707,15 +710,15 @@
         <v>estimates</v>
       </c>
       <c r="G15">
-        <v>45664</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-17054</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B16" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -724,21 +727,18 @@
         <v>FLCM</v>
       </c>
       <c r="E16" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F16" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G16">
-        <v>45691</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-17054</v>
       </c>
       <c r="B17" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -749,16 +749,19 @@
       <c r="E17" t="str">
         <v>approved</v>
       </c>
+      <c r="F17" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G17">
-        <v>45299</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ENT-14372</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B18" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
@@ -769,19 +772,16 @@
       <c r="E18" t="str">
         <v>approved</v>
       </c>
-      <c r="F18" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G18">
-        <v>45512</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-14372</v>
       </c>
       <c r="B19" t="str">
-        <v>RAMP Phase 2</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
@@ -796,58 +796,58 @@
         <v>PDF</v>
       </c>
       <c r="G19">
-        <v>45562</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B20" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D20" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E20" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F20" t="str">
+        <v>PDF</v>
       </c>
       <c r="G20">
-        <v>45695</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B21" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D21" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E21" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F21" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G21">
-        <v>45688</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B22" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
@@ -862,15 +862,15 @@
         <v>PDF</v>
       </c>
       <c r="G22">
-        <v>45701</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B23" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
@@ -885,15 +885,15 @@
         <v>PDF</v>
       </c>
       <c r="G23">
-        <v>45695</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B24" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
@@ -904,16 +904,19 @@
       <c r="E24" t="str">
         <v>approved</v>
       </c>
+      <c r="F24" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G24">
-        <v>45706</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B25" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
@@ -922,138 +925,138 @@
         <v>FLCM</v>
       </c>
       <c r="E25" t="str">
-        <v>estimates</v>
+        <v>approved</v>
       </c>
       <c r="G25">
-        <v>45559</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B26" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D26" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E26" t="str">
         <v>estimates</v>
       </c>
       <c r="G26">
-        <v>45623</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B27" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D27" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E27" t="str">
         <v>estimates</v>
       </c>
       <c r="G27">
-        <v>45355</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B28" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D28" t="str">
-        <v>CorpSec</v>
+        <v>FLCM</v>
       </c>
       <c r="E28" t="str">
         <v>estimates</v>
       </c>
       <c r="G28">
-        <v>45446</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B29" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>BSCM/ESCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E29" t="str">
         <v>estimates</v>
       </c>
       <c r="G29">
-        <v>45477</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B30" t="str">
-        <v>CSDM Upgrade</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D30" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E30" t="str">
         <v>estimates</v>
       </c>
       <c r="G30">
-        <v>45394</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B31" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D31" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E31" t="str">
-        <v>ofs</v>
+        <v>estimates</v>
       </c>
       <c r="G31">
-        <v>45531</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B32" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
@@ -1065,15 +1068,15 @@
         <v>ofs</v>
       </c>
       <c r="G32">
-        <v>45453</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B33" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
@@ -1085,15 +1088,15 @@
         <v>ofs</v>
       </c>
       <c r="G33">
-        <v>45461</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B34" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
@@ -1102,95 +1105,98 @@
         <v>FLCM</v>
       </c>
       <c r="E34" t="str">
-        <v>jrm</v>
+        <v>ofs</v>
       </c>
       <c r="G34">
-        <v>45714</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B35" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D35" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E35" t="str">
-        <v>estimates</v>
+        <v>jrm</v>
       </c>
       <c r="G35">
-        <v>45686</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-15822</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B36" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D36" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E36" t="str">
         <v>estimates</v>
       </c>
       <c r="G36">
-        <v>45650</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-15822</v>
       </c>
       <c r="B37" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D37" t="str">
-        <v>BSCM/ESCM</v>
+        <v>FLCM</v>
       </c>
       <c r="E37" t="str">
         <v>estimates</v>
       </c>
       <c r="G37">
-        <v>45541</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ENT-17853</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B38" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
       </c>
+      <c r="D38" t="str">
+        <v>BSCM/ESCM</v>
+      </c>
       <c r="E38" t="str">
-        <v>ofs</v>
+        <v>estimates</v>
       </c>
       <c r="G38">
-        <v>45691</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-17853</v>
       </c>
       <c r="B39" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
@@ -1199,15 +1205,15 @@
         <v>ofs</v>
       </c>
       <c r="G39">
-        <v>45559</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B40" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
@@ -1216,15 +1222,15 @@
         <v>ofs</v>
       </c>
       <c r="G40">
-        <v>45596</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B41" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1233,15 +1239,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45378</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B42" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1250,15 +1256,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45468</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B43" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1267,15 +1273,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45310</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B44" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1284,15 +1290,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45427</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B45" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1301,15 +1307,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45279</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B46" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1318,15 +1324,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45558</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B47" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1335,15 +1341,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45383</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B48" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1352,15 +1358,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45638</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B49" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1369,15 +1375,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45461</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B50" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1386,15 +1392,15 @@
         <v>ofs</v>
       </c>
       <c r="G50">
-        <v>45371</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B51" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1408,10 +1414,10 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B52" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1420,15 +1426,15 @@
         <v>ofs</v>
       </c>
       <c r="G52">
-        <v>45406</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B53" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1437,15 +1443,15 @@
         <v>ofs</v>
       </c>
       <c r="G53">
-        <v>45364</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B54" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1454,15 +1460,15 @@
         <v>ofs</v>
       </c>
       <c r="G54">
-        <v>45593</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B55" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1471,15 +1477,15 @@
         <v>ofs</v>
       </c>
       <c r="G55">
-        <v>45408</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B56" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1488,15 +1494,15 @@
         <v>ofs</v>
       </c>
       <c r="G56">
-        <v>45595</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B57" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
@@ -1505,15 +1511,15 @@
         <v>ofs</v>
       </c>
       <c r="G57">
-        <v>45392</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B58" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C58" t="str">
         <v>Invite to JRM</v>
@@ -1522,15 +1528,15 @@
         <v>ofs</v>
       </c>
       <c r="G58">
-        <v>45411</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B59" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C59" t="str">
         <v>Invite to JRM</v>
@@ -1544,27 +1550,27 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B60" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C60" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E60" t="str">
-        <v>jrm</v>
+        <v>ofs</v>
       </c>
       <c r="G60">
-        <v>45721</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ENT-18725</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B61" t="str">
-        <v>US Video System - Lenel to Genetec</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C61" t="str">
         <v>Invite to JRM</v>
@@ -1576,9 +1582,26 @@
         <v>45721</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>ENT-18725</v>
+      </c>
+      <c r="B62" t="str">
+        <v>US Video System - Lenel to Genetec</v>
+      </c>
+      <c r="C62" t="str">
+        <v>Invite to JRM</v>
+      </c>
+      <c r="E62" t="str">
+        <v>jrm</v>
+      </c>
+      <c r="G62">
+        <v>45721</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G62"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -441,7 +441,7 @@
         <v>234234</v>
       </c>
       <c r="E2" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="F2" t="str">
         <v/>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G61"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -532,10 +532,10 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>ENT-16374</v>
+        <v>ENT-16031</v>
       </c>
       <c r="B7" t="str">
-        <v>eBIT Migration Account Open Initiative: Citadel Estimates</v>
+        <v>Fraud - Notes generator</v>
       </c>
       <c r="C7" t="str">
         <v>Invite to JRM</v>
@@ -547,15 +547,15 @@
         <v>jrm</v>
       </c>
       <c r="G7">
-        <v>45455</v>
+        <v>45649</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ENT-16031</v>
+        <v>ENT-15917</v>
       </c>
       <c r="B8" t="str">
-        <v>Fraud - Notes generator</v>
+        <v>REBO Bill Payment Investigation Requests</v>
       </c>
       <c r="C8" t="str">
         <v>Invite to JRM</v>
@@ -567,15 +567,15 @@
         <v>jrm</v>
       </c>
       <c r="G8">
-        <v>45649</v>
+        <v>45613</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-15917</v>
+        <v>ENT-17286</v>
       </c>
       <c r="B9" t="str">
-        <v>REBO Bill Payment Investigation Requests</v>
+        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
       </c>
       <c r="C9" t="str">
         <v>Invite to JRM</v>
@@ -584,18 +584,18 @@
         <v>FLCM</v>
       </c>
       <c r="E9" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G9">
-        <v>45613</v>
+        <v>45699</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ENT-17286</v>
+        <v>ENT-17202</v>
       </c>
       <c r="B10" t="str">
-        <v>SAS Viya HMS High Level Estimates- FY 25 and FY 26</v>
+        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
       </c>
       <c r="C10" t="str">
         <v>Invite to JRM</v>
@@ -604,18 +604,18 @@
         <v>FLCM</v>
       </c>
       <c r="E10" t="str">
-        <v>approved</v>
+        <v>jrm</v>
       </c>
       <c r="G10">
-        <v>45699</v>
+        <v>45690</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>ENT-17202</v>
+        <v>ENT-18364</v>
       </c>
       <c r="B11" t="str">
-        <v>EDH to EDGE Consumption Migration for Fraud teams</v>
+        <v>Expansion of US FCM for US Payments</v>
       </c>
       <c r="C11" t="str">
         <v>Invite to JRM</v>
@@ -624,18 +624,21 @@
         <v>FLCM</v>
       </c>
       <c r="E11" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F11" t="str">
+        <v>PDF</v>
       </c>
       <c r="G11">
-        <v>45690</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-18364</v>
+        <v>ENT-17639</v>
       </c>
       <c r="B12" t="str">
-        <v>Expansion of US FCM for US Payments</v>
+        <v>Send DAC ID to FIQM</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -644,21 +647,18 @@
         <v>FLCM</v>
       </c>
       <c r="E12" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F12" t="str">
-        <v>PDF</v>
+        <v>estimates</v>
       </c>
       <c r="G12">
-        <v>45686</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-17089</v>
       </c>
       <c r="B13" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Cloudlink - LP1502 port</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -670,15 +670,15 @@
         <v>estimates</v>
       </c>
       <c r="G13">
-        <v>45700</v>
+        <v>45656</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B14" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -690,15 +690,15 @@
         <v>estimates</v>
       </c>
       <c r="G14">
-        <v>45656</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B15" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -710,15 +710,15 @@
         <v>estimates</v>
       </c>
       <c r="G15">
-        <v>45588</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-17054</v>
       </c>
       <c r="B16" t="str">
-        <v>Data Source to EDGE</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -727,18 +727,21 @@
         <v>FLCM</v>
       </c>
       <c r="E16" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F16" t="str">
+        <v>PDF</v>
       </c>
       <c r="G16">
-        <v>45664</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ENT-17054</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B17" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -749,19 +752,16 @@
       <c r="E17" t="str">
         <v>approved</v>
       </c>
-      <c r="F17" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G17">
-        <v>45691</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-14372</v>
       </c>
       <c r="B18" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
@@ -772,16 +772,19 @@
       <c r="E18" t="str">
         <v>approved</v>
       </c>
+      <c r="F18" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G18">
-        <v>45299</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ENT-14372</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B19" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
@@ -796,58 +799,58 @@
         <v>PDF</v>
       </c>
       <c r="G19">
-        <v>45512</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B20" t="str">
-        <v>RAMP Phase 2</v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D20" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E20" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F20" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G20">
-        <v>45562</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B21" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D21" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E21" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F21" t="str">
+        <v>PDF</v>
       </c>
       <c r="G21">
-        <v>45695</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B22" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
@@ -862,15 +865,15 @@
         <v>PDF</v>
       </c>
       <c r="G22">
-        <v>45688</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B23" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
@@ -885,15 +888,15 @@
         <v>PDF</v>
       </c>
       <c r="G23">
-        <v>45701</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B24" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
@@ -904,19 +907,16 @@
       <c r="E24" t="str">
         <v>approved</v>
       </c>
-      <c r="F24" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G24">
-        <v>45695</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B25" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
@@ -925,138 +925,138 @@
         <v>FLCM</v>
       </c>
       <c r="E25" t="str">
-        <v>approved</v>
+        <v>estimates</v>
       </c>
       <c r="G25">
-        <v>45706</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B26" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D26" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E26" t="str">
         <v>estimates</v>
       </c>
       <c r="G26">
-        <v>45559</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B27" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D27" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E27" t="str">
         <v>estimates</v>
       </c>
       <c r="G27">
-        <v>45623</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B28" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D28" t="str">
-        <v>FLCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E28" t="str">
         <v>estimates</v>
       </c>
       <c r="G28">
-        <v>45355</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B29" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>CorpSec</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E29" t="str">
         <v>estimates</v>
       </c>
       <c r="G29">
-        <v>45446</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B30" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D30" t="str">
-        <v>BSCM/ESCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E30" t="str">
         <v>estimates</v>
       </c>
       <c r="G30">
-        <v>45477</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B31" t="str">
-        <v>CSDM Upgrade</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D31" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E31" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G31">
-        <v>45394</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B32" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
@@ -1068,15 +1068,15 @@
         <v>ofs</v>
       </c>
       <c r="G32">
-        <v>45531</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B33" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
@@ -1088,15 +1088,15 @@
         <v>ofs</v>
       </c>
       <c r="G33">
-        <v>45453</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B34" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
@@ -1105,98 +1105,95 @@
         <v>FLCM</v>
       </c>
       <c r="E34" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G34">
-        <v>45461</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B35" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D35" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E35" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G35">
-        <v>45714</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-15822</v>
       </c>
       <c r="B36" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D36" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E36" t="str">
         <v>estimates</v>
       </c>
       <c r="G36">
-        <v>45686</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ENT-15822</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B37" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D37" t="str">
-        <v>FLCM</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E37" t="str">
         <v>estimates</v>
       </c>
       <c r="G37">
-        <v>45650</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-17853</v>
       </c>
       <c r="B38" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
       </c>
-      <c r="D38" t="str">
-        <v>BSCM/ESCM</v>
-      </c>
       <c r="E38" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G38">
-        <v>45541</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ENT-17853</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B39" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
@@ -1205,15 +1202,15 @@
         <v>ofs</v>
       </c>
       <c r="G39">
-        <v>45691</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B40" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
@@ -1222,15 +1219,15 @@
         <v>ofs</v>
       </c>
       <c r="G40">
-        <v>45559</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B41" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1239,15 +1236,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45596</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B42" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1256,15 +1253,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45378</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B43" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1273,15 +1270,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45468</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B44" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1290,15 +1287,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45310</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B45" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1307,15 +1304,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45427</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B46" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1324,15 +1321,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45279</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B47" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1341,15 +1338,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45558</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B48" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1358,15 +1355,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45383</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B49" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1375,15 +1372,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45638</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B50" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1392,15 +1389,15 @@
         <v>ofs</v>
       </c>
       <c r="G50">
-        <v>45461</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B51" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1414,10 +1411,10 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B52" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1426,15 +1423,15 @@
         <v>ofs</v>
       </c>
       <c r="G52">
-        <v>45371</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B53" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1443,15 +1440,15 @@
         <v>ofs</v>
       </c>
       <c r="G53">
-        <v>45406</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B54" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1460,15 +1457,15 @@
         <v>ofs</v>
       </c>
       <c r="G54">
-        <v>45364</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B55" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1477,15 +1474,15 @@
         <v>ofs</v>
       </c>
       <c r="G55">
-        <v>45593</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B56" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1494,15 +1491,15 @@
         <v>ofs</v>
       </c>
       <c r="G56">
-        <v>45408</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B57" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
@@ -1511,15 +1508,15 @@
         <v>ofs</v>
       </c>
       <c r="G57">
-        <v>45595</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B58" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C58" t="str">
         <v>Invite to JRM</v>
@@ -1528,15 +1525,15 @@
         <v>ofs</v>
       </c>
       <c r="G58">
-        <v>45392</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B59" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C59" t="str">
         <v>Invite to JRM</v>
@@ -1550,27 +1547,27 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B60" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C60" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E60" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G60">
-        <v>45411</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-18725</v>
       </c>
       <c r="B61" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>US Video System - Lenel to Genetec</v>
       </c>
       <c r="C61" t="str">
         <v>Invite to JRM</v>
@@ -1582,26 +1579,9 @@
         <v>45721</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="str">
-        <v>ENT-18725</v>
-      </c>
-      <c r="B62" t="str">
-        <v>US Video System - Lenel to Genetec</v>
-      </c>
-      <c r="C62" t="str">
-        <v>Invite to JRM</v>
-      </c>
-      <c r="E62" t="str">
-        <v>jrm</v>
-      </c>
-      <c r="G62">
-        <v>45721</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G62"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G61"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -464,7 +464,7 @@
         <v>FLCM</v>
       </c>
       <c r="E3" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G3">
         <v>45531</v>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G60"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -655,10 +655,10 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-17089</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B13" t="str">
-        <v>Cloudlink - LP1502 port</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -670,15 +670,15 @@
         <v>estimates</v>
       </c>
       <c r="G13">
-        <v>45656</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B14" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -690,15 +690,15 @@
         <v>estimates</v>
       </c>
       <c r="G14">
-        <v>45588</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-17054</v>
       </c>
       <c r="B15" t="str">
-        <v>Data Source to EDGE</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -707,18 +707,21 @@
         <v>FLCM</v>
       </c>
       <c r="E15" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F15" t="str">
+        <v>PDF</v>
       </c>
       <c r="G15">
-        <v>45664</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ENT-17054</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B16" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -729,19 +732,16 @@
       <c r="E16" t="str">
         <v>approved</v>
       </c>
-      <c r="F16" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G16">
-        <v>45691</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-14372</v>
       </c>
       <c r="B17" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -752,16 +752,19 @@
       <c r="E17" t="str">
         <v>approved</v>
       </c>
+      <c r="F17" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G17">
-        <v>45299</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ENT-14372</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B18" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
@@ -776,58 +779,58 @@
         <v>PDF</v>
       </c>
       <c r="G18">
-        <v>45512</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B19" t="str">
-        <v>RAMP Phase 2</v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D19" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E19" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F19" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G19">
-        <v>45562</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B20" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D20" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E20" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F20" t="str">
+        <v>PDF</v>
       </c>
       <c r="G20">
-        <v>45695</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B21" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
@@ -842,15 +845,15 @@
         <v>PDF</v>
       </c>
       <c r="G21">
-        <v>45688</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B22" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
@@ -865,15 +868,15 @@
         <v>PDF</v>
       </c>
       <c r="G22">
-        <v>45701</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B23" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
@@ -884,19 +887,16 @@
       <c r="E23" t="str">
         <v>approved</v>
       </c>
-      <c r="F23" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G23">
-        <v>45695</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B24" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
@@ -905,138 +905,138 @@
         <v>FLCM</v>
       </c>
       <c r="E24" t="str">
-        <v>approved</v>
+        <v>estimates</v>
       </c>
       <c r="G24">
-        <v>45706</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B25" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D25" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E25" t="str">
         <v>estimates</v>
       </c>
       <c r="G25">
-        <v>45559</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B26" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D26" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E26" t="str">
         <v>estimates</v>
       </c>
       <c r="G26">
-        <v>45623</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B27" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D27" t="str">
-        <v>FLCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E27" t="str">
         <v>estimates</v>
       </c>
       <c r="G27">
-        <v>45355</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B28" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D28" t="str">
-        <v>CorpSec</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E28" t="str">
         <v>estimates</v>
       </c>
       <c r="G28">
-        <v>45446</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B29" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>BSCM/ESCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E29" t="str">
         <v>estimates</v>
       </c>
       <c r="G29">
-        <v>45477</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B30" t="str">
-        <v>CSDM Upgrade</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D30" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E30" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G30">
-        <v>45394</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B31" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
@@ -1048,15 +1048,15 @@
         <v>ofs</v>
       </c>
       <c r="G31">
-        <v>45531</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B32" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
@@ -1068,15 +1068,15 @@
         <v>ofs</v>
       </c>
       <c r="G32">
-        <v>45453</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B33" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
@@ -1085,98 +1085,95 @@
         <v>FLCM</v>
       </c>
       <c r="E33" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G33">
-        <v>45461</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B34" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D34" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E34" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G34">
-        <v>45714</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-15822</v>
       </c>
       <c r="B35" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D35" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E35" t="str">
         <v>estimates</v>
       </c>
       <c r="G35">
-        <v>45686</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ENT-15822</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B36" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D36" t="str">
-        <v>FLCM</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E36" t="str">
         <v>estimates</v>
       </c>
       <c r="G36">
-        <v>45650</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-17853</v>
       </c>
       <c r="B37" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
       </c>
-      <c r="D37" t="str">
-        <v>BSCM/ESCM</v>
-      </c>
       <c r="E37" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G37">
-        <v>45541</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ENT-17853</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B38" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
@@ -1185,15 +1182,15 @@
         <v>ofs</v>
       </c>
       <c r="G38">
-        <v>45691</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B39" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
@@ -1202,15 +1199,15 @@
         <v>ofs</v>
       </c>
       <c r="G39">
-        <v>45559</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B40" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
@@ -1219,15 +1216,15 @@
         <v>ofs</v>
       </c>
       <c r="G40">
-        <v>45596</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B41" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1236,15 +1233,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45378</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B42" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1253,15 +1250,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45468</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B43" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1270,15 +1267,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45310</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B44" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1287,15 +1284,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45427</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B45" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1304,15 +1301,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45279</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B46" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1321,15 +1318,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45558</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B47" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1338,15 +1335,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45383</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B48" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1355,15 +1352,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45638</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B49" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1372,15 +1369,15 @@
         <v>ofs</v>
       </c>
       <c r="G49">
-        <v>45461</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B50" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1394,10 +1391,10 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B51" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1406,15 +1403,15 @@
         <v>ofs</v>
       </c>
       <c r="G51">
-        <v>45371</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B52" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1423,15 +1420,15 @@
         <v>ofs</v>
       </c>
       <c r="G52">
-        <v>45406</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B53" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1440,15 +1437,15 @@
         <v>ofs</v>
       </c>
       <c r="G53">
-        <v>45364</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B54" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1457,15 +1454,15 @@
         <v>ofs</v>
       </c>
       <c r="G54">
-        <v>45593</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B55" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1474,15 +1471,15 @@
         <v>ofs</v>
       </c>
       <c r="G55">
-        <v>45408</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B56" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1491,15 +1488,15 @@
         <v>ofs</v>
       </c>
       <c r="G56">
-        <v>45595</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B57" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
@@ -1508,15 +1505,15 @@
         <v>ofs</v>
       </c>
       <c r="G57">
-        <v>45392</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B58" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C58" t="str">
         <v>Invite to JRM</v>
@@ -1530,27 +1527,27 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B59" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C59" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E59" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G59">
-        <v>45411</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-18725</v>
       </c>
       <c r="B60" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>US Video System - Lenel to Genetec</v>
       </c>
       <c r="C60" t="str">
         <v>Invite to JRM</v>
@@ -1562,26 +1559,9 @@
         <v>45721</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="str">
-        <v>ENT-18725</v>
-      </c>
-      <c r="B61" t="str">
-        <v>US Video System - Lenel to Genetec</v>
-      </c>
-      <c r="C61" t="str">
-        <v>Invite to JRM</v>
-      </c>
-      <c r="E61" t="str">
-        <v>jrm</v>
-      </c>
-      <c r="G61">
-        <v>45721</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G60"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -402,7 +402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G59"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -635,10 +635,10 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>ENT-17639</v>
+        <v>ENT-16108</v>
       </c>
       <c r="B12" t="str">
-        <v>Send DAC ID to FIQM</v>
+        <v>Bring 2 workday views to our EDH Z4</v>
       </c>
       <c r="C12" t="str">
         <v>Invite to JRM</v>
@@ -650,15 +650,15 @@
         <v>estimates</v>
       </c>
       <c r="G12">
-        <v>45700</v>
+        <v>45588</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ENT-16108</v>
+        <v>ENT-17559</v>
       </c>
       <c r="B13" t="str">
-        <v>Bring 2 workday views to our EDH Z4</v>
+        <v>Data Source to EDGE</v>
       </c>
       <c r="C13" t="str">
         <v>Invite to JRM</v>
@@ -670,15 +670,15 @@
         <v>estimates</v>
       </c>
       <c r="G13">
-        <v>45588</v>
+        <v>45664</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ENT-17559</v>
+        <v>ENT-17054</v>
       </c>
       <c r="B14" t="str">
-        <v>Data Source to EDGE</v>
+        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
       </c>
       <c r="C14" t="str">
         <v>Invite to JRM</v>
@@ -687,18 +687,21 @@
         <v>FLCM</v>
       </c>
       <c r="E14" t="str">
-        <v>estimates</v>
+        <v>approved</v>
+      </c>
+      <c r="F14" t="str">
+        <v>PDF</v>
       </c>
       <c r="G14">
-        <v>45664</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ENT-17054</v>
+        <v xml:space="preserve">ENT-16009 </v>
       </c>
       <c r="B15" t="str">
-        <v xml:space="preserve"> FLCM Case Type &amp; Records Modification</v>
+        <v>Actimize Initiative - BSCM</v>
       </c>
       <c r="C15" t="str">
         <v>Invite to JRM</v>
@@ -709,19 +712,16 @@
       <c r="E15" t="str">
         <v>approved</v>
       </c>
-      <c r="F15" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G15">
-        <v>45691</v>
+        <v>45299</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v xml:space="preserve">ENT-16009 </v>
+        <v>ENT-14372</v>
       </c>
       <c r="B16" t="str">
-        <v>Actimize Initiative - BSCM</v>
+        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
       </c>
       <c r="C16" t="str">
         <v>Invite to JRM</v>
@@ -732,16 +732,19 @@
       <c r="E16" t="str">
         <v>approved</v>
       </c>
+      <c r="F16" t="str">
+        <v>PDF</v>
+      </c>
       <c r="G16">
-        <v>45299</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ENT-14372</v>
+        <v>ENT-16940</v>
       </c>
       <c r="B17" t="str">
-        <v>Onboard Applications to TDE, DB Vault &amp; OKV</v>
+        <v>RAMP Phase 2</v>
       </c>
       <c r="C17" t="str">
         <v>Invite to JRM</v>
@@ -756,58 +759,58 @@
         <v>PDF</v>
       </c>
       <c r="G17">
-        <v>45512</v>
+        <v>45562</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ENT-16940</v>
+        <v>ENT-18473</v>
       </c>
       <c r="B18" t="str">
-        <v>RAMP Phase 2</v>
+        <v xml:space="preserve">FCG Operating Model </v>
       </c>
       <c r="C18" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D18" t="str">
-        <v>FLCM</v>
+        <v>FIQM</v>
       </c>
       <c r="E18" t="str">
-        <v>approved</v>
-      </c>
-      <c r="F18" t="str">
-        <v>PDF</v>
+        <v>jrm</v>
       </c>
       <c r="G18">
-        <v>45562</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>ENT-18473</v>
+        <v>ENT-17705</v>
       </c>
       <c r="B19" t="str">
-        <v xml:space="preserve">FCG Operating Model </v>
+        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
       </c>
       <c r="C19" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D19" t="str">
-        <v>FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E19" t="str">
-        <v>jrm</v>
+        <v>approved</v>
+      </c>
+      <c r="F19" t="str">
+        <v>PDF</v>
       </c>
       <c r="G19">
-        <v>45695</v>
+        <v>45688</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ENT-17705</v>
+        <v>ENT-17213</v>
       </c>
       <c r="B20" t="str">
-        <v xml:space="preserve">eBit Web Service Migration Phase 2 </v>
+        <v>FLCM Upgrade and Enhancements ph2</v>
       </c>
       <c r="C20" t="str">
         <v>Invite to JRM</v>
@@ -822,15 +825,15 @@
         <v>PDF</v>
       </c>
       <c r="G20">
-        <v>45688</v>
+        <v>45701</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>ENT-17213</v>
+        <v>ENT-17155</v>
       </c>
       <c r="B21" t="str">
-        <v>FLCM Upgrade and Enhancements ph2</v>
+        <v>NAE move to EDGE</v>
       </c>
       <c r="C21" t="str">
         <v>Invite to JRM</v>
@@ -845,15 +848,15 @@
         <v>PDF</v>
       </c>
       <c r="G21">
-        <v>45701</v>
+        <v>45695</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ENT-17155</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B22" t="str">
-        <v>NAE move to EDGE</v>
+        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
       </c>
       <c r="C22" t="str">
         <v>Invite to JRM</v>
@@ -864,19 +867,16 @@
       <c r="E22" t="str">
         <v>approved</v>
       </c>
-      <c r="F22" t="str">
-        <v>PDF</v>
-      </c>
       <c r="G22">
-        <v>45695</v>
+        <v>45706</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ENT-18591</v>
+        <v>ENT-16938</v>
       </c>
       <c r="B23" t="str">
-        <v>FLCM - TII Data Governance - Work to Review Controls for Important and Core CDEs</v>
+        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
       </c>
       <c r="C23" t="str">
         <v>Invite to JRM</v>
@@ -885,138 +885,138 @@
         <v>FLCM</v>
       </c>
       <c r="E23" t="str">
-        <v>approved</v>
+        <v>estimates</v>
       </c>
       <c r="G23">
-        <v>45706</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ENT-16938</v>
+        <v>ENT-17709</v>
       </c>
       <c r="B24" t="str">
-        <v>SAS Farm Data Exfiltration Risk Deficiency</v>
+        <v>CSDM Retention Policy Initiative</v>
       </c>
       <c r="C24" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D24" t="str">
-        <v>FLCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E24" t="str">
         <v>estimates</v>
       </c>
       <c r="G24">
-        <v>45559</v>
+        <v>45623</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ENT-17709</v>
+        <v>ENT-13982</v>
       </c>
       <c r="B25" t="str">
-        <v>CSDM Retention Policy Initiative</v>
+        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
       </c>
       <c r="C25" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D25" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E25" t="str">
         <v>estimates</v>
       </c>
       <c r="G25">
-        <v>45623</v>
+        <v>45355</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>ENT-13982</v>
+        <v>ENT-16173</v>
       </c>
       <c r="B26" t="str">
-        <v>FINTRAC Incoming Cross Border e-Transfer Travel Rule (Reduced Scope – Reject Payments CBPT-2113)</v>
+        <v>Move HR App off dedicated line</v>
       </c>
       <c r="C26" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D26" t="str">
-        <v>FLCM</v>
+        <v>CorpSec</v>
       </c>
       <c r="E26" t="str">
         <v>estimates</v>
       </c>
       <c r="G26">
-        <v>45355</v>
+        <v>45446</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ENT-16173</v>
+        <v>ENT-16787</v>
       </c>
       <c r="B27" t="str">
-        <v>Move HR App off dedicated line</v>
+        <v>PES Historical Dart Report- Destruction</v>
       </c>
       <c r="C27" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D27" t="str">
-        <v>CorpSec</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E27" t="str">
         <v>estimates</v>
       </c>
       <c r="G27">
-        <v>45446</v>
+        <v>45477</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ENT-16787</v>
+        <v>ENT-15671</v>
       </c>
       <c r="B28" t="str">
-        <v>PES Historical Dart Report- Destruction</v>
+        <v>CSDM Upgrade</v>
       </c>
       <c r="C28" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D28" t="str">
-        <v>BSCM/ESCM</v>
+        <v>MinIO/DreamIO</v>
       </c>
       <c r="E28" t="str">
         <v>estimates</v>
       </c>
       <c r="G28">
-        <v>45477</v>
+        <v>45394</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ENT-15671</v>
+        <v>ENT-16956</v>
       </c>
       <c r="B29" t="str">
-        <v>CSDM Upgrade</v>
+        <v>CPP - Consents and Enhanced Transparency - EDH</v>
       </c>
       <c r="C29" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D29" t="str">
-        <v>MinIO/DreamIO</v>
+        <v>FLCM</v>
       </c>
       <c r="E29" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G29">
-        <v>45394</v>
+        <v>45531</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ENT-16956</v>
+        <v>ENT-16024</v>
       </c>
       <c r="B30" t="str">
-        <v>CPP - Consents and Enhanced Transparency - EDH</v>
+        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
       </c>
       <c r="C30" t="str">
         <v>Invite to JRM</v>
@@ -1028,15 +1028,15 @@
         <v>ofs</v>
       </c>
       <c r="G30">
-        <v>45531</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ENT-16024</v>
+        <v>ENT-16511</v>
       </c>
       <c r="B31" t="str">
-        <v>eBIT Migration Account Open Initiative: Estimates Request</v>
+        <v>Horizon delta Migration | CIW Data Support</v>
       </c>
       <c r="C31" t="str">
         <v>Invite to JRM</v>
@@ -1048,15 +1048,15 @@
         <v>ofs</v>
       </c>
       <c r="G31">
-        <v>45453</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ENT-16511</v>
+        <v>ENT-18723</v>
       </c>
       <c r="B32" t="str">
-        <v>Horizon delta Migration | CIW Data Support</v>
+        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
       </c>
       <c r="C32" t="str">
         <v>Invite to JRM</v>
@@ -1065,98 +1065,95 @@
         <v>FLCM</v>
       </c>
       <c r="E32" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G32">
-        <v>45461</v>
+        <v>45714</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ENT-18723</v>
+        <v>ENT-16748</v>
       </c>
       <c r="B33" t="str">
-        <v>FLCM Account Table Update to Add New Suspense Accounts</v>
+        <v>Project Mercury File Replacement</v>
       </c>
       <c r="C33" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D33" t="str">
-        <v>FLCM</v>
+        <v>FLCM/FIQM</v>
       </c>
       <c r="E33" t="str">
-        <v>jrm</v>
+        <v>estimates</v>
       </c>
       <c r="G33">
-        <v>45714</v>
+        <v>45686</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ENT-16748</v>
+        <v>ENT-15822</v>
       </c>
       <c r="B34" t="str">
-        <v>Project Mercury File Replacement</v>
+        <v>CIPS - Fee Based Project</v>
       </c>
       <c r="C34" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D34" t="str">
-        <v>FLCM/FIQM</v>
+        <v>FLCM</v>
       </c>
       <c r="E34" t="str">
         <v>estimates</v>
       </c>
       <c r="G34">
-        <v>45686</v>
+        <v>45650</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ENT-15822</v>
+        <v xml:space="preserve">ENT-16720 </v>
       </c>
       <c r="B35" t="str">
-        <v>CIPS - Fee Based Project</v>
+        <v>Corporate Security Data Management - POC request</v>
       </c>
       <c r="C35" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="D35" t="str">
-        <v>FLCM</v>
+        <v>BSCM/ESCM</v>
       </c>
       <c r="E35" t="str">
         <v>estimates</v>
       </c>
       <c r="G35">
-        <v>45650</v>
+        <v>45541</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v xml:space="preserve">ENT-16720 </v>
+        <v>ENT-17853</v>
       </c>
       <c r="B36" t="str">
-        <v>Corporate Security Data Management - POC request</v>
+        <v>ECIF R65 consumer regression testing</v>
       </c>
       <c r="C36" t="str">
         <v>Invite to JRM</v>
       </c>
-      <c r="D36" t="str">
-        <v>BSCM/ESCM</v>
-      </c>
       <c r="E36" t="str">
-        <v>estimates</v>
+        <v>ofs</v>
       </c>
       <c r="G36">
-        <v>45541</v>
+        <v>45691</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ENT-17853</v>
+        <v>ENT-17109</v>
       </c>
       <c r="B37" t="str">
-        <v>ECIF R65 consumer regression testing</v>
+        <v>Mobile Credentials for Physical Access control</v>
       </c>
       <c r="C37" t="str">
         <v>Invite to JRM</v>
@@ -1165,15 +1162,15 @@
         <v>ofs</v>
       </c>
       <c r="G37">
-        <v>45691</v>
+        <v>45559</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ENT-17109</v>
+        <v>ENT-16786</v>
       </c>
       <c r="B38" t="str">
-        <v>Mobile Credentials for Physical Access control</v>
+        <v>Fraud Mass Card Issuance</v>
       </c>
       <c r="C38" t="str">
         <v>Invite to JRM</v>
@@ -1182,15 +1179,15 @@
         <v>ofs</v>
       </c>
       <c r="G38">
-        <v>45559</v>
+        <v>45596</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>ENT-16786</v>
+        <v>ENT-14160</v>
       </c>
       <c r="B39" t="str">
-        <v>Fraud Mass Card Issuance</v>
+        <v>Create new NAE views and database roles</v>
       </c>
       <c r="C39" t="str">
         <v>Invite to JRM</v>
@@ -1199,15 +1196,15 @@
         <v>ofs</v>
       </c>
       <c r="G39">
-        <v>45596</v>
+        <v>45378</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ENT-14160</v>
+        <v>ENT-16394</v>
       </c>
       <c r="B40" t="str">
-        <v>Create new NAE views and database roles</v>
+        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
       </c>
       <c r="C40" t="str">
         <v>Invite to JRM</v>
@@ -1216,15 +1213,15 @@
         <v>ofs</v>
       </c>
       <c r="G40">
-        <v>45378</v>
+        <v>45468</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ENT-16394</v>
+        <v>ENT-13691</v>
       </c>
       <c r="B41" t="str">
-        <v>Visa Debit Int OCT - SLMS Adapter Update to Field 60</v>
+        <v>EAML Assurance &amp; FINTRAC Remediation</v>
       </c>
       <c r="C41" t="str">
         <v>Invite to JRM</v>
@@ -1233,15 +1230,15 @@
         <v>ofs</v>
       </c>
       <c r="G41">
-        <v>45468</v>
+        <v>45310</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ENT-13691</v>
+        <v>ENT-15815</v>
       </c>
       <c r="B42" t="str">
-        <v>EAML Assurance &amp; FINTRAC Remediation</v>
+        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
       </c>
       <c r="C42" t="str">
         <v>Invite to JRM</v>
@@ -1250,15 +1247,15 @@
         <v>ofs</v>
       </c>
       <c r="G42">
-        <v>45310</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ENT-15815</v>
+        <v>ENT-13593</v>
       </c>
       <c r="B43" t="str">
-        <v>TSYS WCSA GL Keys Strategic Fix_PI3928</v>
+        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
       </c>
       <c r="C43" t="str">
         <v>Invite to JRM</v>
@@ -1267,15 +1264,15 @@
         <v>ofs</v>
       </c>
       <c r="G43">
-        <v>45427</v>
+        <v>45279</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ENT-13593</v>
+        <v>ENT-13829</v>
       </c>
       <c r="B44" t="str">
-        <v>Bill C16 (Pronouns &amp; Clients Preferred Name)</v>
+        <v>Quasi Cash - Modify MCC6540_PI3578</v>
       </c>
       <c r="C44" t="str">
         <v>Invite to JRM</v>
@@ -1284,15 +1281,15 @@
         <v>ofs</v>
       </c>
       <c r="G44">
-        <v>45279</v>
+        <v>45558</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ENT-13829</v>
+        <v>ENT-14271</v>
       </c>
       <c r="B45" t="str">
-        <v>Quasi Cash - Modify MCC6540_PI3578</v>
+        <v>EWM - OPF - Containerization - DEVO Integration</v>
       </c>
       <c r="C45" t="str">
         <v>Invite to JRM</v>
@@ -1301,15 +1298,15 @@
         <v>ofs</v>
       </c>
       <c r="G45">
-        <v>45558</v>
+        <v>45383</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENT-14271</v>
+        <v>ENT-17801</v>
       </c>
       <c r="B46" t="str">
-        <v>EWM - OPF - Containerization - DEVO Integration</v>
+        <v>Avalor-Risk Orchestration POC</v>
       </c>
       <c r="C46" t="str">
         <v>Invite to JRM</v>
@@ -1318,15 +1315,15 @@
         <v>ofs</v>
       </c>
       <c r="G46">
-        <v>45383</v>
+        <v>45638</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ENT-17801</v>
+        <v>ENT-13880</v>
       </c>
       <c r="B47" t="str">
-        <v>Avalor-Risk Orchestration POC</v>
+        <v>Artemis Program - Complaints Sustainment Improvements</v>
       </c>
       <c r="C47" t="str">
         <v>Invite to JRM</v>
@@ -1335,15 +1332,15 @@
         <v>ofs</v>
       </c>
       <c r="G47">
-        <v>45638</v>
+        <v>45461</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENT-13880</v>
+        <v>ENT-14137</v>
       </c>
       <c r="B48" t="str">
-        <v>Artemis Program - Complaints Sustainment Improvements</v>
+        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
       </c>
       <c r="C48" t="str">
         <v>Invite to JRM</v>
@@ -1352,15 +1349,15 @@
         <v>ofs</v>
       </c>
       <c r="G48">
-        <v>45461</v>
+        <v>45371</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ENT-14137</v>
+        <v>ENT-14052</v>
       </c>
       <c r="B49" t="str">
-        <v>Compass-AIM connectivity to allAccess for non-Core CIBC user info lookup</v>
+        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
       </c>
       <c r="C49" t="str">
         <v>Invite to JRM</v>
@@ -1374,10 +1371,10 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ENT-14052</v>
+        <v>ENT-14203</v>
       </c>
       <c r="B50" t="str">
-        <v>Costco Temp Cards Limit_PSBT-8200/DCTPI-3515</v>
+        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
       </c>
       <c r="C50" t="str">
         <v>Invite to JRM</v>
@@ -1386,15 +1383,15 @@
         <v>ofs</v>
       </c>
       <c r="G50">
-        <v>45371</v>
+        <v>45406</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ENT-14203</v>
+        <v>ENT-14200</v>
       </c>
       <c r="B51" t="str">
-        <v>Bill C16 (Pronouns &amp; Client Preferred Name)</v>
+        <v>WCSA GL Table Clean Up_PI3910</v>
       </c>
       <c r="C51" t="str">
         <v>Invite to JRM</v>
@@ -1403,15 +1400,15 @@
         <v>ofs</v>
       </c>
       <c r="G51">
-        <v>45406</v>
+        <v>45364</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ENT-14200</v>
+        <v>ENT-13952</v>
       </c>
       <c r="B52" t="str">
-        <v>WCSA GL Table Clean Up_PI3910</v>
+        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
       </c>
       <c r="C52" t="str">
         <v>Invite to JRM</v>
@@ -1420,15 +1417,15 @@
         <v>ofs</v>
       </c>
       <c r="G52">
-        <v>45364</v>
+        <v>45593</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ENT-13952</v>
+        <v>ENT-15793</v>
       </c>
       <c r="B53" t="str">
-        <v>Credit Bureau Advancement 2.0 - Vulnerability Index</v>
+        <v>Client Preference Center (CPC) - RBSS support</v>
       </c>
       <c r="C53" t="str">
         <v>Invite to JRM</v>
@@ -1437,15 +1434,15 @@
         <v>ofs</v>
       </c>
       <c r="G53">
-        <v>45593</v>
+        <v>45408</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ENT-15793</v>
+        <v>ENT-16003</v>
       </c>
       <c r="B54" t="str">
-        <v>Client Preference Center (CPC) - RBSS support</v>
+        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
       </c>
       <c r="C54" t="str">
         <v>Invite to JRM</v>
@@ -1454,15 +1451,15 @@
         <v>ofs</v>
       </c>
       <c r="G54">
-        <v>45408</v>
+        <v>45595</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ENT-16003</v>
+        <v>ENT-15698</v>
       </c>
       <c r="B55" t="str">
-        <v>Wires and Drafts Delegated and Supervisor Override Limits - RBSSINTK-9172</v>
+        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
       </c>
       <c r="C55" t="str">
         <v>Invite to JRM</v>
@@ -1471,15 +1468,15 @@
         <v>ofs</v>
       </c>
       <c r="G55">
-        <v>45595</v>
+        <v>45392</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENT-15698</v>
+        <v>ENT-15819</v>
       </c>
       <c r="B56" t="str">
-        <v>Cards 21/5-day Offer Expiry Letters Process Enhancements</v>
+        <v>Loan to Value (LTV)</v>
       </c>
       <c r="C56" t="str">
         <v>Invite to JRM</v>
@@ -1488,15 +1485,15 @@
         <v>ofs</v>
       </c>
       <c r="G56">
-        <v>45392</v>
+        <v>45411</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENT-15819</v>
+        <v>ENT-15919</v>
       </c>
       <c r="B57" t="str">
-        <v>Loan to Value (LTV)</v>
+        <v>Business and Commercial Debit Card replacement</v>
       </c>
       <c r="C57" t="str">
         <v>Invite to JRM</v>
@@ -1510,27 +1507,27 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENT-15919</v>
+        <v>ENT-18748</v>
       </c>
       <c r="B58" t="str">
-        <v>Business and Commercial Debit Card replacement</v>
+        <v>CIP - PPS Readiness</v>
       </c>
       <c r="C58" t="str">
         <v>Invite to JRM</v>
       </c>
       <c r="E58" t="str">
-        <v>ofs</v>
+        <v>jrm</v>
       </c>
       <c r="G58">
-        <v>45411</v>
+        <v>45721</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ENT-18748</v>
+        <v>ENT-18725</v>
       </c>
       <c r="B59" t="str">
-        <v>CIP - PPS Readiness</v>
+        <v>US Video System - Lenel to Genetec</v>
       </c>
       <c r="C59" t="str">
         <v>Invite to JRM</v>
@@ -1542,26 +1539,9 @@
         <v>45721</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="str">
-        <v>ENT-18725</v>
-      </c>
-      <c r="B60" t="str">
-        <v>US Video System - Lenel to Genetec</v>
-      </c>
-      <c r="C60" t="str">
-        <v>Invite to JRM</v>
-      </c>
-      <c r="E60" t="str">
-        <v>jrm</v>
-      </c>
-      <c r="G60">
-        <v>45721</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G60"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G59"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -544,7 +544,7 @@
         <v>FLCM</v>
       </c>
       <c r="E7" t="str">
-        <v>jrm</v>
+        <v>approved</v>
       </c>
       <c r="G7">
         <v>45649</v>

--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -1548,7 +1548,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:Z9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2157,10 +2157,89 @@
         <v>10</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>17054</v>
+      </c>
+      <c r="B9" t="str">
+        <v>344444</v>
+      </c>
+      <c r="C9" t="str">
+        <v>23424</v>
+      </c>
+      <c r="D9" t="str">
+        <v>234234</v>
+      </c>
+      <c r="E9" t="str">
+        <v>234234</v>
+      </c>
+      <c r="F9" t="str">
+        <v>234234</v>
+      </c>
+      <c r="G9" t="str">
+        <v>234234</v>
+      </c>
+      <c r="H9" t="str">
+        <v>234234</v>
+      </c>
+      <c r="I9" t="str">
+        <v>24234</v>
+      </c>
+      <c r="J9" t="str">
+        <v>234</v>
+      </c>
+      <c r="K9" t="str">
+        <v>234</v>
+      </c>
+      <c r="L9" t="str">
+        <v>234</v>
+      </c>
+      <c r="M9" t="str">
+        <v>234</v>
+      </c>
+      <c r="N9" t="str">
+        <v>234</v>
+      </c>
+      <c r="O9" t="str">
+        <v>234</v>
+      </c>
+      <c r="P9" t="str">
+        <v>42</v>
+      </c>
+      <c r="Q9" t="str">
+        <v>234234</v>
+      </c>
+      <c r="R9" t="str">
+        <v>234234</v>
+      </c>
+      <c r="S9" t="str">
+        <v>234234</v>
+      </c>
+      <c r="T9" t="str">
+        <v>234234</v>
+      </c>
+      <c r="U9" t="str">
+        <v>234234</v>
+      </c>
+      <c r="V9" t="str">
+        <v>234234</v>
+      </c>
+      <c r="W9" t="str">
+        <v>234234</v>
+      </c>
+      <c r="X9" t="str">
+        <v>234234</v>
+      </c>
+      <c r="Y9" t="str">
+        <v>2342342</v>
+      </c>
+      <c r="Z9" t="str">
+        <v>342424</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AC8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Z9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -1615,7 +1615,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:Z10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2304,9 +2304,89 @@
         <v/>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>16009</v>
+      </c>
+      <c r="B10" t="str">
+        <v>234234</v>
+      </c>
+      <c r="C10" t="str">
+        <v>234234</v>
+      </c>
+      <c r="D10" t="str">
+        <v>234234</v>
+      </c>
+      <c r="E10" t="str">
+        <v>234234</v>
+      </c>
+      <c r="F10" t="str">
+        <v>234234</v>
+      </c>
+      <c r="G10" t="str">
+        <v>234234</v>
+      </c>
+      <c r="H10" t="str">
+        <v>234234</v>
+      </c>
+      <c r="I10" t="str">
+        <v>234234</v>
+      </c>
+      <c r="J10" t="str">
+        <v>234234</v>
+      </c>
+      <c r="K10" t="str">
+        <v>wer</v>
+      </c>
+      <c r="L10" t="str">
+        <v>234234</v>
+      </c>
+      <c r="M10" t="str">
+        <v>234234</v>
+      </c>
+      <c r="N10" t="str">
+        <v>234234</v>
+      </c>
+      <c r="O10" t="str">
+        <v>234234</v>
+      </c>
+      <c r="P10" t="str">
+        <v>234234</v>
+      </c>
+      <c r="Q10" t="str">
+        <v>234234</v>
+      </c>
+      <c r="R10" t="str">
+        <v>234234</v>
+      </c>
+      <c r="S10" t="str">
+        <v>234</v>
+      </c>
+      <c r="T10" t="str">
+        <v>234</v>
+      </c>
+      <c r="U10" t="str">
+        <v>234234</v>
+      </c>
+      <c r="V10" t="str">
+        <v>234234</v>
+      </c>
+      <c r="W10" t="str">
+        <v>234234</v>
+      </c>
+      <c r="X10" t="str">
+        <v>234234</v>
+      </c>
+      <c r="Y10" t="str">
+        <v>234234</v>
+      </c>
+      <c r="Z10" t="str">
+        <v>234234</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Z9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Z10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -1615,7 +1615,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z9"/>
+  <dimension ref="A1:Z10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2304,9 +2304,89 @@
         <v/>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>ENT-18591</v>
+      </c>
+      <c r="B10" t="str">
+        <v>3434</v>
+      </c>
+      <c r="C10" t="str">
+        <v/>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
+        <v/>
+      </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="P10" t="str">
+        <v/>
+      </c>
+      <c r="Q10" t="str">
+        <v/>
+      </c>
+      <c r="R10" t="str">
+        <v/>
+      </c>
+      <c r="S10" t="str">
+        <v/>
+      </c>
+      <c r="T10" t="str">
+        <v/>
+      </c>
+      <c r="U10" t="str">
+        <v/>
+      </c>
+      <c r="V10" t="str">
+        <v/>
+      </c>
+      <c r="W10" t="str">
+        <v/>
+      </c>
+      <c r="X10" t="str">
+        <v/>
+      </c>
+      <c r="Y10" t="str">
+        <v/>
+      </c>
+      <c r="Z10" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Z9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Z10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Intake_Database.xlsx
+++ b/Intake_Database.xlsx
@@ -1615,7 +1615,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z10"/>
+  <dimension ref="A1:Z9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2226,10 +2226,10 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ENT-16881</v>
+        <v>ENT-18591</v>
       </c>
       <c r="B9" t="str">
-        <v>123123123</v>
+        <v>3434</v>
       </c>
       <c r="C9" t="str">
         <v/>
@@ -2304,89 +2304,9 @@
         <v/>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>ENT-18591</v>
-      </c>
-      <c r="B10" t="str">
-        <v>3434</v>
-      </c>
-      <c r="C10" t="str">
-        <v/>
-      </c>
-      <c r="D10" t="str">
-        <v/>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v/>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v/>
-      </c>
-      <c r="M10" t="str">
-        <v/>
-      </c>
-      <c r="N10" t="str">
-        <v/>
-      </c>
-      <c r="O10" t="str">
-        <v/>
-      </c>
-      <c r="P10" t="str">
-        <v/>
-      </c>
-      <c r="Q10" t="str">
-        <v/>
-      </c>
-      <c r="R10" t="str">
-        <v/>
-      </c>
-      <c r="S10" t="str">
-        <v/>
-      </c>
-      <c r="T10" t="str">
-        <v/>
-      </c>
-      <c r="U10" t="str">
-        <v/>
-      </c>
-      <c r="V10" t="str">
-        <v/>
-      </c>
-      <c r="W10" t="str">
-        <v/>
-      </c>
-      <c r="X10" t="str">
-        <v/>
-      </c>
-      <c r="Y10" t="str">
-        <v/>
-      </c>
-      <c r="Z10" t="str">
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Z10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Z9"/>
   </ignoredErrors>
 </worksheet>
 </file>